--- a/01-modelo/M1_modelo_comparativo.xlsx
+++ b/01-modelo/M1_modelo_comparativo.xlsx
@@ -82,12 +82,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00008000"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -228,26 +228,26 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -325,6 +325,300 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Líquido anual disponível para a sócia, por via — cenário Base</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Comparativo'!$C$22:$F$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Comparativo'!$C$32:$F$32</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>euros</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Ponto de viragem — carga fiscal e contributiva por nível de custos reais</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'PontoViragem'!F7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'PontoViragem'!$A$8:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'PontoViragem'!$F$8:$F$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'PontoViragem'!J7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'PontoViragem'!$A$8:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'PontoViragem'!$J$8:$J$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>custos reais em % do rendimento bruto</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>euros</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -616,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -700,106 +994,120 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="41" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Inputs — folha única de parâmetros do caso, em três cenários de faturação.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+          <t>Inputs — folha única de parâmetros do caso, em três cenários de faturação. Contém a alavanca MOD_COLAB, que alterna entre os dois modelos de colaboração da ata (1 = prestação de serviços, 2 = cedência de sala) e reconfigura toda a estrutura de receita e custo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="41" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>As linhas derivadas no fim da folha Inputs não se preenchem. Entre elas está o teste de rendimentos do art. 6.º n.º 4 al. b) ii) CIRC, e a receita de cedência que seria precisa para o falhar — que é a via para afastar a transparência sem ceder capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>V1 a V4 — uma folha por via, com a mesma estrutura: apuramento, Segurança Social, IRS do agregado, resultado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>IVA — quantificação do IVA perdido no investimento e teste das duas atenuantes.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>PontoViragem — nível de custos reais a partir do qual o simplificado deixa de compensar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+          <t>IVA — quantificação do IVA perdido no investimento e teste das duas atenuantes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Comparativo — output que alimenta o capítulo 3 e o anexo E2.</t>
+          <t>PontoViragem — nível de custos reais a partir do qual o simplificado deixa de compensar, com o gráfico correspondente.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>Comparativo — output que alimenta o capítulo 3 e o anexo E2, com o gráfico do líquido por via.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>Validação — recálculo independente e espaço para assinatura.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Convenções</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Azul sobre amarelo = célula de preenchimento. Verde = ligação a outra folha. Preto = fórmula. Fundo laranja na folha Parâmetros = parâmetro por confirmar.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Percentagens guardadas como fração. Valores anuais, em euros, sem IVA salvo indicação.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Três decisões de modelação que são discutíveis e estão assumidas</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="41" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="25" ht="41" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>1. A comparação entre vias usa o IRS diferencial (coleta do agregado com a atividade menos coleta sem a atividade), e não o IRS total. É o que torna as quatro vias comparáveis quando o cônjuge tem rendimento próprio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>2. O investimento inicial está fora da comparação anual e isolado numa linha de memória. Misturá-lo com o resultado corrente faria a via 1 parecer melhor do que é no ano 1.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>2. O investimento inicial está fora da comparação anual e isolado numa linha de memória. Misturá-lo com o resultado corrente faria a via 1 parecer melhor do que é no ano 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>3. Nas vias societárias, o valor retido na sociedade é mostrado separado do líquido da sócia. Somar os dois responderia a uma pergunta que a cliente não fez.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Reprodução</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>4. O modelo de colaboração é uma escolha única para todos os colaboradores. A ata admite modelos distintos por profissional; uma combinação exige correr o modelo com a faturação repartida. Registado em R1-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Reprodução</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Este ficheiro é gerado por build_m1.py. Alterações estruturais fazem-se no script e regenera-se; alterações de valores fazem-se nas células amarelas.</t>
         </is>
@@ -850,11 +1158,11 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Faturação (cenário Base)</t>
-        </is>
-      </c>
-      <c r="C4" s="33">
-        <f>Inputs!$D$6</f>
+          <t>Rendimento bruto (cenário Base)</t>
+        </is>
+      </c>
+      <c r="C4" s="34">
+        <f>(Inputs!$D$37+Inputs!$D$38)</f>
         <v/>
       </c>
     </row>
@@ -864,8 +1172,8 @@
           <t>Rendimento do cônjuge</t>
         </is>
       </c>
-      <c r="C5" s="33">
-        <f>Inputs!$D$28</f>
+      <c r="C5" s="34">
+        <f>Inputs!$D$32</f>
         <v/>
       </c>
     </row>
@@ -932,747 +1240,747 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="35" t="n">
         <v>0.05</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="21">
         <f>$C$4*A8</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B8))-MAX(0,D8-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E8" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C8+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C8+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$45:$B$53)*((C8+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$57:$B$58)*((C8+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F8" s="35">
+      <c r="E8" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C8+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C8+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$46:$B$54)*((C8+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$58:$B$59)*((C8+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F8" s="36">
         <f>D8+E8</f>
         <v/>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="21">
         <f>MAX(0,$C$4-B8-H8)</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="21">
         <f>MAX(MIN(MAX($C$4-B8,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I8" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G8+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G8+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$45:$B$53)*((G8+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$57:$B$58)*((G8+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J8" s="35">
+      <c r="I8" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G8+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G8+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$46:$B$54)*((G8+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$58:$B$59)*((G8+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J8" s="36">
         <f>H8+I8</f>
         <v/>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="21">
         <f>F8-J8</f>
         <v/>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="30">
         <f>0</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="n">
+      <c r="A9" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="21">
         <f>$C$4*A9</f>
         <v/>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B9))-MAX(0,D9-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E9" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C9+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C9+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$45:$B$53)*((C9+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$57:$B$58)*((C9+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F9" s="35">
+      <c r="E9" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C9+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C9+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$46:$B$54)*((C9+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$58:$B$59)*((C9+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F9" s="36">
         <f>D9+E9</f>
         <v/>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="21">
         <f>MAX(0,$C$4-B9-H9)</f>
         <v/>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="21">
         <f>MAX(MIN(MAX($C$4-B9,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I9" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G9+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G9+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$45:$B$53)*((G9+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$57:$B$58)*((G9+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J9" s="35">
+      <c r="I9" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G9+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G9+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$46:$B$54)*((G9+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$58:$B$59)*((G9+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J9" s="36">
         <f>H9+I9</f>
         <v/>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="21">
         <f>F9-J9</f>
         <v/>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="30">
         <f>IF(AND(K9&gt;=0,K8&lt;0),A9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="35" t="n">
         <v>0.15</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="21">
         <f>$C$4*A10</f>
         <v/>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B10))-MAX(0,D10-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E10" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C10+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C10+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$45:$B$53)*((C10+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$57:$B$58)*((C10+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F10" s="35">
+      <c r="E10" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C10+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C10+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$46:$B$54)*((C10+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$58:$B$59)*((C10+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F10" s="36">
         <f>D10+E10</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="21">
         <f>MAX(0,$C$4-B10-H10)</f>
         <v/>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="21">
         <f>MAX(MIN(MAX($C$4-B10,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I10" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G10+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G10+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$45:$B$53)*((G10+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$57:$B$58)*((G10+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J10" s="35">
+      <c r="I10" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G10+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G10+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$46:$B$54)*((G10+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$58:$B$59)*((G10+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J10" s="36">
         <f>H10+I10</f>
         <v/>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="21">
         <f>F10-J10</f>
         <v/>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="30">
         <f>IF(AND(K10&gt;=0,K9&lt;0),A10,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="n">
+      <c r="A11" s="35" t="n">
         <v>0.2</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="21">
         <f>$C$4*A11</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B11))-MAX(0,D11-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C11+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C11+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$45:$B$53)*((C11+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$57:$B$58)*((C11+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F11" s="35">
+      <c r="E11" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C11+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C11+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$46:$B$54)*((C11+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$58:$B$59)*((C11+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F11" s="36">
         <f>D11+E11</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="21">
         <f>MAX(0,$C$4-B11-H11)</f>
         <v/>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="21">
         <f>MAX(MIN(MAX($C$4-B11,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I11" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G11+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G11+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$45:$B$53)*((G11+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$57:$B$58)*((G11+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J11" s="35">
+      <c r="I11" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G11+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G11+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$46:$B$54)*((G11+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$58:$B$59)*((G11+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J11" s="36">
         <f>H11+I11</f>
         <v/>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="21">
         <f>F11-J11</f>
         <v/>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="30">
         <f>IF(AND(K11&gt;=0,K10&lt;0),A11,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="n">
+      <c r="A12" s="35" t="n">
         <v>0.25</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="21">
         <f>$C$4*A12</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B12))-MAX(0,D12-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E12" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C12+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C12+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$45:$B$53)*((C12+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$57:$B$58)*((C12+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F12" s="35">
+      <c r="E12" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C12+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C12+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$46:$B$54)*((C12+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$58:$B$59)*((C12+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F12" s="36">
         <f>D12+E12</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="21">
         <f>MAX(0,$C$4-B12-H12)</f>
         <v/>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="21">
         <f>MAX(MIN(MAX($C$4-B12,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I12" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G12+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G12+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$45:$B$53)*((G12+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$57:$B$58)*((G12+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J12" s="35">
+      <c r="I12" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G12+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G12+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$46:$B$54)*((G12+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$58:$B$59)*((G12+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J12" s="36">
         <f>H12+I12</f>
         <v/>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="21">
         <f>F12-J12</f>
         <v/>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="30">
         <f>IF(AND(K12&gt;=0,K11&lt;0),A12,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="n">
+      <c r="A13" s="35" t="n">
         <v>0.3</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="21">
         <f>$C$4*A13</f>
         <v/>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B13))-MAX(0,D13-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E13" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C13+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C13+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$45:$B$53)*((C13+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$57:$B$58)*((C13+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F13" s="35">
+      <c r="E13" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C13+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C13+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$46:$B$54)*((C13+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$58:$B$59)*((C13+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F13" s="36">
         <f>D13+E13</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="21">
         <f>MAX(0,$C$4-B13-H13)</f>
         <v/>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="21">
         <f>MAX(MIN(MAX($C$4-B13,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I13" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G13+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G13+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$45:$B$53)*((G13+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$57:$B$58)*((G13+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J13" s="35">
+      <c r="I13" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G13+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G13+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$46:$B$54)*((G13+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$58:$B$59)*((G13+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J13" s="36">
         <f>H13+I13</f>
         <v/>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="21">
         <f>F13-J13</f>
         <v/>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="30">
         <f>IF(AND(K13&gt;=0,K12&lt;0),A13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="n">
+      <c r="A14" s="35" t="n">
         <v>0.35</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="21">
         <f>$C$4*A14</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B14))-MAX(0,D14-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E14" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C14+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C14+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$45:$B$53)*((C14+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$57:$B$58)*((C14+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F14" s="35">
+      <c r="E14" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C14+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C14+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$46:$B$54)*((C14+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$58:$B$59)*((C14+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F14" s="36">
         <f>D14+E14</f>
         <v/>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="21">
         <f>MAX(0,$C$4-B14-H14)</f>
         <v/>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="21">
         <f>MAX(MIN(MAX($C$4-B14,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I14" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G14+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G14+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$45:$B$53)*((G14+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$57:$B$58)*((G14+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J14" s="35">
+      <c r="I14" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G14+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G14+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$46:$B$54)*((G14+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$58:$B$59)*((G14+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J14" s="36">
         <f>H14+I14</f>
         <v/>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="21">
         <f>F14-J14</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="30">
         <f>IF(AND(K14&gt;=0,K13&lt;0),A14,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="n">
+      <c r="A15" s="35" t="n">
         <v>0.4</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="21">
         <f>$C$4*A15</f>
         <v/>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B15))-MAX(0,D15-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E15" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C15+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C15+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$45:$B$53)*((C15+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$57:$B$58)*((C15+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F15" s="35">
+      <c r="E15" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C15+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C15+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$46:$B$54)*((C15+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$58:$B$59)*((C15+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F15" s="36">
         <f>D15+E15</f>
         <v/>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="21">
         <f>MAX(0,$C$4-B15-H15)</f>
         <v/>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="21">
         <f>MAX(MIN(MAX($C$4-B15,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I15" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G15+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G15+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$45:$B$53)*((G15+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$57:$B$58)*((G15+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J15" s="35">
+      <c r="I15" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G15+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G15+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$46:$B$54)*((G15+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$58:$B$59)*((G15+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J15" s="36">
         <f>H15+I15</f>
         <v/>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="21">
         <f>F15-J15</f>
         <v/>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="30">
         <f>IF(AND(K15&gt;=0,K14&lt;0),A15,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="n">
+      <c r="A16" s="35" t="n">
         <v>0.45</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="21">
         <f>$C$4*A16</f>
         <v/>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B16))-MAX(0,D16-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E16" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C16+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C16+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$45:$B$53)*((C16+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$57:$B$58)*((C16+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F16" s="35">
+      <c r="E16" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C16+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C16+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$46:$B$54)*((C16+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$58:$B$59)*((C16+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
         <f>D16+E16</f>
         <v/>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="21">
         <f>MAX(0,$C$4-B16-H16)</f>
         <v/>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="21">
         <f>MAX(MIN(MAX($C$4-B16,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I16" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G16+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G16+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$45:$B$53)*((G16+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$57:$B$58)*((G16+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J16" s="35">
+      <c r="I16" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G16+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G16+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$46:$B$54)*((G16+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$58:$B$59)*((G16+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J16" s="36">
         <f>H16+I16</f>
         <v/>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="21">
         <f>F16-J16</f>
         <v/>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="30">
         <f>IF(AND(K16&gt;=0,K15&lt;0),A16,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="n">
+      <c r="A17" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="21">
         <f>$C$4*A17</f>
         <v/>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B17))-MAX(0,D17-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E17" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C17+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C17+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$45:$B$53)*((C17+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$57:$B$58)*((C17+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F17" s="35">
+      <c r="E17" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C17+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C17+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$46:$B$54)*((C17+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$58:$B$59)*((C17+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F17" s="36">
         <f>D17+E17</f>
         <v/>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="21">
         <f>MAX(0,$C$4-B17-H17)</f>
         <v/>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="21">
         <f>MAX(MIN(MAX($C$4-B17,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I17" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G17+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G17+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$45:$B$53)*((G17+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$57:$B$58)*((G17+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J17" s="35">
+      <c r="I17" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G17+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G17+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$46:$B$54)*((G17+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$58:$B$59)*((G17+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J17" s="36">
         <f>H17+I17</f>
         <v/>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="21">
         <f>F17-J17</f>
         <v/>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="30">
         <f>IF(AND(K17&gt;=0,K16&lt;0),A17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="n">
+      <c r="A18" s="35" t="n">
         <v>0.55</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="21">
         <f>$C$4*A18</f>
         <v/>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B18))-MAX(0,D18-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E18" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C18+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C18+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$45:$B$53)*((C18+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$57:$B$58)*((C18+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F18" s="35">
+      <c r="E18" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C18+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C18+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$46:$B$54)*((C18+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$58:$B$59)*((C18+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F18" s="36">
         <f>D18+E18</f>
         <v/>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="21">
         <f>MAX(0,$C$4-B18-H18)</f>
         <v/>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="21">
         <f>MAX(MIN(MAX($C$4-B18,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I18" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G18+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G18+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$45:$B$53)*((G18+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$57:$B$58)*((G18+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J18" s="35">
+      <c r="I18" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G18+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G18+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$46:$B$54)*((G18+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$58:$B$59)*((G18+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J18" s="36">
         <f>H18+I18</f>
         <v/>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="21">
         <f>F18-J18</f>
         <v/>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="30">
         <f>IF(AND(K18&gt;=0,K17&lt;0),A18,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="n">
+      <c r="A19" s="35" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="21">
         <f>$C$4*A19</f>
         <v/>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B19))-MAX(0,D19-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E19" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C19+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C19+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$45:$B$53)*((C19+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$57:$B$58)*((C19+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F19" s="35">
+      <c r="E19" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C19+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C19+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$46:$B$54)*((C19+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$58:$B$59)*((C19+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F19" s="36">
         <f>D19+E19</f>
         <v/>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="21">
         <f>MAX(0,$C$4-B19-H19)</f>
         <v/>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="21">
         <f>MAX(MIN(MAX($C$4-B19,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I19" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G19+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G19+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$45:$B$53)*((G19+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$57:$B$58)*((G19+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J19" s="35">
+      <c r="I19" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G19+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G19+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$46:$B$54)*((G19+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$58:$B$59)*((G19+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J19" s="36">
         <f>H19+I19</f>
         <v/>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="21">
         <f>F19-J19</f>
         <v/>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="30">
         <f>IF(AND(K19&gt;=0,K18&lt;0),A19,0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="n">
+      <c r="A20" s="35" t="n">
         <v>0.65</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="21">
         <f>$C$4*A20</f>
         <v/>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B20))-MAX(0,D20-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E20" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C20+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C20+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$45:$B$53)*((C20+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$57:$B$58)*((C20+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F20" s="35">
+      <c r="E20" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C20+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C20+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$46:$B$54)*((C20+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$58:$B$59)*((C20+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F20" s="36">
         <f>D20+E20</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="21">
         <f>MAX(0,$C$4-B20-H20)</f>
         <v/>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="21">
         <f>MAX(MIN(MAX($C$4-B20,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I20" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G20+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G20+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$45:$B$53)*((G20+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$57:$B$58)*((G20+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J20" s="35">
+      <c r="I20" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G20+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G20+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$46:$B$54)*((G20+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$58:$B$59)*((G20+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J20" s="36">
         <f>H20+I20</f>
         <v/>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="21">
         <f>F20-J20</f>
         <v/>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="30">
         <f>IF(AND(K20&gt;=0,K19&lt;0),A20,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="n">
+      <c r="A21" s="35" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="21">
         <f>$C$4*A21</f>
         <v/>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B21))-MAX(0,D21-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E21" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C21+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C21+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$45:$B$53)*((C21+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$57:$B$58)*((C21+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F21" s="35">
+      <c r="E21" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C21+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C21+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$46:$B$54)*((C21+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$58:$B$59)*((C21+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F21" s="36">
         <f>D21+E21</f>
         <v/>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="21">
         <f>MAX(0,$C$4-B21-H21)</f>
         <v/>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="21">
         <f>MAX(MIN(MAX($C$4-B21,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I21" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G21+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G21+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$45:$B$53)*((G21+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$57:$B$58)*((G21+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J21" s="35">
+      <c r="I21" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G21+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G21+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$46:$B$54)*((G21+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$58:$B$59)*((G21+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J21" s="36">
         <f>H21+I21</f>
         <v/>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="21">
         <f>F21-J21</f>
         <v/>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="30">
         <f>IF(AND(K21&gt;=0,K20&lt;0),A21,0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="35" t="n">
         <v>0.75</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="21">
         <f>$C$4*A22</f>
         <v/>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="21">
         <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B22))-MAX(0,D22-$C$4*Parametros!$C$18)</f>
         <v/>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="21">
         <f>MAX(MIN($C$4*Parametros!$C$7,Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E22" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((C22+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((C22+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$45:$B$53)*((C22+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$57:$B$58)*((C22+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F22" s="35">
+      <c r="E22" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C22+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C22+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$46:$B$54)*((C22+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$58:$B$59)*((C22+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F22" s="36">
         <f>D22+E22</f>
         <v/>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="21">
         <f>MAX(0,$C$4-B22-H22)</f>
         <v/>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="21">
         <f>MAX(MIN(MAX($C$4-B22,0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="I22" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$45:$B$53)*(((G22+$C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$57:$B$58)*(((G22+$C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$45:$B$53)*((G22+$C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$57:$B$58)*((G22+$C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))-IF(Inputs!$D$29=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$45:$B$53)*((($C$5)/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$57:$B$58)*((($C$5)/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT((($C$5)&gt;Parametros!$B$45:$B$53)*(($C$5)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$5)&gt;Parametros!$B$57:$B$58)*(($C$5)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="J22" s="35">
+      <c r="I22" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G22+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G22+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$46:$B$54)*((G22+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$58:$B$59)*((G22+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$33=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="J22" s="36">
         <f>H22+I22</f>
         <v/>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="21">
         <f>F22-J22</f>
         <v/>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="30">
         <f>IF(AND(K22&gt;=0,K21&lt;0),A22,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Ponto de viragem — peso dos custos reais</t>
         </is>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="24">
         <f>MAX(L8:L22)</f>
         <v/>
       </c>
@@ -1683,12 +1991,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Ponto de viragem — em euros de custos anuais</t>
         </is>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="23">
         <f>C24*$C$4</f>
         <v/>
       </c>
@@ -1706,6 +2014,7 @@
     <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1807,7 +2116,7 @@
         </is>
       </c>
       <c r="D5" s="37">
-        <f>V1_ENI_Simplificado!$D$30</f>
+        <f>V1_ENI_Simplificado!$D$33</f>
         <v/>
       </c>
       <c r="E5" s="38" t="n">
@@ -1837,7 +2146,7 @@
         </is>
       </c>
       <c r="D6" s="37">
-        <f>V1_ENI_Simplificado!$D$20</f>
+        <f>V1_ENI_Simplificado!$D$23</f>
         <v/>
       </c>
       <c r="E6" s="38" t="n">
@@ -1867,7 +2176,7 @@
         </is>
       </c>
       <c r="D7" s="37">
-        <f>V1_ENI_Simplificado!$D$34</f>
+        <f>V1_ENI_Simplificado!$D$37</f>
         <v/>
       </c>
       <c r="E7" s="38" t="n">
@@ -1897,11 +2206,11 @@
         </is>
       </c>
       <c r="D8" s="37">
-        <f>V1_ENI_Simplificado!$D$38</f>
+        <f>V1_ENI_Simplificado!$D$41</f>
         <v/>
       </c>
       <c r="E8" s="38" t="n">
-        <v>8746.42</v>
+        <v>17746.42</v>
       </c>
       <c r="F8" s="39">
         <f>D8-E8</f>
@@ -1935,7 +2244,7 @@
         <v/>
       </c>
       <c r="E10" s="38" t="n">
-        <v>5970.77</v>
+        <v>8192.01</v>
       </c>
       <c r="F10" s="39">
         <f>D10-E10</f>
@@ -1965,7 +2274,7 @@
         <v/>
       </c>
       <c r="E11" s="38" t="n">
-        <v>7507.85</v>
+        <v>9433.85</v>
       </c>
       <c r="F11" s="39">
         <f>D11-E11</f>
@@ -1995,7 +2304,7 @@
         <v/>
       </c>
       <c r="E12" s="38" t="n">
-        <v>13478.62</v>
+        <v>17625.85</v>
       </c>
       <c r="F12" s="39">
         <f>D12-E12</f>
@@ -2025,7 +2334,7 @@
         <v/>
       </c>
       <c r="E13" s="38" t="n">
-        <v>28771.38</v>
+        <v>33624.15</v>
       </c>
       <c r="F13" s="39">
         <f>D13-E13</f>
@@ -2059,7 +2368,7 @@
         <v/>
       </c>
       <c r="E15" s="38" t="n">
-        <v>5786.72</v>
+        <v>8612.719999999999</v>
       </c>
       <c r="F15" s="39">
         <f>D15-E15</f>
@@ -2119,7 +2428,7 @@
         <v/>
       </c>
       <c r="E17" s="38" t="n">
-        <v>12424.72</v>
+        <v>15250.72</v>
       </c>
       <c r="F17" s="39">
         <f>D17-E17</f>
@@ -2149,7 +2458,7 @@
         <v/>
       </c>
       <c r="E18" s="38" t="n">
-        <v>29825.28</v>
+        <v>35999.28</v>
       </c>
       <c r="F18" s="39">
         <f>D18-E18</f>
@@ -2243,7 +2552,7 @@
         <v/>
       </c>
       <c r="E22" s="38" t="n">
-        <v>16605.81</v>
+        <v>20259.81</v>
       </c>
       <c r="F22" s="39">
         <f>D22-E22</f>
@@ -2273,7 +2582,7 @@
         <v/>
       </c>
       <c r="E23" s="38" t="n">
-        <v>22244.89</v>
+        <v>26200.93</v>
       </c>
       <c r="F23" s="39">
         <f>D23-E23</f>
@@ -2303,7 +2612,7 @@
         </is>
       </c>
       <c r="D25" s="37">
-        <f>V1_ENI_Simplificado!$E$30</f>
+        <f>V1_ENI_Simplificado!$E$33</f>
         <v/>
       </c>
       <c r="E25" s="38" t="n">
@@ -2333,7 +2642,7 @@
         </is>
       </c>
       <c r="D26" s="37">
-        <f>V1_ENI_Simplificado!$E$20</f>
+        <f>V1_ENI_Simplificado!$E$23</f>
         <v/>
       </c>
       <c r="E26" s="38" t="n">
@@ -2363,7 +2672,7 @@
         </is>
       </c>
       <c r="D27" s="37">
-        <f>V1_ENI_Simplificado!$E$34</f>
+        <f>V1_ENI_Simplificado!$E$37</f>
         <v/>
       </c>
       <c r="E27" s="38" t="n">
@@ -2393,11 +2702,11 @@
         </is>
       </c>
       <c r="D28" s="37">
-        <f>V1_ENI_Simplificado!$E$38</f>
+        <f>V1_ENI_Simplificado!$E$41</f>
         <v/>
       </c>
       <c r="E28" s="38" t="n">
-        <v>7329.57</v>
+        <v>20829.57</v>
       </c>
       <c r="F28" s="39">
         <f>D28-E28</f>
@@ -2411,18 +2720,18 @@
       <c r="I28" s="41" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>Estado global</t>
         </is>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="25">
         <f>IF(COUNTIF($G$6:$G$28,"DIVERGE")=0,"TODAS AS VERIFICAÇÕES OK","HÁ DIVERGÊNCIAS")</f>
         <v/>
       </c>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="33" t="n"/>
     </row>
     <row r="32" ht="46" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -2447,7 +2756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2896,54 +3205,54 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Coeficiente do simplificado aplicável à receita de cedência de espaço</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>COEF_SALA</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Art. 31.º n.º 1 al. c) CIRS — restantes prestações de serviços</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR (ver R1-29). Depende de N1-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>IRC e tributação da distribuição</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>IRC — taxa aplicável ao primeiro escalão (PME)</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>IRC_PME</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Art. 87.º n.º 2 CIRC</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
-        </is>
-      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>IRC — limite da matéria coletável do primeiro escalão</t>
+          <t>IRC — taxa aplicável ao primeiro escalão (PME)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>IRC_LIM</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="n">
-        <v>50000</v>
+          <t>IRC_PME</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>0.16</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
@@ -2952,249 +3261,249 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>CONFIRMAR 2026</t>
+          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>IRC — taxa geral</t>
+          <t>IRC — limite da matéria coletável do primeiro escalão</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>IRC_GER</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="n">
-        <v>0.2</v>
+          <t>IRC_LIM</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>50000</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Art. 87.º n.º 1 CIRC</t>
+          <t>Art. 87.º n.º 2 CIRC</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
+          <t>CONFIRMAR 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Derrama municipal (município do Porto)</t>
+          <t>IRC — taxa geral</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>DERRAMA</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>0.015</v>
+          <t>IRC_GER</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>0.2</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Art. 18.º Lei 73/2013 + deliberação municipal</t>
+          <t>Art. 87.º n.º 1 CIRC</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>CONFIRMAR município e isenção PME</t>
+          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Derrama incide sobre sociedade transparente? (1=sim / 0=não)</t>
+          <t>Derrama municipal (município do Porto)</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>DERR_TRANSP</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>0</v>
+          <t>DERRAMA</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>0.015</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Questão controvertida — art. 12.º CIRC vs. art. 18.º Lei 73/2013</t>
+          <t>Art. 18.º Lei 73/2013 + deliberação municipal</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>EM ABERTO (ver R1-13)</t>
+          <t>CONFIRMAR município e isenção PME</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Dividendos — taxa liberatória</t>
+          <t>Derrama incide sobre sociedade transparente? (1=sim / 0=não)</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>DIV_LIB</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>0.28</v>
+          <t>DERR_TRANSP</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Art. 71.º n.º 1 CIRS</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
+          <t>Questão controvertida — art. 12.º CIRC vs. art. 18.º Lei 73/2013</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>EM ABERTO (ver R1-13)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>Dividendos — taxa liberatória</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>DIV_LIB</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Art. 71.º n.º 1 CIRS</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
           <t>Dividendos — % considerada em caso de englobamento</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>DIV_ENG</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C30" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Art. 40.º-A n.º 1 CIRS</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Confirmar</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>IVA</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>IVA — taxa normal (continente)</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>IVA_NORM</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Art. 18.º n.º 1 al. c) CIVA</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
-        </is>
-      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
+          <t>IVA — taxa normal (continente)</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>IVA_NORM</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Art. 18.º n.º 1 al. c) CIVA</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
           <t>IVA — taxa reduzida (continente)</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>IVA_RED</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C33" s="12" t="n">
         <v>0.06</v>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Art. 18.º n.º 1 al. a) CIVA + Lista I</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>Validado</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Amortizações (vias com contabilidade)</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Taxa de amortização — obras / benfeitorias em imóvel alheio</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>AM_OBRAS</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>DR 25/2009 — ou período do contrato de arrendamento, se inferior</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR código aplicável</t>
-        </is>
-      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Taxa de amortização — equipamento clínico</t>
+          <t>Taxa de amortização — obras / benfeitorias em imóvel alheio</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>AM_EQUIP</t>
+          <t>AM_OBRAS</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>DR 25/2009, tabela II</t>
+          <t>DR 25/2009 — ou período do contrato de arrendamento, se inferior</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -3206,73 +3515,73 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
+          <t>Taxa de amortização — equipamento clínico</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>AM_EQUIP</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>DR 25/2009, tabela II</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR código aplicável</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
           <t>Taxa de amortização — software</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>AM_SOFT</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C37" s="12" t="n">
         <v>0.3333</v>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>DR 25/2009</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>CONFIRMAR</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Transparência fiscal — limiares do teste (usados na N1, não no cálculo)</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>% mínima de capital detida por profissionais das atividades do art. 151.º</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>TF_CAP</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
-        </is>
-      </c>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>% mínima de rendimentos provenientes de atividades do art. 151.º</t>
+          <t>% mínima de capital detida por profissionais das atividades do art. 151.º</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>TF_REND</t>
+          <t>TF_CAP</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
@@ -3292,121 +3601,128 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
+          <t>% mínima de rendimentos provenientes de atividades do art. 151.º</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>TF_REND</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
           <t>N.º máximo de sócios para o teste da subal. ii)</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>TF_SOCIOS</t>
         </is>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C41" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>Validado</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Escalões de IRS — taxas gerais</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Tabela em vigor: 2025 (Lei n.º 33-A/2025). ATUALIZAR para os escalões do OE2026 antes de qualquer número entrar no relatório. A coluna 'Delta' é a mecânica de cálculo (taxa do escalão menos taxa do anterior) e recalcula sozinha.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Escalão</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Limite inferior</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Limite superior</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Taxa</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Delta (calculado)</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B45" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="15" t="n">
-        <v>8059</v>
-      </c>
-      <c r="D45" s="13" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E45" s="17">
-        <f>D45</f>
-        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="15" t="n">
         <v>8059</v>
       </c>
-      <c r="C46" s="15" t="n">
-        <v>12160</v>
-      </c>
       <c r="D46" s="13" t="n">
-        <v>0.16</v>
+        <v>0.125</v>
       </c>
       <c r="E46" s="17">
-        <f>D46-D45</f>
+        <f>D46</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" s="15" t="n">
+        <v>8059</v>
+      </c>
+      <c r="C47" s="15" t="n">
         <v>12160</v>
       </c>
-      <c r="C47" s="15" t="n">
-        <v>17233</v>
-      </c>
       <c r="D47" s="13" t="n">
-        <v>0.215</v>
+        <v>0.16</v>
       </c>
       <c r="E47" s="17">
         <f>D47-D46</f>
@@ -3415,16 +3731,16 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B48" s="15" t="n">
+        <v>12160</v>
+      </c>
+      <c r="C48" s="15" t="n">
         <v>17233</v>
       </c>
-      <c r="C48" s="15" t="n">
-        <v>22306</v>
-      </c>
       <c r="D48" s="13" t="n">
-        <v>0.244</v>
+        <v>0.215</v>
       </c>
       <c r="E48" s="17">
         <f>D48-D47</f>
@@ -3433,16 +3749,16 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B49" s="15" t="n">
+        <v>17233</v>
+      </c>
+      <c r="C49" s="15" t="n">
         <v>22306</v>
       </c>
-      <c r="C49" s="15" t="n">
-        <v>28400</v>
-      </c>
       <c r="D49" s="13" t="n">
-        <v>0.314</v>
+        <v>0.244</v>
       </c>
       <c r="E49" s="17">
         <f>D49-D48</f>
@@ -3451,16 +3767,16 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B50" s="15" t="n">
+        <v>22306</v>
+      </c>
+      <c r="C50" s="15" t="n">
         <v>28400</v>
       </c>
-      <c r="C50" s="15" t="n">
-        <v>41629</v>
-      </c>
       <c r="D50" s="13" t="n">
-        <v>0.349</v>
+        <v>0.314</v>
       </c>
       <c r="E50" s="17">
         <f>D50-D49</f>
@@ -3469,16 +3785,16 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B51" s="15" t="n">
+        <v>28400</v>
+      </c>
+      <c r="C51" s="15" t="n">
         <v>41629</v>
       </c>
-      <c r="C51" s="15" t="n">
-        <v>44987</v>
-      </c>
       <c r="D51" s="13" t="n">
-        <v>0.431</v>
+        <v>0.349</v>
       </c>
       <c r="E51" s="17">
         <f>D51-D50</f>
@@ -3487,16 +3803,16 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B52" s="15" t="n">
+        <v>41629</v>
+      </c>
+      <c r="C52" s="15" t="n">
         <v>44987</v>
       </c>
-      <c r="C52" s="15" t="n">
-        <v>83696</v>
-      </c>
       <c r="D52" s="13" t="n">
-        <v>0.446</v>
+        <v>0.431</v>
       </c>
       <c r="E52" s="17">
         <f>D52-D51</f>
@@ -3505,102 +3821,120 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53" s="15" t="n">
+        <v>44987</v>
+      </c>
+      <c r="C53" s="15" t="n">
         <v>83696</v>
       </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>sem limite</t>
-        </is>
-      </c>
       <c r="D53" s="13" t="n">
-        <v>0.48</v>
+        <v>0.446</v>
       </c>
       <c r="E53" s="17">
         <f>D53-D52</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B54" s="15" t="n">
+        <v>83696</v>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>sem limite</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E54" s="17">
+        <f>D54-D53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Taxa adicional de solidariedade (art. 68.º-A CIRS)</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
-      <c r="E55" s="7" t="n"/>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Escalão</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Limite inferior</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Limite superior</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Taxa</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>Delta (calculado)</t>
         </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B57" s="15" t="n">
-        <v>80000</v>
-      </c>
-      <c r="C57" s="15" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D57" s="13" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E57" s="17">
-        <f>D57</f>
-        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="15" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E58" s="17">
+        <f>D58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B58" s="15" t="n">
+      <c r="B59" s="15" t="n">
         <v>250000</v>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C59" s="18" t="inlineStr">
         <is>
           <t>sem limite</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D59" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="E58" s="17">
-        <f>D58-D57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="E59" s="17">
+        <f>D59-D58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Legenda: células a azul sobre fundo amarelo são de preenchimento; tudo o resto é fórmula. Nenhuma taxa deve ser escrita dentro de uma fórmula noutra folha — se faltar um parâmetro, acrescenta-se aqui.</t>
         </is>
@@ -3608,8 +3942,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A61:E61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3621,7 +3955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3681,7 +4015,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Faturação</t>
+          <t>Faturação e modelo de colaboração</t>
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
@@ -3693,646 +4027,1015 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Faturação anual de fisioterapia (isenta, art. 9.º CIVA)</t>
+          <t>Faturação anual da própria Dra. Júlia (isenta, art. 9.º CIVA)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>FAT</t>
+          <t>FAT_PROP</t>
         </is>
       </c>
       <c r="C6" s="15" t="n">
-        <v>70000</v>
+        <v>52000</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>95000</v>
+        <v>65000</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>130000</v>
+        <v>85000</v>
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Input cliente 1 — EM FALTA. Placeholder ancorado na referência de ~80.000 € da ata.</t>
+          <t>Input cliente 1 — EM FALTA. Doentes próprios, independentemente do modelo de colaboração.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Faturação anual sujeita a IVA dentro da sociedade (atividade do cônjuge)</t>
+          <t>Faturação anual gerada pelos fisioterapeutas a integrar</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>FAT_TRIB</t>
+          <t>FAT_COLAB</t>
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Input cliente 6 — EM FALTA. Só relevante na via 4 e no cenário de sujeito passivo misto.</t>
+          <t>Input cliente 1 e 5 — EM FALTA. No modelo 1 é faturada pela clínica; no modelo 2 é faturada diretamente pelos profissionais e nunca passa pela clínica.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Custos operacionais anuais</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>MODELO DE COLABORAÇÃO: 1 = prestação de serviços · 2 = cedência de sala</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>MOD_COLAB</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>ALAVANCA. Ata, ponto 4. Alterna toda a estrutura de receita e custo. Sustenta a exposição E2.6.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Renda do espaço</t>
+          <t>Modelo 1 — honorários anuais a pagar aos fisioterapeutas</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>RENDA</t>
+          <t>HONOR</t>
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>12000</v>
+        <v>12600</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>14400</v>
+        <v>21000</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>18000</v>
+        <v>31500</v>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Input cliente 3 — EM FALTA. Baixo/Base = 2 gabinetes; Alto = 3 gabinetes.</t>
+          <t>Input cliente 5 — EM FALTA. Placeholder a 70% da faturação que geram. Ignorado no modelo 2.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Condomínio e encargos do espaço</t>
+          <t>Modelo 2 — receita anual de cedência de sala</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>CONDOM</t>
+          <t>REC_SALA</t>
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>1200</v>
+        <v>5400</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>1500</v>
+        <v>9000</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>1800</v>
+        <v>13500</v>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Input cliente 3 — EM FALTA.</t>
+          <t>Input cliente 5 — EM FALTA. Placeholder a 30% da faturação que geram. Ignorado no modelo 1.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Seguros (RC profissional, multirriscos)</t>
+          <t>Cedência de sala sujeita a IVA? (1 = sim / 0 = arrendamento isento)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>SEGUROS</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>EM FALTA.</t>
+          <t>SALA_TRIB</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Depende de N1-04: arrendamento isento (art. 9.º n.º 29 CIVA) ou prestação de serviços com disponibilização de meios, tributada. Não está resolvido.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Software de gestão e faturação</t>
+          <t>Faturação anual sujeita a IVA dentro da sociedade (atividade do cônjuge)</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>SOFTW</t>
+          <t>FAT_TRIB</t>
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>EM FALTA.</t>
+          <t>Input cliente 6 — EM FALTA. Só relevante na via 4 e no cenário de sujeito passivo misto.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Consumíveis clínicos</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>CONSUM</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>2850</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>3900</v>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>EM FALTA. Placeholder a 3% da faturação.</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Custos operacionais anuais</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Outros custos operacionais</t>
+          <t>Renda do espaço</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>OUTROS</t>
+          <t>RENDA</t>
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1500</v>
+        <v>12000</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>2000</v>
+        <v>14400</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>2500</v>
+        <v>18000</v>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>EM FALTA.</t>
+          <t>Input cliente 3 — EM FALTA. Baixo/Base = 2 gabinetes; Alto = 3 gabinetes.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Honorários a fisioterapeutas a integrar (total anual)</t>
+          <t>Condomínio e encargos do espaço</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>HONOR</t>
+          <t>CONDOM</t>
         </is>
       </c>
       <c r="C15" s="15" t="n">
-        <v>18000</v>
+        <v>1200</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>30000</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>45000</v>
+        <v>1800</v>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Input cliente 5 — EM FALTA. Variável crítica: é o que separa faturação de margem (ata, ponto 6).</t>
+          <t>Input cliente 3 — EM FALTA.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>N.º de fisioterapeutas a integrar</t>
+          <t>Seguros (RC profissional, multirriscos)</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>N_FISIO</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>Ata, ponto 3.</t>
+          <t>SEGUROS</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>EM FALTA.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Investimento inicial (valores sem IVA)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Software de gestão e faturação</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>SOFTW</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>EM FALTA.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Obras e adaptação do espaço</t>
+          <t>Consumíveis clínicos</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>INV_OBRAS</t>
+          <t>CONSUM</t>
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>15000</v>
+        <v>2100</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>25000</v>
+        <v>2850</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>40000</v>
+        <v>3900</v>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Input cliente 4 — EM FALTA.</t>
+          <t>EM FALTA. Placeholder a 3% da faturação.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Equipamento clínico à taxa normal</t>
+          <t>Outros custos operacionais</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>INV_EQUIP</t>
+          <t>OUTROS</t>
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>12000</v>
+        <v>1500</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>30000</v>
+        <v>2500</v>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Input cliente 4 — EM FALTA.</t>
+          <t>EM FALTA.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Equipamento clínico elegível para taxa reduzida</t>
+          <t>N.º de fisioterapeutas a integrar</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>INV_EQUIP_R</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0</v>
+          <t>N_FISIO</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>A confirmar contra as verbas 2.5 e 2.6 da Lista I do CIVA. Se houver elegibilidade, reduz a base do problema de IVA.</t>
+          <t>Ata, ponto 3.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Software e sistemas</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>INV_SOFT</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>EM FALTA.</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Investimento inicial (valores sem IVA)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Vias societárias (3 e 4)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Obras e adaptação do espaço</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>INV_OBRAS</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>Input cliente 4 — EM FALTA.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Remuneração anual bruta de gerência</t>
+          <t>Equipamento clínico à taxa normal</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>REM_GER</t>
+          <t>INV_EQUIP</t>
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>16800</v>
+        <v>20000</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>Variável de decisão, não dado da cliente. Testar sensibilidade.</t>
+        <v>30000</v>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>Input cliente 4 — EM FALTA.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Tributações autónomas estimadas (anual)</t>
+          <t>Equipamento clínico elegível para taxa reduzida</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>TA_EST</t>
+          <t>INV_EQUIP_R</t>
         </is>
       </c>
       <c r="C24" s="15" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>A quantificar pela Fiscalidade em função de viatura e despesas de representação.</t>
+          <t>A confirmar contra as verbas 2.5 e 2.6 da Lista I do CIVA. Se houver elegibilidade, reduz a base do problema de IVA.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Política de distribuição de resultados (% do lucro após imposto)</t>
+          <t>Software e sistemas</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>POL_DIST</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>ALAVANCA. Testar 0% / 50% / 100% — é aqui que se decide se afastar a transparência compensa.</t>
+          <t>INV_SOFT</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>EM FALTA.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>% do capital social detida pelo cônjuge</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>PCT_CONJ</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>Só via 4. Tem de exceder 25% para afastar o teste de capital do art. 6.º n.º 4 al. b) ii) CIRC. Ver N1.</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Vias societárias (3 e 4)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Agregado familiar (IRS)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Remuneração anual bruta de gerência</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>REM_GER</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>16800</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>Variável de decisão, não dado da cliente. Testar sensibilidade.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Rendimento anual do cônjuge fora da estrutura (líquido de deduções específicas)</t>
+          <t>Tributações autónomas estimadas (anual)</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>REND_CONJ</t>
+          <t>TA_EST</t>
         </is>
       </c>
       <c r="C28" s="15" t="n">
-        <v>14000</v>
+        <v>500</v>
       </c>
       <c r="D28" s="15" t="n">
-        <v>18000</v>
+        <v>800</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>Input cliente 6 e 7 — EM FALTA.</t>
+        <v>1200</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>A quantificar pela Fiscalidade em função de viatura e despesas de representação.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Opção por tributação conjunta (1 = sim / 0 = não)</t>
+          <t>Política de distribuição de resultados (% do lucro após imposto)</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>CONJUNTA</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
+          <t>POL_DIST</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>Input cliente 7 — EM FALTA.</t>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>ALAVANCA. Testar 0% / 50% / 100% — é aqui que se decide se afastar a transparência compensa.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>% do capital social detida pelo cônjuge</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>PCT_CONJ</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Só via 4. Tem de exceder 25% para afastar o teste de capital do art. 6.º n.º 4 al. b) ii) CIRC. Ver N1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Agregado familiar (IRS)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Rendimento anual do cônjuge fora da estrutura (líquido de deduções específicas)</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>REND_CONJ</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>Input cliente 6 e 7 — EM FALTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Opção por tributação conjunta (1 = sim / 0 = não)</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>CONJUNTA</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>Input cliente 7 — EM FALTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
           <t>N.º de dependentes</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>N_DEP</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C34" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D34" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E34" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>Input cliente 7 — EM FALTA.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Deduções à coleta estimadas do agregado</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>DED_COL</t>
         </is>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C35" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D35" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="E31" s="15" t="n">
+      <c r="E35" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>EM FALTA. Não afeta a comparação entre vias (cancela-se no diferencial), afeta o IRS total.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Derivadas — não preencher, calculam-se a partir do modelo de colaboração</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Faturação isenta faturada pela estrutura</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>FAT_ISENTA</t>
+        </is>
+      </c>
+      <c r="C37" s="21">
+        <f>Inputs!$C$6+IF(Inputs!$C$8=1,Inputs!$C$7,0)</f>
+        <v/>
+      </c>
+      <c r="D37" s="21">
+        <f>Inputs!$D$6+IF(Inputs!$D$8=1,Inputs!$D$7,0)</f>
+        <v/>
+      </c>
+      <c r="E37" s="21">
+        <f>Inputs!$E$6+IF(Inputs!$E$8=1,Inputs!$E$7,0)</f>
+        <v/>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>No modelo 1 a clínica fatura ao doente a totalidade; no modelo 2 fatura apenas os doentes próprios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Receita de cedência de espaço</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>REC_NAOPROF</t>
+        </is>
+      </c>
+      <c r="C38" s="21">
+        <f>IF(Inputs!$C$8=2,Inputs!$C$10,0)</f>
+        <v/>
+      </c>
+      <c r="D38" s="21">
+        <f>IF(Inputs!$D$8=2,Inputs!$D$10,0)</f>
+        <v/>
+      </c>
+      <c r="E38" s="21">
+        <f>IF(Inputs!$E$8=2,Inputs!$E$10,0)</f>
+        <v/>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>Rendimento que NÃO provém de atividade da lista do art. 151.º CIRS. Ver linha PCT_PROF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Custo com os colaboradores</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>CUSTO_COLAB</t>
+        </is>
+      </c>
+      <c r="C39" s="21">
+        <f>IF(Inputs!$C$8=1,Inputs!$C$9,0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="21">
+        <f>IF(Inputs!$D$8=1,Inputs!$D$9,0)</f>
+        <v/>
+      </c>
+      <c r="E39" s="21">
+        <f>IF(Inputs!$E$8=1,Inputs!$E$9,0)</f>
+        <v/>
+      </c>
+      <c r="F39" s="16" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>MARGEM GERADA PELOS COLABORADORES</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>MARGEM_COLAB</t>
+        </is>
+      </c>
+      <c r="C40" s="23">
+        <f>IF(Inputs!$C$8=1,Inputs!$C$7-Inputs!$C$9,Inputs!$C$10)</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>IF(Inputs!$D$8=1,Inputs!$D$7-Inputs!$D$9,Inputs!$D$10)</f>
+        <v/>
+      </c>
+      <c r="E40" s="23">
+        <f>IF(Inputs!$E$8=1,Inputs!$E$7-Inputs!$E$9,Inputs!$E$10)</f>
+        <v/>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Exposição E2.6. É a resposta à pergunta da ata: qual dos dois modelos deixa mais margem. Alternar MOD_COLAB entre 1 e 2 e comparar esta linha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Receita total da estrutura (incl. cônjuge, se aplicável)</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>REC_TOTAL</t>
+        </is>
+      </c>
+      <c r="C41" s="21">
+        <f>Inputs!$C$37+Inputs!$C$38+Inputs!$C$12</f>
+        <v/>
+      </c>
+      <c r="D41" s="21">
+        <f>Inputs!$D$37+Inputs!$D$38+Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f>Inputs!$E$37+Inputs!$E$38+Inputs!$E$12</f>
+        <v/>
+      </c>
+      <c r="F41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Receita sujeita a IVA (base do pro rata)</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>REC_TRIB</t>
+        </is>
+      </c>
+      <c r="C42" s="21">
+        <f>Inputs!$C$12+IF(Inputs!$C$11=1,Inputs!$C$38,0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="21">
+        <f>Inputs!$D$12+IF(Inputs!$D$11=1,Inputs!$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="E42" s="21">
+        <f>Inputs!$E$12+IF(Inputs!$E$11=1,Inputs!$E$38,0)</f>
+        <v/>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>Depende de N1-04: se a cedência for arrendamento isento, não entra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>% de rendimentos provenientes de atividades da lista do art. 151.º CIRS</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>PCT_PROF</t>
+        </is>
+      </c>
+      <c r="C43" s="24">
+        <f>IF(Inputs!$C$41&lt;=0,0,Inputs!$C$37/Inputs!$C$41)</f>
+        <v/>
+      </c>
+      <c r="D43" s="24">
+        <f>IF(Inputs!$D$41&lt;=0,0,Inputs!$D$37/Inputs!$D$41)</f>
+        <v/>
+      </c>
+      <c r="E43" s="24">
+        <f>IF(Inputs!$E$41&lt;=0,0,Inputs!$E$37/Inputs!$E$41)</f>
+        <v/>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>Teste de rendimentos do art. 6.º n.º 4 al. b) ii) CIRC. Pressupõe que nem a cedência de espaço nem a atividade do cônjuge constam da lista — o segundo ponto é o R1-14, por verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Receita de cedência necessária para FALHAR o teste de rendimentos</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>REC_SALA_MIN</t>
+        </is>
+      </c>
+      <c r="C44" s="21">
+        <f>Inputs!$C$37*(1-Parametros!$C$40)/Parametros!$C$40</f>
+        <v/>
+      </c>
+      <c r="D44" s="21">
+        <f>Inputs!$D$37*(1-Parametros!$C$40)/Parametros!$C$40</f>
+        <v/>
+      </c>
+      <c r="E44" s="21">
+        <f>Inputs!$E$37*(1-Parametros!$C$40)/Parametros!$C$40</f>
+        <v/>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>Álgebra do teste: para os rendimentos profissionais descerem a 75% ou menos, a receita não profissional tem de atingir um terço da faturação profissional. Comparar com a linha REC_NAOPROF antes de propor esta via em N1, secção 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>Teste de rendimentos do art. 6.º n.º 4 al. b) ii) CIRC</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>TESTE_TF</t>
+        </is>
+      </c>
+      <c r="C45" s="25">
+        <f>IF(Inputs!$C$43&gt;Parametros!$C$40,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <v/>
+      </c>
+      <c r="D45" s="25">
+        <f>IF(Inputs!$D$43&gt;Parametros!$C$40,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <v/>
+      </c>
+      <c r="E45" s="25">
+        <f>IF(Inputs!$E$43&gt;Parametros!$C$40,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <v/>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>N1, secção 5. Falhar este teste afasta o regime sem ceder um único euro de capital ao cônjuge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>Exemplo de preenchimento correto — linha ilustrativa</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Faturação anual de fisioterapia</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D34" s="22" t="n">
-        <v>95000</v>
-      </c>
-      <c r="E34" s="22" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Faturação anual da própria Dra. Júlia</t>
+        </is>
+      </c>
+      <c r="C48" s="27" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D48" s="27" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E48" s="27" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>Formato esperado: valor anual, em euros, sem IVA, número puro sem texto.</t>
         </is>
@@ -4352,7 +5055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4424,7 +5127,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Faturação bruta da categoria B</t>
+          <t>Faturação isenta (fisioterapia)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -4432,16 +5135,16 @@
           <t>FAT</t>
         </is>
       </c>
-      <c r="C6" s="23">
-        <f>Inputs!$C$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>Inputs!$D$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>Inputs!$E$6</f>
+      <c r="C6" s="28">
+        <f>Inputs!$C$37</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
+        <f>Inputs!$D$37</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>Inputs!$E$37</f>
         <v/>
       </c>
       <c r="F6" s="16" t="inlineStr"/>
@@ -4449,53 +5152,53 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Coeficiente aplicável</t>
+          <t>Receita de cedência de espaço</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>COEF</t>
-        </is>
-      </c>
-      <c r="C7" s="24">
-        <f>Parametros!$C$15</f>
-        <v/>
-      </c>
-      <c r="D7" s="24">
-        <f>Parametros!$C$15</f>
-        <v/>
-      </c>
-      <c r="E7" s="24">
-        <f>Parametros!$C$15</f>
+          <t>REC_S</t>
+        </is>
+      </c>
+      <c r="C7" s="28">
+        <f>Inputs!$C$38</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>Inputs!$D$38</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>Inputs!$E$38</f>
         <v/>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 1 al. b) CIRS. Fisioterapeutas constam da tabela do art. 151.º — o coeficiente 0,35 não é aplicável.</t>
+          <t>Zero no modelo de prestação de serviços. Ver a alavanca MOD_COLAB na folha Inputs.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Rendimento tributável pelo coeficiente</t>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Rendimento bruto total da categoria B</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>RT_COEF</t>
-        </is>
-      </c>
-      <c r="C8" s="25">
-        <f>$C$6*$C$7</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>$D$6*$D$7</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>$E$6*$E$7</f>
+          <t>RB_TOT</t>
+        </is>
+      </c>
+      <c r="C8" s="23">
+        <f>$C$6+$C$7</f>
+        <v/>
+      </c>
+      <c r="D8" s="23">
+        <f>$D$6+$D$7</f>
+        <v/>
+      </c>
+      <c r="E8" s="23">
+        <f>$E$6+$E$7</f>
         <v/>
       </c>
       <c r="F8" s="16" t="inlineStr"/>
@@ -4503,799 +5206,803 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Limiar de justificação de despesas (15% do rendimento bruto)</t>
+          <t>Coeficiente aplicável à fisioterapia</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>LIMIAR</t>
-        </is>
-      </c>
-      <c r="C9" s="25">
-        <f>$C$6*Parametros!$C$16</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>$D$6*Parametros!$C$16</f>
-        <v/>
-      </c>
-      <c r="E9" s="25">
-        <f>$E$6*Parametros!$C$16</f>
+          <t>COEF</t>
+        </is>
+      </c>
+      <c r="C9" s="29">
+        <f>Parametros!$C$15</f>
+        <v/>
+      </c>
+      <c r="D9" s="29">
+        <f>Parametros!$C$15</f>
+        <v/>
+      </c>
+      <c r="E9" s="29">
+        <f>Parametros!$C$15</f>
         <v/>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 13 CIRS.</t>
+          <t>Art. 31.º n.º 1 al. b) CIRS. Fisioterapeutas constam da tabela do art. 151.º — o coeficiente 0,35 não é aplicável a esta parcela.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Despesas justificáveis — dedução específica</t>
+          <t>Coeficiente aplicável à cedência de espaço</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>D_ESP</t>
-        </is>
-      </c>
-      <c r="C10" s="23">
-        <f>Parametros!$C$17</f>
-        <v/>
-      </c>
-      <c r="D10" s="23">
-        <f>Parametros!$C$17</f>
-        <v/>
-      </c>
-      <c r="E10" s="23">
-        <f>Parametros!$C$17</f>
-        <v/>
-      </c>
-      <c r="F10" s="16" t="inlineStr"/>
+          <t>COEF_S</t>
+        </is>
+      </c>
+      <c r="C10" s="29">
+        <f>Parametros!$C$22</f>
+        <v/>
+      </c>
+      <c r="D10" s="29">
+        <f>Parametros!$C$22</f>
+        <v/>
+      </c>
+      <c r="E10" s="29">
+        <f>Parametros!$C$22</f>
+        <v/>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Coeficiente distinto, e por confirmar (R1-29). Depende de a cedência ser qualificada como prestação de serviços ou como rendimento predial — N1-04.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Despesas justificáveis — rendas do imóvel afeto</t>
+          <t>Rendimento tributável pelos coeficientes</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>D_RENDA</t>
-        </is>
-      </c>
-      <c r="C11" s="23">
-        <f>Inputs!$C$9</f>
-        <v/>
-      </c>
-      <c r="D11" s="23">
-        <f>Inputs!$D$9</f>
-        <v/>
-      </c>
-      <c r="E11" s="23">
-        <f>Inputs!$E$9</f>
-        <v/>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>Art. 31.º n.º 13 al. c) CIRS.</t>
-        </is>
-      </c>
+          <t>RT_COEF</t>
+        </is>
+      </c>
+      <c r="C11" s="21">
+        <f>$C$6*$C$9+$C$7*$C$10</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>$D$6*$D$9+$D$7*$D$10</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>$E$6*$E$9+$E$7*$E$10</f>
+        <v/>
+      </c>
+      <c r="F11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Despesas justificáveis — aquisição de bens e serviços</t>
+          <t>Limiar de justificação de despesas (15% do rendimento bruto)</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>D_BENS</t>
-        </is>
-      </c>
-      <c r="C12" s="23">
-        <f>Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14+Inputs!$C$15</f>
-        <v/>
-      </c>
-      <c r="D12" s="23">
-        <f>Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14+Inputs!$D$15</f>
-        <v/>
-      </c>
-      <c r="E12" s="23">
-        <f>Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14+Inputs!$E$15</f>
+          <t>LIMIAR</t>
+        </is>
+      </c>
+      <c r="C12" s="21">
+        <f>$C$8*Parametros!$C$16</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>$D$8*Parametros!$C$16</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>$E$8*Parametros!$C$16</f>
         <v/>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 13 al. e) CIRS. Inclui os honorários pagos aos fisioterapeutas.</t>
+          <t>Art. 31.º n.º 13 CIRS.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Despesas justificáveis — aquisições de investimento do ano</t>
+          <t>Despesas justificáveis — dedução específica</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>D_INV</t>
-        </is>
-      </c>
-      <c r="C13" s="23">
-        <f>Inputs!$C$18+Inputs!$C$19+Inputs!$C$20+Inputs!$C$21</f>
-        <v/>
-      </c>
-      <c r="D13" s="23">
-        <f>Inputs!$D$18+Inputs!$D$19+Inputs!$D$20+Inputs!$D$21</f>
-        <v/>
-      </c>
-      <c r="E13" s="23">
-        <f>Inputs!$E$18+Inputs!$E$19+Inputs!$E$20+Inputs!$E$21</f>
-        <v/>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>A CONFIRMAR pela Fiscalidade: elegibilidade e grau de afetação das aquisições de investimento para efeitos do art. 31.º n.º 13 al. e). Efeito de ano 1 apenas. Ver R1-08.</t>
-        </is>
-      </c>
+          <t>D_ESP</t>
+        </is>
+      </c>
+      <c r="C13" s="28">
+        <f>Parametros!$C$17</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>Parametros!$C$17</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>Parametros!$C$17</f>
+        <v/>
+      </c>
+      <c r="F13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Total de despesas justificadas</t>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Despesas justificáveis — rendas do imóvel afeto</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>D_TOT</t>
-        </is>
-      </c>
-      <c r="C14" s="27">
-        <f>SUM($C$10:$C$13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="27">
-        <f>SUM($D$10:$D$13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="27">
-        <f>SUM($E$10:$E$13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="16" t="inlineStr"/>
+          <t>D_RENDA</t>
+        </is>
+      </c>
+      <c r="C14" s="28">
+        <f>Inputs!$C$14</f>
+        <v/>
+      </c>
+      <c r="D14" s="28">
+        <f>Inputs!$D$14</f>
+        <v/>
+      </c>
+      <c r="E14" s="28">
+        <f>Inputs!$E$14</f>
+        <v/>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Art. 31.º n.º 13 al. c) CIRS.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Acréscimo por insuficiência de justificação</t>
+          <t>Despesas justificáveis — aquisição de bens e serviços</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>ACRESC</t>
-        </is>
-      </c>
-      <c r="C15" s="25">
-        <f>MAX(0,$C$9-$C$14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>MAX(0,$D$9-$D$14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>MAX(0,$E$9-$E$14)</f>
+          <t>D_BENS</t>
+        </is>
+      </c>
+      <c r="C15" s="28">
+        <f>Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19+Inputs!$C$39</f>
+        <v/>
+      </c>
+      <c r="D15" s="28">
+        <f>Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19+Inputs!$D$39</f>
+        <v/>
+      </c>
+      <c r="E15" s="28">
+        <f>Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19+Inputs!$E$39</f>
         <v/>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 13 CIRS: acresce ao rendimento tributável a diferença positiva.</t>
+          <t>Art. 31.º n.º 13 al. e) CIRS. Inclui os honorários, quando o modelo de colaboração for o de prestação de serviços.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Rendimento da categoria B antes da dedução de contribuições</t>
+          <t>Despesas justificáveis — aquisições de investimento do ano</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>RB_CATB</t>
-        </is>
-      </c>
-      <c r="C16" s="25">
-        <f>$C$8+$C$15</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>$D$8+$D$15</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>$E$8+$E$15</f>
-        <v/>
-      </c>
-      <c r="F16" s="16" t="inlineStr"/>
+          <t>D_INV</t>
+        </is>
+      </c>
+      <c r="C16" s="28">
+        <f>Inputs!$C$22+Inputs!$C$23+Inputs!$C$24+Inputs!$C$25</f>
+        <v/>
+      </c>
+      <c r="D16" s="28">
+        <f>Inputs!$D$22+Inputs!$D$23+Inputs!$D$24+Inputs!$D$25</f>
+        <v/>
+      </c>
+      <c r="E16" s="28">
+        <f>Inputs!$E$22+Inputs!$E$23+Inputs!$E$24+Inputs!$E$25</f>
+        <v/>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>A CONFIRMAR pela Fiscalidade: elegibilidade e grau de afetação das aquisições de investimento para efeitos do art. 31.º n.º 13 al. e). Efeito de ano 1 apenas. Ver R1-08.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Segurança Social — trabalhador independente</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Total de despesas justificadas</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>D_TOT</t>
+        </is>
+      </c>
+      <c r="C17" s="23">
+        <f>SUM($C$13:$C$16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="23">
+        <f>SUM($D$13:$D$16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="23">
+        <f>SUM($E$13:$E$16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Rendimento relevante</t>
+          <t>Acréscimo por insuficiência de justificação</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>SS_REL</t>
-        </is>
-      </c>
-      <c r="C18" s="25">
-        <f>$C$6*Parametros!$C$7</f>
-        <v/>
-      </c>
-      <c r="D18" s="25">
-        <f>$D$6*Parametros!$C$7</f>
-        <v/>
-      </c>
-      <c r="E18" s="25">
-        <f>$E$6*Parametros!$C$7</f>
+          <t>ACRESC</t>
+        </is>
+      </c>
+      <c r="C18" s="21">
+        <f>MAX(0,$C$12-$C$17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>MAX(0,$D$12-$D$17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>MAX(0,$E$12-$E$17)</f>
         <v/>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>Art. 162.º Cód. Contributivo: 70% do valor das prestações de serviços.</t>
+          <t>Art. 31.º n.º 13 CIRS: acresce ao rendimento tributável a diferença positiva.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Base de incidência anual, limitada ao teto</t>
+          <t>Rendimento da categoria B antes da dedução de contribuições</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>SS_BASE</t>
-        </is>
-      </c>
-      <c r="C19" s="25">
-        <f>MIN($C$18,Parametros!$C$6*Parametros!$C$9*12)</f>
-        <v/>
-      </c>
-      <c r="D19" s="25">
-        <f>MIN($D$18,Parametros!$C$6*Parametros!$C$9*12)</f>
-        <v/>
-      </c>
-      <c r="E19" s="25">
-        <f>MIN($E$18,Parametros!$C$6*Parametros!$C$9*12)</f>
-        <v/>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>Teto mensal de 12 x IAS.</t>
-        </is>
-      </c>
+          <t>RB_CATB</t>
+        </is>
+      </c>
+      <c r="C19" s="21">
+        <f>$C$11+$C$18</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>$D$11+$D$18</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>$E$11+$E$18</f>
+        <v/>
+      </c>
+      <c r="F19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>Contribuição anual para a Segurança Social</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>SS_CONTR</t>
-        </is>
-      </c>
-      <c r="C20" s="27">
-        <f>MAX($C$19*Parametros!$C$8,Parametros!$C$10*12)</f>
-        <v/>
-      </c>
-      <c r="D20" s="27">
-        <f>MAX($D$19*Parametros!$C$8,Parametros!$C$10*12)</f>
-        <v/>
-      </c>
-      <c r="E20" s="27">
-        <f>MAX($E$19*Parametros!$C$8,Parametros!$C$10*12)</f>
-        <v/>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>Bloco ausente da ata. Na via 1 a base é a faturação bruta, não a margem — é aqui que está o maior diferencial entre as vias.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Segurança Social — trabalhador independente</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>Rendimento relevante</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>SS_REL</t>
+        </is>
+      </c>
+      <c r="C21" s="21">
+        <f>$C$8*Parametros!$C$7</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>$D$8*Parametros!$C$7</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>$E$8*Parametros!$C$7</f>
+        <v/>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>Art. 162.º Cód. Contributivo: 70% do valor das prestações de serviços. A inclusão da receita de cedência de espaço depende de esta ser qualificada como prestação de serviços — N1-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Base de incidência anual, limitada ao teto</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>SS_BASE</t>
+        </is>
+      </c>
+      <c r="C22" s="21">
+        <f>MIN($C$21,Parametros!$C$6*Parametros!$C$9*12)</f>
+        <v/>
+      </c>
+      <c r="D22" s="21">
+        <f>MIN($D$21,Parametros!$C$6*Parametros!$C$9*12)</f>
+        <v/>
+      </c>
+      <c r="E22" s="21">
+        <f>MIN($E$21,Parametros!$C$6*Parametros!$C$9*12)</f>
+        <v/>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Teto mensal de 12 x IAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Contribuição anual para a Segurança Social</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>SS_CONTR</t>
+        </is>
+      </c>
+      <c r="C23" s="23">
+        <f>MAX($C$22*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <v/>
+      </c>
+      <c r="D23" s="23">
+        <f>MAX($D$22*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <v/>
+      </c>
+      <c r="E23" s="23">
+        <f>MAX($E$22*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <v/>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Bloco ausente da ata. Na via 1 a base é a faturação bruta, não a margem — é aqui que está o maior diferencial entre as vias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
           <t>Parte dedutível em IRS</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>SS_DED</t>
         </is>
       </c>
-      <c r="C21" s="25">
-        <f>MAX(0,$C$20-$C$6*Parametros!$C$18)</f>
-        <v/>
-      </c>
-      <c r="D21" s="25">
-        <f>MAX(0,$D$20-$D$6*Parametros!$C$18)</f>
-        <v/>
-      </c>
-      <c r="E21" s="25">
-        <f>MAX(0,$E$20-$E$6*Parametros!$C$18)</f>
-        <v/>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="C24" s="21">
+        <f>MAX(0,$C$23-$C$8*Parametros!$C$18)</f>
+        <v/>
+      </c>
+      <c r="D24" s="21">
+        <f>MAX(0,$D$23-$D$8*Parametros!$C$18)</f>
+        <v/>
+      </c>
+      <c r="E24" s="21">
+        <f>MAX(0,$E$23-$E$8*Parametros!$C$18)</f>
+        <v/>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Art. 31.º n.º 2 CIRS: dedutível apenas na parte que excede 10% do rendimento bruto.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Rendimento líquido da categoria B</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>RL_CATB</t>
         </is>
       </c>
-      <c r="C22" s="27">
-        <f>$C$16-$C$21</f>
-        <v/>
-      </c>
-      <c r="D22" s="27">
-        <f>$D$16-$D$21</f>
-        <v/>
-      </c>
-      <c r="E22" s="27">
-        <f>$E$16-$E$21</f>
-        <v/>
-      </c>
-      <c r="F22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C25" s="23">
+        <f>$C$19-$C$24</f>
+        <v/>
+      </c>
+      <c r="D25" s="23">
+        <f>$D$19-$D$24</f>
+        <v/>
+      </c>
+      <c r="E25" s="23">
+        <f>$E$19-$E$24</f>
+        <v/>
+      </c>
+      <c r="F25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>IRS do agregado</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Rendimento da sócia sujeito a englobamento</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>R_JUL</t>
         </is>
       </c>
-      <c r="C24" s="27">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="D24" s="27">
-        <f>$D$22</f>
-        <v/>
-      </c>
-      <c r="E24" s="27">
-        <f>$E$22</f>
-        <v/>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="C27" s="23">
+        <f>$C$25</f>
+        <v/>
+      </c>
+      <c r="D27" s="23">
+        <f>$D$25</f>
+        <v/>
+      </c>
+      <c r="E27" s="23">
+        <f>$E$25</f>
+        <v/>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>Só categoria B. Não há remuneração de gerência nesta via.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Rendimento do cônjuge fora da estrutura</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>R_CONJ</t>
-        </is>
-      </c>
-      <c r="C25" s="23">
-        <f>Inputs!$C$28</f>
-        <v/>
-      </c>
-      <c r="D25" s="23">
-        <f>Inputs!$D$28</f>
-        <v/>
-      </c>
-      <c r="E25" s="23">
-        <f>Inputs!$E$28</f>
-        <v/>
-      </c>
-      <c r="F25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Rendimento coletável do agregado — com a atividade</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>RC_COM</t>
-        </is>
-      </c>
-      <c r="C26" s="25">
-        <f>$C$24+$C$25</f>
-        <v/>
-      </c>
-      <c r="D26" s="25">
-        <f>$D$24+$D$25</f>
-        <v/>
-      </c>
-      <c r="E26" s="25">
-        <f>$E$24+$E$25</f>
-        <v/>
-      </c>
-      <c r="F26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Rendimento coletável do agregado — sem a atividade</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>RC_SEM</t>
-        </is>
-      </c>
-      <c r="C27" s="25">
-        <f>$C$25</f>
-        <v/>
-      </c>
-      <c r="D27" s="25">
-        <f>$D$25</f>
-        <v/>
-      </c>
-      <c r="E27" s="25">
-        <f>$E$25</f>
-        <v/>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>Contrafactual. O diferencial entre as duas coletas é o IRS realmente imputável à atividade e é o que torna as quatro vias comparáveis.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Coleta com a atividade (incl. taxa adicional de solidariedade)</t>
+          <t>Rendimento do cônjuge fora da estrutura</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>COL_COM</t>
-        </is>
-      </c>
-      <c r="C28" s="25">
-        <f>IF(Inputs!$C$29=1,2*(SUMPRODUCT((($C$26/2)&gt;Parametros!$B$45:$B$53)*(($C$26/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$26/2)&gt;Parametros!$B$57:$B$58)*(($C$26/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($C$26&gt;Parametros!$B$45:$B$53)*($C$26-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($C$26&gt;Parametros!$B$57:$B$58)*($C$26-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="D28" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((($D$26/2)&gt;Parametros!$B$45:$B$53)*(($D$26/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($D$26/2)&gt;Parametros!$B$57:$B$58)*(($D$26/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($D$26&gt;Parametros!$B$45:$B$53)*($D$26-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($D$26&gt;Parametros!$B$57:$B$58)*($D$26-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="E28" s="25">
-        <f>IF(Inputs!$E$29=1,2*(SUMPRODUCT((($E$26/2)&gt;Parametros!$B$45:$B$53)*(($E$26/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($E$26/2)&gt;Parametros!$B$57:$B$58)*(($E$26/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($E$26&gt;Parametros!$B$45:$B$53)*($E$26-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($E$26&gt;Parametros!$B$57:$B$58)*($E$26-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>Escalões e quociente conjugal na folha Parâmetros. Art. 68.º, 68.º-A e 69.º CIRS.</t>
-        </is>
-      </c>
+          <t>R_CONJ</t>
+        </is>
+      </c>
+      <c r="C28" s="28">
+        <f>Inputs!$C$32</f>
+        <v/>
+      </c>
+      <c r="D28" s="28">
+        <f>Inputs!$D$32</f>
+        <v/>
+      </c>
+      <c r="E28" s="28">
+        <f>Inputs!$E$32</f>
+        <v/>
+      </c>
+      <c r="F28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Coleta sem a atividade</t>
+          <t>Rendimento coletável do agregado — com a atividade</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>COL_SEM</t>
-        </is>
-      </c>
-      <c r="C29" s="25">
-        <f>IF(Inputs!$C$29=1,2*(SUMPRODUCT((($C$27/2)&gt;Parametros!$B$45:$B$53)*(($C$27/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$27/2)&gt;Parametros!$B$57:$B$58)*(($C$27/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($C$27&gt;Parametros!$B$45:$B$53)*($C$27-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($C$27&gt;Parametros!$B$57:$B$58)*($C$27-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="D29" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((($D$27/2)&gt;Parametros!$B$45:$B$53)*(($D$27/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($D$27/2)&gt;Parametros!$B$57:$B$58)*(($D$27/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($D$27&gt;Parametros!$B$45:$B$53)*($D$27-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($D$27&gt;Parametros!$B$57:$B$58)*($D$27-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="E29" s="25">
-        <f>IF(Inputs!$E$29=1,2*(SUMPRODUCT((($E$27/2)&gt;Parametros!$B$45:$B$53)*(($E$27/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($E$27/2)&gt;Parametros!$B$57:$B$58)*(($E$27/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($E$27&gt;Parametros!$B$45:$B$53)*($E$27-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($E$27&gt;Parametros!$B$57:$B$58)*($E$27-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
+          <t>RC_COM</t>
+        </is>
+      </c>
+      <c r="C29" s="21">
+        <f>$C$27+$C$28</f>
+        <v/>
+      </c>
+      <c r="D29" s="21">
+        <f>$D$27+$D$28</f>
+        <v/>
+      </c>
+      <c r="E29" s="21">
+        <f>$E$27+$E$28</f>
         <v/>
       </c>
       <c r="F29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>IRS imputável à atividade</t>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Rendimento coletável do agregado — sem a atividade</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>IRS_ATIV</t>
-        </is>
-      </c>
-      <c r="C30" s="27">
-        <f>$C$28-$C$29</f>
-        <v/>
-      </c>
-      <c r="D30" s="27">
-        <f>$D$28-$D$29</f>
-        <v/>
-      </c>
-      <c r="E30" s="27">
-        <f>$E$28-$E$29</f>
-        <v/>
-      </c>
-      <c r="F30" s="16" t="inlineStr"/>
+          <t>RC_SEM</t>
+        </is>
+      </c>
+      <c r="C30" s="21">
+        <f>$C$28</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f>$D$28</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>$E$28</f>
+        <v/>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Contrafactual. O diferencial entre as duas coletas é o IRS realmente imputável à atividade e é o que torna as quatro vias comparáveis.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>Coleta com a atividade (incl. taxa adicional de solidariedade)</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>COL_COM</t>
+        </is>
+      </c>
+      <c r="C31" s="21">
+        <f>IF(Inputs!$C$33=1,2*(SUMPRODUCT((($C$29/2)&gt;Parametros!$B$46:$B$54)*(($C$29/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$29/2)&gt;Parametros!$B$58:$B$59)*(($C$29/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$29&gt;Parametros!$B$46:$B$54)*($C$29-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$29&gt;Parametros!$B$58:$B$59)*($C$29-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="D31" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((($D$29/2)&gt;Parametros!$B$46:$B$54)*(($D$29/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$29/2)&gt;Parametros!$B$58:$B$59)*(($D$29/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$29&gt;Parametros!$B$46:$B$54)*($D$29-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$29&gt;Parametros!$B$58:$B$59)*($D$29-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="E31" s="21">
+        <f>IF(Inputs!$E$33=1,2*(SUMPRODUCT((($E$29/2)&gt;Parametros!$B$46:$B$54)*(($E$29/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$29/2)&gt;Parametros!$B$58:$B$59)*(($E$29/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$29&gt;Parametros!$B$46:$B$54)*($E$29-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$29&gt;Parametros!$B$58:$B$59)*($E$29-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>Escalões e quociente conjugal na folha Parâmetros. Art. 68.º, 68.º-A e 69.º CIRS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Coleta sem a atividade</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>COL_SEM</t>
+        </is>
+      </c>
+      <c r="C32" s="21">
+        <f>IF(Inputs!$C$33=1,2*(SUMPRODUCT((($C$30/2)&gt;Parametros!$B$46:$B$54)*(($C$30/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$30/2)&gt;Parametros!$B$58:$B$59)*(($C$30/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$30&gt;Parametros!$B$46:$B$54)*($C$30-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$30&gt;Parametros!$B$58:$B$59)*($C$30-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((($D$30/2)&gt;Parametros!$B$46:$B$54)*(($D$30/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$30/2)&gt;Parametros!$B$58:$B$59)*(($D$30/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$30&gt;Parametros!$B$46:$B$54)*($D$30-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$30&gt;Parametros!$B$58:$B$59)*($D$30-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
+        <f>IF(Inputs!$E$33=1,2*(SUMPRODUCT((($E$30/2)&gt;Parametros!$B$46:$B$54)*(($E$30/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$30/2)&gt;Parametros!$B$58:$B$59)*(($E$30/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$30&gt;Parametros!$B$46:$B$54)*($E$30-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$30&gt;Parametros!$B$58:$B$59)*($E$30-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="F32" s="16" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>IRS imputável à atividade</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>IRS_ATIV</t>
+        </is>
+      </c>
+      <c r="C33" s="23">
+        <f>$C$31-$C$32</f>
+        <v/>
+      </c>
+      <c r="D33" s="23">
+        <f>$D$31-$D$32</f>
+        <v/>
+      </c>
+      <c r="E33" s="23">
+        <f>$E$31-$E$32</f>
+        <v/>
+      </c>
+      <c r="F33" s="16" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
           <t>IRS total do agregado, após deduções à coleta (memória)</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>IRS_TOT</t>
         </is>
       </c>
-      <c r="C31" s="25">
-        <f>MAX(0,$C$28-Inputs!$C$31)</f>
-        <v/>
-      </c>
-      <c r="D31" s="25">
-        <f>MAX(0,$D$28-Inputs!$D$31)</f>
-        <v/>
-      </c>
-      <c r="E31" s="25">
-        <f>MAX(0,$E$28-Inputs!$E$31)</f>
-        <v/>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="C34" s="21">
+        <f>MAX(0,$C$31-Inputs!$C$35)</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f>MAX(0,$D$31-Inputs!$D$35)</f>
+        <v/>
+      </c>
+      <c r="E34" s="21">
+        <f>MAX(0,$E$31-Inputs!$E$35)</f>
+        <v/>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Não entra na comparação entre vias; serve para o enquadramento do capítulo 3.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Caixa gerada pela atividade, antes de impostos e contribuições</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>CAIXA</t>
         </is>
       </c>
-      <c r="C33" s="27">
-        <f>Inputs!$C$6+Inputs!$C$7-(Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14+Inputs!$C$15)</f>
-        <v/>
-      </c>
-      <c r="D33" s="27">
-        <f>Inputs!$D$6+Inputs!$D$7-(Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14+Inputs!$D$15)</f>
-        <v/>
-      </c>
-      <c r="E33" s="27">
-        <f>Inputs!$E$6+Inputs!$E$7-(Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14+Inputs!$E$15)</f>
-        <v/>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="C36" s="23">
+        <f>Inputs!$C$37+Inputs!$C$38+Inputs!$C$12-(Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19+Inputs!$C$39)</f>
+        <v/>
+      </c>
+      <c r="D36" s="23">
+        <f>Inputs!$D$37+Inputs!$D$38+Inputs!$D$12-(Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19+Inputs!$D$39)</f>
+        <v/>
+      </c>
+      <c r="E36" s="23">
+        <f>Inputs!$E$37+Inputs!$E$38+Inputs!$E$12-(Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19+Inputs!$E$39)</f>
+        <v/>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Caixa gerada pela atividade, igual nas quatro vias por construção. Exclui o investimento inicial, que é um efeito de ano 1 e está isolado na folha IVA e na linha própria abaixo.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Total de impostos e contribuições</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>CARGA</t>
         </is>
       </c>
-      <c r="C34" s="27">
-        <f>$C$30+$C$20</f>
-        <v/>
-      </c>
-      <c r="D34" s="27">
-        <f>$D$30+$D$20</f>
-        <v/>
-      </c>
-      <c r="E34" s="27">
-        <f>$E$30+$E$20</f>
-        <v/>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="C37" s="23">
+        <f>$C$33+$C$23</f>
+        <v/>
+      </c>
+      <c r="D37" s="23">
+        <f>$D$33+$D$23</f>
+        <v/>
+      </c>
+      <c r="E37" s="23">
+        <f>$E$33+$E$23</f>
+        <v/>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>IRS imputável à atividade + contribuições para a Segurança Social.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Taxa de esforço efetiva sobre a caixa gerada</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>TAXA_EF</t>
         </is>
       </c>
-      <c r="C35" s="28">
-        <f>IF($C$33&lt;=0,0,$C$34/$C$33)</f>
-        <v/>
-      </c>
-      <c r="D35" s="28">
-        <f>IF($D$33&lt;=0,0,$D$34/$D$33)</f>
-        <v/>
-      </c>
-      <c r="E35" s="28">
-        <f>IF($E$33&lt;=0,0,$E$34/$E$33)</f>
-        <v/>
-      </c>
-      <c r="F35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="C38" s="30">
+        <f>IF($C$36&lt;=0,0,$C$37/$C$36)</f>
+        <v/>
+      </c>
+      <c r="D38" s="30">
+        <f>IF($D$36&lt;=0,0,$D$37/$D$36)</f>
+        <v/>
+      </c>
+      <c r="E38" s="30">
+        <f>IF($E$36&lt;=0,0,$E$37/$E$36)</f>
+        <v/>
+      </c>
+      <c r="F38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Valor retido na sociedade (não disponibilizado à sócia)</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>RETIDO</t>
         </is>
       </c>
-      <c r="C36" s="25">
+      <c r="C39" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="D36" s="25">
+      <c r="D39" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="E36" s="25">
+      <c r="E39" s="21">
         <f>0</f>
-        <v/>
-      </c>
-      <c r="F36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Valor atribuído ao cônjuge por via de dividendos, líquido</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>LIQ_CJ</t>
-        </is>
-      </c>
-      <c r="C37" s="25">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D37" s="25">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E37" s="25">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>Só via 4. É uma transferência real de rendimento dentro do agregado e tem de ser explicitada — não é indiferente à sócia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="26" t="inlineStr">
-        <is>
-          <t>LÍQUIDO DISPONÍVEL PARA A SÓCIA</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>LIQ_SOC</t>
-        </is>
-      </c>
-      <c r="C38" s="27">
-        <f>$C$33-$C$34-$C$36-$C$37</f>
-        <v/>
-      </c>
-      <c r="D38" s="27">
-        <f>$D$33-$D$34-$D$36-$D$37</f>
-        <v/>
-      </c>
-      <c r="E38" s="27">
-        <f>$E$33-$E$34-$E$36-$E$37</f>
-        <v/>
-      </c>
-      <c r="F38" s="16" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="26" t="inlineStr">
-        <is>
-          <t>LÍQUIDO DISPONÍVEL PARA O AGREGADO</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>LIQ_AGR</t>
-        </is>
-      </c>
-      <c r="C39" s="27">
-        <f>$C$38+$C$37</f>
-        <v/>
-      </c>
-      <c r="D39" s="27">
-        <f>$D$38+$D$37</f>
-        <v/>
-      </c>
-      <c r="E39" s="27">
-        <f>$E$38+$E$37</f>
         <v/>
       </c>
       <c r="F39" s="16" t="inlineStr"/>
@@ -5303,27 +6010,106 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
+          <t>Valor atribuído ao cônjuge por via de dividendos, líquido</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>LIQ_CJ</t>
+        </is>
+      </c>
+      <c r="C40" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D40" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E40" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Só via 4. É uma transferência real de rendimento dentro do agregado e tem de ser explicitada — não é indiferente à sócia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>LÍQUIDO DISPONÍVEL PARA A SÓCIA</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>LIQ_SOC</t>
+        </is>
+      </c>
+      <c r="C41" s="23">
+        <f>$C$36-$C$37-$C$39-$C$40</f>
+        <v/>
+      </c>
+      <c r="D41" s="23">
+        <f>$D$36-$D$37-$D$39-$D$40</f>
+        <v/>
+      </c>
+      <c r="E41" s="23">
+        <f>$E$36-$E$37-$E$39-$E$40</f>
+        <v/>
+      </c>
+      <c r="F41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>LÍQUIDO DISPONÍVEL PARA O AGREGADO</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>LIQ_AGR</t>
+        </is>
+      </c>
+      <c r="C42" s="23">
+        <f>$C$41+$C$40</f>
+        <v/>
+      </c>
+      <c r="D42" s="23">
+        <f>$D$41+$D$40</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f>$E$41+$E$40</f>
+        <v/>
+      </c>
+      <c r="F42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
           <t>Memória — investimento e IVA não dedutível suportados no ano 1</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>INV_A1</t>
         </is>
       </c>
-      <c r="C40" s="25">
-        <f>Inputs!$C$18+Inputs!$C$19+Inputs!$C$20+Inputs!$C$21</f>
-        <v/>
-      </c>
-      <c r="D40" s="25">
-        <f>Inputs!$D$18+Inputs!$D$19+Inputs!$D$20+Inputs!$D$21</f>
-        <v/>
-      </c>
-      <c r="E40" s="25">
-        <f>Inputs!$E$18+Inputs!$E$19+Inputs!$E$20+Inputs!$E$21</f>
-        <v/>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="C43" s="21">
+        <f>Inputs!$C$22+Inputs!$C$23+Inputs!$C$24+Inputs!$C$25</f>
+        <v/>
+      </c>
+      <c r="D43" s="21">
+        <f>Inputs!$D$22+Inputs!$D$23+Inputs!$D$24+Inputs!$D$25</f>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f>Inputs!$E$22+Inputs!$E$23+Inputs!$E$24+Inputs!$E$25</f>
+        <v/>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>Excluído da comparação anual acima. Quantificação do IVA na folha IVA.</t>
         </is>
@@ -5415,7 +6201,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Faturação bruta</t>
+          <t>Receita bruta (fisioterapia + cedência de espaço)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5423,16 +6209,16 @@
           <t>FAT</t>
         </is>
       </c>
-      <c r="C6" s="23">
-        <f>Inputs!$C$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>Inputs!$D$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>Inputs!$E$6</f>
+      <c r="C6" s="28">
+        <f>Inputs!$C$37+Inputs!$C$38</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
+        <f>Inputs!$D$37+Inputs!$D$38</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>Inputs!$E$37+Inputs!$E$38</f>
         <v/>
       </c>
       <c r="F6" s="16" t="inlineStr"/>
@@ -5448,16 +6234,16 @@
           <t>C_OP</t>
         </is>
       </c>
-      <c r="C7" s="23">
-        <f>Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14</f>
-        <v/>
-      </c>
-      <c r="D7" s="23">
-        <f>Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14</f>
-        <v/>
-      </c>
-      <c r="E7" s="23">
-        <f>Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14</f>
+      <c r="C7" s="28">
+        <f>Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19</f>
         <v/>
       </c>
       <c r="F7" s="16" t="inlineStr"/>
@@ -5465,7 +6251,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Honorários a fisioterapeutas</t>
+          <t>Custo com os colaboradores</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5473,16 +6259,16 @@
           <t>C_HON</t>
         </is>
       </c>
-      <c r="C8" s="23">
-        <f>Inputs!$C$15</f>
-        <v/>
-      </c>
-      <c r="D8" s="23">
-        <f>Inputs!$D$15</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>Inputs!$E$15</f>
+      <c r="C8" s="28">
+        <f>Inputs!$C$39</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
+        <f>Inputs!$D$39</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>Inputs!$E$39</f>
         <v/>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -5502,16 +6288,16 @@
           <t>AMORT</t>
         </is>
       </c>
-      <c r="C9" s="25">
-        <f>Inputs!$C$18*Parametros!$C$34+(Inputs!$C$19+Inputs!$C$20)*Parametros!$C$35+Inputs!$C$21*Parametros!$C$36</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>Inputs!$D$18*Parametros!$C$34+(Inputs!$D$19+Inputs!$D$20)*Parametros!$C$35+Inputs!$D$21*Parametros!$C$36</f>
-        <v/>
-      </c>
-      <c r="E9" s="25">
-        <f>Inputs!$E$18*Parametros!$C$34+(Inputs!$E$19+Inputs!$E$20)*Parametros!$C$35+Inputs!$E$21*Parametros!$C$36</f>
+      <c r="C9" s="21">
+        <f>Inputs!$C$22*Parametros!$C$35+(Inputs!$C$23+Inputs!$C$24)*Parametros!$C$36+Inputs!$C$25*Parametros!$C$37</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>Inputs!$D$22*Parametros!$C$35+(Inputs!$D$23+Inputs!$D$24)*Parametros!$C$36+Inputs!$D$25*Parametros!$C$37</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>Inputs!$E$22*Parametros!$C$35+(Inputs!$E$23+Inputs!$E$24)*Parametros!$C$36+Inputs!$E$25*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="F9" s="16" t="inlineStr">
@@ -5521,7 +6307,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Lucro tributável antes de contribuições</t>
         </is>
@@ -5531,15 +6317,15 @@
           <t>LT_ANTES</t>
         </is>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="23">
         <f>$C$6-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="23">
         <f>$D$6-$D$7-$D$8-$D$9</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="23">
         <f>$E$6-$E$7-$E$8-$E$9</f>
         <v/>
       </c>
@@ -5568,15 +6354,15 @@
           <t>SS_BASE</t>
         </is>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="21">
         <f>MIN(MAX($C$10,0),Parametros!$C$6*Parametros!$C$9*12)</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="21">
         <f>MIN(MAX($D$10,0),Parametros!$C$6*Parametros!$C$9*12)</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="21">
         <f>MIN(MAX($E$10,0),Parametros!$C$6*Parametros!$C$9*12)</f>
         <v/>
       </c>
@@ -5587,7 +6373,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Contribuição anual para a Segurança Social</t>
         </is>
@@ -5597,22 +6383,22 @@
           <t>SS_CONTR</t>
         </is>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="23">
         <f>MAX($C$12*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="23">
         <f>MAX($D$12*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="23">
         <f>MAX($E$12*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="F13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Lucro tributável após dedução das contribuições</t>
         </is>
@@ -5622,15 +6408,15 @@
           <t>LT</t>
         </is>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="23">
         <f>MAX(0,$C$10-$C$13)</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="23">
         <f>MAX(0,$D$10-$D$13)</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="23">
         <f>MAX(0,$E$10-$E$13)</f>
         <v/>
       </c>
@@ -5653,7 +6439,7 @@
       <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Rendimento da sócia sujeito a englobamento</t>
         </is>
@@ -5663,15 +6449,15 @@
           <t>R_JUL</t>
         </is>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="23">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="23">
         <f>$D$14</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="23">
         <f>$E$14</f>
         <v/>
       </c>
@@ -5692,16 +6478,16 @@
           <t>R_CONJ</t>
         </is>
       </c>
-      <c r="C17" s="23">
-        <f>Inputs!$C$28</f>
-        <v/>
-      </c>
-      <c r="D17" s="23">
-        <f>Inputs!$D$28</f>
-        <v/>
-      </c>
-      <c r="E17" s="23">
-        <f>Inputs!$E$28</f>
+      <c r="C17" s="28">
+        <f>Inputs!$C$32</f>
+        <v/>
+      </c>
+      <c r="D17" s="28">
+        <f>Inputs!$D$32</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>Inputs!$E$32</f>
         <v/>
       </c>
       <c r="F17" s="16" t="inlineStr"/>
@@ -5717,15 +6503,15 @@
           <t>RC_COM</t>
         </is>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="21">
         <f>$C$16+$C$17</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="21">
         <f>$D$16+$D$17</f>
         <v/>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="21">
         <f>$E$16+$E$17</f>
         <v/>
       </c>
@@ -5742,15 +6528,15 @@
           <t>RC_SEM</t>
         </is>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="21">
         <f>$C$17</f>
         <v/>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="21">
         <f>$D$17</f>
         <v/>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="21">
         <f>$E$17</f>
         <v/>
       </c>
@@ -5771,16 +6557,16 @@
           <t>COL_COM</t>
         </is>
       </c>
-      <c r="C20" s="25">
-        <f>IF(Inputs!$C$29=1,2*(SUMPRODUCT((($C$18/2)&gt;Parametros!$B$45:$B$53)*(($C$18/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$18/2)&gt;Parametros!$B$57:$B$58)*(($C$18/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($C$18&gt;Parametros!$B$45:$B$53)*($C$18-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($C$18&gt;Parametros!$B$57:$B$58)*($C$18-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="D20" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((($D$18/2)&gt;Parametros!$B$45:$B$53)*(($D$18/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($D$18/2)&gt;Parametros!$B$57:$B$58)*(($D$18/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($D$18&gt;Parametros!$B$45:$B$53)*($D$18-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($D$18&gt;Parametros!$B$57:$B$58)*($D$18-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="E20" s="25">
-        <f>IF(Inputs!$E$29=1,2*(SUMPRODUCT((($E$18/2)&gt;Parametros!$B$45:$B$53)*(($E$18/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($E$18/2)&gt;Parametros!$B$57:$B$58)*(($E$18/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($E$18&gt;Parametros!$B$45:$B$53)*($E$18-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($E$18&gt;Parametros!$B$57:$B$58)*($E$18-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
+      <c r="C20" s="21">
+        <f>IF(Inputs!$C$33=1,2*(SUMPRODUCT((($C$18/2)&gt;Parametros!$B$46:$B$54)*(($C$18/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$18/2)&gt;Parametros!$B$58:$B$59)*(($C$18/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$18&gt;Parametros!$B$46:$B$54)*($C$18-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$18&gt;Parametros!$B$58:$B$59)*($C$18-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((($D$18/2)&gt;Parametros!$B$46:$B$54)*(($D$18/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$18/2)&gt;Parametros!$B$58:$B$59)*(($D$18/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$18&gt;Parametros!$B$46:$B$54)*($D$18-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$18&gt;Parametros!$B$58:$B$59)*($D$18-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>IF(Inputs!$E$33=1,2*(SUMPRODUCT((($E$18/2)&gt;Parametros!$B$46:$B$54)*(($E$18/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$18/2)&gt;Parametros!$B$58:$B$59)*(($E$18/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$18&gt;Parametros!$B$46:$B$54)*($E$18-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$18&gt;Parametros!$B$58:$B$59)*($E$18-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
         <v/>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -5800,22 +6586,22 @@
           <t>COL_SEM</t>
         </is>
       </c>
-      <c r="C21" s="25">
-        <f>IF(Inputs!$C$29=1,2*(SUMPRODUCT((($C$19/2)&gt;Parametros!$B$45:$B$53)*(($C$19/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$19/2)&gt;Parametros!$B$57:$B$58)*(($C$19/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($C$19&gt;Parametros!$B$45:$B$53)*($C$19-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($C$19&gt;Parametros!$B$57:$B$58)*($C$19-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="D21" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((($D$19/2)&gt;Parametros!$B$45:$B$53)*(($D$19/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($D$19/2)&gt;Parametros!$B$57:$B$58)*(($D$19/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($D$19&gt;Parametros!$B$45:$B$53)*($D$19-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($D$19&gt;Parametros!$B$57:$B$58)*($D$19-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="E21" s="25">
-        <f>IF(Inputs!$E$29=1,2*(SUMPRODUCT((($E$19/2)&gt;Parametros!$B$45:$B$53)*(($E$19/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($E$19/2)&gt;Parametros!$B$57:$B$58)*(($E$19/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($E$19&gt;Parametros!$B$45:$B$53)*($E$19-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($E$19&gt;Parametros!$B$57:$B$58)*($E$19-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
+      <c r="C21" s="21">
+        <f>IF(Inputs!$C$33=1,2*(SUMPRODUCT((($C$19/2)&gt;Parametros!$B$46:$B$54)*(($C$19/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$19/2)&gt;Parametros!$B$58:$B$59)*(($C$19/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$19&gt;Parametros!$B$46:$B$54)*($C$19-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$19&gt;Parametros!$B$58:$B$59)*($C$19-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((($D$19/2)&gt;Parametros!$B$46:$B$54)*(($D$19/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$19/2)&gt;Parametros!$B$58:$B$59)*(($D$19/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$19&gt;Parametros!$B$46:$B$54)*($D$19-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$19&gt;Parametros!$B$58:$B$59)*($D$19-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>IF(Inputs!$E$33=1,2*(SUMPRODUCT((($E$19/2)&gt;Parametros!$B$46:$B$54)*(($E$19/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$19/2)&gt;Parametros!$B$58:$B$59)*(($E$19/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$19&gt;Parametros!$B$46:$B$54)*($E$19-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$19&gt;Parametros!$B$58:$B$59)*($E$19-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
         <v/>
       </c>
       <c r="F21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>IRS imputável à atividade</t>
         </is>
@@ -5825,15 +6611,15 @@
           <t>IRS_ATIV</t>
         </is>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="23">
         <f>$C$20-$C$21</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="23">
         <f>$D$20-$D$21</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="23">
         <f>$E$20-$E$21</f>
         <v/>
       </c>
@@ -5850,16 +6636,16 @@
           <t>IRS_TOT</t>
         </is>
       </c>
-      <c r="C23" s="25">
-        <f>MAX(0,$C$20-Inputs!$C$31)</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
-        <f>MAX(0,$D$20-Inputs!$D$31)</f>
-        <v/>
-      </c>
-      <c r="E23" s="25">
-        <f>MAX(0,$E$20-Inputs!$E$31)</f>
+      <c r="C23" s="21">
+        <f>MAX(0,$C$20-Inputs!$C$35)</f>
+        <v/>
+      </c>
+      <c r="D23" s="21">
+        <f>MAX(0,$D$20-Inputs!$D$35)</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>MAX(0,$E$20-Inputs!$E$35)</f>
         <v/>
       </c>
       <c r="F23" s="16" t="inlineStr">
@@ -5881,7 +6667,7 @@
       <c r="F24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Caixa gerada pela atividade, antes de impostos e contribuições</t>
         </is>
@@ -5891,16 +6677,16 @@
           <t>CAIXA</t>
         </is>
       </c>
-      <c r="C25" s="27">
-        <f>Inputs!$C$6+Inputs!$C$7-(Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14+Inputs!$C$15)</f>
-        <v/>
-      </c>
-      <c r="D25" s="27">
-        <f>Inputs!$D$6+Inputs!$D$7-(Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14+Inputs!$D$15)</f>
-        <v/>
-      </c>
-      <c r="E25" s="27">
-        <f>Inputs!$E$6+Inputs!$E$7-(Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14+Inputs!$E$15)</f>
+      <c r="C25" s="23">
+        <f>Inputs!$C$37+Inputs!$C$38+Inputs!$C$12-(Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19+Inputs!$C$39)</f>
+        <v/>
+      </c>
+      <c r="D25" s="23">
+        <f>Inputs!$D$37+Inputs!$D$38+Inputs!$D$12-(Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19+Inputs!$D$39)</f>
+        <v/>
+      </c>
+      <c r="E25" s="23">
+        <f>Inputs!$E$37+Inputs!$E$38+Inputs!$E$12-(Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19+Inputs!$E$39)</f>
         <v/>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -5910,7 +6696,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Total de impostos e contribuições</t>
         </is>
@@ -5920,15 +6706,15 @@
           <t>CARGA</t>
         </is>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="23">
         <f>$C$22+$C$13</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="23">
         <f>$D$22+$D$13</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="23">
         <f>$E$22+$E$13</f>
         <v/>
       </c>
@@ -5949,15 +6735,15 @@
           <t>TAXA_EF</t>
         </is>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="30">
         <f>IF($C$25&lt;=0,0,$C$26/$C$25)</f>
         <v/>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="30">
         <f>IF($D$25&lt;=0,0,$D$26/$D$25)</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="30">
         <f>IF($E$25&lt;=0,0,$E$26/$E$25)</f>
         <v/>
       </c>
@@ -5974,15 +6760,15 @@
           <t>RETIDO</t>
         </is>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="21">
         <f>0</f>
         <v/>
       </c>
@@ -5999,15 +6785,15 @@
           <t>LIQ_CJ</t>
         </is>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="21">
         <f>0</f>
         <v/>
       </c>
@@ -6018,7 +6804,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA A SÓCIA</t>
         </is>
@@ -6028,22 +6814,22 @@
           <t>LIQ_SOC</t>
         </is>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="23">
         <f>$C$25-$C$26-$C$28-$C$29</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="23">
         <f>$D$25-$D$26-$D$28-$D$29</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="23">
         <f>$E$25-$E$26-$E$28-$E$29</f>
         <v/>
       </c>
       <c r="F30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA O AGREGADO</t>
         </is>
@@ -6053,15 +6839,15 @@
           <t>LIQ_AGR</t>
         </is>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="23">
         <f>$C$30+$C$29</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="23">
         <f>$D$30+$D$29</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="23">
         <f>$E$30+$E$29</f>
         <v/>
       </c>
@@ -6078,16 +6864,16 @@
           <t>INV_A1</t>
         </is>
       </c>
-      <c r="C32" s="25">
-        <f>Inputs!$C$18+Inputs!$C$19+Inputs!$C$20+Inputs!$C$21</f>
-        <v/>
-      </c>
-      <c r="D32" s="25">
-        <f>Inputs!$D$18+Inputs!$D$19+Inputs!$D$20+Inputs!$D$21</f>
-        <v/>
-      </c>
-      <c r="E32" s="25">
-        <f>Inputs!$E$18+Inputs!$E$19+Inputs!$E$20+Inputs!$E$21</f>
+      <c r="C32" s="21">
+        <f>Inputs!$C$22+Inputs!$C$23+Inputs!$C$24+Inputs!$C$25</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f>Inputs!$D$22+Inputs!$D$23+Inputs!$D$24+Inputs!$D$25</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
+        <f>Inputs!$E$22+Inputs!$E$23+Inputs!$E$24+Inputs!$E$25</f>
         <v/>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -6182,7 +6968,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Prestações de serviços</t>
+          <t>Receita bruta (fisioterapia + cedência de espaço)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -6190,16 +6976,16 @@
           <t>FAT</t>
         </is>
       </c>
-      <c r="C6" s="23">
-        <f>Inputs!$C$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>Inputs!$D$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>Inputs!$E$6</f>
+      <c r="C6" s="28">
+        <f>Inputs!$C$37+Inputs!$C$38</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
+        <f>Inputs!$D$37+Inputs!$D$38</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>Inputs!$E$37+Inputs!$E$38</f>
         <v/>
       </c>
       <c r="F6" s="16" t="inlineStr"/>
@@ -6215,16 +7001,16 @@
           <t>C_OP</t>
         </is>
       </c>
-      <c r="C7" s="23">
-        <f>Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14</f>
-        <v/>
-      </c>
-      <c r="D7" s="23">
-        <f>Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14</f>
-        <v/>
-      </c>
-      <c r="E7" s="23">
-        <f>Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14</f>
+      <c r="C7" s="28">
+        <f>Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19</f>
         <v/>
       </c>
       <c r="F7" s="16" t="inlineStr"/>
@@ -6232,7 +7018,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Honorários a fisioterapeutas</t>
+          <t>Custo com os colaboradores</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -6240,16 +7026,16 @@
           <t>C_HON</t>
         </is>
       </c>
-      <c r="C8" s="23">
-        <f>Inputs!$C$15</f>
-        <v/>
-      </c>
-      <c r="D8" s="23">
-        <f>Inputs!$D$15</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>Inputs!$E$15</f>
+      <c r="C8" s="28">
+        <f>Inputs!$C$39</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
+        <f>Inputs!$D$39</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>Inputs!$E$39</f>
         <v/>
       </c>
       <c r="F8" s="16" t="inlineStr"/>
@@ -6265,16 +7051,16 @@
           <t>AMORT</t>
         </is>
       </c>
-      <c r="C9" s="25">
-        <f>Inputs!$C$18*Parametros!$C$34+(Inputs!$C$19+Inputs!$C$20)*Parametros!$C$35+Inputs!$C$21*Parametros!$C$36</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>Inputs!$D$18*Parametros!$C$34+(Inputs!$D$19+Inputs!$D$20)*Parametros!$C$35+Inputs!$D$21*Parametros!$C$36</f>
-        <v/>
-      </c>
-      <c r="E9" s="25">
-        <f>Inputs!$E$18*Parametros!$C$34+(Inputs!$E$19+Inputs!$E$20)*Parametros!$C$35+Inputs!$E$21*Parametros!$C$36</f>
+      <c r="C9" s="21">
+        <f>Inputs!$C$22*Parametros!$C$35+(Inputs!$C$23+Inputs!$C$24)*Parametros!$C$36+Inputs!$C$25*Parametros!$C$37</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>Inputs!$D$22*Parametros!$C$35+(Inputs!$D$23+Inputs!$D$24)*Parametros!$C$36+Inputs!$D$25*Parametros!$C$37</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>Inputs!$E$22*Parametros!$C$35+(Inputs!$E$23+Inputs!$E$24)*Parametros!$C$36+Inputs!$E$25*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="F9" s="16" t="inlineStr"/>
@@ -6290,16 +7076,16 @@
           <t>REM</t>
         </is>
       </c>
-      <c r="C10" s="23">
-        <f>Inputs!$C$23</f>
-        <v/>
-      </c>
-      <c r="D10" s="23">
-        <f>Inputs!$D$23</f>
-        <v/>
-      </c>
-      <c r="E10" s="23">
-        <f>Inputs!$E$23</f>
+      <c r="C10" s="28">
+        <f>Inputs!$C$27</f>
+        <v/>
+      </c>
+      <c r="D10" s="28">
+        <f>Inputs!$D$27</f>
+        <v/>
+      </c>
+      <c r="E10" s="28">
+        <f>Inputs!$E$27</f>
         <v/>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -6319,15 +7105,15 @@
           <t>BASE_MOE</t>
         </is>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="21">
         <f>MAX($C$10,Parametros!$C$6*Parametros!$C$13*12)</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <f>MAX($D$10,Parametros!$C$6*Parametros!$C$13*12)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="21">
         <f>MAX($E$10,Parametros!$C$6*Parametros!$C$13*12)</f>
         <v/>
       </c>
@@ -6348,22 +7134,22 @@
           <t>TSU_ENT</t>
         </is>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="21">
         <f>$C$11*Parametros!$C$11</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="21">
         <f>$D$11*Parametros!$C$11</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="21">
         <f>$E$11*Parametros!$C$11</f>
         <v/>
       </c>
       <c r="F12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Lucro tributável</t>
         </is>
@@ -6373,15 +7159,15 @@
           <t>LT</t>
         </is>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="23">
         <f>$C$6-$C$7-$C$8-$C$9-$C$10-$C$12</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="23">
         <f>$D$6-$D$7-$D$8-$D$9-$D$10-$D$12</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="23">
         <f>$E$6-$E$7-$E$8-$E$9-$E$10-$E$12</f>
         <v/>
       </c>
@@ -6398,16 +7184,16 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="C14" s="23">
-        <f>Inputs!$C$24</f>
-        <v/>
-      </c>
-      <c r="D14" s="23">
-        <f>Inputs!$D$24</f>
-        <v/>
-      </c>
-      <c r="E14" s="23">
-        <f>Inputs!$E$24</f>
+      <c r="C14" s="28">
+        <f>Inputs!$C$28</f>
+        <v/>
+      </c>
+      <c r="D14" s="28">
+        <f>Inputs!$D$28</f>
+        <v/>
+      </c>
+      <c r="E14" s="28">
+        <f>Inputs!$E$28</f>
         <v/>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -6427,16 +7213,16 @@
           <t>DERR</t>
         </is>
       </c>
-      <c r="C15" s="25">
-        <f>MAX($C$13,0)*Parametros!$C$26*Parametros!$C$27</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>MAX($D$13,0)*Parametros!$C$26*Parametros!$C$27</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>MAX($E$13,0)*Parametros!$C$26*Parametros!$C$27</f>
+      <c r="C15" s="21">
+        <f>MAX($C$13,0)*Parametros!$C$27*Parametros!$C$28</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>MAX($D$13,0)*Parametros!$C$27*Parametros!$C$28</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>MAX($E$13,0)*Parametros!$C$27*Parametros!$C$28</f>
         <v/>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -6446,7 +7232,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Lucro imputável à sócia</t>
         </is>
@@ -6456,15 +7242,15 @@
           <t>LUCRO_IMP</t>
         </is>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="23">
         <f>MAX($C$13,0)</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="23">
         <f>MAX($D$13,0)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="23">
         <f>MAX($E$13,0)</f>
         <v/>
       </c>
@@ -6497,15 +7283,15 @@
           <t>SS_TRAB</t>
         </is>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="21">
         <f>$C$11*Parametros!$C$12</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="21">
         <f>$D$11*Parametros!$C$12</f>
         <v/>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="21">
         <f>$E$11*Parametros!$C$12</f>
         <v/>
       </c>
@@ -6522,15 +7308,15 @@
           <t>DED_A</t>
         </is>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="21">
         <f>MIN($C$10,MAX(Parametros!$C$21,$C$18))</f>
         <v/>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="21">
         <f>MIN($D$10,MAX(Parametros!$C$21,$D$18))</f>
         <v/>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="21">
         <f>MIN($E$10,MAX(Parametros!$C$21,$E$18))</f>
         <v/>
       </c>
@@ -6551,15 +7337,15 @@
           <t>RL_CATA</t>
         </is>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="21">
         <f>MAX(0,$C$10-$C$19)</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="21">
         <f>MAX(0,$D$10-$D$19)</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="21">
         <f>MAX(0,$E$10-$E$19)</f>
         <v/>
       </c>
@@ -6578,7 +7364,7 @@
       <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Rendimento da sócia sujeito a englobamento</t>
         </is>
@@ -6588,15 +7374,15 @@
           <t>R_JUL</t>
         </is>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="23">
         <f>$C$20+$C$16</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="23">
         <f>$D$20+$D$16</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="23">
         <f>$E$20+$E$16</f>
         <v/>
       </c>
@@ -6617,16 +7403,16 @@
           <t>R_CONJ</t>
         </is>
       </c>
-      <c r="C23" s="23">
-        <f>Inputs!$C$28</f>
-        <v/>
-      </c>
-      <c r="D23" s="23">
-        <f>Inputs!$D$28</f>
-        <v/>
-      </c>
-      <c r="E23" s="23">
-        <f>Inputs!$E$28</f>
+      <c r="C23" s="28">
+        <f>Inputs!$C$32</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>Inputs!$D$32</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>Inputs!$E$32</f>
         <v/>
       </c>
       <c r="F23" s="16" t="inlineStr"/>
@@ -6642,15 +7428,15 @@
           <t>RC_COM</t>
         </is>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="21">
         <f>$C$22+$C$23</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="21">
         <f>$D$22+$D$23</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="21">
         <f>$E$22+$E$23</f>
         <v/>
       </c>
@@ -6667,15 +7453,15 @@
           <t>RC_SEM</t>
         </is>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="21">
         <f>$C$23</f>
         <v/>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="21">
         <f>$D$23</f>
         <v/>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="21">
         <f>$E$23</f>
         <v/>
       </c>
@@ -6696,16 +7482,16 @@
           <t>COL_COM</t>
         </is>
       </c>
-      <c r="C26" s="25">
-        <f>IF(Inputs!$C$29=1,2*(SUMPRODUCT((($C$24/2)&gt;Parametros!$B$45:$B$53)*(($C$24/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$24/2)&gt;Parametros!$B$57:$B$58)*(($C$24/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($C$24&gt;Parametros!$B$45:$B$53)*($C$24-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($C$24&gt;Parametros!$B$57:$B$58)*($C$24-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="D26" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((($D$24/2)&gt;Parametros!$B$45:$B$53)*(($D$24/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($D$24/2)&gt;Parametros!$B$57:$B$58)*(($D$24/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($D$24&gt;Parametros!$B$45:$B$53)*($D$24-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($D$24&gt;Parametros!$B$57:$B$58)*($D$24-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="E26" s="25">
-        <f>IF(Inputs!$E$29=1,2*(SUMPRODUCT((($E$24/2)&gt;Parametros!$B$45:$B$53)*(($E$24/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($E$24/2)&gt;Parametros!$B$57:$B$58)*(($E$24/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($E$24&gt;Parametros!$B$45:$B$53)*($E$24-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($E$24&gt;Parametros!$B$57:$B$58)*($E$24-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
+      <c r="C26" s="21">
+        <f>IF(Inputs!$C$33=1,2*(SUMPRODUCT((($C$24/2)&gt;Parametros!$B$46:$B$54)*(($C$24/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$24/2)&gt;Parametros!$B$58:$B$59)*(($C$24/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$24&gt;Parametros!$B$46:$B$54)*($C$24-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$24&gt;Parametros!$B$58:$B$59)*($C$24-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="D26" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((($D$24/2)&gt;Parametros!$B$46:$B$54)*(($D$24/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$24/2)&gt;Parametros!$B$58:$B$59)*(($D$24/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$24&gt;Parametros!$B$46:$B$54)*($D$24-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$24&gt;Parametros!$B$58:$B$59)*($D$24-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>IF(Inputs!$E$33=1,2*(SUMPRODUCT((($E$24/2)&gt;Parametros!$B$46:$B$54)*(($E$24/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$24/2)&gt;Parametros!$B$58:$B$59)*(($E$24/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$24&gt;Parametros!$B$46:$B$54)*($E$24-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$24&gt;Parametros!$B$58:$B$59)*($E$24-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
         <v/>
       </c>
       <c r="F26" s="16" t="inlineStr">
@@ -6725,22 +7511,22 @@
           <t>COL_SEM</t>
         </is>
       </c>
-      <c r="C27" s="25">
-        <f>IF(Inputs!$C$29=1,2*(SUMPRODUCT((($C$25/2)&gt;Parametros!$B$45:$B$53)*(($C$25/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$25/2)&gt;Parametros!$B$57:$B$58)*(($C$25/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($C$25&gt;Parametros!$B$45:$B$53)*($C$25-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($C$25&gt;Parametros!$B$57:$B$58)*($C$25-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="D27" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((($D$25/2)&gt;Parametros!$B$45:$B$53)*(($D$25/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($D$25/2)&gt;Parametros!$B$57:$B$58)*(($D$25/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($D$25&gt;Parametros!$B$45:$B$53)*($D$25-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($D$25&gt;Parametros!$B$57:$B$58)*($D$25-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="E27" s="25">
-        <f>IF(Inputs!$E$29=1,2*(SUMPRODUCT((($E$25/2)&gt;Parametros!$B$45:$B$53)*(($E$25/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($E$25/2)&gt;Parametros!$B$57:$B$58)*(($E$25/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($E$25&gt;Parametros!$B$45:$B$53)*($E$25-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($E$25&gt;Parametros!$B$57:$B$58)*($E$25-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
+      <c r="C27" s="21">
+        <f>IF(Inputs!$C$33=1,2*(SUMPRODUCT((($C$25/2)&gt;Parametros!$B$46:$B$54)*(($C$25/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$25/2)&gt;Parametros!$B$58:$B$59)*(($C$25/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$25&gt;Parametros!$B$46:$B$54)*($C$25-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$25&gt;Parametros!$B$58:$B$59)*($C$25-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="D27" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((($D$25/2)&gt;Parametros!$B$46:$B$54)*(($D$25/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$25/2)&gt;Parametros!$B$58:$B$59)*(($D$25/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$25&gt;Parametros!$B$46:$B$54)*($D$25-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$25&gt;Parametros!$B$58:$B$59)*($D$25-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f>IF(Inputs!$E$33=1,2*(SUMPRODUCT((($E$25/2)&gt;Parametros!$B$46:$B$54)*(($E$25/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$25/2)&gt;Parametros!$B$58:$B$59)*(($E$25/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$25&gt;Parametros!$B$46:$B$54)*($E$25-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$25&gt;Parametros!$B$58:$B$59)*($E$25-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
         <v/>
       </c>
       <c r="F27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>IRS imputável à atividade</t>
         </is>
@@ -6750,15 +7536,15 @@
           <t>IRS_ATIV</t>
         </is>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="23">
         <f>$C$26-$C$27</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="23">
         <f>$D$26-$D$27</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="23">
         <f>$E$26-$E$27</f>
         <v/>
       </c>
@@ -6775,16 +7561,16 @@
           <t>IRS_TOT</t>
         </is>
       </c>
-      <c r="C29" s="25">
-        <f>MAX(0,$C$26-Inputs!$C$31)</f>
-        <v/>
-      </c>
-      <c r="D29" s="25">
-        <f>MAX(0,$D$26-Inputs!$D$31)</f>
-        <v/>
-      </c>
-      <c r="E29" s="25">
-        <f>MAX(0,$E$26-Inputs!$E$31)</f>
+      <c r="C29" s="21">
+        <f>MAX(0,$C$26-Inputs!$C$35)</f>
+        <v/>
+      </c>
+      <c r="D29" s="21">
+        <f>MAX(0,$D$26-Inputs!$D$35)</f>
+        <v/>
+      </c>
+      <c r="E29" s="21">
+        <f>MAX(0,$E$26-Inputs!$E$35)</f>
         <v/>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -6806,7 +7592,7 @@
       <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>Caixa gerada pela atividade, antes de impostos e contribuições</t>
         </is>
@@ -6816,16 +7602,16 @@
           <t>CAIXA</t>
         </is>
       </c>
-      <c r="C31" s="27">
-        <f>Inputs!$C$6+Inputs!$C$7-(Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14+Inputs!$C$15)</f>
-        <v/>
-      </c>
-      <c r="D31" s="27">
-        <f>Inputs!$D$6+Inputs!$D$7-(Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14+Inputs!$D$15)</f>
-        <v/>
-      </c>
-      <c r="E31" s="27">
-        <f>Inputs!$E$6+Inputs!$E$7-(Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14+Inputs!$E$15)</f>
+      <c r="C31" s="23">
+        <f>Inputs!$C$37+Inputs!$C$38+Inputs!$C$12-(Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19+Inputs!$C$39)</f>
+        <v/>
+      </c>
+      <c r="D31" s="23">
+        <f>Inputs!$D$37+Inputs!$D$38+Inputs!$D$12-(Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19+Inputs!$D$39)</f>
+        <v/>
+      </c>
+      <c r="E31" s="23">
+        <f>Inputs!$E$37+Inputs!$E$38+Inputs!$E$12-(Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19+Inputs!$E$39)</f>
         <v/>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -6835,7 +7621,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>Total de impostos e contribuições</t>
         </is>
@@ -6845,15 +7631,15 @@
           <t>CARGA</t>
         </is>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="23">
         <f>$C$28+$C$18+$C$12+$C$14+$C$15</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="23">
         <f>$D$28+$D$18+$D$12+$D$14+$D$15</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="23">
         <f>$E$28+$E$18+$E$12+$E$14+$E$15</f>
         <v/>
       </c>
@@ -6874,15 +7660,15 @@
           <t>TAXA_EF</t>
         </is>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="30">
         <f>IF($C$31&lt;=0,0,$C$32/$C$31)</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="30">
         <f>IF($D$31&lt;=0,0,$D$32/$D$31)</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="30">
         <f>IF($E$31&lt;=0,0,$E$32/$E$31)</f>
         <v/>
       </c>
@@ -6899,16 +7685,16 @@
           <t>RETIDO</t>
         </is>
       </c>
-      <c r="C34" s="25">
-        <f>MAX(0,(Inputs!$C$6+Inputs!$C$7-(Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14+Inputs!$C$15))-$C$10-$C$12-$C$14-$C$15)*(1-Inputs!$C$25)</f>
-        <v/>
-      </c>
-      <c r="D34" s="25">
-        <f>MAX(0,(Inputs!$D$6+Inputs!$D$7-(Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14+Inputs!$D$15))-$D$10-$D$12-$D$14-$D$15)*(1-Inputs!$D$25)</f>
-        <v/>
-      </c>
-      <c r="E34" s="25">
-        <f>MAX(0,(Inputs!$E$6+Inputs!$E$7-(Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14+Inputs!$E$15))-$E$10-$E$12-$E$14-$E$15)*(1-Inputs!$E$25)</f>
+      <c r="C34" s="21">
+        <f>MAX(0,(Inputs!$C$37+Inputs!$C$38+Inputs!$C$12-(Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19+Inputs!$C$39))-$C$10-$C$12-$C$14-$C$15)*(1-Inputs!$C$29)</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f>MAX(0,(Inputs!$D$37+Inputs!$D$38+Inputs!$D$12-(Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19+Inputs!$D$39))-$D$10-$D$12-$D$14-$D$15)*(1-Inputs!$D$29)</f>
+        <v/>
+      </c>
+      <c r="E34" s="21">
+        <f>MAX(0,(Inputs!$E$37+Inputs!$E$38+Inputs!$E$12-(Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19+Inputs!$E$39))-$E$10-$E$12-$E$14-$E$15)*(1-Inputs!$E$29)</f>
         <v/>
       </c>
       <c r="F34" s="16" t="inlineStr"/>
@@ -6924,15 +7710,15 @@
           <t>LIQ_CJ</t>
         </is>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="21">
         <f>0</f>
         <v/>
       </c>
@@ -6943,7 +7729,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA A SÓCIA</t>
         </is>
@@ -6953,22 +7739,22 @@
           <t>LIQ_SOC</t>
         </is>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="23">
         <f>$C$31-$C$32-$C$34-$C$35</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="23">
         <f>$D$31-$D$32-$D$34-$D$35</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="23">
         <f>$E$31-$E$32-$E$34-$E$35</f>
         <v/>
       </c>
       <c r="F36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA O AGREGADO</t>
         </is>
@@ -6978,15 +7764,15 @@
           <t>LIQ_AGR</t>
         </is>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="23">
         <f>$C$36+$C$35</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="23">
         <f>$D$36+$D$35</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="23">
         <f>$E$36+$E$35</f>
         <v/>
       </c>
@@ -7003,16 +7789,16 @@
           <t>INV_A1</t>
         </is>
       </c>
-      <c r="C38" s="25">
-        <f>Inputs!$C$18+Inputs!$C$19+Inputs!$C$20+Inputs!$C$21</f>
-        <v/>
-      </c>
-      <c r="D38" s="25">
-        <f>Inputs!$D$18+Inputs!$D$19+Inputs!$D$20+Inputs!$D$21</f>
-        <v/>
-      </c>
-      <c r="E38" s="25">
-        <f>Inputs!$E$18+Inputs!$E$19+Inputs!$E$20+Inputs!$E$21</f>
+      <c r="C38" s="21">
+        <f>Inputs!$C$22+Inputs!$C$23+Inputs!$C$24+Inputs!$C$25</f>
+        <v/>
+      </c>
+      <c r="D38" s="21">
+        <f>Inputs!$D$22+Inputs!$D$23+Inputs!$D$24+Inputs!$D$25</f>
+        <v/>
+      </c>
+      <c r="E38" s="21">
+        <f>Inputs!$E$22+Inputs!$E$23+Inputs!$E$24+Inputs!$E$25</f>
         <v/>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -7107,7 +7893,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Prestações de serviços isentas (fisioterapia)</t>
+          <t>Receita isenta (fisioterapia + cedência de espaço, se isenta)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -7115,16 +7901,16 @@
           <t>FAT</t>
         </is>
       </c>
-      <c r="C6" s="23">
-        <f>Inputs!$C$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>Inputs!$D$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>Inputs!$E$6</f>
+      <c r="C6" s="28">
+        <f>Inputs!$C$37+IF(Inputs!$C$11=1,0,Inputs!$C$38)</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
+        <f>Inputs!$D$37+IF(Inputs!$D$11=1,0,Inputs!$D$38)</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>Inputs!$E$37+IF(Inputs!$E$11=1,0,Inputs!$E$38)</f>
         <v/>
       </c>
       <c r="F6" s="16" t="inlineStr"/>
@@ -7132,7 +7918,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Prestações de serviços tributadas (atividade do cônjuge)</t>
+          <t>Receita sujeita a IVA (cônjuge e/ou cedência tributada)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -7140,16 +7926,16 @@
           <t>FAT_T</t>
         </is>
       </c>
-      <c r="C7" s="23">
-        <f>Inputs!$C$7</f>
-        <v/>
-      </c>
-      <c r="D7" s="23">
-        <f>Inputs!$D$7</f>
-        <v/>
-      </c>
-      <c r="E7" s="23">
-        <f>Inputs!$E$7</f>
+      <c r="C7" s="28">
+        <f>Inputs!$C$42</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>Inputs!$D$42</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>Inputs!$E$42</f>
         <v/>
       </c>
       <c r="F7" s="16" t="inlineStr"/>
@@ -7165,16 +7951,16 @@
           <t>C_OP</t>
         </is>
       </c>
-      <c r="C8" s="23">
-        <f>Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14</f>
-        <v/>
-      </c>
-      <c r="D8" s="23">
-        <f>Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14</f>
+      <c r="C8" s="28">
+        <f>Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
+        <f>Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19</f>
         <v/>
       </c>
       <c r="F8" s="16" t="inlineStr"/>
@@ -7182,7 +7968,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Honorários a fisioterapeutas</t>
+          <t>Custo com os colaboradores</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -7190,16 +7976,16 @@
           <t>C_HON</t>
         </is>
       </c>
-      <c r="C9" s="23">
-        <f>Inputs!$C$15</f>
-        <v/>
-      </c>
-      <c r="D9" s="23">
-        <f>Inputs!$D$15</f>
-        <v/>
-      </c>
-      <c r="E9" s="23">
-        <f>Inputs!$E$15</f>
+      <c r="C9" s="28">
+        <f>Inputs!$C$39</f>
+        <v/>
+      </c>
+      <c r="D9" s="28">
+        <f>Inputs!$D$39</f>
+        <v/>
+      </c>
+      <c r="E9" s="28">
+        <f>Inputs!$E$39</f>
         <v/>
       </c>
       <c r="F9" s="16" t="inlineStr"/>
@@ -7215,16 +8001,16 @@
           <t>AMORT</t>
         </is>
       </c>
-      <c r="C10" s="25">
-        <f>Inputs!$C$18*Parametros!$C$34+(Inputs!$C$19+Inputs!$C$20)*Parametros!$C$35+Inputs!$C$21*Parametros!$C$36</f>
-        <v/>
-      </c>
-      <c r="D10" s="25">
-        <f>Inputs!$D$18*Parametros!$C$34+(Inputs!$D$19+Inputs!$D$20)*Parametros!$C$35+Inputs!$D$21*Parametros!$C$36</f>
-        <v/>
-      </c>
-      <c r="E10" s="25">
-        <f>Inputs!$E$18*Parametros!$C$34+(Inputs!$E$19+Inputs!$E$20)*Parametros!$C$35+Inputs!$E$21*Parametros!$C$36</f>
+      <c r="C10" s="21">
+        <f>Inputs!$C$22*Parametros!$C$35+(Inputs!$C$23+Inputs!$C$24)*Parametros!$C$36+Inputs!$C$25*Parametros!$C$37</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>Inputs!$D$22*Parametros!$C$35+(Inputs!$D$23+Inputs!$D$24)*Parametros!$C$36+Inputs!$D$25*Parametros!$C$37</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>Inputs!$E$22*Parametros!$C$35+(Inputs!$E$23+Inputs!$E$24)*Parametros!$C$36+Inputs!$E$25*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="F10" s="16" t="inlineStr"/>
@@ -7240,16 +8026,16 @@
           <t>REM</t>
         </is>
       </c>
-      <c r="C11" s="23">
-        <f>Inputs!$C$23</f>
-        <v/>
-      </c>
-      <c r="D11" s="23">
-        <f>Inputs!$D$23</f>
-        <v/>
-      </c>
-      <c r="E11" s="23">
-        <f>Inputs!$E$23</f>
+      <c r="C11" s="28">
+        <f>Inputs!$C$27</f>
+        <v/>
+      </c>
+      <c r="D11" s="28">
+        <f>Inputs!$D$27</f>
+        <v/>
+      </c>
+      <c r="E11" s="28">
+        <f>Inputs!$E$27</f>
         <v/>
       </c>
       <c r="F11" s="16" t="inlineStr"/>
@@ -7265,15 +8051,15 @@
           <t>BASE_MOE</t>
         </is>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="21">
         <f>MAX($C$11,Parametros!$C$6*Parametros!$C$13*12)</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="21">
         <f>MAX($D$11,Parametros!$C$6*Parametros!$C$13*12)</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="21">
         <f>MAX($E$11,Parametros!$C$6*Parametros!$C$13*12)</f>
         <v/>
       </c>
@@ -7290,22 +8076,22 @@
           <t>TSU_ENT</t>
         </is>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="21">
         <f>$C$12*Parametros!$C$11</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="21">
         <f>$D$12*Parametros!$C$11</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="21">
         <f>$E$12*Parametros!$C$11</f>
         <v/>
       </c>
       <c r="F13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Lucro tributável</t>
         </is>
@@ -7315,15 +8101,15 @@
           <t>LT</t>
         </is>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="23">
         <f>$C$6+$C$7-$C$8-$C$9-$C$10-$C$11-$C$13</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="23">
         <f>$D$6+$D$7-$D$8-$D$9-$D$10-$D$11-$D$13</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="23">
         <f>$E$6+$E$7-$E$8-$E$9-$E$10-$E$11-$E$13</f>
         <v/>
       </c>
@@ -7340,16 +8126,16 @@
           <t>IRC</t>
         </is>
       </c>
-      <c r="C15" s="25">
-        <f>MIN(MAX($C$14,0),Parametros!$C$24)*Parametros!$C$23+MAX(0,MAX($C$14,0)-Parametros!$C$24)*Parametros!$C$25</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>MIN(MAX($D$14,0),Parametros!$C$24)*Parametros!$C$23+MAX(0,MAX($D$14,0)-Parametros!$C$24)*Parametros!$C$25</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>MIN(MAX($E$14,0),Parametros!$C$24)*Parametros!$C$23+MAX(0,MAX($E$14,0)-Parametros!$C$24)*Parametros!$C$25</f>
+      <c r="C15" s="21">
+        <f>MIN(MAX($C$14,0),Parametros!$C$25)*Parametros!$C$24+MAX(0,MAX($C$14,0)-Parametros!$C$25)*Parametros!$C$26</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>MIN(MAX($D$14,0),Parametros!$C$25)*Parametros!$C$24+MAX(0,MAX($D$14,0)-Parametros!$C$25)*Parametros!$C$26</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>MIN(MAX($E$14,0),Parametros!$C$25)*Parametros!$C$24+MAX(0,MAX($E$14,0)-Parametros!$C$25)*Parametros!$C$26</f>
         <v/>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -7369,16 +8155,16 @@
           <t>DERR</t>
         </is>
       </c>
-      <c r="C16" s="25">
-        <f>MAX($C$14,0)*Parametros!$C$26</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>MAX($D$14,0)*Parametros!$C$26</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>MAX($E$14,0)*Parametros!$C$26</f>
+      <c r="C16" s="21">
+        <f>MAX($C$14,0)*Parametros!$C$27</f>
+        <v/>
+      </c>
+      <c r="D16" s="21">
+        <f>MAX($D$14,0)*Parametros!$C$27</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>MAX($E$14,0)*Parametros!$C$27</f>
         <v/>
       </c>
       <c r="F16" s="16" t="inlineStr">
@@ -7398,22 +8184,22 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="C17" s="23">
-        <f>Inputs!$C$24</f>
-        <v/>
-      </c>
-      <c r="D17" s="23">
-        <f>Inputs!$D$24</f>
-        <v/>
-      </c>
-      <c r="E17" s="23">
-        <f>Inputs!$E$24</f>
+      <c r="C17" s="28">
+        <f>Inputs!$C$28</f>
+        <v/>
+      </c>
+      <c r="D17" s="28">
+        <f>Inputs!$D$28</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>Inputs!$E$28</f>
         <v/>
       </c>
       <c r="F17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Lucro após imposto</t>
         </is>
@@ -7423,15 +8209,15 @@
           <t>LUCRO_LIQ</t>
         </is>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="23">
         <f>$C$14-$C$15-$C$16-$C$17</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="23">
         <f>$D$14-$D$15-$D$16-$D$17</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="23">
         <f>$E$14-$E$15-$E$16-$E$17</f>
         <v/>
       </c>
@@ -7460,16 +8246,16 @@
           <t>CX_DIST</t>
         </is>
       </c>
-      <c r="C20" s="25">
-        <f>MAX(0,(Inputs!$C$6+Inputs!$C$7-(Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14+Inputs!$C$15))-$C$11-$C$13-$C$15-$C$16-$C$17)</f>
-        <v/>
-      </c>
-      <c r="D20" s="25">
-        <f>MAX(0,(Inputs!$D$6+Inputs!$D$7-(Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14+Inputs!$D$15))-$D$11-$D$13-$D$15-$D$16-$D$17)</f>
-        <v/>
-      </c>
-      <c r="E20" s="25">
-        <f>MAX(0,(Inputs!$E$6+Inputs!$E$7-(Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14+Inputs!$E$15))-$E$11-$E$13-$E$15-$E$16-$E$17)</f>
+      <c r="C20" s="21">
+        <f>MAX(0,(Inputs!$C$37+Inputs!$C$38+Inputs!$C$12-(Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19+Inputs!$C$39))-$C$11-$C$13-$C$15-$C$16-$C$17)</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>MAX(0,(Inputs!$D$37+Inputs!$D$38+Inputs!$D$12-(Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19+Inputs!$D$39))-$D$11-$D$13-$D$15-$D$16-$D$17)</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>MAX(0,(Inputs!$E$37+Inputs!$E$38+Inputs!$E$12-(Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19+Inputs!$E$39))-$E$11-$E$13-$E$15-$E$16-$E$17)</f>
         <v/>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -7489,16 +8275,16 @@
           <t>POL</t>
         </is>
       </c>
-      <c r="C21" s="24">
-        <f>Inputs!$C$25</f>
-        <v/>
-      </c>
-      <c r="D21" s="24">
-        <f>Inputs!$D$25</f>
-        <v/>
-      </c>
-      <c r="E21" s="24">
-        <f>Inputs!$E$25</f>
+      <c r="C21" s="29">
+        <f>Inputs!$C$29</f>
+        <v/>
+      </c>
+      <c r="D21" s="29">
+        <f>Inputs!$D$29</f>
+        <v/>
+      </c>
+      <c r="E21" s="29">
+        <f>Inputs!$E$29</f>
         <v/>
       </c>
       <c r="F21" s="16" t="inlineStr">
@@ -7518,15 +8304,15 @@
           <t>DIST</t>
         </is>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="21">
         <f>$C$20*$C$21</f>
         <v/>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="21">
         <f>$D$20*$D$21</f>
         <v/>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="21">
         <f>$E$20*$E$21</f>
         <v/>
       </c>
@@ -7543,16 +8329,16 @@
           <t>PCT_CJ</t>
         </is>
       </c>
-      <c r="C23" s="24">
-        <f>Inputs!$C$26</f>
-        <v/>
-      </c>
-      <c r="D23" s="24">
-        <f>Inputs!$D$26</f>
-        <v/>
-      </c>
-      <c r="E23" s="24">
-        <f>Inputs!$E$26</f>
+      <c r="C23" s="29">
+        <f>Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>Inputs!$D$30</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>Inputs!$E$30</f>
         <v/>
       </c>
       <c r="F23" s="16" t="inlineStr"/>
@@ -7568,15 +8354,15 @@
           <t>DIV_JUL</t>
         </is>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="21">
         <f>$C$22*(1-$C$23)</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="21">
         <f>$D$22*(1-$D$23)</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="21">
         <f>$E$22*(1-$E$23)</f>
         <v/>
       </c>
@@ -7593,15 +8379,15 @@
           <t>DIV_CJ</t>
         </is>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="21">
         <f>$C$22*$C$23</f>
         <v/>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="21">
         <f>$D$22*$D$23</f>
         <v/>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="21">
         <f>$E$22*$E$23</f>
         <v/>
       </c>
@@ -7622,13 +8408,13 @@
           <t>ENGLOB</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="31" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="16" t="inlineStr">
@@ -7648,16 +8434,16 @@
           <t>IMP_DIV</t>
         </is>
       </c>
-      <c r="C27" s="25">
-        <f>IF($C$26=1,0,($C$24+$C$25)*Parametros!$C$28)</f>
-        <v/>
-      </c>
-      <c r="D27" s="25">
-        <f>IF($D$26=1,0,($D$24+$D$25)*Parametros!$C$28)</f>
-        <v/>
-      </c>
-      <c r="E27" s="25">
-        <f>IF($E$26=1,0,($E$24+$E$25)*Parametros!$C$28)</f>
+      <c r="C27" s="21">
+        <f>IF($C$26=1,0,($C$24+$C$25)*Parametros!$C$29)</f>
+        <v/>
+      </c>
+      <c r="D27" s="21">
+        <f>IF($D$26=1,0,($D$24+$D$25)*Parametros!$C$29)</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f>IF($E$26=1,0,($E$24+$E$25)*Parametros!$C$29)</f>
         <v/>
       </c>
       <c r="F27" s="16" t="inlineStr"/>
@@ -7675,7 +8461,7 @@
       <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Rendimento da sócia sujeito a englobamento</t>
         </is>
@@ -7685,16 +8471,16 @@
           <t>R_JUL</t>
         </is>
       </c>
-      <c r="C29" s="27">
-        <f>MAX(0,$C$11-MIN($C$11,MAX(Parametros!$C$21,$C$12*Parametros!$C$12)))+IF($C$26=1,$C$24*Parametros!$C$29,0)</f>
-        <v/>
-      </c>
-      <c r="D29" s="27">
-        <f>MAX(0,$D$11-MIN($D$11,MAX(Parametros!$C$21,$D$12*Parametros!$C$12)))+IF($D$26=1,$D$24*Parametros!$C$29,0)</f>
-        <v/>
-      </c>
-      <c r="E29" s="27">
-        <f>MAX(0,$E$11-MIN($E$11,MAX(Parametros!$C$21,$E$12*Parametros!$C$12)))+IF($E$26=1,$E$24*Parametros!$C$29,0)</f>
+      <c r="C29" s="23">
+        <f>MAX(0,$C$11-MIN($C$11,MAX(Parametros!$C$21,$C$12*Parametros!$C$12)))+IF($C$26=1,$C$24*Parametros!$C$30,0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="23">
+        <f>MAX(0,$D$11-MIN($D$11,MAX(Parametros!$C$21,$D$12*Parametros!$C$12)))+IF($D$26=1,$D$24*Parametros!$C$30,0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="23">
+        <f>MAX(0,$E$11-MIN($E$11,MAX(Parametros!$C$21,$E$12*Parametros!$C$12)))+IF($E$26=1,$E$24*Parametros!$C$30,0)</f>
         <v/>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -7714,16 +8500,16 @@
           <t>R_CONJ</t>
         </is>
       </c>
-      <c r="C30" s="25">
-        <f>Inputs!$C$28+IF($C$26=1,$C$25*Parametros!$C$29,0)</f>
-        <v/>
-      </c>
-      <c r="D30" s="25">
-        <f>Inputs!$D$28+IF($D$26=1,$D$25*Parametros!$C$29,0)</f>
-        <v/>
-      </c>
-      <c r="E30" s="25">
-        <f>Inputs!$E$28+IF($E$26=1,$E$25*Parametros!$C$29,0)</f>
+      <c r="C30" s="21">
+        <f>Inputs!$C$32+IF($C$26=1,$C$25*Parametros!$C$30,0)</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f>Inputs!$D$32+IF($D$26=1,$D$25*Parametros!$C$30,0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>Inputs!$E$32+IF($E$26=1,$E$25*Parametros!$C$30,0)</f>
         <v/>
       </c>
       <c r="F30" s="16" t="inlineStr"/>
@@ -7739,15 +8525,15 @@
           <t>RC_COM</t>
         </is>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="21">
         <f>$C$29+$C$30</f>
         <v/>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="21">
         <f>$D$29+$D$30</f>
         <v/>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="21">
         <f>$E$29+$E$30</f>
         <v/>
       </c>
@@ -7764,16 +8550,16 @@
           <t>RC_SEM</t>
         </is>
       </c>
-      <c r="C32" s="23">
-        <f>Inputs!$C$28</f>
-        <v/>
-      </c>
-      <c r="D32" s="23">
-        <f>Inputs!$D$28</f>
-        <v/>
-      </c>
-      <c r="E32" s="23">
-        <f>Inputs!$E$28</f>
+      <c r="C32" s="28">
+        <f>Inputs!$C$32</f>
+        <v/>
+      </c>
+      <c r="D32" s="28">
+        <f>Inputs!$D$32</f>
+        <v/>
+      </c>
+      <c r="E32" s="28">
+        <f>Inputs!$E$32</f>
         <v/>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -7793,16 +8579,16 @@
           <t>COL_COM</t>
         </is>
       </c>
-      <c r="C33" s="25">
-        <f>IF(Inputs!$C$29=1,2*(SUMPRODUCT((($C$31/2)&gt;Parametros!$B$45:$B$53)*(($C$31/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$31/2)&gt;Parametros!$B$57:$B$58)*(($C$31/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($C$31&gt;Parametros!$B$45:$B$53)*($C$31-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($C$31&gt;Parametros!$B$57:$B$58)*($C$31-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="D33" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((($D$31/2)&gt;Parametros!$B$45:$B$53)*(($D$31/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($D$31/2)&gt;Parametros!$B$57:$B$58)*(($D$31/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($D$31&gt;Parametros!$B$45:$B$53)*($D$31-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($D$31&gt;Parametros!$B$57:$B$58)*($D$31-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="E33" s="25">
-        <f>IF(Inputs!$E$29=1,2*(SUMPRODUCT((($E$31/2)&gt;Parametros!$B$45:$B$53)*(($E$31/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($E$31/2)&gt;Parametros!$B$57:$B$58)*(($E$31/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($E$31&gt;Parametros!$B$45:$B$53)*($E$31-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($E$31&gt;Parametros!$B$57:$B$58)*($E$31-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
+      <c r="C33" s="21">
+        <f>IF(Inputs!$C$33=1,2*(SUMPRODUCT((($C$31/2)&gt;Parametros!$B$46:$B$54)*(($C$31/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$31/2)&gt;Parametros!$B$58:$B$59)*(($C$31/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$31&gt;Parametros!$B$46:$B$54)*($C$31-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$31&gt;Parametros!$B$58:$B$59)*($C$31-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="D33" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((($D$31/2)&gt;Parametros!$B$46:$B$54)*(($D$31/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$31/2)&gt;Parametros!$B$58:$B$59)*(($D$31/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$31&gt;Parametros!$B$46:$B$54)*($D$31-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$31&gt;Parametros!$B$58:$B$59)*($D$31-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="E33" s="21">
+        <f>IF(Inputs!$E$33=1,2*(SUMPRODUCT((($E$31/2)&gt;Parametros!$B$46:$B$54)*(($E$31/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$31/2)&gt;Parametros!$B$58:$B$59)*(($E$31/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$31&gt;Parametros!$B$46:$B$54)*($E$31-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$31&gt;Parametros!$B$58:$B$59)*($E$31-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
         <v/>
       </c>
       <c r="F33" s="16" t="inlineStr"/>
@@ -7818,22 +8604,22 @@
           <t>COL_SEM</t>
         </is>
       </c>
-      <c r="C34" s="25">
-        <f>IF(Inputs!$C$29=1,2*(SUMPRODUCT((($C$32/2)&gt;Parametros!$B$45:$B$53)*(($C$32/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($C$32/2)&gt;Parametros!$B$57:$B$58)*(($C$32/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($C$32&gt;Parametros!$B$45:$B$53)*($C$32-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($C$32&gt;Parametros!$B$57:$B$58)*($C$32-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="D34" s="25">
-        <f>IF(Inputs!$D$29=1,2*(SUMPRODUCT((($D$32/2)&gt;Parametros!$B$45:$B$53)*(($D$32/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($D$32/2)&gt;Parametros!$B$57:$B$58)*(($D$32/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($D$32&gt;Parametros!$B$45:$B$53)*($D$32-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($D$32&gt;Parametros!$B$57:$B$58)*($D$32-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
-        <v/>
-      </c>
-      <c r="E34" s="25">
-        <f>IF(Inputs!$E$29=1,2*(SUMPRODUCT((($E$32/2)&gt;Parametros!$B$45:$B$53)*(($E$32/2)-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT((($E$32/2)&gt;Parametros!$B$57:$B$58)*(($E$32/2)-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58)),SUMPRODUCT(($E$32&gt;Parametros!$B$45:$B$53)*($E$32-Parametros!$B$45:$B$53)*Parametros!$E$45:$E$53)+SUMPRODUCT(($E$32&gt;Parametros!$B$57:$B$58)*($E$32-Parametros!$B$57:$B$58)*Parametros!$E$57:$E$58))</f>
+      <c r="C34" s="21">
+        <f>IF(Inputs!$C$33=1,2*(SUMPRODUCT((($C$32/2)&gt;Parametros!$B$46:$B$54)*(($C$32/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$32/2)&gt;Parametros!$B$58:$B$59)*(($C$32/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$32&gt;Parametros!$B$46:$B$54)*($C$32-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$32&gt;Parametros!$B$58:$B$59)*($C$32-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f>IF(Inputs!$D$33=1,2*(SUMPRODUCT((($D$32/2)&gt;Parametros!$B$46:$B$54)*(($D$32/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$32/2)&gt;Parametros!$B$58:$B$59)*(($D$32/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$32&gt;Parametros!$B$46:$B$54)*($D$32-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$32&gt;Parametros!$B$58:$B$59)*($D$32-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <v/>
+      </c>
+      <c r="E34" s="21">
+        <f>IF(Inputs!$E$33=1,2*(SUMPRODUCT((($E$32/2)&gt;Parametros!$B$46:$B$54)*(($E$32/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$32/2)&gt;Parametros!$B$58:$B$59)*(($E$32/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$32&gt;Parametros!$B$46:$B$54)*($E$32-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$32&gt;Parametros!$B$58:$B$59)*($E$32-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
         <v/>
       </c>
       <c r="F34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>IRS imputável à atividade</t>
         </is>
@@ -7843,15 +8629,15 @@
           <t>IRS_ATIV</t>
         </is>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="23">
         <f>$C$33-$C$34</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="23">
         <f>$D$33-$D$34</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="23">
         <f>$E$33-$E$34</f>
         <v/>
       </c>
@@ -7868,16 +8654,16 @@
           <t>IRS_TOT</t>
         </is>
       </c>
-      <c r="C36" s="25">
-        <f>MAX(0,$C$33-Inputs!$C$31)</f>
-        <v/>
-      </c>
-      <c r="D36" s="25">
-        <f>MAX(0,$D$33-Inputs!$D$31)</f>
-        <v/>
-      </c>
-      <c r="E36" s="25">
-        <f>MAX(0,$E$33-Inputs!$E$31)</f>
+      <c r="C36" s="21">
+        <f>MAX(0,$C$33-Inputs!$C$35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="21">
+        <f>MAX(0,$D$33-Inputs!$D$35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="21">
+        <f>MAX(0,$E$33-Inputs!$E$35)</f>
         <v/>
       </c>
       <c r="F36" s="16" t="inlineStr"/>
@@ -7893,15 +8679,15 @@
           <t>SS_TRAB</t>
         </is>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="21">
         <f>$C$12*Parametros!$C$12</f>
         <v/>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="21">
         <f>$D$12*Parametros!$C$12</f>
         <v/>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="21">
         <f>$E$12*Parametros!$C$12</f>
         <v/>
       </c>
@@ -7920,7 +8706,7 @@
       <c r="F38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="26" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>Caixa gerada pela atividade, antes de impostos e contribuições</t>
         </is>
@@ -7930,16 +8716,16 @@
           <t>CAIXA</t>
         </is>
       </c>
-      <c r="C39" s="27">
-        <f>Inputs!$C$6+Inputs!$C$7-(Inputs!$C$9+Inputs!$C$10+Inputs!$C$11+Inputs!$C$12+Inputs!$C$13+Inputs!$C$14+Inputs!$C$15)</f>
-        <v/>
-      </c>
-      <c r="D39" s="27">
-        <f>Inputs!$D$6+Inputs!$D$7-(Inputs!$D$9+Inputs!$D$10+Inputs!$D$11+Inputs!$D$12+Inputs!$D$13+Inputs!$D$14+Inputs!$D$15)</f>
-        <v/>
-      </c>
-      <c r="E39" s="27">
-        <f>Inputs!$E$6+Inputs!$E$7-(Inputs!$E$9+Inputs!$E$10+Inputs!$E$11+Inputs!$E$12+Inputs!$E$13+Inputs!$E$14+Inputs!$E$15)</f>
+      <c r="C39" s="23">
+        <f>Inputs!$C$37+Inputs!$C$38+Inputs!$C$12-(Inputs!$C$14+Inputs!$C$15+Inputs!$C$16+Inputs!$C$17+Inputs!$C$18+Inputs!$C$19+Inputs!$C$39)</f>
+        <v/>
+      </c>
+      <c r="D39" s="23">
+        <f>Inputs!$D$37+Inputs!$D$38+Inputs!$D$12-(Inputs!$D$14+Inputs!$D$15+Inputs!$D$16+Inputs!$D$17+Inputs!$D$18+Inputs!$D$19+Inputs!$D$39)</f>
+        <v/>
+      </c>
+      <c r="E39" s="23">
+        <f>Inputs!$E$37+Inputs!$E$38+Inputs!$E$12-(Inputs!$E$14+Inputs!$E$15+Inputs!$E$16+Inputs!$E$17+Inputs!$E$18+Inputs!$E$19+Inputs!$E$39)</f>
         <v/>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -7949,7 +8735,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>Total de impostos e contribuições</t>
         </is>
@@ -7959,15 +8745,15 @@
           <t>CARGA</t>
         </is>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="23">
         <f>$C$35+$C$37+$C$13+$C$15+$C$16+$C$17+$C$27</f>
         <v/>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="23">
         <f>$D$35+$D$37+$D$13+$D$15+$D$16+$D$17+$D$27</f>
         <v/>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="23">
         <f>$E$35+$E$37+$E$13+$E$15+$E$16+$E$17+$E$27</f>
         <v/>
       </c>
@@ -7988,15 +8774,15 @@
           <t>TAXA_EF</t>
         </is>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="30">
         <f>IF($C$39&lt;=0,0,$C$40/$C$39)</f>
         <v/>
       </c>
-      <c r="D41" s="28">
+      <c r="D41" s="30">
         <f>IF($D$39&lt;=0,0,$D$40/$D$39)</f>
         <v/>
       </c>
-      <c r="E41" s="28">
+      <c r="E41" s="30">
         <f>IF($E$39&lt;=0,0,$E$40/$E$39)</f>
         <v/>
       </c>
@@ -8013,15 +8799,15 @@
           <t>RETIDO</t>
         </is>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="21">
         <f>$C$20-$C$22</f>
         <v/>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="21">
         <f>$D$20-$D$22</f>
         <v/>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="21">
         <f>$E$20-$E$22</f>
         <v/>
       </c>
@@ -8038,16 +8824,16 @@
           <t>LIQ_CJ</t>
         </is>
       </c>
-      <c r="C43" s="25">
-        <f>$C$25-IF($C$26=1,0,$C$25*Parametros!$C$28)</f>
-        <v/>
-      </c>
-      <c r="D43" s="25">
-        <f>$D$25-IF($D$26=1,0,$D$25*Parametros!$C$28)</f>
-        <v/>
-      </c>
-      <c r="E43" s="25">
-        <f>$E$25-IF($E$26=1,0,$E$25*Parametros!$C$28)</f>
+      <c r="C43" s="21">
+        <f>$C$25-IF($C$26=1,0,$C$25*Parametros!$C$29)</f>
+        <v/>
+      </c>
+      <c r="D43" s="21">
+        <f>$D$25-IF($D$26=1,0,$D$25*Parametros!$C$29)</f>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f>$E$25-IF($E$26=1,0,$E$25*Parametros!$C$29)</f>
         <v/>
       </c>
       <c r="F43" s="16" t="inlineStr">
@@ -8057,7 +8843,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA A SÓCIA</t>
         </is>
@@ -8067,22 +8853,22 @@
           <t>LIQ_SOC</t>
         </is>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="23">
         <f>$C$39-$C$40-$C$42-$C$43</f>
         <v/>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="23">
         <f>$D$39-$D$40-$D$42-$D$43</f>
         <v/>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="23">
         <f>$E$39-$E$40-$E$42-$E$43</f>
         <v/>
       </c>
       <c r="F44" s="16" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA O AGREGADO</t>
         </is>
@@ -8092,15 +8878,15 @@
           <t>LIQ_AGR</t>
         </is>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="23">
         <f>$C$44+$C$43</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="23">
         <f>$D$44+$D$43</f>
         <v/>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="23">
         <f>$E$44+$E$43</f>
         <v/>
       </c>
@@ -8117,16 +8903,16 @@
           <t>INV_A1</t>
         </is>
       </c>
-      <c r="C46" s="25">
-        <f>Inputs!$C$18+Inputs!$C$19+Inputs!$C$20+Inputs!$C$21</f>
-        <v/>
-      </c>
-      <c r="D46" s="25">
-        <f>Inputs!$D$18+Inputs!$D$19+Inputs!$D$20+Inputs!$D$21</f>
-        <v/>
-      </c>
-      <c r="E46" s="25">
-        <f>Inputs!$E$18+Inputs!$E$19+Inputs!$E$20+Inputs!$E$21</f>
+      <c r="C46" s="21">
+        <f>Inputs!$C$22+Inputs!$C$23+Inputs!$C$24+Inputs!$C$25</f>
+        <v/>
+      </c>
+      <c r="D46" s="21">
+        <f>Inputs!$D$22+Inputs!$D$23+Inputs!$D$24+Inputs!$D$25</f>
+        <v/>
+      </c>
+      <c r="E46" s="21">
+        <f>Inputs!$E$22+Inputs!$E$23+Inputs!$E$24+Inputs!$E$25</f>
         <v/>
       </c>
       <c r="F46" s="16" t="inlineStr">
@@ -8229,16 +9015,16 @@
           <t>I_OBRAS</t>
         </is>
       </c>
-      <c r="C6" s="25">
-        <f>Inputs!$C$18*Parametros!$C$31</f>
-        <v/>
-      </c>
-      <c r="D6" s="25">
-        <f>Inputs!$D$18*Parametros!$C$31</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>Inputs!$E$18*Parametros!$C$31</f>
+      <c r="C6" s="21">
+        <f>Inputs!$C$22*Parametros!$C$32</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
+        <f>Inputs!$D$22*Parametros!$C$32</f>
+        <v/>
+      </c>
+      <c r="E6" s="21">
+        <f>Inputs!$E$22*Parametros!$C$32</f>
         <v/>
       </c>
       <c r="F6" s="16" t="inlineStr"/>
@@ -8254,16 +9040,16 @@
           <t>I_EQN</t>
         </is>
       </c>
-      <c r="C7" s="25">
-        <f>Inputs!$C$19*Parametros!$C$31</f>
-        <v/>
-      </c>
-      <c r="D7" s="25">
-        <f>Inputs!$D$19*Parametros!$C$31</f>
-        <v/>
-      </c>
-      <c r="E7" s="25">
-        <f>Inputs!$E$19*Parametros!$C$31</f>
+      <c r="C7" s="21">
+        <f>Inputs!$C$23*Parametros!$C$32</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>Inputs!$D$23*Parametros!$C$32</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>Inputs!$E$23*Parametros!$C$32</f>
         <v/>
       </c>
       <c r="F7" s="16" t="inlineStr"/>
@@ -8279,16 +9065,16 @@
           <t>I_EQR</t>
         </is>
       </c>
-      <c r="C8" s="25">
-        <f>Inputs!$C$20*Parametros!$C$32</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>Inputs!$D$20*Parametros!$C$32</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>Inputs!$E$20*Parametros!$C$32</f>
+      <c r="C8" s="21">
+        <f>Inputs!$C$24*Parametros!$C$33</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>Inputs!$D$24*Parametros!$C$33</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>Inputs!$E$24*Parametros!$C$33</f>
         <v/>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -8308,22 +9094,22 @@
           <t>I_SOFT</t>
         </is>
       </c>
-      <c r="C9" s="25">
-        <f>Inputs!$C$21*Parametros!$C$31</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>Inputs!$D$21*Parametros!$C$31</f>
-        <v/>
-      </c>
-      <c r="E9" s="25">
-        <f>Inputs!$E$21*Parametros!$C$31</f>
+      <c r="C9" s="21">
+        <f>Inputs!$C$25*Parametros!$C$32</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>Inputs!$D$25*Parametros!$C$32</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>Inputs!$E$25*Parametros!$C$32</f>
         <v/>
       </c>
       <c r="F9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Total de IVA suportado no investimento</t>
         </is>
@@ -8333,15 +9119,15 @@
           <t>I_TOT</t>
         </is>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="23">
         <f>SUM($C$6:$C$9)</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="23">
         <f>SUM($D$6:$D$9)</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="23">
         <f>SUM($E$6:$E$9)</f>
         <v/>
       </c>
@@ -8370,15 +9156,15 @@
           <t>D_ISENTO</t>
         </is>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="21">
         <f>0</f>
         <v/>
       </c>
@@ -8389,7 +9175,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>IVA perdido, convertido em custo do investimento</t>
         </is>
@@ -8399,15 +9185,15 @@
           <t>P_ISENTO</t>
         </is>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="23">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="23">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="23">
         <f>$E$10</f>
         <v/>
       </c>
@@ -8440,16 +9226,16 @@
           <t>PRO_RATA</t>
         </is>
       </c>
-      <c r="C15" s="28">
-        <f>IF((Inputs!$C$6+Inputs!$C$7)&lt;=0,0,Inputs!$C$7/(Inputs!$C$6+Inputs!$C$7))</f>
-        <v/>
-      </c>
-      <c r="D15" s="28">
-        <f>IF((Inputs!$D$6+Inputs!$D$7)&lt;=0,0,Inputs!$D$7/(Inputs!$D$6+Inputs!$D$7))</f>
-        <v/>
-      </c>
-      <c r="E15" s="28">
-        <f>IF((Inputs!$E$6+Inputs!$E$7)&lt;=0,0,Inputs!$E$7/(Inputs!$E$6+Inputs!$E$7))</f>
+      <c r="C15" s="30">
+        <f>IF(Inputs!$C$41&lt;=0,0,Inputs!$C$42/Inputs!$C$41)</f>
+        <v/>
+      </c>
+      <c r="D15" s="30">
+        <f>IF(Inputs!$D$41&lt;=0,0,Inputs!$D$42/Inputs!$D$41)</f>
+        <v/>
+      </c>
+      <c r="E15" s="30">
+        <f>IF(Inputs!$E$41&lt;=0,0,Inputs!$E$42/Inputs!$E$41)</f>
         <v/>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -8495,15 +9281,15 @@
           <t>D_PRORATA</t>
         </is>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="21">
         <f>$C$10*$C$15</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="21">
         <f>$D$10*$D$15</f>
         <v/>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="21">
         <f>$E$10*$E$15</f>
         <v/>
       </c>
@@ -8520,15 +9306,15 @@
           <t>D_REAL</t>
         </is>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="21">
         <f>$C$10*$C$16+$C$10*(1-$C$16)*$C$15</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="21">
         <f>$D$10*$D$16+$D$10*(1-$D$16)*$D$15</f>
         <v/>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="21">
         <f>$E$10*$E$16+$E$10*(1-$E$16)*$E$15</f>
         <v/>
       </c>
@@ -8539,7 +9325,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>IVA recuperável na melhor hipótese</t>
         </is>
@@ -8549,22 +9335,22 @@
           <t>D_MELHOR</t>
         </is>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="23">
         <f>MAX($C$17,$C$18)</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="23">
         <f>MAX($D$17,$D$18)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="23">
         <f>MAX($E$17,$E$18)</f>
         <v/>
       </c>
       <c r="F19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>IVA perdido na via 4</t>
         </is>
@@ -8574,22 +9360,22 @@
           <t>P_MISTO</t>
         </is>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="23">
         <f>$C$10-$C$19</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="23">
         <f>$D$10-$D$19</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="23">
         <f>$E$10-$E$19</f>
         <v/>
       </c>
       <c r="F20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Ganho de IVA atribuível à entrada do cônjuge</t>
         </is>
@@ -8599,15 +9385,15 @@
           <t>GANHO</t>
         </is>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="23">
         <f>$C$13-$C$20</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="23">
         <f>$D$13-$D$20</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="23">
         <f>$E$13-$E$20</f>
         <v/>
       </c>
@@ -8656,7 +9442,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Poupança de IVA nesse cenário</t>
         </is>
@@ -8666,16 +9452,16 @@
           <t>SENS_GAN</t>
         </is>
       </c>
-      <c r="C24" s="27">
-        <f>Inputs!$C$19*$C$23*(Parametros!$C$31-Parametros!$C$32)</f>
-        <v/>
-      </c>
-      <c r="D24" s="27">
-        <f>Inputs!$D$19*$D$23*(Parametros!$C$31-Parametros!$C$32)</f>
-        <v/>
-      </c>
-      <c r="E24" s="27">
-        <f>Inputs!$E$19*$E$23*(Parametros!$C$31-Parametros!$C$32)</f>
+      <c r="C24" s="23">
+        <f>Inputs!$C$23*$C$23*(Parametros!$C$32-Parametros!$C$33)</f>
+        <v/>
+      </c>
+      <c r="D24" s="23">
+        <f>Inputs!$D$23*$D$23*(Parametros!$C$32-Parametros!$C$33)</f>
+        <v/>
+      </c>
+      <c r="E24" s="23">
+        <f>Inputs!$E$23*$E$23*(Parametros!$C$32-Parametros!$C$33)</f>
         <v/>
       </c>
       <c r="F24" s="16" t="inlineStr"/>
@@ -8703,26 +9489,26 @@
           <t>C_CORR</t>
         </is>
       </c>
-      <c r="C26" s="23">
-        <f>Inputs!$C$12+Inputs!$C$13+Inputs!$C$14</f>
-        <v/>
-      </c>
-      <c r="D26" s="23">
-        <f>Inputs!$D$12+Inputs!$D$13+Inputs!$D$14</f>
-        <v/>
-      </c>
-      <c r="E26" s="23">
-        <f>Inputs!$E$12+Inputs!$E$13+Inputs!$E$14</f>
+      <c r="C26" s="28">
+        <f>Inputs!$C$17+Inputs!$C$18+Inputs!$C$19</f>
+        <v/>
+      </c>
+      <c r="D26" s="28">
+        <f>Inputs!$D$17+Inputs!$D$18+Inputs!$D$19</f>
+        <v/>
+      </c>
+      <c r="E26" s="28">
+        <f>Inputs!$E$17+Inputs!$E$18+Inputs!$E$19</f>
         <v/>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>Renda excluída: o arrendamento é isento salvo renúncia (art. 9.º n.º 29 CIVA). Honorários de fisioterapeutas excluídos: também isentos pelo art. 9.º n.º 1.</t>
+          <t>Renda paga excluída: o arrendamento é isento salvo renúncia (art. 9.º n.º 29 CIVA). Honorários de fisioterapeutas excluídos: também isentos pelo art. 9.º n.º 1.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>IVA anual suportado e não dedutível (vias 1 a 3)</t>
         </is>
@@ -8732,16 +9518,16 @@
           <t>C_IVA</t>
         </is>
       </c>
-      <c r="C27" s="27">
-        <f>$C$26*Parametros!$C$31</f>
-        <v/>
-      </c>
-      <c r="D27" s="27">
-        <f>$D$26*Parametros!$C$31</f>
-        <v/>
-      </c>
-      <c r="E27" s="27">
-        <f>$E$26*Parametros!$C$31</f>
+      <c r="C27" s="23">
+        <f>$C$26*Parametros!$C$32</f>
+        <v/>
+      </c>
+      <c r="D27" s="23">
+        <f>$D$26*Parametros!$C$32</f>
+        <v/>
+      </c>
+      <c r="E27" s="23">
+        <f>$E$26*Parametros!$C$32</f>
         <v/>
       </c>
       <c r="F27" s="16" t="inlineStr"/>
@@ -8838,19 +9624,19 @@
           <t>Caixa gerada pela atividade</t>
         </is>
       </c>
-      <c r="C6" s="23">
-        <f>V1_ENI_Simplificado!$C$33</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
+      <c r="C6" s="28">
+        <f>V1_ENI_Simplificado!$C$36</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
         <f>V2_ENI_ContOrg!$C$25</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="28">
         <f>V3_Soc_Transparente!$C$31</f>
         <v/>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="28">
         <f>V4_Soc_NaoTransparente!$C$39</f>
         <v/>
       </c>
@@ -8866,19 +9652,19 @@
           <t>IRS imputável à atividade</t>
         </is>
       </c>
-      <c r="C7" s="23">
-        <f>V1_ENI_Simplificado!$C$30</f>
-        <v/>
-      </c>
-      <c r="D7" s="23">
+      <c r="C7" s="28">
+        <f>V1_ENI_Simplificado!$C$33</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
         <f>V2_ENI_ContOrg!$C$22</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="28">
         <f>V3_Soc_Transparente!$C$28</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="28">
         <f>V4_Soc_NaoTransparente!$C$35</f>
         <v/>
       </c>
@@ -8890,19 +9676,19 @@
           <t>Segurança Social (todas as componentes)</t>
         </is>
       </c>
-      <c r="C8" s="23">
-        <f>V1_ENI_Simplificado!$C$20</f>
-        <v/>
-      </c>
-      <c r="D8" s="23">
+      <c r="C8" s="28">
+        <f>V1_ENI_Simplificado!$C$23</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
         <f>V2_ENI_ContOrg!$C$13</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="28">
         <f>V3_Soc_Transparente!$C$18+V3_Soc_Transparente!$C$12</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="28">
         <f>V4_Soc_NaoTransparente!$C$37+V4_Soc_NaoTransparente!$C$13</f>
         <v/>
       </c>
@@ -8918,19 +9704,19 @@
           <t>IRC, derrama e tributações autónomas</t>
         </is>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="28">
         <f>V3_Soc_Transparente!$C$14+V3_Soc_Transparente!$C$15</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="28">
         <f>V4_Soc_NaoTransparente!$C$15+V4_Soc_NaoTransparente!$C$16+V4_Soc_NaoTransparente!$C$17</f>
         <v/>
       </c>
@@ -8942,43 +9728,43 @@
           <t>Imposto sobre a distribuição</t>
         </is>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="28">
         <f>V4_Soc_NaoTransparente!$C$27</f>
         <v/>
       </c>
       <c r="G10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>TOTAL DE IMPOSTOS E CONTRIBUIÇÕES</t>
         </is>
       </c>
-      <c r="C11" s="27">
-        <f>V1_ENI_Simplificado!$C$34</f>
-        <v/>
-      </c>
-      <c r="D11" s="27">
+      <c r="C11" s="23">
+        <f>V1_ENI_Simplificado!$C$37</f>
+        <v/>
+      </c>
+      <c r="D11" s="23">
         <f>V2_ENI_ContOrg!$C$26</f>
         <v/>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="23">
         <f>V3_Soc_Transparente!$C$32</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="23">
         <f>V4_Soc_NaoTransparente!$C$40</f>
         <v/>
       </c>
@@ -8990,19 +9776,19 @@
           <t>Taxa de esforço sobre a caixa gerada</t>
         </is>
       </c>
-      <c r="C12" s="24">
-        <f>V1_ENI_Simplificado!$C$35</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
+      <c r="C12" s="29">
+        <f>V1_ENI_Simplificado!$C$38</f>
+        <v/>
+      </c>
+      <c r="D12" s="29">
         <f>V2_ENI_ContOrg!$C$27</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="29">
         <f>V3_Soc_Transparente!$C$33</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="29">
         <f>V4_Soc_NaoTransparente!$C$41</f>
         <v/>
       </c>
@@ -9014,19 +9800,19 @@
           <t>Valor retido na sociedade</t>
         </is>
       </c>
-      <c r="C13" s="23">
-        <f>V1_ENI_Simplificado!$C$36</f>
-        <v/>
-      </c>
-      <c r="D13" s="23">
+      <c r="C13" s="28">
+        <f>V1_ENI_Simplificado!$C$39</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
         <f>V2_ENI_ContOrg!$C$28</f>
         <v/>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="28">
         <f>V3_Soc_Transparente!$C$34</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="28">
         <f>V4_Soc_NaoTransparente!$C$42</f>
         <v/>
       </c>
@@ -9042,43 +9828,43 @@
           <t>Valor atribuído ao cônjuge</t>
         </is>
       </c>
-      <c r="C14" s="23">
-        <f>V1_ENI_Simplificado!$C$37</f>
-        <v/>
-      </c>
-      <c r="D14" s="23">
+      <c r="C14" s="28">
+        <f>V1_ENI_Simplificado!$C$40</f>
+        <v/>
+      </c>
+      <c r="D14" s="28">
         <f>V2_ENI_ContOrg!$C$29</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="28">
         <f>V3_Soc_Transparente!$C$35</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="28">
         <f>V4_Soc_NaoTransparente!$C$43</f>
         <v/>
       </c>
       <c r="G14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA A SÓCIA</t>
         </is>
       </c>
-      <c r="C15" s="27">
-        <f>V1_ENI_Simplificado!$C$38</f>
-        <v/>
-      </c>
-      <c r="D15" s="27">
+      <c r="C15" s="23">
+        <f>V1_ENI_Simplificado!$C$41</f>
+        <v/>
+      </c>
+      <c r="D15" s="23">
         <f>V2_ENI_ContOrg!$C$30</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="23">
         <f>V3_Soc_Transparente!$C$36</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="23">
         <f>V4_Soc_NaoTransparente!$C$44</f>
         <v/>
       </c>
@@ -9089,24 +9875,24 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA O AGREGADO</t>
         </is>
       </c>
-      <c r="C16" s="27">
-        <f>V1_ENI_Simplificado!$C$39</f>
-        <v/>
-      </c>
-      <c r="D16" s="27">
+      <c r="C16" s="23">
+        <f>V1_ENI_Simplificado!$C$42</f>
+        <v/>
+      </c>
+      <c r="D16" s="23">
         <f>V2_ENI_ContOrg!$C$31</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="23">
         <f>V3_Soc_Transparente!$C$37</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="23">
         <f>V4_Soc_NaoTransparente!$C$45</f>
         <v/>
       </c>
@@ -9118,36 +9904,36 @@
           <t>Diferencial face à via 1 (líquido para a sócia)</t>
         </is>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="21">
         <f>C15-$C$15</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="21">
         <f>D15-$C$15</f>
         <v/>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="21">
         <f>E15-$C$15</f>
         <v/>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="21">
         <f>F15-$C$15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Via com maior líquido para a sócia</t>
         </is>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="25">
         <f>INDEX($C$5:$F$5,1,MATCH(MAX($C$15:$F$15),$C$15:$F$15,0))</f>
         <v/>
       </c>
-      <c r="D18" s="31" t="n"/>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="33" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -9201,19 +9987,19 @@
           <t>Caixa gerada pela atividade</t>
         </is>
       </c>
-      <c r="C23" s="23">
-        <f>V1_ENI_Simplificado!$D$33</f>
-        <v/>
-      </c>
-      <c r="D23" s="23">
+      <c r="C23" s="28">
+        <f>V1_ENI_Simplificado!$D$36</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
         <f>V2_ENI_ContOrg!$D$25</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="28">
         <f>V3_Soc_Transparente!$D$31</f>
         <v/>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="28">
         <f>V4_Soc_NaoTransparente!$D$39</f>
         <v/>
       </c>
@@ -9229,19 +10015,19 @@
           <t>IRS imputável à atividade</t>
         </is>
       </c>
-      <c r="C24" s="23">
-        <f>V1_ENI_Simplificado!$D$30</f>
-        <v/>
-      </c>
-      <c r="D24" s="23">
+      <c r="C24" s="28">
+        <f>V1_ENI_Simplificado!$D$33</f>
+        <v/>
+      </c>
+      <c r="D24" s="28">
         <f>V2_ENI_ContOrg!$D$22</f>
         <v/>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="28">
         <f>V3_Soc_Transparente!$D$28</f>
         <v/>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="28">
         <f>V4_Soc_NaoTransparente!$D$35</f>
         <v/>
       </c>
@@ -9253,19 +10039,19 @@
           <t>Segurança Social (todas as componentes)</t>
         </is>
       </c>
-      <c r="C25" s="23">
-        <f>V1_ENI_Simplificado!$D$20</f>
-        <v/>
-      </c>
-      <c r="D25" s="23">
+      <c r="C25" s="28">
+        <f>V1_ENI_Simplificado!$D$23</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
         <f>V2_ENI_ContOrg!$D$13</f>
         <v/>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="28">
         <f>V3_Soc_Transparente!$D$18+V3_Soc_Transparente!$D$12</f>
         <v/>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="28">
         <f>V4_Soc_NaoTransparente!$D$37+V4_Soc_NaoTransparente!$D$13</f>
         <v/>
       </c>
@@ -9281,19 +10067,19 @@
           <t>IRC, derrama e tributações autónomas</t>
         </is>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="28">
         <f>V3_Soc_Transparente!$D$14+V3_Soc_Transparente!$D$15</f>
         <v/>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="28">
         <f>V4_Soc_NaoTransparente!$D$15+V4_Soc_NaoTransparente!$D$16+V4_Soc_NaoTransparente!$D$17</f>
         <v/>
       </c>
@@ -9305,43 +10091,43 @@
           <t>Imposto sobre a distribuição</t>
         </is>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="28">
         <f>V4_Soc_NaoTransparente!$D$27</f>
         <v/>
       </c>
       <c r="G27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>TOTAL DE IMPOSTOS E CONTRIBUIÇÕES</t>
         </is>
       </c>
-      <c r="C28" s="27">
-        <f>V1_ENI_Simplificado!$D$34</f>
-        <v/>
-      </c>
-      <c r="D28" s="27">
+      <c r="C28" s="23">
+        <f>V1_ENI_Simplificado!$D$37</f>
+        <v/>
+      </c>
+      <c r="D28" s="23">
         <f>V2_ENI_ContOrg!$D$26</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="23">
         <f>V3_Soc_Transparente!$D$32</f>
         <v/>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="23">
         <f>V4_Soc_NaoTransparente!$D$40</f>
         <v/>
       </c>
@@ -9353,19 +10139,19 @@
           <t>Taxa de esforço sobre a caixa gerada</t>
         </is>
       </c>
-      <c r="C29" s="24">
-        <f>V1_ENI_Simplificado!$D$35</f>
-        <v/>
-      </c>
-      <c r="D29" s="24">
+      <c r="C29" s="29">
+        <f>V1_ENI_Simplificado!$D$38</f>
+        <v/>
+      </c>
+      <c r="D29" s="29">
         <f>V2_ENI_ContOrg!$D$27</f>
         <v/>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="29">
         <f>V3_Soc_Transparente!$D$33</f>
         <v/>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="29">
         <f>V4_Soc_NaoTransparente!$D$41</f>
         <v/>
       </c>
@@ -9377,19 +10163,19 @@
           <t>Valor retido na sociedade</t>
         </is>
       </c>
-      <c r="C30" s="23">
-        <f>V1_ENI_Simplificado!$D$36</f>
-        <v/>
-      </c>
-      <c r="D30" s="23">
+      <c r="C30" s="28">
+        <f>V1_ENI_Simplificado!$D$39</f>
+        <v/>
+      </c>
+      <c r="D30" s="28">
         <f>V2_ENI_ContOrg!$D$28</f>
         <v/>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="28">
         <f>V3_Soc_Transparente!$D$34</f>
         <v/>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="28">
         <f>V4_Soc_NaoTransparente!$D$42</f>
         <v/>
       </c>
@@ -9405,43 +10191,43 @@
           <t>Valor atribuído ao cônjuge</t>
         </is>
       </c>
-      <c r="C31" s="23">
-        <f>V1_ENI_Simplificado!$D$37</f>
-        <v/>
-      </c>
-      <c r="D31" s="23">
+      <c r="C31" s="28">
+        <f>V1_ENI_Simplificado!$D$40</f>
+        <v/>
+      </c>
+      <c r="D31" s="28">
         <f>V2_ENI_ContOrg!$D$29</f>
         <v/>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="28">
         <f>V3_Soc_Transparente!$D$35</f>
         <v/>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="28">
         <f>V4_Soc_NaoTransparente!$D$43</f>
         <v/>
       </c>
       <c r="G31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA A SÓCIA</t>
         </is>
       </c>
-      <c r="C32" s="27">
-        <f>V1_ENI_Simplificado!$D$38</f>
-        <v/>
-      </c>
-      <c r="D32" s="27">
+      <c r="C32" s="23">
+        <f>V1_ENI_Simplificado!$D$41</f>
+        <v/>
+      </c>
+      <c r="D32" s="23">
         <f>V2_ENI_ContOrg!$D$30</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="23">
         <f>V3_Soc_Transparente!$D$36</f>
         <v/>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="23">
         <f>V4_Soc_NaoTransparente!$D$44</f>
         <v/>
       </c>
@@ -9452,24 +10238,24 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA O AGREGADO</t>
         </is>
       </c>
-      <c r="C33" s="27">
-        <f>V1_ENI_Simplificado!$D$39</f>
-        <v/>
-      </c>
-      <c r="D33" s="27">
+      <c r="C33" s="23">
+        <f>V1_ENI_Simplificado!$D$42</f>
+        <v/>
+      </c>
+      <c r="D33" s="23">
         <f>V2_ENI_ContOrg!$D$31</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="23">
         <f>V3_Soc_Transparente!$D$37</f>
         <v/>
       </c>
-      <c r="F33" s="27">
+      <c r="F33" s="23">
         <f>V4_Soc_NaoTransparente!$D$45</f>
         <v/>
       </c>
@@ -9481,36 +10267,36 @@
           <t>Diferencial face à via 1 (líquido para a sócia)</t>
         </is>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="21">
         <f>C32-$C$32</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="21">
         <f>D32-$C$32</f>
         <v/>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="21">
         <f>E32-$C$32</f>
         <v/>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="21">
         <f>F32-$C$32</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Via com maior líquido para a sócia</t>
         </is>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="25">
         <f>INDEX($C$22:$F$22,1,MATCH(MAX($C$32:$F$32),$C$32:$F$32,0))</f>
         <v/>
       </c>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="33" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -9564,19 +10350,19 @@
           <t>Caixa gerada pela atividade</t>
         </is>
       </c>
-      <c r="C40" s="23">
-        <f>V1_ENI_Simplificado!$E$33</f>
-        <v/>
-      </c>
-      <c r="D40" s="23">
+      <c r="C40" s="28">
+        <f>V1_ENI_Simplificado!$E$36</f>
+        <v/>
+      </c>
+      <c r="D40" s="28">
         <f>V2_ENI_ContOrg!$E$25</f>
         <v/>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="28">
         <f>V3_Soc_Transparente!$E$31</f>
         <v/>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="28">
         <f>V4_Soc_NaoTransparente!$E$39</f>
         <v/>
       </c>
@@ -9592,19 +10378,19 @@
           <t>IRS imputável à atividade</t>
         </is>
       </c>
-      <c r="C41" s="23">
-        <f>V1_ENI_Simplificado!$E$30</f>
-        <v/>
-      </c>
-      <c r="D41" s="23">
+      <c r="C41" s="28">
+        <f>V1_ENI_Simplificado!$E$33</f>
+        <v/>
+      </c>
+      <c r="D41" s="28">
         <f>V2_ENI_ContOrg!$E$22</f>
         <v/>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="28">
         <f>V3_Soc_Transparente!$E$28</f>
         <v/>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="28">
         <f>V4_Soc_NaoTransparente!$E$35</f>
         <v/>
       </c>
@@ -9616,19 +10402,19 @@
           <t>Segurança Social (todas as componentes)</t>
         </is>
       </c>
-      <c r="C42" s="23">
-        <f>V1_ENI_Simplificado!$E$20</f>
-        <v/>
-      </c>
-      <c r="D42" s="23">
+      <c r="C42" s="28">
+        <f>V1_ENI_Simplificado!$E$23</f>
+        <v/>
+      </c>
+      <c r="D42" s="28">
         <f>V2_ENI_ContOrg!$E$13</f>
         <v/>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="28">
         <f>V3_Soc_Transparente!$E$18+V3_Soc_Transparente!$E$12</f>
         <v/>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="28">
         <f>V4_Soc_NaoTransparente!$E$37+V4_Soc_NaoTransparente!$E$13</f>
         <v/>
       </c>
@@ -9644,19 +10430,19 @@
           <t>IRC, derrama e tributações autónomas</t>
         </is>
       </c>
-      <c r="C43" s="23">
+      <c r="C43" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="28">
         <f>V3_Soc_Transparente!$E$14+V3_Soc_Transparente!$E$15</f>
         <v/>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="28">
         <f>V4_Soc_NaoTransparente!$E$15+V4_Soc_NaoTransparente!$E$16+V4_Soc_NaoTransparente!$E$17</f>
         <v/>
       </c>
@@ -9668,43 +10454,43 @@
           <t>Imposto sobre a distribuição</t>
         </is>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="28">
         <f>0</f>
         <v/>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="28">
         <f>V4_Soc_NaoTransparente!$E$27</f>
         <v/>
       </c>
       <c r="G44" s="16" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>TOTAL DE IMPOSTOS E CONTRIBUIÇÕES</t>
         </is>
       </c>
-      <c r="C45" s="27">
-        <f>V1_ENI_Simplificado!$E$34</f>
-        <v/>
-      </c>
-      <c r="D45" s="27">
+      <c r="C45" s="23">
+        <f>V1_ENI_Simplificado!$E$37</f>
+        <v/>
+      </c>
+      <c r="D45" s="23">
         <f>V2_ENI_ContOrg!$E$26</f>
         <v/>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="23">
         <f>V3_Soc_Transparente!$E$32</f>
         <v/>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="23">
         <f>V4_Soc_NaoTransparente!$E$40</f>
         <v/>
       </c>
@@ -9716,19 +10502,19 @@
           <t>Taxa de esforço sobre a caixa gerada</t>
         </is>
       </c>
-      <c r="C46" s="24">
-        <f>V1_ENI_Simplificado!$E$35</f>
-        <v/>
-      </c>
-      <c r="D46" s="24">
+      <c r="C46" s="29">
+        <f>V1_ENI_Simplificado!$E$38</f>
+        <v/>
+      </c>
+      <c r="D46" s="29">
         <f>V2_ENI_ContOrg!$E$27</f>
         <v/>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="29">
         <f>V3_Soc_Transparente!$E$33</f>
         <v/>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="29">
         <f>V4_Soc_NaoTransparente!$E$41</f>
         <v/>
       </c>
@@ -9740,19 +10526,19 @@
           <t>Valor retido na sociedade</t>
         </is>
       </c>
-      <c r="C47" s="23">
-        <f>V1_ENI_Simplificado!$E$36</f>
-        <v/>
-      </c>
-      <c r="D47" s="23">
+      <c r="C47" s="28">
+        <f>V1_ENI_Simplificado!$E$39</f>
+        <v/>
+      </c>
+      <c r="D47" s="28">
         <f>V2_ENI_ContOrg!$E$28</f>
         <v/>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="28">
         <f>V3_Soc_Transparente!$E$34</f>
         <v/>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="28">
         <f>V4_Soc_NaoTransparente!$E$42</f>
         <v/>
       </c>
@@ -9768,43 +10554,43 @@
           <t>Valor atribuído ao cônjuge</t>
         </is>
       </c>
-      <c r="C48" s="23">
-        <f>V1_ENI_Simplificado!$E$37</f>
-        <v/>
-      </c>
-      <c r="D48" s="23">
+      <c r="C48" s="28">
+        <f>V1_ENI_Simplificado!$E$40</f>
+        <v/>
+      </c>
+      <c r="D48" s="28">
         <f>V2_ENI_ContOrg!$E$29</f>
         <v/>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="28">
         <f>V3_Soc_Transparente!$E$35</f>
         <v/>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="28">
         <f>V4_Soc_NaoTransparente!$E$43</f>
         <v/>
       </c>
       <c r="G48" s="16" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA A SÓCIA</t>
         </is>
       </c>
-      <c r="C49" s="27">
-        <f>V1_ENI_Simplificado!$E$38</f>
-        <v/>
-      </c>
-      <c r="D49" s="27">
+      <c r="C49" s="23">
+        <f>V1_ENI_Simplificado!$E$41</f>
+        <v/>
+      </c>
+      <c r="D49" s="23">
         <f>V2_ENI_ContOrg!$E$30</f>
         <v/>
       </c>
-      <c r="E49" s="27">
+      <c r="E49" s="23">
         <f>V3_Soc_Transparente!$E$36</f>
         <v/>
       </c>
-      <c r="F49" s="27">
+      <c r="F49" s="23">
         <f>V4_Soc_NaoTransparente!$E$44</f>
         <v/>
       </c>
@@ -9815,24 +10601,24 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>LÍQUIDO DISPONÍVEL PARA O AGREGADO</t>
         </is>
       </c>
-      <c r="C50" s="27">
-        <f>V1_ENI_Simplificado!$E$39</f>
-        <v/>
-      </c>
-      <c r="D50" s="27">
+      <c r="C50" s="23">
+        <f>V1_ENI_Simplificado!$E$42</f>
+        <v/>
+      </c>
+      <c r="D50" s="23">
         <f>V2_ENI_ContOrg!$E$31</f>
         <v/>
       </c>
-      <c r="E50" s="27">
+      <c r="E50" s="23">
         <f>V3_Soc_Transparente!$E$37</f>
         <v/>
       </c>
-      <c r="F50" s="27">
+      <c r="F50" s="23">
         <f>V4_Soc_NaoTransparente!$E$45</f>
         <v/>
       </c>
@@ -9844,36 +10630,36 @@
           <t>Diferencial face à via 1 (líquido para a sócia)</t>
         </is>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="21">
         <f>C49-$C$49</f>
         <v/>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="21">
         <f>D49-$C$49</f>
         <v/>
       </c>
-      <c r="E51" s="25">
+      <c r="E51" s="21">
         <f>E49-$C$49</f>
         <v/>
       </c>
-      <c r="F51" s="25">
+      <c r="F51" s="21">
         <f>F49-$C$49</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>Via com maior líquido para a sócia</t>
         </is>
       </c>
-      <c r="C52" s="30">
+      <c r="C52" s="25">
         <f>INDEX($C$39:$F$39,1,MATCH(MAX($C$49:$F$49),$C$49:$F$49,0))</f>
         <v/>
       </c>
-      <c r="D52" s="31" t="n"/>
-      <c r="E52" s="31" t="n"/>
-      <c r="F52" s="32" t="n"/>
+      <c r="D52" s="32" t="n"/>
+      <c r="E52" s="32" t="n"/>
+      <c r="F52" s="33" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -9891,5 +10677,6 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/01-modelo/M1_modelo_comparativo.xlsx
+++ b/01-modelo/M1_modelo_comparativo.xlsx
@@ -21,7 +21,9 @@
     <sheet name="BreakEven" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Espaco" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Validacao" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Alertas" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="RiscoLaboral" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Alertas" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Conjuge" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -598,7 +600,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Resultado líquido por nível de procura — 2 vs. 3 gabinetes</a:t>
+              <a:t>Break-even anual por peso dos colaboradores na receita</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -612,7 +614,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Espaco'!B34</f>
+              <f>'BreakEven'!C45</f>
             </strRef>
           </tx>
           <spPr>
@@ -630,21 +632,107 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Espaco'!$A$35:$A$50</f>
+              <f>'BreakEven'!$A$46:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Espaco'!$B$35:$B$50</f>
+              <f>'BreakEven'!$C$46:$C$54</f>
             </numRef>
           </val>
         </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>peso dos colaboradores</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>euros</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Resultado líquido por nível de procura — 2 vs. 3 gabinetes</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="0"/>
+          <order val="0"/>
           <tx>
             <strRef>
-              <f>'Espaco'!C34</f>
+              <f>'Espaco'!B40</f>
             </strRef>
           </tx>
           <spPr>
@@ -662,12 +750,44 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Espaco'!$A$35:$A$50</f>
+              <f>'Espaco'!$A$41:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Espaco'!$C$35:$C$50</f>
+              <f>'Espaco'!$B$41:$B$56</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Espaco'!C40</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Espaco'!$A$41:$A$56</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Espaco'!$C$41:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -791,6 +911,33 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>19</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1106,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1263,103 +1410,138 @@
     <row r="24" ht="28" customHeight="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Alertas — verificação de plausibilidade empresarial e semáforo global. Enquanto houver um alerta bloqueante ativo, nenhum número sai do ficheiro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Três break-even distintos, que nunca se misturam</t>
+          <t>RiscoLaboral — passivo contingente da requalificação dos colaboradores, e o mapa dos indícios do art. 12.º n.º 1 do Código do Trabalho. Dois deles verificam-se por natureza numa clínica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Conjuge — custo de complexidade da entrada do cônjuge: ganhos de um lado, custos do outro, e o que não é quantificável.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Break-even FISCAL (folha PontoViragem): a partir de que nível de custos reais uma estrutura fiscal passa a ser melhor do que outra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Break-even OPERACIONAL (folha BreakEven): a partir de que faturação a clínica cobre os custos.</t>
+          <t>Alertas — verificação de plausibilidade empresarial e semáforo global. Enquanto houver um alerta bloqueante ativo, nenhum número sai do ficheiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Três break-even distintos, que nunca se misturam</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>RENDIMENTO-ALVO (folha BreakEven): que faturação é precisa para a fundadora receber o que quer receber. Nunca usar a mesma palavra para os três numa frase dita à cliente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Convenções</t>
+          <t>Break-even FISCAL (folha PontoViragem): a partir de que nível de custos reais uma estrutura fiscal passa a ser melhor do que outra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Break-even OPERACIONAL (folha BreakEven): a partir de que faturação a clínica cobre os custos.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
+          <t>RENDIMENTO-ALVO (folha BreakEven): que faturação é precisa para a fundadora receber o que quer receber. Nunca usar a mesma palavra para os três numa frase dita à cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Convenções</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
           <t>Azul sobre amarelo = célula de preenchimento. Verde = ligação a outra folha. Preto = fórmula. Fundo laranja na folha Parâmetros = parâmetro por confirmar.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Percentagens guardadas como fração. Valores anuais, em euros, sem IVA salvo indicação.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Três decisões de modelação que são discutíveis e estão assumidas</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="41" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="35" ht="41" customHeight="1">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>1. A comparação entre vias usa o IRS diferencial (coleta do agregado com a atividade menos coleta sem a atividade), e não o IRS total. É o que torna as quatro vias comparáveis quando o cônjuge tem rendimento próprio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>2. O investimento inicial está fora da comparação anual e isolado numa linha de memória. Misturá-lo com o resultado corrente faria a via 1 parecer melhor do que é no ano 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>3. Nas vias societárias, o valor retido na sociedade é mostrado separado do líquido da sócia. Somar os dois responderia a uma pergunta que a cliente não fez.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>4. O modelo de colaboração é uma escolha única para todos os colaboradores. A ata admite modelos distintos por profissional; uma combinação exige correr o modelo com a faturação repartida. Registado em R1-30.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Reprodução</t>
+          <t>2. O investimento inicial está fora da comparação anual e isolado numa linha de memória. Misturá-lo com o resultado corrente faria a via 1 parecer melhor do que é no ano 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>3. Nas vias societárias, o valor retido na sociedade é mostrado separado do líquido da sócia. Somar os dois responderia a uma pergunta que a cliente não fez.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>4. O modelo de colaboração é uma escolha única para todos os colaboradores. A ata admite modelos distintos por profissional; uma combinação exige correr o modelo com a faturação repartida. Registado em R1-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Para quem é este trabalho</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="41" customHeight="1">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>A cliente final tem zero experiência empresarial e está a montar a primeira estrutura da vida dela, com arrendamento, obras e integração de pessoas. As consequências de a matemática não funcionar não são um relatório desatualizado — são dívida pessoal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="41" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Consequência prática para quem usar este modelo: toda a conclusão tem de acabar em unidades que a cliente controla — doentes por dia, euros por mês — e o cenário de baixa tem de ser apresentado em dinheiro, não só a recomendação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Reprodução</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Este ficheiro é gerado por build_m1.py. Alterações estruturais fazem-se no script e regenera-se; alterações de valores fazem-se nas células amarelas.</t>
         </is>
@@ -2641,7 +2823,7 @@
         <v/>
       </c>
       <c r="C8" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B8))-MAX(0,D8-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B8))-MAX(0,D8-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D8" s="28">
@@ -2649,7 +2831,7 @@
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C8+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C8+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$46:$B$54)*((C8+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$58:$B$59)*((C8+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C8+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C8+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$50:$B$58)*((C8+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$62:$B$63)*((C8+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F8" s="43">
@@ -2665,7 +2847,7 @@
         <v/>
       </c>
       <c r="I8" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G8+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G8+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$46:$B$54)*((G8+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$58:$B$59)*((G8+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G8+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G8+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$50:$B$58)*((G8+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$62:$B$63)*((G8+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J8" s="43">
@@ -2690,7 +2872,7 @@
         <v/>
       </c>
       <c r="C9" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B9))-MAX(0,D9-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B9))-MAX(0,D9-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D9" s="28">
@@ -2698,7 +2880,7 @@
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C9+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C9+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$46:$B$54)*((C9+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$58:$B$59)*((C9+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C9+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C9+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$50:$B$58)*((C9+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$62:$B$63)*((C9+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F9" s="43">
@@ -2714,7 +2896,7 @@
         <v/>
       </c>
       <c r="I9" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G9+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G9+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$46:$B$54)*((G9+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$58:$B$59)*((G9+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G9+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G9+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$50:$B$58)*((G9+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$62:$B$63)*((G9+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J9" s="43">
@@ -2739,7 +2921,7 @@
         <v/>
       </c>
       <c r="C10" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B10))-MAX(0,D10-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B10))-MAX(0,D10-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D10" s="28">
@@ -2747,7 +2929,7 @@
         <v/>
       </c>
       <c r="E10" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C10+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C10+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$46:$B$54)*((C10+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$58:$B$59)*((C10+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C10+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C10+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$50:$B$58)*((C10+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$62:$B$63)*((C10+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F10" s="43">
@@ -2763,7 +2945,7 @@
         <v/>
       </c>
       <c r="I10" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G10+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G10+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$46:$B$54)*((G10+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$58:$B$59)*((G10+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G10+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G10+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$50:$B$58)*((G10+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$62:$B$63)*((G10+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J10" s="43">
@@ -2788,7 +2970,7 @@
         <v/>
       </c>
       <c r="C11" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B11))-MAX(0,D11-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B11))-MAX(0,D11-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D11" s="28">
@@ -2796,7 +2978,7 @@
         <v/>
       </c>
       <c r="E11" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C11+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C11+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$46:$B$54)*((C11+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$58:$B$59)*((C11+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C11+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C11+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$50:$B$58)*((C11+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$62:$B$63)*((C11+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F11" s="43">
@@ -2812,7 +2994,7 @@
         <v/>
       </c>
       <c r="I11" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G11+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G11+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$46:$B$54)*((G11+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$58:$B$59)*((G11+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G11+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G11+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$50:$B$58)*((G11+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$62:$B$63)*((G11+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J11" s="43">
@@ -2837,7 +3019,7 @@
         <v/>
       </c>
       <c r="C12" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B12))-MAX(0,D12-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B12))-MAX(0,D12-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D12" s="28">
@@ -2845,7 +3027,7 @@
         <v/>
       </c>
       <c r="E12" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C12+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C12+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$46:$B$54)*((C12+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$58:$B$59)*((C12+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C12+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C12+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$50:$B$58)*((C12+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$62:$B$63)*((C12+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F12" s="43">
@@ -2861,7 +3043,7 @@
         <v/>
       </c>
       <c r="I12" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G12+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G12+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$46:$B$54)*((G12+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$58:$B$59)*((G12+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G12+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G12+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$50:$B$58)*((G12+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$62:$B$63)*((G12+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J12" s="43">
@@ -2886,7 +3068,7 @@
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B13))-MAX(0,D13-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B13))-MAX(0,D13-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D13" s="28">
@@ -2894,7 +3076,7 @@
         <v/>
       </c>
       <c r="E13" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C13+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C13+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$46:$B$54)*((C13+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$58:$B$59)*((C13+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C13+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C13+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$50:$B$58)*((C13+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$62:$B$63)*((C13+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F13" s="43">
@@ -2910,7 +3092,7 @@
         <v/>
       </c>
       <c r="I13" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G13+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G13+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$46:$B$54)*((G13+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$58:$B$59)*((G13+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G13+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G13+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$50:$B$58)*((G13+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$62:$B$63)*((G13+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J13" s="43">
@@ -2935,7 +3117,7 @@
         <v/>
       </c>
       <c r="C14" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B14))-MAX(0,D14-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B14))-MAX(0,D14-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D14" s="28">
@@ -2943,7 +3125,7 @@
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C14+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C14+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$46:$B$54)*((C14+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$58:$B$59)*((C14+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C14+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C14+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$50:$B$58)*((C14+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$62:$B$63)*((C14+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F14" s="43">
@@ -2959,7 +3141,7 @@
         <v/>
       </c>
       <c r="I14" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G14+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G14+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$46:$B$54)*((G14+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$58:$B$59)*((G14+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G14+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G14+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$50:$B$58)*((G14+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$62:$B$63)*((G14+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J14" s="43">
@@ -2984,7 +3166,7 @@
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B15))-MAX(0,D15-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B15))-MAX(0,D15-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D15" s="28">
@@ -2992,7 +3174,7 @@
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C15+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C15+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$46:$B$54)*((C15+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$58:$B$59)*((C15+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C15+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C15+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$50:$B$58)*((C15+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$62:$B$63)*((C15+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F15" s="43">
@@ -3008,7 +3190,7 @@
         <v/>
       </c>
       <c r="I15" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G15+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G15+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$46:$B$54)*((G15+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$58:$B$59)*((G15+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G15+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G15+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$50:$B$58)*((G15+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$62:$B$63)*((G15+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J15" s="43">
@@ -3033,7 +3215,7 @@
         <v/>
       </c>
       <c r="C16" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B16))-MAX(0,D16-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B16))-MAX(0,D16-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D16" s="28">
@@ -3041,7 +3223,7 @@
         <v/>
       </c>
       <c r="E16" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C16+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C16+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$46:$B$54)*((C16+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$58:$B$59)*((C16+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C16+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C16+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$50:$B$58)*((C16+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$62:$B$63)*((C16+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F16" s="43">
@@ -3057,7 +3239,7 @@
         <v/>
       </c>
       <c r="I16" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G16+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G16+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$46:$B$54)*((G16+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$58:$B$59)*((G16+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G16+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G16+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$50:$B$58)*((G16+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$62:$B$63)*((G16+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J16" s="43">
@@ -3082,7 +3264,7 @@
         <v/>
       </c>
       <c r="C17" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B17))-MAX(0,D17-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B17))-MAX(0,D17-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D17" s="28">
@@ -3090,7 +3272,7 @@
         <v/>
       </c>
       <c r="E17" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C17+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C17+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$46:$B$54)*((C17+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$58:$B$59)*((C17+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C17+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C17+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$50:$B$58)*((C17+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$62:$B$63)*((C17+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F17" s="43">
@@ -3106,7 +3288,7 @@
         <v/>
       </c>
       <c r="I17" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G17+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G17+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$46:$B$54)*((G17+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$58:$B$59)*((G17+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G17+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G17+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$50:$B$58)*((G17+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$62:$B$63)*((G17+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J17" s="43">
@@ -3131,7 +3313,7 @@
         <v/>
       </c>
       <c r="C18" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B18))-MAX(0,D18-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B18))-MAX(0,D18-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D18" s="28">
@@ -3139,7 +3321,7 @@
         <v/>
       </c>
       <c r="E18" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C18+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C18+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$46:$B$54)*((C18+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$58:$B$59)*((C18+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C18+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C18+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$50:$B$58)*((C18+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$62:$B$63)*((C18+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F18" s="43">
@@ -3155,7 +3337,7 @@
         <v/>
       </c>
       <c r="I18" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G18+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G18+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$46:$B$54)*((G18+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$58:$B$59)*((G18+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G18+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G18+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$50:$B$58)*((G18+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$62:$B$63)*((G18+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J18" s="43">
@@ -3180,7 +3362,7 @@
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B19))-MAX(0,D19-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B19))-MAX(0,D19-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D19" s="28">
@@ -3188,7 +3370,7 @@
         <v/>
       </c>
       <c r="E19" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C19+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C19+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$46:$B$54)*((C19+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$58:$B$59)*((C19+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C19+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C19+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$50:$B$58)*((C19+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$62:$B$63)*((C19+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F19" s="43">
@@ -3204,7 +3386,7 @@
         <v/>
       </c>
       <c r="I19" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G19+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G19+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$46:$B$54)*((G19+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$58:$B$59)*((G19+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G19+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G19+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$50:$B$58)*((G19+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$62:$B$63)*((G19+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J19" s="43">
@@ -3229,7 +3411,7 @@
         <v/>
       </c>
       <c r="C20" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B20))-MAX(0,D20-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B20))-MAX(0,D20-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D20" s="28">
@@ -3237,7 +3419,7 @@
         <v/>
       </c>
       <c r="E20" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C20+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C20+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$46:$B$54)*((C20+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$58:$B$59)*((C20+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C20+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C20+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$50:$B$58)*((C20+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$62:$B$63)*((C20+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F20" s="43">
@@ -3253,7 +3435,7 @@
         <v/>
       </c>
       <c r="I20" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G20+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G20+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$46:$B$54)*((G20+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$58:$B$59)*((G20+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G20+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G20+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$50:$B$58)*((G20+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$62:$B$63)*((G20+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J20" s="43">
@@ -3278,7 +3460,7 @@
         <v/>
       </c>
       <c r="C21" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B21))-MAX(0,D21-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B21))-MAX(0,D21-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D21" s="28">
@@ -3286,7 +3468,7 @@
         <v/>
       </c>
       <c r="E21" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C21+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C21+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$46:$B$54)*((C21+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$58:$B$59)*((C21+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C21+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C21+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$50:$B$58)*((C21+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$62:$B$63)*((C21+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F21" s="43">
@@ -3302,7 +3484,7 @@
         <v/>
       </c>
       <c r="I21" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G21+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G21+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$46:$B$54)*((G21+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$58:$B$59)*((G21+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G21+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G21+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$50:$B$58)*((G21+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$62:$B$63)*((G21+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J21" s="43">
@@ -3327,7 +3509,7 @@
         <v/>
       </c>
       <c r="C22" s="28">
-        <f>$C$4*Parametros!$C$15+MAX(0,$C$4*Parametros!$C$16-(Parametros!$C$17+B22))-MAX(0,D22-$C$4*Parametros!$C$18)</f>
+        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B22))-MAX(0,D22-$C$4*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D22" s="28">
@@ -3335,7 +3517,7 @@
         <v/>
       </c>
       <c r="E22" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((C22+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((C22+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$46:$B$54)*((C22+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$58:$B$59)*((C22+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C22+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C22+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$50:$B$58)*((C22+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$62:$B$63)*((C22+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F22" s="43">
@@ -3351,7 +3533,7 @@
         <v/>
       </c>
       <c r="I22" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$46:$B$54)*(((G22+$C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$58:$B$59)*(((G22+$C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$46:$B$54)*((G22+$C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$58:$B$59)*((G22+$C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$46:$B$54)*((($C$5)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$58:$B$59)*((($C$5)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT((($C$5)&gt;Parametros!$B$46:$B$54)*(($C$5)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$5)&gt;Parametros!$B$58:$B$59)*(($C$5)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G22+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G22+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$50:$B$58)*((G22+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$62:$B$63)*((G22+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="J22" s="43">
@@ -3417,7 +3599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3924,7 +4106,7 @@
         <v/>
       </c>
       <c r="D23" s="28">
-        <f>A23*Parametros!$C$15+MAX(0,A23*Parametros!$C$16-B23)-MAX(0,E23-A23*Parametros!$C$18)</f>
+        <f>A23*Parametros!$C$19+MAX(0,A23*Parametros!$C$20-B23)-MAX(0,E23-A23*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E23" s="28">
@@ -3932,7 +4114,7 @@
         <v/>
       </c>
       <c r="F23" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D23+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D23+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D23+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D23+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D23+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D23+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D23+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D23+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D23+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D23+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D23+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D23+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D23+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D23+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D23+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D23+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G23" s="43">
@@ -3940,15 +4122,15 @@
         <v/>
       </c>
       <c r="H23" s="28">
-        <f>MAX(0,A23-B23-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I23)</f>
+        <f>MAX(0,A23-B23-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I23)</f>
         <v/>
       </c>
       <c r="I23" s="28">
-        <f>MAX(MIN(MAX(A23-B23-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A23-B23-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J23" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H23+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H23+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H23+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H23+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H23+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H23+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H23+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H23+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H23+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H23+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H23+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H23+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H23+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H23+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H23+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H23+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K23" s="43">
@@ -3956,15 +4138,15 @@
         <v/>
       </c>
       <c r="L23" s="28">
-        <f>A23-B23-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A23-B23-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M23" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L23,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L23,0)</f>
         <v/>
       </c>
       <c r="N23" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M23+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M23+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M23+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M23+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M23+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M23+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M23+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M23+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M23+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M23+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M23+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M23+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M23+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M23+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M23+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M23+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O23" s="43">
@@ -3997,7 +4179,7 @@
         <v/>
       </c>
       <c r="D24" s="28">
-        <f>A24*Parametros!$C$15+MAX(0,A24*Parametros!$C$16-B24)-MAX(0,E24-A24*Parametros!$C$18)</f>
+        <f>A24*Parametros!$C$19+MAX(0,A24*Parametros!$C$20-B24)-MAX(0,E24-A24*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E24" s="28">
@@ -4005,7 +4187,7 @@
         <v/>
       </c>
       <c r="F24" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D24+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D24+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D24+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D24+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D24+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D24+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D24+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D24+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D24+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D24+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D24+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D24+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D24+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D24+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D24+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D24+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G24" s="43">
@@ -4013,15 +4195,15 @@
         <v/>
       </c>
       <c r="H24" s="28">
-        <f>MAX(0,A24-B24-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I24)</f>
+        <f>MAX(0,A24-B24-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I24)</f>
         <v/>
       </c>
       <c r="I24" s="28">
-        <f>MAX(MIN(MAX(A24-B24-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A24-B24-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J24" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H24+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H24+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H24+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H24+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H24+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H24+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H24+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H24+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H24+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H24+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H24+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H24+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H24+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H24+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H24+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H24+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K24" s="43">
@@ -4029,15 +4211,15 @@
         <v/>
       </c>
       <c r="L24" s="28">
-        <f>A24-B24-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A24-B24-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M24" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L24,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L24,0)</f>
         <v/>
       </c>
       <c r="N24" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M24+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M24+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M24+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M24+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M24+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M24+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M24+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M24+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M24+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M24+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M24+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M24+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M24+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M24+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M24+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M24+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O24" s="43">
@@ -4070,7 +4252,7 @@
         <v/>
       </c>
       <c r="D25" s="28">
-        <f>A25*Parametros!$C$15+MAX(0,A25*Parametros!$C$16-B25)-MAX(0,E25-A25*Parametros!$C$18)</f>
+        <f>A25*Parametros!$C$19+MAX(0,A25*Parametros!$C$20-B25)-MAX(0,E25-A25*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E25" s="28">
@@ -4078,7 +4260,7 @@
         <v/>
       </c>
       <c r="F25" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D25+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D25+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D25+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D25+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D25+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D25+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D25+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D25+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D25+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D25+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D25+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D25+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D25+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D25+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D25+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D25+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G25" s="43">
@@ -4086,15 +4268,15 @@
         <v/>
       </c>
       <c r="H25" s="28">
-        <f>MAX(0,A25-B25-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I25)</f>
+        <f>MAX(0,A25-B25-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I25)</f>
         <v/>
       </c>
       <c r="I25" s="28">
-        <f>MAX(MIN(MAX(A25-B25-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A25-B25-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J25" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H25+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H25+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H25+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H25+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H25+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H25+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H25+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H25+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H25+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H25+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H25+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H25+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H25+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H25+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H25+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H25+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K25" s="43">
@@ -4102,15 +4284,15 @@
         <v/>
       </c>
       <c r="L25" s="28">
-        <f>A25-B25-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A25-B25-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M25" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L25,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L25,0)</f>
         <v/>
       </c>
       <c r="N25" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M25+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M25+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M25+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M25+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M25+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M25+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M25+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M25+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M25+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M25+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M25+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M25+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M25+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M25+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M25+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M25+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O25" s="43">
@@ -4143,7 +4325,7 @@
         <v/>
       </c>
       <c r="D26" s="28">
-        <f>A26*Parametros!$C$15+MAX(0,A26*Parametros!$C$16-B26)-MAX(0,E26-A26*Parametros!$C$18)</f>
+        <f>A26*Parametros!$C$19+MAX(0,A26*Parametros!$C$20-B26)-MAX(0,E26-A26*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E26" s="28">
@@ -4151,7 +4333,7 @@
         <v/>
       </c>
       <c r="F26" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D26+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D26+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D26+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D26+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D26+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D26+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D26+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D26+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D26+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D26+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D26+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D26+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D26+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D26+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D26+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D26+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G26" s="43">
@@ -4159,15 +4341,15 @@
         <v/>
       </c>
       <c r="H26" s="28">
-        <f>MAX(0,A26-B26-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I26)</f>
+        <f>MAX(0,A26-B26-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I26)</f>
         <v/>
       </c>
       <c r="I26" s="28">
-        <f>MAX(MIN(MAX(A26-B26-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A26-B26-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J26" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H26+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H26+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H26+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H26+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H26+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H26+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H26+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H26+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H26+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H26+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H26+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H26+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H26+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H26+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H26+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H26+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K26" s="43">
@@ -4175,15 +4357,15 @@
         <v/>
       </c>
       <c r="L26" s="28">
-        <f>A26-B26-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A26-B26-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M26" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L26,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L26,0)</f>
         <v/>
       </c>
       <c r="N26" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M26+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M26+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M26+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M26+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M26+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M26+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M26+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M26+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M26+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M26+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M26+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M26+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M26+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M26+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M26+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M26+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O26" s="43">
@@ -4216,7 +4398,7 @@
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>A27*Parametros!$C$15+MAX(0,A27*Parametros!$C$16-B27)-MAX(0,E27-A27*Parametros!$C$18)</f>
+        <f>A27*Parametros!$C$19+MAX(0,A27*Parametros!$C$20-B27)-MAX(0,E27-A27*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E27" s="28">
@@ -4224,7 +4406,7 @@
         <v/>
       </c>
       <c r="F27" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D27+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D27+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D27+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D27+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D27+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D27+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D27+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D27+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D27+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D27+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D27+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D27+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D27+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D27+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D27+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D27+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G27" s="43">
@@ -4232,15 +4414,15 @@
         <v/>
       </c>
       <c r="H27" s="28">
-        <f>MAX(0,A27-B27-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I27)</f>
+        <f>MAX(0,A27-B27-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I27)</f>
         <v/>
       </c>
       <c r="I27" s="28">
-        <f>MAX(MIN(MAX(A27-B27-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A27-B27-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J27" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H27+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H27+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H27+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H27+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H27+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H27+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H27+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H27+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H27+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H27+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H27+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H27+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H27+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H27+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H27+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H27+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K27" s="43">
@@ -4248,15 +4430,15 @@
         <v/>
       </c>
       <c r="L27" s="28">
-        <f>A27-B27-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A27-B27-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M27" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L27,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L27,0)</f>
         <v/>
       </c>
       <c r="N27" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M27+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M27+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M27+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M27+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M27+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M27+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M27+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M27+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M27+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M27+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M27+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M27+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M27+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M27+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M27+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M27+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O27" s="43">
@@ -4289,7 +4471,7 @@
         <v/>
       </c>
       <c r="D28" s="28">
-        <f>A28*Parametros!$C$15+MAX(0,A28*Parametros!$C$16-B28)-MAX(0,E28-A28*Parametros!$C$18)</f>
+        <f>A28*Parametros!$C$19+MAX(0,A28*Parametros!$C$20-B28)-MAX(0,E28-A28*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E28" s="28">
@@ -4297,7 +4479,7 @@
         <v/>
       </c>
       <c r="F28" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D28+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D28+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D28+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D28+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D28+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D28+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D28+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D28+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D28+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D28+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D28+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D28+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D28+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D28+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D28+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D28+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G28" s="43">
@@ -4305,15 +4487,15 @@
         <v/>
       </c>
       <c r="H28" s="28">
-        <f>MAX(0,A28-B28-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I28)</f>
+        <f>MAX(0,A28-B28-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I28)</f>
         <v/>
       </c>
       <c r="I28" s="28">
-        <f>MAX(MIN(MAX(A28-B28-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A28-B28-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J28" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H28+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H28+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H28+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H28+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H28+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H28+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H28+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H28+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H28+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H28+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H28+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H28+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H28+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H28+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H28+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H28+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K28" s="43">
@@ -4321,15 +4503,15 @@
         <v/>
       </c>
       <c r="L28" s="28">
-        <f>A28-B28-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A28-B28-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M28" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L28,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L28,0)</f>
         <v/>
       </c>
       <c r="N28" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M28+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M28+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M28+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M28+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M28+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M28+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M28+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M28+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M28+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M28+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M28+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M28+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M28+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M28+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M28+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M28+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O28" s="43">
@@ -4362,7 +4544,7 @@
         <v/>
       </c>
       <c r="D29" s="28">
-        <f>A29*Parametros!$C$15+MAX(0,A29*Parametros!$C$16-B29)-MAX(0,E29-A29*Parametros!$C$18)</f>
+        <f>A29*Parametros!$C$19+MAX(0,A29*Parametros!$C$20-B29)-MAX(0,E29-A29*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E29" s="28">
@@ -4370,7 +4552,7 @@
         <v/>
       </c>
       <c r="F29" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D29+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D29+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D29+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D29+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D29+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D29+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D29+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D29+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D29+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D29+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D29+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D29+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D29+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D29+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D29+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D29+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G29" s="43">
@@ -4378,15 +4560,15 @@
         <v/>
       </c>
       <c r="H29" s="28">
-        <f>MAX(0,A29-B29-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I29)</f>
+        <f>MAX(0,A29-B29-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I29)</f>
         <v/>
       </c>
       <c r="I29" s="28">
-        <f>MAX(MIN(MAX(A29-B29-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A29-B29-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J29" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H29+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H29+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H29+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H29+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H29+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H29+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H29+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H29+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H29+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H29+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H29+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H29+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H29+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H29+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H29+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H29+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K29" s="43">
@@ -4394,15 +4576,15 @@
         <v/>
       </c>
       <c r="L29" s="28">
-        <f>A29-B29-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A29-B29-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M29" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L29,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L29,0)</f>
         <v/>
       </c>
       <c r="N29" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M29+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M29+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M29+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M29+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M29+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M29+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M29+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M29+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M29+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M29+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M29+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M29+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M29+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M29+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M29+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M29+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O29" s="43">
@@ -4435,7 +4617,7 @@
         <v/>
       </c>
       <c r="D30" s="28">
-        <f>A30*Parametros!$C$15+MAX(0,A30*Parametros!$C$16-B30)-MAX(0,E30-A30*Parametros!$C$18)</f>
+        <f>A30*Parametros!$C$19+MAX(0,A30*Parametros!$C$20-B30)-MAX(0,E30-A30*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E30" s="28">
@@ -4443,7 +4625,7 @@
         <v/>
       </c>
       <c r="F30" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D30+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D30+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D30+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D30+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D30+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D30+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D30+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D30+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D30+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D30+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D30+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D30+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D30+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D30+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D30+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D30+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G30" s="43">
@@ -4451,15 +4633,15 @@
         <v/>
       </c>
       <c r="H30" s="28">
-        <f>MAX(0,A30-B30-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I30)</f>
+        <f>MAX(0,A30-B30-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I30)</f>
         <v/>
       </c>
       <c r="I30" s="28">
-        <f>MAX(MIN(MAX(A30-B30-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A30-B30-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J30" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H30+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H30+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H30+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H30+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H30+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H30+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H30+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H30+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H30+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H30+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H30+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H30+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H30+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H30+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H30+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H30+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K30" s="43">
@@ -4467,15 +4649,15 @@
         <v/>
       </c>
       <c r="L30" s="28">
-        <f>A30-B30-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A30-B30-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M30" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L30,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L30,0)</f>
         <v/>
       </c>
       <c r="N30" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M30+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M30+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M30+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M30+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M30+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M30+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M30+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M30+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M30+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M30+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M30+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M30+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M30+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M30+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M30+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M30+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O30" s="43">
@@ -4508,7 +4690,7 @@
         <v/>
       </c>
       <c r="D31" s="28">
-        <f>A31*Parametros!$C$15+MAX(0,A31*Parametros!$C$16-B31)-MAX(0,E31-A31*Parametros!$C$18)</f>
+        <f>A31*Parametros!$C$19+MAX(0,A31*Parametros!$C$20-B31)-MAX(0,E31-A31*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E31" s="28">
@@ -4516,7 +4698,7 @@
         <v/>
       </c>
       <c r="F31" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D31+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D31+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D31+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D31+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D31+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D31+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D31+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D31+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D31+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D31+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D31+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D31+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D31+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D31+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D31+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D31+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G31" s="43">
@@ -4524,15 +4706,15 @@
         <v/>
       </c>
       <c r="H31" s="28">
-        <f>MAX(0,A31-B31-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I31)</f>
+        <f>MAX(0,A31-B31-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I31)</f>
         <v/>
       </c>
       <c r="I31" s="28">
-        <f>MAX(MIN(MAX(A31-B31-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A31-B31-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J31" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H31+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H31+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H31+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H31+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H31+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H31+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H31+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H31+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H31+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H31+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H31+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H31+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H31+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H31+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H31+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H31+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K31" s="43">
@@ -4540,15 +4722,15 @@
         <v/>
       </c>
       <c r="L31" s="28">
-        <f>A31-B31-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A31-B31-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M31" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L31,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L31,0)</f>
         <v/>
       </c>
       <c r="N31" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M31+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M31+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M31+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M31+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M31+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M31+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M31+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M31+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M31+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M31+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M31+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M31+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M31+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M31+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M31+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M31+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O31" s="43">
@@ -4581,7 +4763,7 @@
         <v/>
       </c>
       <c r="D32" s="28">
-        <f>A32*Parametros!$C$15+MAX(0,A32*Parametros!$C$16-B32)-MAX(0,E32-A32*Parametros!$C$18)</f>
+        <f>A32*Parametros!$C$19+MAX(0,A32*Parametros!$C$20-B32)-MAX(0,E32-A32*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E32" s="28">
@@ -4589,7 +4771,7 @@
         <v/>
       </c>
       <c r="F32" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D32+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D32+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D32+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D32+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D32+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D32+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D32+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D32+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D32+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D32+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D32+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D32+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D32+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D32+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D32+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D32+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G32" s="43">
@@ -4597,15 +4779,15 @@
         <v/>
       </c>
       <c r="H32" s="28">
-        <f>MAX(0,A32-B32-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I32)</f>
+        <f>MAX(0,A32-B32-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I32)</f>
         <v/>
       </c>
       <c r="I32" s="28">
-        <f>MAX(MIN(MAX(A32-B32-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A32-B32-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J32" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H32+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H32+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H32+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H32+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H32+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H32+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H32+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H32+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H32+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H32+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H32+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H32+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H32+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H32+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H32+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H32+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K32" s="43">
@@ -4613,15 +4795,15 @@
         <v/>
       </c>
       <c r="L32" s="28">
-        <f>A32-B32-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A32-B32-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M32" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L32,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L32,0)</f>
         <v/>
       </c>
       <c r="N32" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M32+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M32+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M32+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M32+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M32+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M32+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M32+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M32+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M32+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M32+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M32+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M32+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M32+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M32+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M32+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M32+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O32" s="43">
@@ -4654,7 +4836,7 @@
         <v/>
       </c>
       <c r="D33" s="28">
-        <f>A33*Parametros!$C$15+MAX(0,A33*Parametros!$C$16-B33)-MAX(0,E33-A33*Parametros!$C$18)</f>
+        <f>A33*Parametros!$C$19+MAX(0,A33*Parametros!$C$20-B33)-MAX(0,E33-A33*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E33" s="28">
@@ -4662,7 +4844,7 @@
         <v/>
       </c>
       <c r="F33" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D33+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D33+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D33+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D33+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D33+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D33+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D33+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D33+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D33+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D33+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D33+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D33+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D33+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D33+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D33+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D33+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G33" s="43">
@@ -4670,15 +4852,15 @@
         <v/>
       </c>
       <c r="H33" s="28">
-        <f>MAX(0,A33-B33-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I33)</f>
+        <f>MAX(0,A33-B33-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I33)</f>
         <v/>
       </c>
       <c r="I33" s="28">
-        <f>MAX(MIN(MAX(A33-B33-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A33-B33-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J33" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H33+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H33+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H33+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H33+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H33+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H33+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H33+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H33+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H33+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H33+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H33+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H33+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H33+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H33+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H33+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H33+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K33" s="43">
@@ -4686,15 +4868,15 @@
         <v/>
       </c>
       <c r="L33" s="28">
-        <f>A33-B33-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A33-B33-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M33" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L33,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L33,0)</f>
         <v/>
       </c>
       <c r="N33" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M33+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M33+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M33+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M33+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M33+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M33+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M33+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M33+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M33+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M33+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M33+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M33+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M33+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M33+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M33+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M33+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O33" s="43">
@@ -4727,7 +4909,7 @@
         <v/>
       </c>
       <c r="D34" s="28">
-        <f>A34*Parametros!$C$15+MAX(0,A34*Parametros!$C$16-B34)-MAX(0,E34-A34*Parametros!$C$18)</f>
+        <f>A34*Parametros!$C$19+MAX(0,A34*Parametros!$C$20-B34)-MAX(0,E34-A34*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E34" s="28">
@@ -4735,7 +4917,7 @@
         <v/>
       </c>
       <c r="F34" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D34+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D34+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D34+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D34+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D34+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D34+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D34+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D34+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D34+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D34+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D34+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D34+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D34+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D34+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D34+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D34+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G34" s="43">
@@ -4743,15 +4925,15 @@
         <v/>
       </c>
       <c r="H34" s="28">
-        <f>MAX(0,A34-B34-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I34)</f>
+        <f>MAX(0,A34-B34-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I34)</f>
         <v/>
       </c>
       <c r="I34" s="28">
-        <f>MAX(MIN(MAX(A34-B34-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A34-B34-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J34" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H34+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H34+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H34+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H34+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H34+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H34+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H34+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H34+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H34+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H34+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H34+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H34+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H34+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H34+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H34+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H34+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K34" s="43">
@@ -4759,15 +4941,15 @@
         <v/>
       </c>
       <c r="L34" s="28">
-        <f>A34-B34-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A34-B34-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M34" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L34,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L34,0)</f>
         <v/>
       </c>
       <c r="N34" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M34+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M34+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M34+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M34+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M34+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M34+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M34+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M34+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M34+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M34+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M34+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M34+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M34+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M34+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M34+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M34+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O34" s="43">
@@ -4800,7 +4982,7 @@
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>A35*Parametros!$C$15+MAX(0,A35*Parametros!$C$16-B35)-MAX(0,E35-A35*Parametros!$C$18)</f>
+        <f>A35*Parametros!$C$19+MAX(0,A35*Parametros!$C$20-B35)-MAX(0,E35-A35*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E35" s="28">
@@ -4808,7 +4990,7 @@
         <v/>
       </c>
       <c r="F35" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D35+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((D35+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((D35+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((D35+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((D35+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((D35+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((D35+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((D35+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D35+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D35+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D35+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D35+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D35+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D35+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D35+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D35+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="G35" s="43">
@@ -4816,15 +4998,15 @@
         <v/>
       </c>
       <c r="H35" s="28">
-        <f>MAX(0,A35-B35-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-I35)</f>
+        <f>MAX(0,A35-B35-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I35)</f>
         <v/>
       </c>
       <c r="I35" s="28">
-        <f>MAX(MIN(MAX(A35-B35-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A35-B35-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J35" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H35+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((H35+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((H35+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((H35+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((H35+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((H35+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((H35+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((H35+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H35+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H35+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H35+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H35+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H35+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H35+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H35+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H35+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="K35" s="43">
@@ -4832,15 +5014,15 @@
         <v/>
       </c>
       <c r="L35" s="28">
-        <f>A35-B35-(Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A35-B35-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M35" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$21,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L35,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L35,0)</f>
         <v/>
       </c>
       <c r="N35" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M35+Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((M35+Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((M35+Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((M35+Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((M35+Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((M35+Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((M35+Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((M35+Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$46:$B$54)*(((Inputs!$D$37)/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$58:$B$59)*(((Inputs!$D$37)/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$46:$B$54)*((Inputs!$D$37)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$58:$B$59)*((Inputs!$D$37)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M35+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M35+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M35+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M35+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M35+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M35+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M35+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M35+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="O35" s="43">
@@ -4893,20 +5075,270 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Como o break-even se move com o peso dos colaboradores</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+    </row>
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Quando a faturação vem da própria Dra. Júlia, quase toda ela é margem. Quando vem de um colaborador pago a uma percentagem da sessão, sobra a diferença. Esta tabela mostra o que acontece ao break-even à medida que o peso dos colaboradores sobe, mantendo a receita total constante. A subida não é proporcional: o break-even é os custos fixos a dividir pela margem, e quando a margem se aproxima de zero o break-even dispara para o infinito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Peso dos colaboradores na receita</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Margem de contribuição (%)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Break-even anual</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Break-even mensal</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Utilização necessária</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" s="37">
+        <f>1-Inputs!$D$23-A46*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C46" s="43">
+        <f>IF(B46&lt;=0,"não atinge",$D$10/B46)</f>
+        <v/>
+      </c>
+      <c r="D46" s="43">
+        <f>IF(B46&lt;=0,"não atinge",C46/12)</f>
+        <v/>
+      </c>
+      <c r="E46" s="37">
+        <f>IF(B46&lt;=0,"n/a",C46/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B47" s="37">
+        <f>1-Inputs!$D$23-A47*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C47" s="43">
+        <f>IF(B47&lt;=0,"não atinge",$D$10/B47)</f>
+        <v/>
+      </c>
+      <c r="D47" s="43">
+        <f>IF(B47&lt;=0,"não atinge",C47/12)</f>
+        <v/>
+      </c>
+      <c r="E47" s="37">
+        <f>IF(B47&lt;=0,"n/a",C47/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B48" s="37">
+        <f>1-Inputs!$D$23-A48*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C48" s="43">
+        <f>IF(B48&lt;=0,"não atinge",$D$10/B48)</f>
+        <v/>
+      </c>
+      <c r="D48" s="43">
+        <f>IF(B48&lt;=0,"não atinge",C48/12)</f>
+        <v/>
+      </c>
+      <c r="E48" s="37">
+        <f>IF(B48&lt;=0,"n/a",C48/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B49" s="37">
+        <f>1-Inputs!$D$23-A49*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C49" s="43">
+        <f>IF(B49&lt;=0,"não atinge",$D$10/B49)</f>
+        <v/>
+      </c>
+      <c r="D49" s="43">
+        <f>IF(B49&lt;=0,"não atinge",C49/12)</f>
+        <v/>
+      </c>
+      <c r="E49" s="37">
+        <f>IF(B49&lt;=0,"n/a",C49/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B50" s="37">
+        <f>1-Inputs!$D$23-A50*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C50" s="43">
+        <f>IF(B50&lt;=0,"não atinge",$D$10/B50)</f>
+        <v/>
+      </c>
+      <c r="D50" s="43">
+        <f>IF(B50&lt;=0,"não atinge",C50/12)</f>
+        <v/>
+      </c>
+      <c r="E50" s="37">
+        <f>IF(B50&lt;=0,"n/a",C50/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B51" s="37">
+        <f>1-Inputs!$D$23-A51*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C51" s="43">
+        <f>IF(B51&lt;=0,"não atinge",$D$10/B51)</f>
+        <v/>
+      </c>
+      <c r="D51" s="43">
+        <f>IF(B51&lt;=0,"não atinge",C51/12)</f>
+        <v/>
+      </c>
+      <c r="E51" s="37">
+        <f>IF(B51&lt;=0,"n/a",C51/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="42" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="B52" s="37">
+        <f>1-Inputs!$D$23-A52*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C52" s="43">
+        <f>IF(B52&lt;=0,"não atinge",$D$10/B52)</f>
+        <v/>
+      </c>
+      <c r="D52" s="43">
+        <f>IF(B52&lt;=0,"não atinge",C52/12)</f>
+        <v/>
+      </c>
+      <c r="E52" s="37">
+        <f>IF(B52&lt;=0,"n/a",C52/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B53" s="37">
+        <f>1-Inputs!$D$23-A53*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C53" s="43">
+        <f>IF(B53&lt;=0,"não atinge",$D$10/B53)</f>
+        <v/>
+      </c>
+      <c r="D53" s="43">
+        <f>IF(B53&lt;=0,"não atinge",C53/12)</f>
+        <v/>
+      </c>
+      <c r="E53" s="37">
+        <f>IF(B53&lt;=0,"n/a",C53/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B54" s="37">
+        <f>1-Inputs!$D$23-A54*Inputs!$D$12</f>
+        <v/>
+      </c>
+      <c r="C54" s="43">
+        <f>IF(B54&lt;=0,"não atinge",$D$10/B54)</f>
+        <v/>
+      </c>
+      <c r="D54" s="43">
+        <f>IF(B54&lt;=0,"não atinge",C54/12)</f>
+        <v/>
+      </c>
+      <c r="E54" s="37">
+        <f>IF(B54&lt;=0,"n/a",C54/(BreakEven!$D$14*Operacao!$D$21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>A ata regista, no ponto 6, que «se uma parte relevante da faturação corresponder a honorários de prestadores, a margem efetiva pode não justificar a alteração de estrutura». Esta tabela é essa frase em números — e mostra que o problema aparece muito antes de a margem chegar a zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>A via 4 não consta desta tabela: o líquido depende da política de distribuição e da opção de englobamento, que são decisões e não funções da faturação. Para a via 4, fixar essas alavancas na folha Inputs e ler o resultado na folha Comparativo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A21:R21"/>
-    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A58:R58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4916,7 +5348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5392,11 +5824,11 @@
         </is>
       </c>
       <c r="C26" s="28">
-        <f>($C$9+$C$10)*Parametros!$C$32</f>
+        <f>($C$9+$C$10)*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="D26" s="28">
-        <f>($D$9+$D$10)*Parametros!$C$32</f>
+        <f>($D$9+$D$10)*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="E26" s="17" t="inlineStr">
@@ -5500,7 +5932,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>A partir de que procura compensa o terceiro gabinete</t>
+          <t>O custo do degrau — se o terceiro gabinete não encher</t>
         </is>
       </c>
       <c r="B32" s="7" t="n"/>
@@ -5508,169 +5940,118 @@
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
     </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Custo fixo adicional anual da opção B</t>
+        </is>
+      </c>
+      <c r="C33" s="27">
+        <f>$D$22-$C$22</f>
+        <v/>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>Renda e condomínio a mais, todos os anos, independentemente de haver doentes para os ocupar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Custo do degrau, líquido de impostos</t>
+        </is>
+      </c>
+      <c r="C34" s="27">
+        <f>($D$22-$C$22)*(1-$C$16)</f>
+        <v/>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>É este o valor que a Dra. Júlia perde por ano se escolher três gabinetes e a procura não passar do que dois comportavam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Investimento adicional da opção B</t>
+        </is>
+      </c>
+      <c r="C35" s="27">
+        <f>$D$27-$C$27</f>
+        <v/>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>Obras, equipamento e IVA irrecuperável a mais, de uma só vez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Consultas anuais adicionais necessárias para o degrau se pagar</t>
+        </is>
+      </c>
+      <c r="C36" s="23">
+        <f>IF($C$13*(1-$C$14)&lt;=0,0,($D$22-$C$22)/($C$13*(1-$C$14)))</f>
+        <v/>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>Traduzido para a única unidade que a cliente controla: doentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>A partir de que procura compensa o terceiro gabinete</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>O eixo é a PROCURA, em consultas por ano — não a taxa de utilização. Comparar as duas opções à mesma percentagem de utilização daria automaticamente mais 50% de consultas à opção de três gabinetes, e a comparação não significaria nada. À mesma procura, cada opção atende o que a sua capacidade permite, e o terceiro gabinete só vale alguma coisa quando a procura ultrapassa a capacidade de dois.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Procura anual (consultas)</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Resultado líquido — 2 gabinetes</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Resultado líquido — 3 gabinetes</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Diferencial</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Viragem</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B35" s="28">
-        <f>(MIN(A35,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
-        <v/>
-      </c>
-      <c r="C35" s="28">
-        <f>(MIN(A35,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
-        <v/>
-      </c>
-      <c r="D35" s="43">
-        <f>C35-B35</f>
-        <v/>
-      </c>
-      <c r="E35" s="24">
-        <f>0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="38" t="n">
-        <v>1400</v>
-      </c>
-      <c r="B36" s="28">
-        <f>(MIN(A36,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
-        <v/>
-      </c>
-      <c r="C36" s="28">
-        <f>(MIN(A36,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
-        <v/>
-      </c>
-      <c r="D36" s="43">
-        <f>C36-B36</f>
-        <v/>
-      </c>
-      <c r="E36" s="24">
-        <f>IF(AND(D36&gt;=0,D35&lt;0),A36,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="38" t="n">
-        <v>1800</v>
-      </c>
-      <c r="B37" s="28">
-        <f>(MIN(A37,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
-        <v/>
-      </c>
-      <c r="C37" s="28">
-        <f>(MIN(A37,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
-        <v/>
-      </c>
-      <c r="D37" s="43">
-        <f>C37-B37</f>
-        <v/>
-      </c>
-      <c r="E37" s="24">
-        <f>IF(AND(D37&gt;=0,D36&lt;0),A37,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="38" t="n">
-        <v>2200</v>
-      </c>
-      <c r="B38" s="28">
-        <f>(MIN(A38,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
-        <v/>
-      </c>
-      <c r="C38" s="28">
-        <f>(MIN(A38,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
-        <v/>
-      </c>
-      <c r="D38" s="43">
-        <f>C38-B38</f>
-        <v/>
-      </c>
-      <c r="E38" s="24">
-        <f>IF(AND(D38&gt;=0,D37&lt;0),A38,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="38" t="n">
-        <v>2600</v>
-      </c>
-      <c r="B39" s="28">
-        <f>(MIN(A39,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
-        <v/>
-      </c>
-      <c r="C39" s="28">
-        <f>(MIN(A39,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
-        <v/>
-      </c>
-      <c r="D39" s="43">
-        <f>C39-B39</f>
-        <v/>
-      </c>
-      <c r="E39" s="24">
-        <f>IF(AND(D39&gt;=0,D38&lt;0),A39,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="38" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B40" s="28">
-        <f>(MIN(A40,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
-        <v/>
-      </c>
-      <c r="C40" s="28">
-        <f>(MIN(A40,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
-        <v/>
-      </c>
-      <c r="D40" s="43">
-        <f>C40-B40</f>
-        <v/>
-      </c>
-      <c r="E40" s="24">
-        <f>IF(AND(D40&gt;=0,D39&lt;0),A40,0)</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="38" t="n">
-        <v>3400</v>
+        <v>1000</v>
       </c>
       <c r="B41" s="28">
         <f>(MIN(A41,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5685,13 +6066,13 @@
         <v/>
       </c>
       <c r="E41" s="24">
-        <f>IF(AND(D41&gt;=0,D40&lt;0),A41,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="38" t="n">
-        <v>3800</v>
+        <v>1400</v>
       </c>
       <c r="B42" s="28">
         <f>(MIN(A42,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5712,7 +6093,7 @@
     </row>
     <row r="43">
       <c r="A43" s="38" t="n">
-        <v>4200</v>
+        <v>1800</v>
       </c>
       <c r="B43" s="28">
         <f>(MIN(A43,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5733,7 +6114,7 @@
     </row>
     <row r="44">
       <c r="A44" s="38" t="n">
-        <v>4600</v>
+        <v>2200</v>
       </c>
       <c r="B44" s="28">
         <f>(MIN(A44,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5754,7 +6135,7 @@
     </row>
     <row r="45">
       <c r="A45" s="38" t="n">
-        <v>5000</v>
+        <v>2600</v>
       </c>
       <c r="B45" s="28">
         <f>(MIN(A45,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5775,7 +6156,7 @@
     </row>
     <row r="46">
       <c r="A46" s="38" t="n">
-        <v>5400</v>
+        <v>3000</v>
       </c>
       <c r="B46" s="28">
         <f>(MIN(A46,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5796,7 +6177,7 @@
     </row>
     <row r="47">
       <c r="A47" s="38" t="n">
-        <v>5800</v>
+        <v>3400</v>
       </c>
       <c r="B47" s="28">
         <f>(MIN(A47,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5817,7 +6198,7 @@
     </row>
     <row r="48">
       <c r="A48" s="38" t="n">
-        <v>6200</v>
+        <v>3800</v>
       </c>
       <c r="B48" s="28">
         <f>(MIN(A48,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5838,7 +6219,7 @@
     </row>
     <row r="49">
       <c r="A49" s="38" t="n">
-        <v>6600</v>
+        <v>4200</v>
       </c>
       <c r="B49" s="28">
         <f>(MIN(A49,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5859,7 +6240,7 @@
     </row>
     <row r="50">
       <c r="A50" s="38" t="n">
-        <v>7000</v>
+        <v>4600</v>
       </c>
       <c r="B50" s="28">
         <f>(MIN(A50,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
@@ -5878,41 +6259,167 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="38" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B51" s="28">
+        <f>(MIN(A51,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
+        <v/>
+      </c>
+      <c r="C51" s="28">
+        <f>(MIN(A51,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
+        <v/>
+      </c>
+      <c r="D51" s="43">
+        <f>C51-B51</f>
+        <v/>
+      </c>
+      <c r="E51" s="24">
+        <f>IF(AND(D51&gt;=0,D50&lt;0),A51,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="38" t="n">
+        <v>5400</v>
+      </c>
+      <c r="B52" s="28">
+        <f>(MIN(A52,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
+        <v/>
+      </c>
+      <c r="C52" s="28">
+        <f>(MIN(A52,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
+        <v/>
+      </c>
+      <c r="D52" s="43">
+        <f>C52-B52</f>
+        <v/>
+      </c>
+      <c r="E52" s="24">
+        <f>IF(AND(D52&gt;=0,D51&lt;0),A52,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="38" t="n">
+        <v>5800</v>
+      </c>
+      <c r="B53" s="28">
+        <f>(MIN(A53,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
+        <v/>
+      </c>
+      <c r="C53" s="28">
+        <f>(MIN(A53,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
+        <v/>
+      </c>
+      <c r="D53" s="43">
+        <f>C53-B53</f>
+        <v/>
+      </c>
+      <c r="E53" s="24">
+        <f>IF(AND(D53&gt;=0,D52&lt;0),A53,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="38" t="n">
+        <v>6200</v>
+      </c>
+      <c r="B54" s="28">
+        <f>(MIN(A54,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
+        <v/>
+      </c>
+      <c r="C54" s="28">
+        <f>(MIN(A54,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
+        <v/>
+      </c>
+      <c r="D54" s="43">
+        <f>C54-B54</f>
+        <v/>
+      </c>
+      <c r="E54" s="24">
+        <f>IF(AND(D54&gt;=0,D53&lt;0),A54,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="38" t="n">
+        <v>6600</v>
+      </c>
+      <c r="B55" s="28">
+        <f>(MIN(A55,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
+        <v/>
+      </c>
+      <c r="C55" s="28">
+        <f>(MIN(A55,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
+        <v/>
+      </c>
+      <c r="D55" s="43">
+        <f>C55-B55</f>
+        <v/>
+      </c>
+      <c r="E55" s="24">
+        <f>IF(AND(D55&gt;=0,D54&lt;0),A55,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="38" t="n">
+        <v>7000</v>
+      </c>
+      <c r="B56" s="28">
+        <f>(MIN(A56,$C$18)*$C$13*(1-$C$14)-$C$22)*(1-$C$16)</f>
+        <v/>
+      </c>
+      <c r="C56" s="28">
+        <f>(MIN(A56,$D$18)*$D$13*(1-$D$14)-$D$22)*(1-$D$16)</f>
+        <v/>
+      </c>
+      <c r="D56" s="43">
+        <f>C56-B56</f>
+        <v/>
+      </c>
+      <c r="E56" s="24">
+        <f>IF(AND(D56&gt;=0,D55&lt;0),A56,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>O TERCEIRO GABINETE COMPENSA A PARTIR DE (consultas/ano)</t>
         </is>
       </c>
-      <c r="C52" s="23">
-        <f>IF(MAX(E35:E50)=0,"Nunca compensa no intervalo analisado",MAX(E35:E50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="C58" s="23">
+        <f>IF(MAX(E41:E56)=0,"Nunca compensa no intervalo analisado",MAX(E41:E56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
         <is>
           <t>…o que corresponde, no espaço de 2 gabinetes, a uma utilização de</t>
         </is>
       </c>
-      <c r="C53" s="25">
-        <f>IF(ISNUMBER($C$52),$C$52/$C$18,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="C59" s="25">
+        <f>IF(ISNUMBER($C$58),$C$58/$C$18,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>Consultas por dia úteis implícitas nesse ponto</t>
         </is>
       </c>
-      <c r="C54" s="21">
-        <f>IF(ISNUMBER($C$52),$C$52/Operacao!$D$7,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="C60" s="21">
+        <f>IF(ISNUMBER($C$58),$C$58/Operacao!$D$7,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>Leitura: abaixo do ponto de viragem, o terceiro gabinete é renda e obras a mais sem receita adicional — a opção de dois gabinetes ganha por diferença de custo fixo. Acima, a opção de dois perde consultas por falta de espaço e a de três recupera o custo. A pergunta a fazer à cliente não é qual espaço prefere: é quantos doentes por dia espera atender no fim do segundo ano. Resolução do varrimento: 400 consultas por ano. O ponto de viragem real situa-se algures no intervalo anterior ao indicado — refinar por interpolação se a decisão ficar perto do limite. Registado em R1-34.</t>
         </is>
@@ -5921,8 +6428,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A62:E62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6667,6 +7174,549 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>M1 — Requalificação laboral: passivo contingente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>A ata identificou o risco e ninguém lhe pôs um número. Este é o número. Se a relação com os fisioterapeutas for requalificada como contrato de trabalho, a clínica passa a dever contribuições retroativas sobre tudo o que lhes pagou, com juros e coima. É o único risco deste projeto capaz de destruir o plano inteiro de uma vez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Nota / norma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Exposição</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Honorários anuais pagos aos colaboradores</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="C6" s="35">
+        <f>Inputs!$C$44</f>
+        <v/>
+      </c>
+      <c r="D6" s="35">
+        <f>Inputs!$D$44</f>
+        <v/>
+      </c>
+      <c r="E6" s="35">
+        <f>Inputs!$E$44</f>
+        <v/>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Só existe exposição no modelo de prestação de serviços. Na cedência de sala o fluxo é o inverso e o risco é outro — o de a cedência ser requalificada como prestação de serviços.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Anos de exposição retroativa</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>ANOS</t>
+        </is>
+      </c>
+      <c r="C7" s="50">
+        <f>Parametros!$C$16</f>
+        <v/>
+      </c>
+      <c r="D7" s="50">
+        <f>Parametros!$C$16</f>
+        <v/>
+      </c>
+      <c r="E7" s="50">
+        <f>Parametros!$C$16</f>
+        <v/>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Prazo de prescrição das contribuições. A inspeção não olha só para o ano corrente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Base de incidência retroativa</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C8" s="27">
+        <f>$C$6*$C$7</f>
+        <v/>
+      </c>
+      <c r="D8" s="27">
+        <f>$D$6*$D$7</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>$E$6*$E$7</f>
+        <v/>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Assume honorários constantes ao longo do período. Se crescerem, a exposição cresce com eles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Contribuições devidas em caso de requalificação</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Contribuições a cargo da entidade</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>TSU_E</t>
+        </is>
+      </c>
+      <c r="C10" s="28">
+        <f>$C$8*Parametros!$C$14</f>
+        <v/>
+      </c>
+      <c r="D10" s="28">
+        <f>$D$8*Parametros!$C$14</f>
+        <v/>
+      </c>
+      <c r="E10" s="28">
+        <f>$E$8*Parametros!$C$14</f>
+        <v/>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>Art. 53.º Cód. Contributivo. É a parcela que a clínica nunca pagou e passa a dever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Contribuições a cargo do trabalhador, não retidas</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>TSU_T</t>
+        </is>
+      </c>
+      <c r="C11" s="28">
+        <f>$C$8*Parametros!$C$15</f>
+        <v/>
+      </c>
+      <c r="D11" s="28">
+        <f>$D$8*Parametros!$C$15</f>
+        <v/>
+      </c>
+      <c r="E11" s="28">
+        <f>$E$8*Parametros!$C$15</f>
+        <v/>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>A entidade é responsável pela entrega. Na prática, é dívida da clínica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Juros de mora estimados</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>JUROS</t>
+        </is>
+      </c>
+      <c r="C12" s="28">
+        <f>($C$10+$C$11)*Parametros!$C$17*$C$7/2</f>
+        <v/>
+      </c>
+      <c r="D12" s="28">
+        <f>($D$10+$D$11)*Parametros!$C$17*$D$7/2</f>
+        <v/>
+      </c>
+      <c r="E12" s="28">
+        <f>($E$10+$E$11)*Parametros!$C$17*$E$7/2</f>
+        <v/>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Aproximação: metade do período médio de mora sobre o total em dívida. Ordem de grandeza, não liquidação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Coima estimada</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>COIMA</t>
+        </is>
+      </c>
+      <c r="C13" s="28">
+        <f>$C$10*0.5</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>$D$10*0.5</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>$E$10*0.5</f>
+        <v/>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>ESTIMATIVA GROSSEIRA, a 50% das contribuições da entidade. A moldura das contraordenações por falta de comunicação de admissão e de pagamento de contribuições tem de ser confirmada pela Fiscalidade ou por advogado. Ver R1-38.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>PASSIVO CONTINGENTE TOTAL</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>PASSIVO</t>
+        </is>
+      </c>
+      <c r="C14" s="27">
+        <f>$C$10+$C$11+$C$12+$C$13</f>
+        <v/>
+      </c>
+      <c r="D14" s="27">
+        <f>$D$10+$D$11+$D$12+$D$13</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>$E$10+$E$11+$E$12+$E$13</f>
+        <v/>
+      </c>
+      <c r="F14" s="17" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Dimensão do risco</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Resultado líquido anual da via de referência (via 2)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>LIQ_REF</t>
+        </is>
+      </c>
+      <c r="C16" s="35">
+        <f>V2_ENI_ContOrg!$C$30</f>
+        <v/>
+      </c>
+      <c r="D16" s="35">
+        <f>V2_ENI_ContOrg!$D$30</f>
+        <v/>
+      </c>
+      <c r="E16" s="35">
+        <f>V2_ENI_ContOrg!$E$30</f>
+        <v/>
+      </c>
+      <c r="F16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>ANOS DE RESULTADO LÍQUIDO QUE O PASSIVO CONSOME</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>ANOS_RES</t>
+        </is>
+      </c>
+      <c r="C17" s="46">
+        <f>IF($C$16&lt;=0,"n/a",$C$14/$C$16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="46">
+        <f>IF($D$16&lt;=0,"n/a",$D$14/$D$16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="46">
+        <f>IF($E$16&lt;=0,"n/a",$E$14/$E$16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>É esta a frase a dizer à cliente, e não a percentagem: quantos anos de trabalho pago desaparecem se isto correr mal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Passivo em % do investimento inicial</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>VS_INV</t>
+        </is>
+      </c>
+      <c r="C18" s="37">
+        <f>IF((Inputs!$C$27+Inputs!$C$28+Inputs!$C$29+Inputs!$C$30)&lt;=0,0,$C$14/(Inputs!$C$27+Inputs!$C$28+Inputs!$C$29+Inputs!$C$30))</f>
+        <v/>
+      </c>
+      <c r="D18" s="37">
+        <f>IF((Inputs!$D$27+Inputs!$D$28+Inputs!$D$29+Inputs!$D$30)&lt;=0,0,$D$14/(Inputs!$D$27+Inputs!$D$28+Inputs!$D$29+Inputs!$D$30))</f>
+        <v/>
+      </c>
+      <c r="E18" s="37">
+        <f>IF((Inputs!$E$27+Inputs!$E$28+Inputs!$E$29+Inputs!$E$30)&lt;=0,0,$E$14/(Inputs!$E$27+Inputs!$E$28+Inputs!$E$29+Inputs!$E$30))</f>
+        <v/>
+      </c>
+      <c r="F18" s="17" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Indícios de laboralidade — art. 12.º n.º 1 do Código do Trabalho</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>A presunção de contrato de trabalho opera quando se verifiquem ALGUMAS destas características. Não é preciso que se verifiquem todas. Marcar 1 onde se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>a) O local de trabalho pertence ao beneficiário da atividade ou é por ele determinado</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>ESTRUTURALMENTE PRESENTE numa clínica. O fisioterapeuta trabalha no espaço da Dra. Júlia. Não é evitável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>b) Os equipamentos e instrumentos de trabalho pertencem ao beneficiário da atividade</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>ESTRUTURALMENTE PRESENTE se o equipamento clínico for da clínica. Evitável apenas se o profissional usar material próprio, o que raramente acontece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>c) O prestador observa horas de início e de termo determinadas pelo beneficiário</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>EVITÁVEL, e é a decisão mais importante. Se a marcação de consultas for feita pela clínica com horário imposto, este indício verifica-se.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>d) É paga, com certa periodicidade, uma quantia certa ao prestador</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>EVITÁVEL. Honorários variáveis em função das sessões efetivamente realizadas afastam-no; um valor fixo mensal verifica-o.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>e) O prestador desempenha funções de direção ou chefia na estrutura da empresa</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Improvável nesta fase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>N.º de indícios verificados (de 5)</t>
+        </is>
+      </c>
+      <c r="C28" s="23">
+        <f>SUM($C$22:$C$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>LEITURA</t>
+        </is>
+      </c>
+      <c r="C29" s="51">
+        <f>IF($C$28&gt;=3,"RISCO ELEVADO — presunção provável",IF($C$28=2,"RISCO ESTRUTURAL — os dois indícios inevitáveis já se verificam","RISCO CONTIDO"))</f>
+        <v/>
+      </c>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="40" t="n"/>
+    </row>
+    <row r="31" ht="92" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>O que este quadro mostra, e é o essencial: numa clínica, os indícios a) e b) verificam-se desde o primeiro dia e não são evitáveis — o profissional trabalha no espaço e com o equipamento da clínica. A margem de manobra está inteiramente em c) e d), ou seja, no horário e na forma de remuneração. É aí que a blindagem contratual e, sobretudo, a prática diária têm de trabalhar. Um contrato bem redigido que seja desmentido pelo funcionamento real não protege ninguém.
+A presunção é ilidível, mas inverte o ónus da prova: passa a caber à clínica demonstrar que não há contrato de trabalho. A redação dos contratos e o parecer laboral estão fora do nosso âmbito; identificar e quantificar o risco, não.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="C29:E29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6781,7 +7831,7 @@
         </is>
       </c>
       <c r="B10" s="50">
-        <f>SUM(Parametros!$F$6:$F$41)</f>
+        <f>SUM(Parametros!$F$6:$F$45)</f>
         <v/>
       </c>
       <c r="C10" s="48">
@@ -7135,6 +8185,442 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>M1 — Entrada do cônjuge: custo de complexidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>A hipótese foi levantada na reunião e ficou em análise, nem descartada nem recomendada. Esta folha põe de um lado tudo o que a entrada do cônjuge dá e do outro tudo o que custa, para que a decisão não se tome pela metade que é mais fácil de calcular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>A premissa de que tudo depende</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Toda esta folha assume que a atividade do cônjuge NÃO consta da tabela do art. 151.º CIRS. Se constar — por enquadramento como desportista ou pelo código residual — a entrada dele não afasta a transparência fiscal com percentagem de capital nenhuma, e tudo o que está abaixo passa a ser custo sem contrapartida. A premissa nunca foi verificada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Premissa verificada? (1 = sim / 0 = não)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>PREMISSA</t>
+        </is>
+      </c>
+      <c r="C7" s="50">
+        <f>Alertas!$B$5</f>
+        <v/>
+      </c>
+      <c r="D7" s="50">
+        <f>Alertas!$B$5</f>
+        <v/>
+      </c>
+      <c r="E7" s="50">
+        <f>Alertas!$B$5</f>
+        <v/>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Interruptor na folha Alertas. Ver R1-14 e N1-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>O que a entrada do cônjuge dá</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>IVA recuperável atribuível à entrada do cônjuge</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>G_IVA</t>
+        </is>
+      </c>
+      <c r="C9" s="35">
+        <f>IVA!$C$21</f>
+        <v/>
+      </c>
+      <c r="D9" s="35">
+        <f>IVA!$D$21</f>
+        <v/>
+      </c>
+      <c r="E9" s="35">
+        <f>IVA!$E$21</f>
+        <v/>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Zero enquanto o cônjuge não faturar DENTRO da sociedade. Deter capital não dá IVA nenhum: são duas decisões diferentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Diferencial de líquido para a sócia, via 4 face à via 3</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>G_ESTR</t>
+        </is>
+      </c>
+      <c r="C10" s="35">
+        <f>V4_Soc_NaoTransparente!$C$44-V3_Soc_Transparente!$C$36</f>
+        <v/>
+      </c>
+      <c r="D10" s="35">
+        <f>V4_Soc_NaoTransparente!$D$44-V3_Soc_Transparente!$D$36</f>
+        <v/>
+      </c>
+      <c r="E10" s="35">
+        <f>V4_Soc_NaoTransparente!$E$44-V3_Soc_Transparente!$E$36</f>
+        <v/>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>Negativo significa que afastar a transparência custa dinheiro à sócia nas condições atuais de distribuição. Depende inteiramente da alavanca POL_DIST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Total dos ganhos anuais</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>G_TOT</t>
+        </is>
+      </c>
+      <c r="C11" s="27">
+        <f>$C$9+$C$10</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>$D$9+$D$10</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>$E$9+$E$10</f>
+        <v/>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>O ganho de IVA é de uma só vez, no ano do investimento; o diferencial de estrutura é recorrente. Somá-los na mesma linha é uma simplificação — ler as duas linhas acima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>O que a entrada do cônjuge custa</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Quota de lucros atribuída ao cônjuge, por ano</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>C_QUOTA</t>
+        </is>
+      </c>
+      <c r="C13" s="35">
+        <f>V4_Soc_NaoTransparente!$C$43</f>
+        <v/>
+      </c>
+      <c r="D13" s="35">
+        <f>V4_Soc_NaoTransparente!$D$43</f>
+        <v/>
+      </c>
+      <c r="E13" s="35">
+        <f>V4_Soc_NaoTransparente!$E$43</f>
+        <v/>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Dentro do agregado é uma transferência, não uma perda. Fora dele — divórcio, sucessão — é definitiva. O relatório tem de dizer as duas coisas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Custo administrativo anual de sujeito passivo misto</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>C_ADM</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>A PREENCHER com a estimativa do contabilista: segregação documental, pro rata ou afetação real, regularizações anuais, obrigações declarativas adicionais. Não é zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Custo de constituição e de alterações societárias</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>C_CONST</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>A PREENCHER. Custo único.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Total dos custos anuais</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>C_TOT</t>
+        </is>
+      </c>
+      <c r="C16" s="27">
+        <f>$C$13+$C$14+$C$15</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>$D$13+$D$14+$D$15</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>$E$13+$E$14+$E$15</f>
+        <v/>
+      </c>
+      <c r="F16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Saldo</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>SALDO ANUAL DA OPERAÇÃO, NA ESFERA DA SÓCIA</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>SALDO</t>
+        </is>
+      </c>
+      <c r="C18" s="27">
+        <f>$C$11-$C$16</f>
+        <v/>
+      </c>
+      <c r="D18" s="27">
+        <f>$D$11-$D$16</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>$E$11-$E$16</f>
+        <v/>
+      </c>
+      <c r="F18" s="17" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>SALDO ANUAL NA ESFERA DO AGREGADO</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>SALDO_AGR</t>
+        </is>
+      </c>
+      <c r="C19" s="27">
+        <f>$C$11-$C$14-$C$15</f>
+        <v/>
+      </c>
+      <c r="D19" s="27">
+        <f>$D$11-$D$14-$D$15</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>$E$11-$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>Exclui a quota de lucros do cônjuge, que dentro do agregado não sai. É a leitura mais favorável possível à operação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>VEREDITO</t>
+        </is>
+      </c>
+      <c r="C20" s="26">
+        <f>IF($C$7=0,"NÃO DECIDÍVEL — premissa por verificar",IF($C$18&gt;0,"Favorável na esfera da sócia",IF($C$19&gt;0,"Favorável apenas na ótica do agregado, não na da sócia","Desfavorável nas condições atuais")))</f>
+        <v/>
+      </c>
+      <c r="D20" s="26">
+        <f>IF($D$7=0,"NÃO DECIDÍVEL — premissa por verificar",IF($D$18&gt;0,"Favorável na esfera da sócia",IF($D$19&gt;0,"Favorável apenas na ótica do agregado, não na da sócia","Desfavorável nas condições atuais")))</f>
+        <v/>
+      </c>
+      <c r="E20" s="26">
+        <f>IF($E$7=0,"NÃO DECIDÍVEL — premissa por verificar",IF($E$18&gt;0,"Favorável na esfera da sócia",IF($E$19&gt;0,"Favorável apenas na ótica do agregado, não na da sócia","Desfavorável nas condições atuais")))</f>
+        <v/>
+      </c>
+      <c r="F20" s="17" t="inlineStr"/>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>O que esta folha não quantifica, e tem de ser dito por palavras no capítulo 7: a perda de controlo qualificado, já que uma participação superior a 25% dá capacidade de bloqueio das deliberações que exijam maioria de três quartos; o efeito em caso de divórcio ou sucessão; e o risco de o desenho ser lido como artificial ao abrigo do art. 38.º n.º 2 da LGT se a participação não tiver substância económica real. Nenhuma destas três coisas tem preço, e todas podem ser mais caras do que o saldo acima.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7146,7 +8632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7439,38 +8925,55 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IRS — categoria B e regras de determinação</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Trabalhador por conta de outrem — taxa a cargo da entidade empregadora</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>TSU_ENT</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Art. 53.º Cód. Contributivo</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Coeficiente do regime simplificado (atividades do art. 151.º)</t>
+          <t>Trabalhador por conta de outrem — taxa a cargo do trabalhador</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>COEF</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0.75</v>
+          <t>TSU_TRAB</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>0.11</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 1 al. b) CIRS — fisioterapeutas constam da tabela do art. 151.º</t>
+          <t>Art. 53.º Cód. Contributivo</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Validado</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
@@ -7480,109 +8983,92 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Limiar de justificação de despesas</t>
+          <t>Prazo de prescrição das contribuições (anos)</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>LIM_JUST</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>0.15</v>
+          <t>PRESCR</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>5</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 13 CIRS</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
+          <t>Art. 187.º Cód. Contributivo</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR (ver R1-37)</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Dedução específica considerada na justificação de despesas</t>
+          <t>Taxa anual de juros de mora aplicada às contribuições em falta</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>DED_ESP</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>4104</v>
+          <t>JUROS_MORA</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.05</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 13 al. a) CIRS</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Confirmar valor em vigor</t>
+          <t>Regime dos juros de mora de dívidas ao Estado</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR taxa em vigor</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Contribuições SS — dedutíveis na parte que excede esta % do rendimento bruto</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>LIM_CONTRIB</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Art. 31.º n.º 2 CIRS</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>IRS — categoria B e regras de determinação</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Limiar de permanência no regime simplificado (rendimento bruto)</t>
+          <t>Coeficiente do regime simplificado (atividades do art. 151.º)</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>LIM_SIMPL</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>200000</v>
+          <t>COEF</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>0.75</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Art. 28.º n.º 2 CIRS</t>
+          <t>Art. 31.º n.º 1 al. b) CIRS — fisioterapeutas constam da tabela do art. 151.º</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Validado</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
@@ -7592,25 +9078,25 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Período mínimo de permanência na opção por contabilidade organizada (anos)</t>
+          <t>Limiar de justificação de despesas</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>PERM_OPCAO</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>3</v>
+          <t>LIM_JUST</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>0.15</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Art. 28.º n.º 5 CIRS</t>
+          <t>Art. 31.º n.º 13 CIRS</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Validado</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
@@ -7620,12 +9106,12 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Dedução específica da categoria A</t>
+          <t>Dedução específica considerada na justificação de despesas</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>DED_CATA</t>
+          <t>DED_ESP</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
@@ -7633,7 +9119,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Art. 25.º n.º 1 al. a) CIRS</t>
+          <t>Art. 31.º n.º 13 al. a) CIRS</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -7648,120 +9134,137 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Coeficiente do simplificado aplicável à receita de cedência de espaço</t>
+          <t>Contribuições SS — dedutíveis na parte que excede esta % do rendimento bruto</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>COEF_SALA</t>
+          <t>LIM_CONTRIB</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 1 al. c) CIRS — restantes prestações de serviços</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR (ver R1-29). Depende de N1-04</t>
+          <t>Art. 31.º n.º 2 CIRS</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>IRC e tributação da distribuição</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Limiar de permanência no regime simplificado (rendimento bruto)</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>LIM_SIMPL</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Art. 28.º n.º 2 CIRS</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>IRC — taxa aplicável ao primeiro escalão (PME)</t>
+          <t>Período mínimo de permanência na opção por contabilidade organizada (anos)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>IRC_PME</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>0.16</v>
+          <t>PERM_OPCAO</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Art. 87.º n.º 2 CIRC</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
+          <t>Art. 28.º n.º 5 CIRS</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>IRC — limite da matéria coletável do primeiro escalão</t>
+          <t>Dedução específica da categoria A</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>IRC_LIM</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>50000</v>
+          <t>DED_CATA</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>4104</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Art. 87.º n.º 2 CIRC</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR 2026</t>
+          <t>Art. 25.º n.º 1 al. a) CIRS</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar valor em vigor</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>IRC — taxa geral</t>
+          <t>Coeficiente do simplificado aplicável à receita de cedência de espaço</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>IRC_GER</t>
+          <t>COEF_SALA</t>
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Art. 87.º n.º 1 CIRC</t>
+          <t>Art. 31.º n.º 1 al. c) CIRS — restantes prestações de serviços</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
+          <t>CONFIRMAR (ver R1-29). Depende de N1-04</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
@@ -7769,55 +9272,38 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Derrama municipal (município do Porto)</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>DERRAMA</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Art. 18.º Lei 73/2013 + deliberação municipal</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR município e isenção PME</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>IRC e tributação da distribuição</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Derrama incide sobre sociedade transparente? (1=sim / 0=não)</t>
+          <t>IRC — taxa aplicável ao primeiro escalão (PME)</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>DERR_TRANSP</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>0</v>
+          <t>IRC_PME</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>0.16</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Questão controvertida — art. 12.º CIRC vs. art. 18.º Lei 73/2013</t>
+          <t>Art. 87.º n.º 2 CIRC</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>EM ABERTO (ver R1-13)</t>
+          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
@@ -7827,120 +9313,137 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Dividendos — taxa liberatória</t>
+          <t>IRC — limite da matéria coletável do primeiro escalão</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>DIV_LIB</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>0.28</v>
+          <t>IRC_LIM</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>50000</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Art. 71.º n.º 1 CIRS</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
+          <t>Art. 87.º n.º 2 CIRC</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR 2026</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Dividendos — % considerada em caso de englobamento</t>
+          <t>IRC — taxa geral</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>DIV_ENG</t>
+          <t>IRC_GER</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Art. 40.º-A n.º 1 CIRS</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
+          <t>Art. 87.º n.º 1 CIRC</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Derrama municipal (município do Porto)</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>DERRAMA</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Art. 18.º Lei 73/2013 + deliberação municipal</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR município e isenção PME</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>IVA — taxa normal (continente)</t>
+          <t>Derrama incide sobre sociedade transparente? (1=sim / 0=não)</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>IVA_NORM</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="n">
-        <v>0.23</v>
+          <t>DERR_TRANSP</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Art. 18.º n.º 1 al. c) CIVA</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
+          <t>Questão controvertida — art. 12.º CIRC vs. art. 18.º Lei 73/2013</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>EM ABERTO (ver R1-13)</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>IVA — taxa reduzida (continente)</t>
+          <t>Dividendos — taxa liberatória</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>IVA_RED</t>
+          <t>DIV_LIB</t>
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>0.06</v>
+        <v>0.28</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Art. 18.º n.º 1 al. a) CIVA + Lista I</t>
+          <t>Art. 71.º n.º 1 CIRS</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Validado</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
@@ -7948,104 +9451,104 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Amortizações (vias com contabilidade)</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Dividendos — % considerada em caso de englobamento</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>DIV_ENG</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Art. 40.º-A n.º 1 CIRS</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Taxa de amortização — obras / benfeitorias em imóvel alheio</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>AM_OBRAS</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>DR 25/2009 — ou período do contrato de arrendamento, se inferior</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR código aplicável</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Taxa de amortização — equipamento clínico</t>
+          <t>IVA — taxa normal (continente)</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>AM_EQUIP</t>
+          <t>IVA_NORM</t>
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>DR 25/2009, tabela II</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR código aplicável</t>
+          <t>Art. 18.º n.º 1 al. c) CIVA</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Taxa de amortização — software</t>
+          <t>IVA — taxa reduzida (continente)</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>AM_SOFT</t>
+          <t>IVA_RED</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>0.3333</v>
+        <v>0.06</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>DR 25/2009</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR</t>
+          <t>Art. 18.º n.º 1 al. a) CIVA + Lista I</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Transparência fiscal — limiares do teste (usados na N1, não no cálculo)</t>
+          <t>Amortizações (vias com contabilidade)</t>
         </is>
       </c>
       <c r="B38" s="7" t="n"/>
@@ -8056,234 +9559,257 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>% mínima de capital detida por profissionais das atividades do art. 151.º</t>
+          <t>Taxa de amortização — obras / benfeitorias em imóvel alheio</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>TF_CAP</t>
+          <t>AM_OBRAS</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
+          <t>DR 25/2009 — ou período do contrato de arrendamento, se inferior</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR código aplicável</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>% mínima de rendimentos provenientes de atividades do art. 151.º</t>
+          <t>Taxa de amortização — equipamento clínico</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>TF_REND</t>
+          <t>AM_EQUIP</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
+          <t>DR 25/2009, tabela II</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR código aplicável</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>Taxa de amortização — software</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>AM_SOFT</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>DR 25/2009</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Transparência fiscal — limiares do teste (usados na N1, não no cálculo)</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>% mínima de capital detida por profissionais das atividades do art. 151.º</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>TF_CAP</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>% mínima de rendimentos provenientes de atividades do art. 151.º</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>TF_REND</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
           <t>N.º máximo de sócios para o teste da subal. ii)</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>TF_SOCIOS</t>
         </is>
       </c>
-      <c r="C41" s="15" t="n">
+      <c r="C45" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Validado</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Escalões de IRS — taxas gerais</t>
         </is>
       </c>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Tabela em vigor: 2025 (Lei n.º 33-A/2025). ATUALIZAR para os escalões do OE2026 antes de qualquer número entrar no relatório. A coluna 'Delta' é a mecânica de cálculo (taxa do escalão menos taxa do anterior) e recalcula sozinha.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Escalão</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Limite inferior</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Limite superior</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Taxa</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Delta (calculado)</t>
         </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="16" t="n">
-        <v>8059</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E46" s="18">
-        <f>D46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>8059</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>12160</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E47" s="18">
-        <f>D47-D46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>12160</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>17233</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E48" s="18">
-        <f>D48-D47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B49" s="16" t="n">
-        <v>17233</v>
-      </c>
-      <c r="C49" s="16" t="n">
-        <v>22306</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="E49" s="18">
-        <f>D49-D48</f>
-        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B50" s="16" t="n">
-        <v>22306</v>
+        <v>0</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>28400</v>
+        <v>8059</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>0.314</v>
+        <v>0.125</v>
       </c>
       <c r="E50" s="18">
-        <f>D50-D49</f>
+        <f>D50</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B51" s="16" t="n">
-        <v>28400</v>
+        <v>8059</v>
       </c>
       <c r="C51" s="16" t="n">
-        <v>41629</v>
+        <v>12160</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>0.349</v>
+        <v>0.16</v>
       </c>
       <c r="E51" s="18">
         <f>D51-D50</f>
@@ -8292,16 +9818,16 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B52" s="16" t="n">
-        <v>41629</v>
+        <v>12160</v>
       </c>
       <c r="C52" s="16" t="n">
-        <v>44987</v>
+        <v>17233</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>0.431</v>
+        <v>0.215</v>
       </c>
       <c r="E52" s="18">
         <f>D52-D51</f>
@@ -8310,16 +9836,16 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B53" s="16" t="n">
-        <v>44987</v>
+        <v>17233</v>
       </c>
       <c r="C53" s="16" t="n">
-        <v>83696</v>
+        <v>22306</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>0.446</v>
+        <v>0.244</v>
       </c>
       <c r="E53" s="18">
         <f>D53-D52</f>
@@ -8328,102 +9854,174 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B54" s="16" t="n">
-        <v>83696</v>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>sem limite</t>
-        </is>
+        <v>22306</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>28400</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>0.48</v>
+        <v>0.314</v>
       </c>
       <c r="E54" s="18">
         <f>D54-D53</f>
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>28400</v>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>41629</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="E55" s="18">
+        <f>D55-D54</f>
+        <v/>
+      </c>
+    </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Taxa adicional de solidariedade (art. 68.º-A CIRS)</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="n"/>
-      <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
-      <c r="E56" s="7" t="n"/>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Escalão</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Limite inferior</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Limite superior</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Taxa</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Delta (calculado)</t>
-        </is>
+      <c r="A56" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B56" s="16" t="n">
+        <v>41629</v>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>44987</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="E56" s="18">
+        <f>D56-D55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B57" s="16" t="n">
+        <v>44987</v>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>83696</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="E57" s="18">
+        <f>D57-D56</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B58" s="16" t="n">
+        <v>83696</v>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>sem limite</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E58" s="18">
+        <f>D58-D57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Taxa adicional de solidariedade (art. 68.º-A CIRS)</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Escalão</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Limite inferior</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Limite superior</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Taxa</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Delta (calculado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B58" s="16" t="n">
+      <c r="B62" s="16" t="n">
         <v>80000</v>
       </c>
-      <c r="C58" s="16" t="n">
+      <c r="C62" s="16" t="n">
         <v>250000</v>
       </c>
-      <c r="D58" s="14" t="n">
+      <c r="D62" s="14" t="n">
         <v>0.025</v>
       </c>
-      <c r="E58" s="18">
-        <f>D58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="n">
+      <c r="E62" s="18">
+        <f>D62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B59" s="16" t="n">
+      <c r="B63" s="16" t="n">
         <v>250000</v>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>sem limite</t>
         </is>
       </c>
-      <c r="D59" s="14" t="n">
+      <c r="D63" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="E59" s="18">
-        <f>D59-D58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="E63" s="18">
+        <f>D63-D62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Legenda: células a azul sobre fundo amarelo são de preenchimento; tudo o resto é fórmula. Nenhuma taxa deve ser escrita dentro de uma fórmula noutra folha — se faltar um parâmetro, acrescenta-se aqui.</t>
         </is>
@@ -8431,8 +10029,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A48:E48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10992,15 +12590,15 @@
         </is>
       </c>
       <c r="C49" s="28">
-        <f>Inputs!$C$42*(1-Parametros!$C$40)/Parametros!$C$40</f>
+        <f>Inputs!$C$42*(1-Parametros!$C$44)/Parametros!$C$44</f>
         <v/>
       </c>
       <c r="D49" s="28">
-        <f>Inputs!$D$42*(1-Parametros!$C$40)/Parametros!$C$40</f>
+        <f>Inputs!$D$42*(1-Parametros!$C$44)/Parametros!$C$44</f>
         <v/>
       </c>
       <c r="E49" s="28">
-        <f>Inputs!$E$42*(1-Parametros!$C$40)/Parametros!$C$40</f>
+        <f>Inputs!$E$42*(1-Parametros!$C$44)/Parametros!$C$44</f>
         <v/>
       </c>
       <c r="F49" s="17" t="inlineStr">
@@ -11021,15 +12619,15 @@
         </is>
       </c>
       <c r="C50" s="26">
-        <f>IF(Inputs!$C$48&gt;Parametros!$C$40,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <f>IF(Inputs!$C$48&gt;Parametros!$C$44,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
         <v/>
       </c>
       <c r="D50" s="26">
-        <f>IF(Inputs!$D$48&gt;Parametros!$C$40,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <f>IF(Inputs!$D$48&gt;Parametros!$C$44,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
         <v/>
       </c>
       <c r="E50" s="26">
-        <f>IF(Inputs!$E$48&gt;Parametros!$C$40,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <f>IF(Inputs!$E$48&gt;Parametros!$C$44,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
         <v/>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -11240,15 +12838,15 @@
         </is>
       </c>
       <c r="C9" s="36">
-        <f>Parametros!$C$15</f>
+        <f>Parametros!$C$19</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Parametros!$C$15</f>
+        <f>Parametros!$C$19</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>Parametros!$C$15</f>
+        <f>Parametros!$C$19</f>
         <v/>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -11269,15 +12867,15 @@
         </is>
       </c>
       <c r="C10" s="36">
-        <f>Parametros!$C$22</f>
+        <f>Parametros!$C$26</f>
         <v/>
       </c>
       <c r="D10" s="36">
-        <f>Parametros!$C$22</f>
+        <f>Parametros!$C$26</f>
         <v/>
       </c>
       <c r="E10" s="36">
-        <f>Parametros!$C$22</f>
+        <f>Parametros!$C$26</f>
         <v/>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -11323,15 +12921,15 @@
         </is>
       </c>
       <c r="C12" s="28">
-        <f>$C$8*Parametros!$C$16</f>
+        <f>$C$8*Parametros!$C$20</f>
         <v/>
       </c>
       <c r="D12" s="28">
-        <f>$D$8*Parametros!$C$16</f>
+        <f>$D$8*Parametros!$C$20</f>
         <v/>
       </c>
       <c r="E12" s="28">
-        <f>$E$8*Parametros!$C$16</f>
+        <f>$E$8*Parametros!$C$20</f>
         <v/>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -11352,15 +12950,15 @@
         </is>
       </c>
       <c r="C13" s="35">
-        <f>Parametros!$C$17</f>
+        <f>Parametros!$C$21</f>
         <v/>
       </c>
       <c r="D13" s="35">
-        <f>Parametros!$C$17</f>
+        <f>Parametros!$C$21</f>
         <v/>
       </c>
       <c r="E13" s="35">
-        <f>Parametros!$C$17</f>
+        <f>Parametros!$C$21</f>
         <v/>
       </c>
       <c r="F13" s="17" t="inlineStr"/>
@@ -11642,15 +13240,15 @@
         </is>
       </c>
       <c r="C24" s="28">
-        <f>MAX(0,$C$23-$C$8*Parametros!$C$18)</f>
+        <f>MAX(0,$C$23-$C$8*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="D24" s="28">
-        <f>MAX(0,$D$23-$D$8*Parametros!$C$18)</f>
+        <f>MAX(0,$D$23-$D$8*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="E24" s="28">
-        <f>MAX(0,$E$23-$E$8*Parametros!$C$18)</f>
+        <f>MAX(0,$E$23-$E$8*Parametros!$C$22)</f>
         <v/>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -11816,15 +13414,15 @@
         </is>
       </c>
       <c r="C31" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$29/2)&gt;Parametros!$B$46:$B$54)*(($C$29/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$29/2)&gt;Parametros!$B$58:$B$59)*(($C$29/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$29&gt;Parametros!$B$46:$B$54)*($C$29-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$29&gt;Parametros!$B$58:$B$59)*($C$29-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$29/2)&gt;Parametros!$B$50:$B$58)*(($C$29/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$29/2)&gt;Parametros!$B$62:$B$63)*(($C$29/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$29&gt;Parametros!$B$50:$B$58)*($C$29-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$29&gt;Parametros!$B$62:$B$63)*($C$29-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="D31" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$29/2)&gt;Parametros!$B$46:$B$54)*(($D$29/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$29/2)&gt;Parametros!$B$58:$B$59)*(($D$29/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$29&gt;Parametros!$B$46:$B$54)*($D$29-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$29&gt;Parametros!$B$58:$B$59)*($D$29-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$29/2)&gt;Parametros!$B$50:$B$58)*(($D$29/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$29/2)&gt;Parametros!$B$62:$B$63)*(($D$29/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$29&gt;Parametros!$B$50:$B$58)*($D$29-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$29&gt;Parametros!$B$62:$B$63)*($D$29-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="E31" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$29/2)&gt;Parametros!$B$46:$B$54)*(($E$29/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$29/2)&gt;Parametros!$B$58:$B$59)*(($E$29/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$29&gt;Parametros!$B$46:$B$54)*($E$29-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$29&gt;Parametros!$B$58:$B$59)*($E$29-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$29/2)&gt;Parametros!$B$50:$B$58)*(($E$29/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$29/2)&gt;Parametros!$B$62:$B$63)*(($E$29/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$29&gt;Parametros!$B$50:$B$58)*($E$29-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$29&gt;Parametros!$B$62:$B$63)*($E$29-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F31" s="17" t="inlineStr">
@@ -11845,15 +13443,15 @@
         </is>
       </c>
       <c r="C32" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$30/2)&gt;Parametros!$B$46:$B$54)*(($C$30/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$30/2)&gt;Parametros!$B$58:$B$59)*(($C$30/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$30&gt;Parametros!$B$46:$B$54)*($C$30-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$30&gt;Parametros!$B$58:$B$59)*($C$30-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$30/2)&gt;Parametros!$B$50:$B$58)*(($C$30/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$30/2)&gt;Parametros!$B$62:$B$63)*(($C$30/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$30&gt;Parametros!$B$50:$B$58)*($C$30-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$30&gt;Parametros!$B$62:$B$63)*($C$30-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="D32" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$30/2)&gt;Parametros!$B$46:$B$54)*(($D$30/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$30/2)&gt;Parametros!$B$58:$B$59)*(($D$30/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$30&gt;Parametros!$B$46:$B$54)*($D$30-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$30&gt;Parametros!$B$58:$B$59)*($D$30-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$30/2)&gt;Parametros!$B$50:$B$58)*(($D$30/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$30/2)&gt;Parametros!$B$62:$B$63)*(($D$30/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$30&gt;Parametros!$B$50:$B$58)*($D$30-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$30&gt;Parametros!$B$62:$B$63)*($D$30-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="E32" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$30/2)&gt;Parametros!$B$46:$B$54)*(($E$30/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$30/2)&gt;Parametros!$B$58:$B$59)*(($E$30/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$30&gt;Parametros!$B$46:$B$54)*($E$30-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$30&gt;Parametros!$B$58:$B$59)*($E$30-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$30/2)&gt;Parametros!$B$50:$B$58)*(($E$30/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$30/2)&gt;Parametros!$B$62:$B$63)*(($E$30/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$30&gt;Parametros!$B$50:$B$58)*($E$30-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$30&gt;Parametros!$B$62:$B$63)*($E$30-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F32" s="17" t="inlineStr"/>
@@ -12314,15 +13912,15 @@
         </is>
       </c>
       <c r="C9" s="28">
-        <f>Inputs!$C$27*Parametros!$C$35+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$36+Inputs!$C$30*Parametros!$C$37</f>
+        <f>Inputs!$C$27*Parametros!$C$39+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$40+Inputs!$C$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37</f>
+        <f>Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>Inputs!$E$27*Parametros!$C$35+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$36+Inputs!$E$30*Parametros!$C$37</f>
+        <f>Inputs!$E$27*Parametros!$C$39+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$40+Inputs!$E$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -12583,15 +14181,15 @@
         </is>
       </c>
       <c r="C20" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$18/2)&gt;Parametros!$B$46:$B$54)*(($C$18/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$18/2)&gt;Parametros!$B$58:$B$59)*(($C$18/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$18&gt;Parametros!$B$46:$B$54)*($C$18-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$18&gt;Parametros!$B$58:$B$59)*($C$18-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$18/2)&gt;Parametros!$B$50:$B$58)*(($C$18/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$18/2)&gt;Parametros!$B$62:$B$63)*(($C$18/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$18&gt;Parametros!$B$50:$B$58)*($C$18-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$18&gt;Parametros!$B$62:$B$63)*($C$18-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="D20" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$18/2)&gt;Parametros!$B$46:$B$54)*(($D$18/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$18/2)&gt;Parametros!$B$58:$B$59)*(($D$18/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$18&gt;Parametros!$B$46:$B$54)*($D$18-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$18&gt;Parametros!$B$58:$B$59)*($D$18-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$18/2)&gt;Parametros!$B$50:$B$58)*(($D$18/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$18/2)&gt;Parametros!$B$62:$B$63)*(($D$18/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$18&gt;Parametros!$B$50:$B$58)*($D$18-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$18&gt;Parametros!$B$62:$B$63)*($D$18-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="E20" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$18/2)&gt;Parametros!$B$46:$B$54)*(($E$18/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$18/2)&gt;Parametros!$B$58:$B$59)*(($E$18/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$18&gt;Parametros!$B$46:$B$54)*($E$18-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$18&gt;Parametros!$B$58:$B$59)*($E$18-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$18/2)&gt;Parametros!$B$50:$B$58)*(($E$18/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$18/2)&gt;Parametros!$B$62:$B$63)*(($E$18/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$18&gt;Parametros!$B$50:$B$58)*($E$18-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$18&gt;Parametros!$B$62:$B$63)*($E$18-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -12612,15 +14210,15 @@
         </is>
       </c>
       <c r="C21" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$19/2)&gt;Parametros!$B$46:$B$54)*(($C$19/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$19/2)&gt;Parametros!$B$58:$B$59)*(($C$19/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$19&gt;Parametros!$B$46:$B$54)*($C$19-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$19&gt;Parametros!$B$58:$B$59)*($C$19-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$19/2)&gt;Parametros!$B$50:$B$58)*(($C$19/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$19/2)&gt;Parametros!$B$62:$B$63)*(($C$19/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$19&gt;Parametros!$B$50:$B$58)*($C$19-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$19&gt;Parametros!$B$62:$B$63)*($C$19-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="D21" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$19/2)&gt;Parametros!$B$46:$B$54)*(($D$19/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$19/2)&gt;Parametros!$B$58:$B$59)*(($D$19/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$19&gt;Parametros!$B$46:$B$54)*($D$19-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$19&gt;Parametros!$B$58:$B$59)*($D$19-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$19/2)&gt;Parametros!$B$50:$B$58)*(($D$19/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$19/2)&gt;Parametros!$B$62:$B$63)*(($D$19/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$19&gt;Parametros!$B$50:$B$58)*($D$19-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$19&gt;Parametros!$B$62:$B$63)*($D$19-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="E21" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$19/2)&gt;Parametros!$B$46:$B$54)*(($E$19/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$19/2)&gt;Parametros!$B$58:$B$59)*(($E$19/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$19&gt;Parametros!$B$46:$B$54)*($E$19-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$19&gt;Parametros!$B$58:$B$59)*($E$19-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$19/2)&gt;Parametros!$B$50:$B$58)*(($E$19/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$19/2)&gt;Parametros!$B$62:$B$63)*(($E$19/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$19&gt;Parametros!$B$50:$B$58)*($E$19-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$19&gt;Parametros!$B$62:$B$63)*($E$19-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F21" s="17" t="inlineStr"/>
@@ -13077,15 +14675,15 @@
         </is>
       </c>
       <c r="C9" s="28">
-        <f>Inputs!$C$27*Parametros!$C$35+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$36+Inputs!$C$30*Parametros!$C$37</f>
+        <f>Inputs!$C$27*Parametros!$C$39+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$40+Inputs!$C$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37</f>
+        <f>Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>Inputs!$E$27*Parametros!$C$35+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$36+Inputs!$E$30*Parametros!$C$37</f>
+        <f>Inputs!$E$27*Parametros!$C$39+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$40+Inputs!$E$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="F9" s="17" t="inlineStr"/>
@@ -13239,15 +14837,15 @@
         </is>
       </c>
       <c r="C15" s="28">
-        <f>MAX($C$13,0)*Parametros!$C$27*Parametros!$C$28</f>
+        <f>MAX($C$13,0)*Parametros!$C$31*Parametros!$C$32</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>MAX($D$13,0)*Parametros!$C$27*Parametros!$C$28</f>
+        <f>MAX($D$13,0)*Parametros!$C$31*Parametros!$C$32</f>
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>MAX($E$13,0)*Parametros!$C$27*Parametros!$C$28</f>
+        <f>MAX($E$13,0)*Parametros!$C$31*Parametros!$C$32</f>
         <v/>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -13334,15 +14932,15 @@
         </is>
       </c>
       <c r="C19" s="28">
-        <f>MIN($C$10,MAX(Parametros!$C$21,$C$18))</f>
+        <f>MIN($C$10,MAX(Parametros!$C$25,$C$18))</f>
         <v/>
       </c>
       <c r="D19" s="28">
-        <f>MIN($D$10,MAX(Parametros!$C$21,$D$18))</f>
+        <f>MIN($D$10,MAX(Parametros!$C$25,$D$18))</f>
         <v/>
       </c>
       <c r="E19" s="28">
-        <f>MIN($E$10,MAX(Parametros!$C$21,$E$18))</f>
+        <f>MIN($E$10,MAX(Parametros!$C$25,$E$18))</f>
         <v/>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -13508,15 +15106,15 @@
         </is>
       </c>
       <c r="C26" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$24/2)&gt;Parametros!$B$46:$B$54)*(($C$24/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$24/2)&gt;Parametros!$B$58:$B$59)*(($C$24/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$24&gt;Parametros!$B$46:$B$54)*($C$24-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$24&gt;Parametros!$B$58:$B$59)*($C$24-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$24/2)&gt;Parametros!$B$50:$B$58)*(($C$24/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$24/2)&gt;Parametros!$B$62:$B$63)*(($C$24/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$24&gt;Parametros!$B$50:$B$58)*($C$24-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$24&gt;Parametros!$B$62:$B$63)*($C$24-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="D26" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$24/2)&gt;Parametros!$B$46:$B$54)*(($D$24/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$24/2)&gt;Parametros!$B$58:$B$59)*(($D$24/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$24&gt;Parametros!$B$46:$B$54)*($D$24-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$24&gt;Parametros!$B$58:$B$59)*($D$24-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$24/2)&gt;Parametros!$B$50:$B$58)*(($D$24/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$24/2)&gt;Parametros!$B$62:$B$63)*(($D$24/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$24&gt;Parametros!$B$50:$B$58)*($D$24-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$24&gt;Parametros!$B$62:$B$63)*($D$24-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="E26" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$24/2)&gt;Parametros!$B$46:$B$54)*(($E$24/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$24/2)&gt;Parametros!$B$58:$B$59)*(($E$24/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$24&gt;Parametros!$B$46:$B$54)*($E$24-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$24&gt;Parametros!$B$58:$B$59)*($E$24-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$24/2)&gt;Parametros!$B$50:$B$58)*(($E$24/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$24/2)&gt;Parametros!$B$62:$B$63)*(($E$24/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$24&gt;Parametros!$B$50:$B$58)*($E$24-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$24&gt;Parametros!$B$62:$B$63)*($E$24-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -13537,15 +15135,15 @@
         </is>
       </c>
       <c r="C27" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$25/2)&gt;Parametros!$B$46:$B$54)*(($C$25/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$25/2)&gt;Parametros!$B$58:$B$59)*(($C$25/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$25&gt;Parametros!$B$46:$B$54)*($C$25-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$25&gt;Parametros!$B$58:$B$59)*($C$25-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$25/2)&gt;Parametros!$B$50:$B$58)*(($C$25/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$25/2)&gt;Parametros!$B$62:$B$63)*(($C$25/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$25&gt;Parametros!$B$50:$B$58)*($C$25-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$25&gt;Parametros!$B$62:$B$63)*($C$25-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$25/2)&gt;Parametros!$B$46:$B$54)*(($D$25/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$25/2)&gt;Parametros!$B$58:$B$59)*(($D$25/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$25&gt;Parametros!$B$46:$B$54)*($D$25-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$25&gt;Parametros!$B$58:$B$59)*($D$25-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$25/2)&gt;Parametros!$B$50:$B$58)*(($D$25/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$25/2)&gt;Parametros!$B$62:$B$63)*(($D$25/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$25&gt;Parametros!$B$50:$B$58)*($D$25-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$25&gt;Parametros!$B$62:$B$63)*($D$25-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="E27" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$25/2)&gt;Parametros!$B$46:$B$54)*(($E$25/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$25/2)&gt;Parametros!$B$58:$B$59)*(($E$25/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$25&gt;Parametros!$B$46:$B$54)*($E$25-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$25&gt;Parametros!$B$58:$B$59)*($E$25-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$25/2)&gt;Parametros!$B$50:$B$58)*(($E$25/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$25/2)&gt;Parametros!$B$62:$B$63)*(($E$25/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$25&gt;Parametros!$B$50:$B$58)*($E$25-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$25&gt;Parametros!$B$62:$B$63)*($E$25-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
@@ -14027,15 +15625,15 @@
         </is>
       </c>
       <c r="C10" s="28">
-        <f>Inputs!$C$27*Parametros!$C$35+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$36+Inputs!$C$30*Parametros!$C$37</f>
+        <f>Inputs!$C$27*Parametros!$C$39+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$40+Inputs!$C$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="D10" s="28">
-        <f>Inputs!$D$27*Parametros!$C$35+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$36+Inputs!$D$30*Parametros!$C$37</f>
+        <f>Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="E10" s="28">
-        <f>Inputs!$E$27*Parametros!$C$35+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$36+Inputs!$E$30*Parametros!$C$37</f>
+        <f>Inputs!$E$27*Parametros!$C$39+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$40+Inputs!$E$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="F10" s="17" t="inlineStr"/>
@@ -14152,15 +15750,15 @@
         </is>
       </c>
       <c r="C15" s="28">
-        <f>MIN(MAX($C$14,0),Parametros!$C$25)*Parametros!$C$24+MAX(0,MAX($C$14,0)-Parametros!$C$25)*Parametros!$C$26</f>
+        <f>MIN(MAX($C$14,0),Parametros!$C$29)*Parametros!$C$28+MAX(0,MAX($C$14,0)-Parametros!$C$29)*Parametros!$C$30</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>MIN(MAX($D$14,0),Parametros!$C$25)*Parametros!$C$24+MAX(0,MAX($D$14,0)-Parametros!$C$25)*Parametros!$C$26</f>
+        <f>MIN(MAX($D$14,0),Parametros!$C$29)*Parametros!$C$28+MAX(0,MAX($D$14,0)-Parametros!$C$29)*Parametros!$C$30</f>
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>MIN(MAX($E$14,0),Parametros!$C$25)*Parametros!$C$24+MAX(0,MAX($E$14,0)-Parametros!$C$25)*Parametros!$C$26</f>
+        <f>MIN(MAX($E$14,0),Parametros!$C$29)*Parametros!$C$28+MAX(0,MAX($E$14,0)-Parametros!$C$29)*Parametros!$C$30</f>
         <v/>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -14181,15 +15779,15 @@
         </is>
       </c>
       <c r="C16" s="28">
-        <f>MAX($C$14,0)*Parametros!$C$27</f>
+        <f>MAX($C$14,0)*Parametros!$C$31</f>
         <v/>
       </c>
       <c r="D16" s="28">
-        <f>MAX($D$14,0)*Parametros!$C$27</f>
+        <f>MAX($D$14,0)*Parametros!$C$31</f>
         <v/>
       </c>
       <c r="E16" s="28">
-        <f>MAX($E$14,0)*Parametros!$C$27</f>
+        <f>MAX($E$14,0)*Parametros!$C$31</f>
         <v/>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -14460,15 +16058,15 @@
         </is>
       </c>
       <c r="C27" s="28">
-        <f>IF($C$26=1,0,($C$24+$C$25)*Parametros!$C$29)</f>
+        <f>IF($C$26=1,0,($C$24+$C$25)*Parametros!$C$33)</f>
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>IF($D$26=1,0,($D$24+$D$25)*Parametros!$C$29)</f>
+        <f>IF($D$26=1,0,($D$24+$D$25)*Parametros!$C$33)</f>
         <v/>
       </c>
       <c r="E27" s="28">
-        <f>IF($E$26=1,0,($E$24+$E$25)*Parametros!$C$29)</f>
+        <f>IF($E$26=1,0,($E$24+$E$25)*Parametros!$C$33)</f>
         <v/>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
@@ -14497,15 +16095,15 @@
         </is>
       </c>
       <c r="C29" s="27">
-        <f>MAX(0,$C$11-MIN($C$11,MAX(Parametros!$C$21,$C$12*Parametros!$C$12)))+IF($C$26=1,$C$24*Parametros!$C$30,0)</f>
+        <f>MAX(0,$C$11-MIN($C$11,MAX(Parametros!$C$25,$C$12*Parametros!$C$12)))+IF($C$26=1,$C$24*Parametros!$C$34,0)</f>
         <v/>
       </c>
       <c r="D29" s="27">
-        <f>MAX(0,$D$11-MIN($D$11,MAX(Parametros!$C$21,$D$12*Parametros!$C$12)))+IF($D$26=1,$D$24*Parametros!$C$30,0)</f>
+        <f>MAX(0,$D$11-MIN($D$11,MAX(Parametros!$C$25,$D$12*Parametros!$C$12)))+IF($D$26=1,$D$24*Parametros!$C$34,0)</f>
         <v/>
       </c>
       <c r="E29" s="27">
-        <f>MAX(0,$E$11-MIN($E$11,MAX(Parametros!$C$21,$E$12*Parametros!$C$12)))+IF($E$26=1,$E$24*Parametros!$C$30,0)</f>
+        <f>MAX(0,$E$11-MIN($E$11,MAX(Parametros!$C$25,$E$12*Parametros!$C$12)))+IF($E$26=1,$E$24*Parametros!$C$34,0)</f>
         <v/>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -14526,15 +16124,15 @@
         </is>
       </c>
       <c r="C30" s="28">
-        <f>Inputs!$C$37+IF($C$26=1,$C$25*Parametros!$C$30,0)</f>
+        <f>Inputs!$C$37+IF($C$26=1,$C$25*Parametros!$C$34,0)</f>
         <v/>
       </c>
       <c r="D30" s="28">
-        <f>Inputs!$D$37+IF($D$26=1,$D$25*Parametros!$C$30,0)</f>
+        <f>Inputs!$D$37+IF($D$26=1,$D$25*Parametros!$C$34,0)</f>
         <v/>
       </c>
       <c r="E30" s="28">
-        <f>Inputs!$E$37+IF($E$26=1,$E$25*Parametros!$C$30,0)</f>
+        <f>Inputs!$E$37+IF($E$26=1,$E$25*Parametros!$C$34,0)</f>
         <v/>
       </c>
       <c r="F30" s="17" t="inlineStr"/>
@@ -14605,15 +16203,15 @@
         </is>
       </c>
       <c r="C33" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$31/2)&gt;Parametros!$B$46:$B$54)*(($C$31/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$31/2)&gt;Parametros!$B$58:$B$59)*(($C$31/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$31&gt;Parametros!$B$46:$B$54)*($C$31-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$31&gt;Parametros!$B$58:$B$59)*($C$31-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$31/2)&gt;Parametros!$B$50:$B$58)*(($C$31/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$31/2)&gt;Parametros!$B$62:$B$63)*(($C$31/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$31&gt;Parametros!$B$50:$B$58)*($C$31-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$31&gt;Parametros!$B$62:$B$63)*($C$31-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="D33" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$31/2)&gt;Parametros!$B$46:$B$54)*(($D$31/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$31/2)&gt;Parametros!$B$58:$B$59)*(($D$31/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$31&gt;Parametros!$B$46:$B$54)*($D$31-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$31&gt;Parametros!$B$58:$B$59)*($D$31-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$31/2)&gt;Parametros!$B$50:$B$58)*(($D$31/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$31/2)&gt;Parametros!$B$62:$B$63)*(($D$31/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$31&gt;Parametros!$B$50:$B$58)*($D$31-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$31&gt;Parametros!$B$62:$B$63)*($D$31-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="E33" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$31/2)&gt;Parametros!$B$46:$B$54)*(($E$31/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$31/2)&gt;Parametros!$B$58:$B$59)*(($E$31/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$31&gt;Parametros!$B$46:$B$54)*($E$31-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$31&gt;Parametros!$B$58:$B$59)*($E$31-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$31/2)&gt;Parametros!$B$50:$B$58)*(($E$31/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$31/2)&gt;Parametros!$B$62:$B$63)*(($E$31/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$31&gt;Parametros!$B$50:$B$58)*($E$31-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$31&gt;Parametros!$B$62:$B$63)*($E$31-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F33" s="17" t="inlineStr"/>
@@ -14630,15 +16228,15 @@
         </is>
       </c>
       <c r="C34" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$32/2)&gt;Parametros!$B$46:$B$54)*(($C$32/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($C$32/2)&gt;Parametros!$B$58:$B$59)*(($C$32/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($C$32&gt;Parametros!$B$46:$B$54)*($C$32-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($C$32&gt;Parametros!$B$58:$B$59)*($C$32-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$32/2)&gt;Parametros!$B$50:$B$58)*(($C$32/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$32/2)&gt;Parametros!$B$62:$B$63)*(($C$32/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$32&gt;Parametros!$B$50:$B$58)*($C$32-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$32&gt;Parametros!$B$62:$B$63)*($C$32-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="D34" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$32/2)&gt;Parametros!$B$46:$B$54)*(($D$32/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($D$32/2)&gt;Parametros!$B$58:$B$59)*(($D$32/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($D$32&gt;Parametros!$B$46:$B$54)*($D$32-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($D$32&gt;Parametros!$B$58:$B$59)*($D$32-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$32/2)&gt;Parametros!$B$50:$B$58)*(($D$32/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$32/2)&gt;Parametros!$B$62:$B$63)*(($D$32/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$32&gt;Parametros!$B$50:$B$58)*($D$32-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$32&gt;Parametros!$B$62:$B$63)*($D$32-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="E34" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$32/2)&gt;Parametros!$B$46:$B$54)*(($E$32/2)-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT((($E$32/2)&gt;Parametros!$B$58:$B$59)*(($E$32/2)-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59)),SUMPRODUCT(($E$32&gt;Parametros!$B$46:$B$54)*($E$32-Parametros!$B$46:$B$54)*Parametros!$E$46:$E$54)+SUMPRODUCT(($E$32&gt;Parametros!$B$58:$B$59)*($E$32-Parametros!$B$58:$B$59)*Parametros!$E$58:$E$59))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$32/2)&gt;Parametros!$B$50:$B$58)*(($E$32/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$32/2)&gt;Parametros!$B$62:$B$63)*(($E$32/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$32&gt;Parametros!$B$50:$B$58)*($E$32-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$32&gt;Parametros!$B$62:$B$63)*($E$32-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
         <v/>
       </c>
       <c r="F34" s="17" t="inlineStr"/>
@@ -14850,15 +16448,15 @@
         </is>
       </c>
       <c r="C43" s="28">
-        <f>$C$25-IF($C$26=1,0,$C$25*Parametros!$C$29)</f>
+        <f>$C$25-IF($C$26=1,0,$C$25*Parametros!$C$33)</f>
         <v/>
       </c>
       <c r="D43" s="28">
-        <f>$D$25-IF($D$26=1,0,$D$25*Parametros!$C$29)</f>
+        <f>$D$25-IF($D$26=1,0,$D$25*Parametros!$C$33)</f>
         <v/>
       </c>
       <c r="E43" s="28">
-        <f>$E$25-IF($E$26=1,0,$E$25*Parametros!$C$29)</f>
+        <f>$E$25-IF($E$26=1,0,$E$25*Parametros!$C$33)</f>
         <v/>
       </c>
       <c r="F43" s="17" t="inlineStr">
@@ -15041,15 +16639,15 @@
         </is>
       </c>
       <c r="C6" s="28">
-        <f>Inputs!$C$27*Parametros!$C$32</f>
+        <f>Inputs!$C$27*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="D6" s="28">
-        <f>Inputs!$D$27*Parametros!$C$32</f>
+        <f>Inputs!$D$27*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="E6" s="28">
-        <f>Inputs!$E$27*Parametros!$C$32</f>
+        <f>Inputs!$E$27*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="F6" s="17" t="inlineStr"/>
@@ -15066,15 +16664,15 @@
         </is>
       </c>
       <c r="C7" s="28">
-        <f>Inputs!$C$28*Parametros!$C$32</f>
+        <f>Inputs!$C$28*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="D7" s="28">
-        <f>Inputs!$D$28*Parametros!$C$32</f>
+        <f>Inputs!$D$28*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="E7" s="28">
-        <f>Inputs!$E$28*Parametros!$C$32</f>
+        <f>Inputs!$E$28*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="F7" s="17" t="inlineStr"/>
@@ -15091,15 +16689,15 @@
         </is>
       </c>
       <c r="C8" s="28">
-        <f>Inputs!$C$29*Parametros!$C$33</f>
+        <f>Inputs!$C$29*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="D8" s="28">
-        <f>Inputs!$D$29*Parametros!$C$33</f>
+        <f>Inputs!$D$29*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>Inputs!$E$29*Parametros!$C$33</f>
+        <f>Inputs!$E$29*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -15120,15 +16718,15 @@
         </is>
       </c>
       <c r="C9" s="28">
-        <f>Inputs!$C$30*Parametros!$C$32</f>
+        <f>Inputs!$C$30*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>Inputs!$D$30*Parametros!$C$32</f>
+        <f>Inputs!$D$30*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>Inputs!$E$30*Parametros!$C$32</f>
+        <f>Inputs!$E$30*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="F9" s="17" t="inlineStr"/>
@@ -15478,15 +17076,15 @@
         </is>
       </c>
       <c r="C24" s="27">
-        <f>Inputs!$C$28*$C$23*(Parametros!$C$32-Parametros!$C$33)</f>
+        <f>Inputs!$C$28*$C$23*(Parametros!$C$36-Parametros!$C$37)</f>
         <v/>
       </c>
       <c r="D24" s="27">
-        <f>Inputs!$D$28*$D$23*(Parametros!$C$32-Parametros!$C$33)</f>
+        <f>Inputs!$D$28*$D$23*(Parametros!$C$36-Parametros!$C$37)</f>
         <v/>
       </c>
       <c r="E24" s="27">
-        <f>Inputs!$E$28*$E$23*(Parametros!$C$32-Parametros!$C$33)</f>
+        <f>Inputs!$E$28*$E$23*(Parametros!$C$36-Parametros!$C$37)</f>
         <v/>
       </c>
       <c r="F24" s="17" t="inlineStr"/>
@@ -15544,15 +17142,15 @@
         </is>
       </c>
       <c r="C27" s="27">
-        <f>$C$26*Parametros!$C$32</f>
+        <f>$C$26*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="D27" s="27">
-        <f>$D$26*Parametros!$C$32</f>
+        <f>$D$26*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="E27" s="27">
-        <f>$E$26*Parametros!$C$32</f>
+        <f>$E$26*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="F27" s="17" t="inlineStr"/>

--- a/01-modelo/M1_modelo_comparativo.xlsx
+++ b/01-modelo/M1_modelo_comparativo.xlsx
@@ -24,6 +24,7 @@
     <sheet name="RiscoLaboral" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Alertas" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Conjuge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Tesouraria" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -201,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -272,6 +273,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -856,6 +859,117 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Saldo de tesouraria acumulado — ano 1</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Saldo acumulado</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Tesouraria'!$C$24:$N$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>mês</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>euros</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -947,6 +1061,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1253,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1424,124 +1565,152 @@
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>Tesouraria — ano 1 mês a mês, fundo de maneio e vista a três anos. Responde à pergunta que vem antes de todas as outras: quanto dinheiro é preciso ter na mão antes de abrir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>Alertas — verificação de plausibilidade empresarial e semáforo global. Enquanto houver um alerta bloqueante ativo, nenhum número sai do ficheiro.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Três break-even distintos, que nunca se misturam</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Break-even FISCAL (folha PontoViragem): a partir de que nível de custos reais uma estrutura fiscal passa a ser melhor do que outra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Rentabilidade e solvência são perguntas diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="41" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Break-even OPERACIONAL (folha BreakEven): a partir de que faturação a clínica cobre os custos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
+          <t>As folhas das quatro vias, o Comparativo e o BreakEven dizem se o negócio é rentável. A folha Tesouraria diz se sobrevive ao primeiro ano. Um negócio rentável fica sem dinheiro quando o investimento se paga à cabeça, a receita sobe devagar e há pagamentos que chegam em bloco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="41" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>RENDIMENTO-ALVO (folha BreakEven): que faturação é precisa para a fundadora receber o que quer receber. Nunca usar a mesma palavra para os três numa frase dita à cliente.</t>
+          <t>Para quem abre pela primeira vez, a segunda pergunta é a que morde primeiro. O número a dar à cliente antes de qualquer conversa sobre ENI ou sociedade é o total de dinheiro necessário antes de abrir, na folha Tesouraria.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Convenções</t>
+          <t>Três break-even distintos, que nunca se misturam</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Azul sobre amarelo = célula de preenchimento. Verde = ligação a outra folha. Preto = fórmula. Fundo laranja na folha Parâmetros = parâmetro por confirmar.</t>
+          <t>Break-even FISCAL (folha PontoViragem): a partir de que nível de custos reais uma estrutura fiscal passa a ser melhor do que outra.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Percentagens guardadas como fração. Valores anuais, em euros, sem IVA salvo indicação.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Três decisões de modelação que são discutíveis e estão assumidas</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="41" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>1. A comparação entre vias usa o IRS diferencial (coleta do agregado com a atividade menos coleta sem a atividade), e não o IRS total. É o que torna as quatro vias comparáveis quando o cônjuge tem rendimento próprio.</t>
+          <t>Break-even OPERACIONAL (folha BreakEven): a partir de que faturação a clínica cobre os custos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>RENDIMENTO-ALVO (folha BreakEven): que faturação é precisa para a fundadora receber o que quer receber. Nunca usar a mesma palavra para os três numa frase dita à cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Convenções</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t>Azul sobre amarelo = célula de preenchimento. Verde = ligação a outra folha. Preto = fórmula. Fundo laranja na folha Parâmetros = parâmetro por confirmar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Percentagens guardadas como fração. Valores anuais, em euros, sem IVA salvo indicação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Três decisões de modelação que são discutíveis e estão assumidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="41" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>1. A comparação entre vias usa o IRS diferencial (coleta do agregado com a atividade menos coleta sem a atividade), e não o IRS total. É o que torna as quatro vias comparáveis quando o cônjuge tem rendimento próprio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
           <t>2. O investimento inicial está fora da comparação anual e isolado numa linha de memória. Misturá-lo com o resultado corrente faria a via 1 parecer melhor do que é no ano 1.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>3. Nas vias societárias, o valor retido na sociedade é mostrado separado do líquido da sócia. Somar os dois responderia a uma pergunta que a cliente não fez.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="B38" s="3" t="inlineStr">
+    <row r="42" ht="28" customHeight="1">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>4. O modelo de colaboração é uma escolha única para todos os colaboradores. A ata admite modelos distintos por profissional; uma combinação exige correr o modelo com a faturação repartida. Registado em R1-30.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="2" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Para quem é este trabalho</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="41" customHeight="1">
-      <c r="B40" s="3" t="inlineStr">
+    <row r="44" ht="41" customHeight="1">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>A cliente final tem zero experiência empresarial e está a montar a primeira estrutura da vida dela, com arrendamento, obras e integração de pessoas. As consequências de a matemática não funcionar não são um relatório desatualizado — são dívida pessoal.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="41" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
+    <row r="45" ht="41" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Consequência prática para quem usar este modelo: toda a conclusão tem de acabar em unidades que a cliente controla — doentes por dia, euros por mês — e o cenário de baixa tem de ser apresentado em dinheiro, não só a recomendação.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="2" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Reprodução</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="47" ht="28" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Este ficheiro é gerado por build_m1.py. Alterações estruturais fazem-se no script e regenera-se; alterações de valores fazem-se nas células amarelas.</t>
         </is>
@@ -8626,6 +8795,1523 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>M1 — Tesouraria do ano 1 e necessidade de fundo de maneio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Um negócio pode ser rentável e mesmo assim ficar sem dinheiro. O investimento paga-se todo no início, a receita sobe devagar, e há pagamentos que chegam em bloco. Esta folha responde à única pergunta que importa antes de assinar seja o que for: quanto dinheiro é preciso ter na mão para chegar ao fim do primeiro ano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Fundos necessários no arranque</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Investimento em obras, equipamento e software</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="C5" s="35">
+        <f>Inputs!$D$27+Inputs!$D$28+Inputs!$D$29+Inputs!$D$30</f>
+        <v/>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>IVA irrecuperável sobre o investimento</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>IVA_IRR</t>
+        </is>
+      </c>
+      <c r="C6" s="35">
+        <f>IVA!$D$10</f>
+        <v/>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Sai da conta e não volta: a fisioterapia é isenta sem direito à dedução.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Caução do arrendamento (meses de renda)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>MESES_CAUC</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Rubrica que quase sempre se esquece no plano de investimento. Confirmar com a proposta de arrendamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Caução do arrendamento</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>CAUCAO</t>
+        </is>
+      </c>
+      <c r="C8" s="28">
+        <f>$C$7*Inputs!$D$19/12</f>
+        <v/>
+      </c>
+      <c r="D8" s="17" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL A DESEMBOLSAR NO ARRANQUE</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>ARRANQUE</t>
+        </is>
+      </c>
+      <c r="C9" s="27">
+        <f>$C$5+$C$6+$C$8</f>
+        <v/>
+      </c>
+      <c r="D9" s="17" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Ano 1, mês a mês</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n"/>
+      <c r="P11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 2</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 3</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 4</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 5</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 6</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 7</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 8</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 9</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 10</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 11</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Mês 12</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>Ano 1</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Taxa de ocupação dos gabinetes</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>OCUP</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P13" s="17" t="inlineStr">
+        <is>
+          <t>RAMPA DE ARRANQUE. É a fila de inputs mais importante desta folha e a que ninguém quer preencher com honestidade. Uma clínica nova não abre à ocupação de cruzeiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Consultas do mês</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>CONS</t>
+        </is>
+      </c>
+      <c r="C14" s="24">
+        <f>(Operacao!$D$21/12)*C$13</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>(Operacao!$D$21/12)*D$13</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>(Operacao!$D$21/12)*E$13</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>(Operacao!$D$21/12)*F$13</f>
+        <v/>
+      </c>
+      <c r="G14" s="24">
+        <f>(Operacao!$D$21/12)*G$13</f>
+        <v/>
+      </c>
+      <c r="H14" s="24">
+        <f>(Operacao!$D$21/12)*H$13</f>
+        <v/>
+      </c>
+      <c r="I14" s="24">
+        <f>(Operacao!$D$21/12)*I$13</f>
+        <v/>
+      </c>
+      <c r="J14" s="24">
+        <f>(Operacao!$D$21/12)*J$13</f>
+        <v/>
+      </c>
+      <c r="K14" s="24">
+        <f>(Operacao!$D$21/12)*K$13</f>
+        <v/>
+      </c>
+      <c r="L14" s="24">
+        <f>(Operacao!$D$21/12)*L$13</f>
+        <v/>
+      </c>
+      <c r="M14" s="24">
+        <f>(Operacao!$D$21/12)*M$13</f>
+        <v/>
+      </c>
+      <c r="N14" s="24">
+        <f>(Operacao!$D$21/12)*N$13</f>
+        <v/>
+      </c>
+      <c r="O14" s="52">
+        <f>SUM(C14:N14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="17" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Faturação do mês</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
+      <c r="C15" s="27">
+        <f>C$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="D15" s="27">
+        <f>D$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>E$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="F15" s="27">
+        <f>F$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="G15" s="27">
+        <f>G$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="H15" s="27">
+        <f>H$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="I15" s="27">
+        <f>I$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="J15" s="27">
+        <f>J$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="K15" s="27">
+        <f>K$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="L15" s="27">
+        <f>L$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="M15" s="27">
+        <f>M$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="N15" s="27">
+        <f>N$14*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="O15" s="43">
+        <f>SUM(C15:N15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="17" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>% recebida no próprio mês</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>PCT_PRONTO</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P16" s="17" t="inlineStr">
+        <is>
+          <t>Consultas particulares pagam-se na hora; subsistemas e seguros pagam a 30 dias ou mais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Recebimentos</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="C17" s="27">
+        <f>C$15*C$16</f>
+        <v/>
+      </c>
+      <c r="D17" s="27">
+        <f>D$15*D$16+C$15*(1-C$16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>E$15*E$16+D$15*(1-D$16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="27">
+        <f>F$15*F$16+E$15*(1-E$16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="27">
+        <f>G$15*G$16+F$15*(1-F$16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="27">
+        <f>H$15*H$16+G$15*(1-G$16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="27">
+        <f>I$15*I$16+H$15*(1-H$16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="27">
+        <f>J$15*J$16+I$15*(1-I$16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="27">
+        <f>K$15*K$16+J$15*(1-J$16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="27">
+        <f>L$15*L$16+K$15*(1-K$16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="27">
+        <f>M$15*M$16+L$15*(1-L$16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="27">
+        <f>N$15*N$16+M$15*(1-M$16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="43">
+        <f>SUM(C17:N17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="17" t="inlineStr">
+        <is>
+          <t>O desfasamento entre faturar e receber é dinheiro que falta em caixa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Custos variáveis (consumíveis e colaboradores)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="C18" s="28">
+        <f>C$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="D18" s="28">
+        <f>D$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="E18" s="28">
+        <f>E$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>F$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="G18" s="28">
+        <f>G$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="H18" s="28">
+        <f>H$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="I18" s="28">
+        <f>I$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="J18" s="28">
+        <f>J$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="K18" s="28">
+        <f>K$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="L18" s="28">
+        <f>L$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="M18" s="28">
+        <f>M$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="N18" s="28">
+        <f>N$15*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="O18" s="43">
+        <f>SUM(C18:N18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="17" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Custos fixos</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="C19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="D19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="E19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="F19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="G19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="H19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="I19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="J19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="K19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="L19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="M19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="N19" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="O19" s="43">
+        <f>SUM(C19:N19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="17" t="inlineStr">
+        <is>
+          <t>Renda, condomínio, seguros, software e outros. Pagam-se haja ou não doentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Segurança Social</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="C20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="D20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="E20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="F20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="G20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="H20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="I20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="J20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="K20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="L20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="M20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="N20" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="O20" s="43">
+        <f>SUM(C20:N20)</f>
+        <v/>
+      </c>
+      <c r="P20" s="17" t="inlineStr">
+        <is>
+          <t>Aproximação de cruzeiro. No primeiro ano a base é a declarada, não o lucro do próprio ano. Ver R1-40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>IRS — pagamentos por conta</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>IRS_PC</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="43">
+        <f>SUM(C21:N21)</f>
+        <v/>
+      </c>
+      <c r="P21" s="17" t="inlineStr">
+        <is>
+          <t>A PREENCHER, e é uma armadilha clássica: no ano 1 os pagamentos por conta são calculados sobre o rendimento do ano ANTERIOR, no regime antigo. Paga-se IRS do passado enquanto se está a investir no futuro. Vencem em julho, setembro e dezembro — meses 7, 9 e 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Investimento e caução</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>INV_M</t>
+        </is>
+      </c>
+      <c r="C22" s="28">
+        <f>$C$9</f>
+        <v/>
+      </c>
+      <c r="D22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="43">
+        <f>SUM(C22:N22)</f>
+        <v/>
+      </c>
+      <c r="P22" s="17" t="inlineStr">
+        <is>
+          <t>Todo no mês 1. Se a empreitada for faseada, repartir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>SALDO DO MÊS</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>SALDO</t>
+        </is>
+      </c>
+      <c r="C23" s="27">
+        <f>C$17-C$18-C$19-C$20-C$21-C$22</f>
+        <v/>
+      </c>
+      <c r="D23" s="27">
+        <f>D$17-D$18-D$19-D$20-D$21-D$22</f>
+        <v/>
+      </c>
+      <c r="E23" s="27">
+        <f>E$17-E$18-E$19-E$20-E$21-E$22</f>
+        <v/>
+      </c>
+      <c r="F23" s="27">
+        <f>F$17-F$18-F$19-F$20-F$21-F$22</f>
+        <v/>
+      </c>
+      <c r="G23" s="27">
+        <f>G$17-G$18-G$19-G$20-G$21-G$22</f>
+        <v/>
+      </c>
+      <c r="H23" s="27">
+        <f>H$17-H$18-H$19-H$20-H$21-H$22</f>
+        <v/>
+      </c>
+      <c r="I23" s="27">
+        <f>I$17-I$18-I$19-I$20-I$21-I$22</f>
+        <v/>
+      </c>
+      <c r="J23" s="27">
+        <f>J$17-J$18-J$19-J$20-J$21-J$22</f>
+        <v/>
+      </c>
+      <c r="K23" s="27">
+        <f>K$17-K$18-K$19-K$20-K$21-K$22</f>
+        <v/>
+      </c>
+      <c r="L23" s="27">
+        <f>L$17-L$18-L$19-L$20-L$21-L$22</f>
+        <v/>
+      </c>
+      <c r="M23" s="27">
+        <f>M$17-M$18-M$19-M$20-M$21-M$22</f>
+        <v/>
+      </c>
+      <c r="N23" s="27">
+        <f>N$17-N$18-N$19-N$20-N$21-N$22</f>
+        <v/>
+      </c>
+      <c r="O23" s="43">
+        <f>SUM(C23:N23)</f>
+        <v/>
+      </c>
+      <c r="P23" s="17" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>SALDO ACUMULADO</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>ACUM</t>
+        </is>
+      </c>
+      <c r="C24" s="27">
+        <f>C$23</f>
+        <v/>
+      </c>
+      <c r="D24" s="27">
+        <f>C$24+D$23</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>D$24+E$23</f>
+        <v/>
+      </c>
+      <c r="F24" s="27">
+        <f>E$24+F$23</f>
+        <v/>
+      </c>
+      <c r="G24" s="27">
+        <f>F$24+G$23</f>
+        <v/>
+      </c>
+      <c r="H24" s="27">
+        <f>G$24+H$23</f>
+        <v/>
+      </c>
+      <c r="I24" s="27">
+        <f>H$24+I$23</f>
+        <v/>
+      </c>
+      <c r="J24" s="27">
+        <f>I$24+J$23</f>
+        <v/>
+      </c>
+      <c r="K24" s="27">
+        <f>J$24+K$23</f>
+        <v/>
+      </c>
+      <c r="L24" s="27">
+        <f>K$24+L$23</f>
+        <v/>
+      </c>
+      <c r="M24" s="27">
+        <f>L$24+M$23</f>
+        <v/>
+      </c>
+      <c r="N24" s="27">
+        <f>M$24+N$23</f>
+        <v/>
+      </c>
+      <c r="P24" s="17" t="inlineStr">
+        <is>
+          <t>É esta a linha que decide se o projeto sobrevive ao primeiro ano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Marcador do ponto mais baixo</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>MARC_MIN</t>
+        </is>
+      </c>
+      <c r="C25" s="24">
+        <f>IF(C$24=MIN($C$24:$N$24),1,0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>IF(D$24=MIN($C$24:$N$24),2,0)</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>IF(E$24=MIN($C$24:$N$24),3,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>IF(F$24=MIN($C$24:$N$24),4,0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>IF(G$24=MIN($C$24:$N$24),5,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="24">
+        <f>IF(H$24=MIN($C$24:$N$24),6,0)</f>
+        <v/>
+      </c>
+      <c r="I25" s="24">
+        <f>IF(I$24=MIN($C$24:$N$24),7,0)</f>
+        <v/>
+      </c>
+      <c r="J25" s="24">
+        <f>IF(J$24=MIN($C$24:$N$24),8,0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="24">
+        <f>IF(K$24=MIN($C$24:$N$24),9,0)</f>
+        <v/>
+      </c>
+      <c r="L25" s="24">
+        <f>IF(L$24=MIN($C$24:$N$24),10,0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="24">
+        <f>IF(M$24=MIN($C$24:$N$24),11,0)</f>
+        <v/>
+      </c>
+      <c r="N25" s="24">
+        <f>IF(N$24=MIN($C$24:$N$24),12,0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="17" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Marcador de recuperação</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>MARC</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="24">
+        <f>IF(AND(D$24&gt;=0,C$24&lt;0),2,0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>IF(AND(E$24&gt;=0,D$24&lt;0),3,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="24">
+        <f>IF(AND(F$24&gt;=0,E$24&lt;0),4,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="24">
+        <f>IF(AND(G$24&gt;=0,F$24&lt;0),5,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="24">
+        <f>IF(AND(H$24&gt;=0,G$24&lt;0),6,0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="24">
+        <f>IF(AND(I$24&gt;=0,H$24&lt;0),7,0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="24">
+        <f>IF(AND(J$24&gt;=0,I$24&lt;0),8,0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="24">
+        <f>IF(AND(K$24&gt;=0,J$24&lt;0),9,0)</f>
+        <v/>
+      </c>
+      <c r="L26" s="24">
+        <f>IF(AND(L$24&gt;=0,K$24&lt;0),10,0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="24">
+        <f>IF(AND(M$24&gt;=0,L$24&lt;0),11,0)</f>
+        <v/>
+      </c>
+      <c r="N26" s="24">
+        <f>IF(AND(N$24&gt;=0,M$24&lt;0),12,0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="17" t="inlineStr"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>NECESSIDADE MÁXIMA DE TESOURARIA</t>
+        </is>
+      </c>
+      <c r="C28" s="27">
+        <f>-MIN($C$24:$N$24)</f>
+        <v/>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>O ponto mais fundo do saldo acumulado. JÁ INCLUI o investimento e a caução, porque eles saem da mesma conta bancária — não somar outra vez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   da qual, investimento e caução</t>
+        </is>
+      </c>
+      <c r="C29" s="27">
+        <f>$C$9</f>
+        <v/>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Desembolso de uma só vez, no arranque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   da qual, cobertura do défice operacional</t>
+        </is>
+      </c>
+      <c r="C30" s="27">
+        <f>-MIN($C$24:$N$24)-$C$9</f>
+        <v/>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>O que a operação consome enquanto a receita não chega para os custos. É a parte que quase ninguém orça, e é a que apanha quem abre pela primeira vez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Mês em que o saldo acumulado atinge o ponto mais baixo</t>
+        </is>
+      </c>
+      <c r="C31" s="23">
+        <f>MAX($C$25:$N$25)</f>
+        <v/>
+      </c>
+      <c r="E31" s="17" t="inlineStr"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Mês em que o saldo acumulado volta a ser positivo</t>
+        </is>
+      </c>
+      <c r="C32" s="23">
+        <f>IF(MAX($C$26:$N$26)=0,"Não recupera dentro do ano 1",MAX($C$26:$N$26))</f>
+        <v/>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>Se não recuperar dentro do ano 1, o fundo de maneio tem de cobrir também o ano 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Margem de segurança (meses de custos fixos)</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>A PREENCHER. Nenhuma projeção acerta. Três meses é uma convenção prudente para quem não tem outra fonte de rendimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Margem de segurança, em euros</t>
+        </is>
+      </c>
+      <c r="C35" s="28">
+        <f>$C$33*BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL DE DINHEIRO NECESSÁRIO ANTES DE ABRIR</t>
+        </is>
+      </c>
+      <c r="C36" s="53">
+        <f>$C$28+$C$35</f>
+        <v/>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>Investimento, caução e fundo de maneio. É este o número a dizer à cliente antes de qualquer conversa sobre estrutura fiscal. Se ela não o tiver ou não o conseguir financiar, a discussão sobre ENI ou sociedade é prematura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Visão a três anos</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Ano 1</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Ano 2</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Ano 3</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Taxa de ocupação média do ano</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>OCUP</t>
+        </is>
+      </c>
+      <c r="C40" s="13">
+        <f>AVERAGE($C$13:$N$13)</f>
+        <v/>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>Ano 1 é a média da rampa. Anos 2 e 3 a preencher — e a justificar com o plano de captação de doentes, que não existe e é o pressuposto silencioso de tudo isto (R1-41).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>Faturação</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
+      <c r="C41" s="27">
+        <f>Operacao!$D$21*$C$40*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="D41" s="27">
+        <f>Operacao!$D$21*$D$40*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="E41" s="27">
+        <f>Operacao!$D$21*$E$40*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="F41" s="17" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Custos variáveis</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="C42" s="28">
+        <f>$C$41*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="D42" s="28">
+        <f>$D$41*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="E42" s="28">
+        <f>$E$41*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="F42" s="17" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Custos fixos</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="C43" s="35">
+        <f>BreakEven!$D$10</f>
+        <v/>
+      </c>
+      <c r="D43" s="35">
+        <f>BreakEven!$D$10</f>
+        <v/>
+      </c>
+      <c r="E43" s="35">
+        <f>BreakEven!$D$10</f>
+        <v/>
+      </c>
+      <c r="F43" s="17" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Resultado operacional</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="C44" s="27">
+        <f>$C$41-$C$42-$C$43</f>
+        <v/>
+      </c>
+      <c r="D44" s="27">
+        <f>$D$41-$D$42-$D$43</f>
+        <v/>
+      </c>
+      <c r="E44" s="27">
+        <f>$E$41-$E$42-$E$43</f>
+        <v/>
+      </c>
+      <c r="F44" s="17" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Impostos e contribuições estimados</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="C45" s="28">
+        <f>MAX(0,$C$44)*V2_ENI_ContOrg!$D$27</f>
+        <v/>
+      </c>
+      <c r="D45" s="28">
+        <f>MAX(0,$D$44)*V2_ENI_ContOrg!$D$27</f>
+        <v/>
+      </c>
+      <c r="E45" s="28">
+        <f>MAX(0,$E$44)*V2_ENI_ContOrg!$D$27</f>
+        <v/>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>Aplica a taxa de esforço da via 2 no cenário Base. Aproximação: a taxa real varia com o nível de rendimento. Ver R1-33.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Resultado líquido</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>LIQ</t>
+        </is>
+      </c>
+      <c r="C46" s="27">
+        <f>$C$44-$C$45</f>
+        <v/>
+      </c>
+      <c r="D46" s="27">
+        <f>$D$44-$D$45</f>
+        <v/>
+      </c>
+      <c r="E46" s="27">
+        <f>$E$44-$E$45</f>
+        <v/>
+      </c>
+      <c r="F46" s="17" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>Caixa acumulada desde o arranque</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>CX</t>
+        </is>
+      </c>
+      <c r="C47" s="27">
+        <f>$C$46-$C$9</f>
+        <v/>
+      </c>
+      <c r="D47" s="27">
+        <f>$C$47+$D$46</f>
+        <v/>
+      </c>
+      <c r="E47" s="27">
+        <f>$D$47+$E$46</f>
+        <v/>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>Inclui o desembolso inicial. O ano em que esta linha passa a positiva é o payback real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>Esta visão a três anos assume custos fixos constantes e preço constante. Não é uma projeção financeira completa — é o suficiente para responder a «quando é que recupero o que meti» e a «o ano 1 é sustentável». Uma projeção completa exigiria inflação de custos, renovação de equipamento e evolução da tabela de preços, e nenhuma dessas coisas está informada. Registado em R1-42.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="E33:N33"/>
+    <mergeCell ref="E36:N36"/>
+    <mergeCell ref="A49:P49"/>
+    <mergeCell ref="E31:N31"/>
+    <mergeCell ref="E30:N30"/>
+    <mergeCell ref="E29:N29"/>
+    <mergeCell ref="E32:N32"/>
+    <mergeCell ref="E28:N28"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/01-modelo/M1_modelo_comparativo.xlsx
+++ b/01-modelo/M1_modelo_comparativo.xlsx
@@ -2992,7 +2992,7 @@
         <v/>
       </c>
       <c r="C8" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B8))-MAX(0,D8-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B8))-MAX(0,D8-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D8" s="28">
@@ -3000,7 +3000,7 @@
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C8+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C8+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$50:$B$58)*((C8+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$62:$B$63)*((C8+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C8+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C8+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C8+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$55:$B$63)*((C8+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C8+$C$5)&gt;Parametros!$B$67:$B$68)*((C8+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F8" s="43">
@@ -3016,7 +3016,7 @@
         <v/>
       </c>
       <c r="I8" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G8+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G8+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$50:$B$58)*((G8+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$62:$B$63)*((G8+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G8+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G8+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G8+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$55:$B$63)*((G8+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G8+$C$5)&gt;Parametros!$B$67:$B$68)*((G8+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J8" s="43">
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="C9" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B9))-MAX(0,D9-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B9))-MAX(0,D9-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D9" s="28">
@@ -3049,7 +3049,7 @@
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C9+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C9+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$50:$B$58)*((C9+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$62:$B$63)*((C9+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C9+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C9+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C9+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$55:$B$63)*((C9+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C9+$C$5)&gt;Parametros!$B$67:$B$68)*((C9+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F9" s="43">
@@ -3065,7 +3065,7 @@
         <v/>
       </c>
       <c r="I9" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G9+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G9+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$50:$B$58)*((G9+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$62:$B$63)*((G9+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G9+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G9+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G9+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$55:$B$63)*((G9+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G9+$C$5)&gt;Parametros!$B$67:$B$68)*((G9+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J9" s="43">
@@ -3090,7 +3090,7 @@
         <v/>
       </c>
       <c r="C10" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B10))-MAX(0,D10-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B10))-MAX(0,D10-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D10" s="28">
@@ -3098,7 +3098,7 @@
         <v/>
       </c>
       <c r="E10" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C10+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C10+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$50:$B$58)*((C10+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$62:$B$63)*((C10+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C10+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C10+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C10+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$55:$B$63)*((C10+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C10+$C$5)&gt;Parametros!$B$67:$B$68)*((C10+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F10" s="43">
@@ -3114,7 +3114,7 @@
         <v/>
       </c>
       <c r="I10" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G10+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G10+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$50:$B$58)*((G10+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$62:$B$63)*((G10+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G10+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G10+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G10+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$55:$B$63)*((G10+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G10+$C$5)&gt;Parametros!$B$67:$B$68)*((G10+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J10" s="43">
@@ -3139,7 +3139,7 @@
         <v/>
       </c>
       <c r="C11" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B11))-MAX(0,D11-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B11))-MAX(0,D11-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D11" s="28">
@@ -3147,7 +3147,7 @@
         <v/>
       </c>
       <c r="E11" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C11+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C11+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$50:$B$58)*((C11+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$62:$B$63)*((C11+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C11+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C11+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C11+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$55:$B$63)*((C11+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C11+$C$5)&gt;Parametros!$B$67:$B$68)*((C11+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F11" s="43">
@@ -3163,7 +3163,7 @@
         <v/>
       </c>
       <c r="I11" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G11+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G11+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$50:$B$58)*((G11+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$62:$B$63)*((G11+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G11+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G11+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G11+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$55:$B$63)*((G11+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G11+$C$5)&gt;Parametros!$B$67:$B$68)*((G11+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J11" s="43">
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="C12" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B12))-MAX(0,D12-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B12))-MAX(0,D12-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D12" s="28">
@@ -3196,7 +3196,7 @@
         <v/>
       </c>
       <c r="E12" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C12+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C12+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$50:$B$58)*((C12+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$62:$B$63)*((C12+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C12+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C12+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C12+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$55:$B$63)*((C12+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C12+$C$5)&gt;Parametros!$B$67:$B$68)*((C12+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F12" s="43">
@@ -3212,7 +3212,7 @@
         <v/>
       </c>
       <c r="I12" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G12+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G12+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$50:$B$58)*((G12+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$62:$B$63)*((G12+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G12+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G12+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G12+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$55:$B$63)*((G12+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G12+$C$5)&gt;Parametros!$B$67:$B$68)*((G12+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J12" s="43">
@@ -3237,7 +3237,7 @@
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B13))-MAX(0,D13-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B13))-MAX(0,D13-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D13" s="28">
@@ -3245,7 +3245,7 @@
         <v/>
       </c>
       <c r="E13" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C13+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C13+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$50:$B$58)*((C13+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$62:$B$63)*((C13+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C13+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C13+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C13+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$55:$B$63)*((C13+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C13+$C$5)&gt;Parametros!$B$67:$B$68)*((C13+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F13" s="43">
@@ -3261,7 +3261,7 @@
         <v/>
       </c>
       <c r="I13" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G13+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G13+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$50:$B$58)*((G13+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$62:$B$63)*((G13+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G13+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G13+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G13+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$55:$B$63)*((G13+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G13+$C$5)&gt;Parametros!$B$67:$B$68)*((G13+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J13" s="43">
@@ -3286,7 +3286,7 @@
         <v/>
       </c>
       <c r="C14" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B14))-MAX(0,D14-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B14))-MAX(0,D14-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D14" s="28">
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C14+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C14+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$50:$B$58)*((C14+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$62:$B$63)*((C14+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C14+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C14+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C14+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$55:$B$63)*((C14+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C14+$C$5)&gt;Parametros!$B$67:$B$68)*((C14+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F14" s="43">
@@ -3310,7 +3310,7 @@
         <v/>
       </c>
       <c r="I14" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G14+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G14+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$50:$B$58)*((G14+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$62:$B$63)*((G14+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G14+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G14+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G14+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$55:$B$63)*((G14+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G14+$C$5)&gt;Parametros!$B$67:$B$68)*((G14+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J14" s="43">
@@ -3335,7 +3335,7 @@
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B15))-MAX(0,D15-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B15))-MAX(0,D15-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D15" s="28">
@@ -3343,7 +3343,7 @@
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C15+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C15+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$50:$B$58)*((C15+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$62:$B$63)*((C15+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C15+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C15+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C15+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$55:$B$63)*((C15+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C15+$C$5)&gt;Parametros!$B$67:$B$68)*((C15+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F15" s="43">
@@ -3359,7 +3359,7 @@
         <v/>
       </c>
       <c r="I15" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G15+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G15+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$50:$B$58)*((G15+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$62:$B$63)*((G15+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G15+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G15+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G15+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$55:$B$63)*((G15+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G15+$C$5)&gt;Parametros!$B$67:$B$68)*((G15+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J15" s="43">
@@ -3384,7 +3384,7 @@
         <v/>
       </c>
       <c r="C16" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B16))-MAX(0,D16-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B16))-MAX(0,D16-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D16" s="28">
@@ -3392,7 +3392,7 @@
         <v/>
       </c>
       <c r="E16" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C16+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C16+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$50:$B$58)*((C16+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$62:$B$63)*((C16+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C16+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C16+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C16+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$55:$B$63)*((C16+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C16+$C$5)&gt;Parametros!$B$67:$B$68)*((C16+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F16" s="43">
@@ -3408,7 +3408,7 @@
         <v/>
       </c>
       <c r="I16" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G16+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G16+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$50:$B$58)*((G16+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$62:$B$63)*((G16+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G16+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G16+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G16+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$55:$B$63)*((G16+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G16+$C$5)&gt;Parametros!$B$67:$B$68)*((G16+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J16" s="43">
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="C17" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B17))-MAX(0,D17-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B17))-MAX(0,D17-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D17" s="28">
@@ -3441,7 +3441,7 @@
         <v/>
       </c>
       <c r="E17" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C17+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C17+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$50:$B$58)*((C17+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$62:$B$63)*((C17+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C17+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C17+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C17+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$55:$B$63)*((C17+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C17+$C$5)&gt;Parametros!$B$67:$B$68)*((C17+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F17" s="43">
@@ -3457,7 +3457,7 @@
         <v/>
       </c>
       <c r="I17" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G17+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G17+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$50:$B$58)*((G17+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$62:$B$63)*((G17+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G17+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G17+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G17+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$55:$B$63)*((G17+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G17+$C$5)&gt;Parametros!$B$67:$B$68)*((G17+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J17" s="43">
@@ -3482,7 +3482,7 @@
         <v/>
       </c>
       <c r="C18" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B18))-MAX(0,D18-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B18))-MAX(0,D18-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D18" s="28">
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="E18" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C18+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C18+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$50:$B$58)*((C18+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$62:$B$63)*((C18+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C18+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C18+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C18+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$55:$B$63)*((C18+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C18+$C$5)&gt;Parametros!$B$67:$B$68)*((C18+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F18" s="43">
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="I18" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G18+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G18+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$50:$B$58)*((G18+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$62:$B$63)*((G18+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G18+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G18+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G18+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$55:$B$63)*((G18+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G18+$C$5)&gt;Parametros!$B$67:$B$68)*((G18+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J18" s="43">
@@ -3531,7 +3531,7 @@
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B19))-MAX(0,D19-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B19))-MAX(0,D19-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D19" s="28">
@@ -3539,7 +3539,7 @@
         <v/>
       </c>
       <c r="E19" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C19+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C19+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$50:$B$58)*((C19+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$62:$B$63)*((C19+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C19+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C19+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C19+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$55:$B$63)*((C19+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C19+$C$5)&gt;Parametros!$B$67:$B$68)*((C19+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F19" s="43">
@@ -3555,7 +3555,7 @@
         <v/>
       </c>
       <c r="I19" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G19+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G19+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$50:$B$58)*((G19+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$62:$B$63)*((G19+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G19+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G19+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G19+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$55:$B$63)*((G19+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G19+$C$5)&gt;Parametros!$B$67:$B$68)*((G19+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J19" s="43">
@@ -3580,7 +3580,7 @@
         <v/>
       </c>
       <c r="C20" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B20))-MAX(0,D20-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B20))-MAX(0,D20-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D20" s="28">
@@ -3588,7 +3588,7 @@
         <v/>
       </c>
       <c r="E20" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C20+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C20+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$50:$B$58)*((C20+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$62:$B$63)*((C20+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C20+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C20+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C20+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$55:$B$63)*((C20+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C20+$C$5)&gt;Parametros!$B$67:$B$68)*((C20+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F20" s="43">
@@ -3604,7 +3604,7 @@
         <v/>
       </c>
       <c r="I20" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G20+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G20+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$50:$B$58)*((G20+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$62:$B$63)*((G20+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G20+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G20+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G20+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$55:$B$63)*((G20+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G20+$C$5)&gt;Parametros!$B$67:$B$68)*((G20+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J20" s="43">
@@ -3629,7 +3629,7 @@
         <v/>
       </c>
       <c r="C21" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B21))-MAX(0,D21-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B21))-MAX(0,D21-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D21" s="28">
@@ -3637,7 +3637,7 @@
         <v/>
       </c>
       <c r="E21" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C21+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C21+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$50:$B$58)*((C21+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$62:$B$63)*((C21+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C21+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C21+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C21+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$55:$B$63)*((C21+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C21+$C$5)&gt;Parametros!$B$67:$B$68)*((C21+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F21" s="43">
@@ -3653,7 +3653,7 @@
         <v/>
       </c>
       <c r="I21" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G21+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G21+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$50:$B$58)*((G21+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$62:$B$63)*((G21+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G21+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G21+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G21+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$55:$B$63)*((G21+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G21+$C$5)&gt;Parametros!$B$67:$B$68)*((G21+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J21" s="43">
@@ -3678,7 +3678,7 @@
         <v/>
       </c>
       <c r="C22" s="28">
-        <f>$C$4*Parametros!$C$19+MAX(0,$C$4*Parametros!$C$20-(Parametros!$C$21+B22))-MAX(0,D22-$C$4*Parametros!$C$22)</f>
+        <f>$C$4*Parametros!$C$24+MAX(0,$C$4*Parametros!$C$25-(Parametros!$C$26+B22))-MAX(0,D22-$C$4*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D22" s="28">
@@ -3686,7 +3686,7 @@
         <v/>
       </c>
       <c r="E22" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((C22+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((C22+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$50:$B$58)*((C22+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$62:$B$63)*((C22+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((C22+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((C22+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((C22+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$55:$B$63)*((C22+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((C22+$C$5)&gt;Parametros!$B$67:$B$68)*((C22+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F22" s="43">
@@ -3702,7 +3702,7 @@
         <v/>
       </c>
       <c r="I22" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$50:$B$58)*(((G22+$C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$62:$B$63)*(((G22+$C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$50:$B$58)*((G22+$C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$62:$B$63)*((G22+$C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$50:$B$58)*((($C$5)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$62:$B$63)*((($C$5)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT((($C$5)&gt;Parametros!$B$50:$B$58)*(($C$5)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$5)&gt;Parametros!$B$62:$B$63)*(($C$5)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$55:$B$63)*(((G22+$C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((G22+$C$5)/2)&gt;Parametros!$B$67:$B$68)*(((G22+$C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$55:$B$63)*((G22+$C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((G22+$C$5)&gt;Parametros!$B$67:$B$68)*((G22+$C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$55:$B$63)*((($C$5)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((($C$5)/2)&gt;Parametros!$B$67:$B$68)*((($C$5)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT((($C$5)&gt;Parametros!$B$55:$B$63)*(($C$5)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$5)&gt;Parametros!$B$67:$B$68)*(($C$5)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="J22" s="43">
@@ -4275,7 +4275,7 @@
         <v/>
       </c>
       <c r="D23" s="28">
-        <f>A23*Parametros!$C$19+MAX(0,A23*Parametros!$C$20-B23)-MAX(0,E23-A23*Parametros!$C$22)</f>
+        <f>A23*Parametros!$C$24+MAX(0,A23*Parametros!$C$25-B23)-MAX(0,E23-A23*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E23" s="28">
@@ -4283,7 +4283,7 @@
         <v/>
       </c>
       <c r="F23" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D23+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D23+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D23+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D23+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D23+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D23+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D23+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D23+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D23+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D23+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D23+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D23+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D23+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D23+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D23+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D23+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G23" s="43">
@@ -4291,15 +4291,15 @@
         <v/>
       </c>
       <c r="H23" s="28">
-        <f>MAX(0,A23-B23-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I23)</f>
+        <f>MAX(0,A23-B23-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I23)</f>
         <v/>
       </c>
       <c r="I23" s="28">
-        <f>MAX(MIN(MAX(A23-B23-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A23-B23-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J23" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H23+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H23+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H23+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H23+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H23+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H23+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H23+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H23+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H23+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H23+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H23+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H23+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H23+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H23+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H23+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H23+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K23" s="43">
@@ -4307,15 +4307,15 @@
         <v/>
       </c>
       <c r="L23" s="28">
-        <f>A23-B23-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A23-B23-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M23" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L23,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L23,0)</f>
         <v/>
       </c>
       <c r="N23" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M23+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M23+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M23+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M23+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M23+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M23+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M23+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M23+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M23+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M23+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M23+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M23+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M23+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M23+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M23+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M23+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O23" s="43">
@@ -4348,7 +4348,7 @@
         <v/>
       </c>
       <c r="D24" s="28">
-        <f>A24*Parametros!$C$19+MAX(0,A24*Parametros!$C$20-B24)-MAX(0,E24-A24*Parametros!$C$22)</f>
+        <f>A24*Parametros!$C$24+MAX(0,A24*Parametros!$C$25-B24)-MAX(0,E24-A24*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E24" s="28">
@@ -4356,7 +4356,7 @@
         <v/>
       </c>
       <c r="F24" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D24+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D24+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D24+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D24+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D24+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D24+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D24+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D24+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D24+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D24+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D24+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D24+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D24+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D24+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D24+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D24+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G24" s="43">
@@ -4364,15 +4364,15 @@
         <v/>
       </c>
       <c r="H24" s="28">
-        <f>MAX(0,A24-B24-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I24)</f>
+        <f>MAX(0,A24-B24-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I24)</f>
         <v/>
       </c>
       <c r="I24" s="28">
-        <f>MAX(MIN(MAX(A24-B24-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A24-B24-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J24" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H24+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H24+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H24+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H24+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H24+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H24+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H24+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H24+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H24+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H24+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H24+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H24+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H24+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H24+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H24+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H24+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K24" s="43">
@@ -4380,15 +4380,15 @@
         <v/>
       </c>
       <c r="L24" s="28">
-        <f>A24-B24-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A24-B24-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M24" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L24,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L24,0)</f>
         <v/>
       </c>
       <c r="N24" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M24+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M24+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M24+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M24+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M24+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M24+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M24+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M24+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M24+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M24+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M24+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M24+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M24+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M24+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M24+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M24+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O24" s="43">
@@ -4421,7 +4421,7 @@
         <v/>
       </c>
       <c r="D25" s="28">
-        <f>A25*Parametros!$C$19+MAX(0,A25*Parametros!$C$20-B25)-MAX(0,E25-A25*Parametros!$C$22)</f>
+        <f>A25*Parametros!$C$24+MAX(0,A25*Parametros!$C$25-B25)-MAX(0,E25-A25*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E25" s="28">
@@ -4429,7 +4429,7 @@
         <v/>
       </c>
       <c r="F25" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D25+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D25+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D25+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D25+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D25+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D25+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D25+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D25+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D25+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D25+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D25+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D25+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D25+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D25+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D25+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D25+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G25" s="43">
@@ -4437,15 +4437,15 @@
         <v/>
       </c>
       <c r="H25" s="28">
-        <f>MAX(0,A25-B25-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I25)</f>
+        <f>MAX(0,A25-B25-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I25)</f>
         <v/>
       </c>
       <c r="I25" s="28">
-        <f>MAX(MIN(MAX(A25-B25-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A25-B25-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J25" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H25+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H25+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H25+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H25+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H25+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H25+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H25+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H25+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H25+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H25+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H25+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H25+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H25+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H25+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H25+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H25+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K25" s="43">
@@ -4453,15 +4453,15 @@
         <v/>
       </c>
       <c r="L25" s="28">
-        <f>A25-B25-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A25-B25-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M25" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L25,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L25,0)</f>
         <v/>
       </c>
       <c r="N25" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M25+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M25+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M25+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M25+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M25+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M25+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M25+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M25+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M25+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M25+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M25+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M25+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M25+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M25+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M25+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M25+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O25" s="43">
@@ -4494,7 +4494,7 @@
         <v/>
       </c>
       <c r="D26" s="28">
-        <f>A26*Parametros!$C$19+MAX(0,A26*Parametros!$C$20-B26)-MAX(0,E26-A26*Parametros!$C$22)</f>
+        <f>A26*Parametros!$C$24+MAX(0,A26*Parametros!$C$25-B26)-MAX(0,E26-A26*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E26" s="28">
@@ -4502,7 +4502,7 @@
         <v/>
       </c>
       <c r="F26" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D26+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D26+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D26+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D26+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D26+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D26+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D26+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D26+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D26+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D26+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D26+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D26+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D26+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D26+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D26+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D26+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G26" s="43">
@@ -4510,15 +4510,15 @@
         <v/>
       </c>
       <c r="H26" s="28">
-        <f>MAX(0,A26-B26-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I26)</f>
+        <f>MAX(0,A26-B26-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I26)</f>
         <v/>
       </c>
       <c r="I26" s="28">
-        <f>MAX(MIN(MAX(A26-B26-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A26-B26-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J26" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H26+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H26+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H26+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H26+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H26+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H26+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H26+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H26+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H26+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H26+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H26+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H26+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H26+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H26+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H26+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H26+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K26" s="43">
@@ -4526,15 +4526,15 @@
         <v/>
       </c>
       <c r="L26" s="28">
-        <f>A26-B26-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A26-B26-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M26" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L26,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L26,0)</f>
         <v/>
       </c>
       <c r="N26" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M26+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M26+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M26+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M26+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M26+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M26+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M26+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M26+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M26+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M26+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M26+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M26+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M26+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M26+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M26+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M26+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O26" s="43">
@@ -4567,7 +4567,7 @@
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>A27*Parametros!$C$19+MAX(0,A27*Parametros!$C$20-B27)-MAX(0,E27-A27*Parametros!$C$22)</f>
+        <f>A27*Parametros!$C$24+MAX(0,A27*Parametros!$C$25-B27)-MAX(0,E27-A27*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E27" s="28">
@@ -4575,7 +4575,7 @@
         <v/>
       </c>
       <c r="F27" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D27+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D27+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D27+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D27+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D27+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D27+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D27+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D27+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D27+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D27+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D27+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D27+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D27+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D27+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D27+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D27+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G27" s="43">
@@ -4583,15 +4583,15 @@
         <v/>
       </c>
       <c r="H27" s="28">
-        <f>MAX(0,A27-B27-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I27)</f>
+        <f>MAX(0,A27-B27-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I27)</f>
         <v/>
       </c>
       <c r="I27" s="28">
-        <f>MAX(MIN(MAX(A27-B27-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A27-B27-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J27" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H27+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H27+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H27+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H27+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H27+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H27+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H27+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H27+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H27+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H27+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H27+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H27+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H27+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H27+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H27+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H27+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K27" s="43">
@@ -4599,15 +4599,15 @@
         <v/>
       </c>
       <c r="L27" s="28">
-        <f>A27-B27-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A27-B27-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M27" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L27,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L27,0)</f>
         <v/>
       </c>
       <c r="N27" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M27+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M27+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M27+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M27+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M27+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M27+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M27+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M27+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M27+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M27+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M27+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M27+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M27+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M27+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M27+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M27+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O27" s="43">
@@ -4640,7 +4640,7 @@
         <v/>
       </c>
       <c r="D28" s="28">
-        <f>A28*Parametros!$C$19+MAX(0,A28*Parametros!$C$20-B28)-MAX(0,E28-A28*Parametros!$C$22)</f>
+        <f>A28*Parametros!$C$24+MAX(0,A28*Parametros!$C$25-B28)-MAX(0,E28-A28*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E28" s="28">
@@ -4648,7 +4648,7 @@
         <v/>
       </c>
       <c r="F28" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D28+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D28+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D28+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D28+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D28+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D28+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D28+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D28+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D28+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D28+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D28+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D28+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D28+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D28+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D28+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D28+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G28" s="43">
@@ -4656,15 +4656,15 @@
         <v/>
       </c>
       <c r="H28" s="28">
-        <f>MAX(0,A28-B28-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I28)</f>
+        <f>MAX(0,A28-B28-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I28)</f>
         <v/>
       </c>
       <c r="I28" s="28">
-        <f>MAX(MIN(MAX(A28-B28-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A28-B28-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J28" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H28+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H28+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H28+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H28+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H28+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H28+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H28+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H28+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H28+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H28+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H28+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H28+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H28+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H28+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H28+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H28+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K28" s="43">
@@ -4672,15 +4672,15 @@
         <v/>
       </c>
       <c r="L28" s="28">
-        <f>A28-B28-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A28-B28-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M28" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L28,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L28,0)</f>
         <v/>
       </c>
       <c r="N28" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M28+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M28+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M28+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M28+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M28+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M28+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M28+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M28+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M28+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M28+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M28+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M28+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M28+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M28+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M28+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M28+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O28" s="43">
@@ -4713,7 +4713,7 @@
         <v/>
       </c>
       <c r="D29" s="28">
-        <f>A29*Parametros!$C$19+MAX(0,A29*Parametros!$C$20-B29)-MAX(0,E29-A29*Parametros!$C$22)</f>
+        <f>A29*Parametros!$C$24+MAX(0,A29*Parametros!$C$25-B29)-MAX(0,E29-A29*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E29" s="28">
@@ -4721,7 +4721,7 @@
         <v/>
       </c>
       <c r="F29" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D29+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D29+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D29+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D29+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D29+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D29+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D29+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D29+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D29+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D29+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D29+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D29+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D29+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D29+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D29+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D29+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G29" s="43">
@@ -4729,15 +4729,15 @@
         <v/>
       </c>
       <c r="H29" s="28">
-        <f>MAX(0,A29-B29-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I29)</f>
+        <f>MAX(0,A29-B29-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I29)</f>
         <v/>
       </c>
       <c r="I29" s="28">
-        <f>MAX(MIN(MAX(A29-B29-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A29-B29-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J29" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H29+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H29+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H29+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H29+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H29+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H29+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H29+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H29+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H29+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H29+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H29+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H29+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H29+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H29+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H29+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H29+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K29" s="43">
@@ -4745,15 +4745,15 @@
         <v/>
       </c>
       <c r="L29" s="28">
-        <f>A29-B29-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A29-B29-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M29" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L29,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L29,0)</f>
         <v/>
       </c>
       <c r="N29" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M29+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M29+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M29+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M29+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M29+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M29+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M29+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M29+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M29+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M29+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M29+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M29+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M29+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M29+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M29+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M29+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O29" s="43">
@@ -4786,7 +4786,7 @@
         <v/>
       </c>
       <c r="D30" s="28">
-        <f>A30*Parametros!$C$19+MAX(0,A30*Parametros!$C$20-B30)-MAX(0,E30-A30*Parametros!$C$22)</f>
+        <f>A30*Parametros!$C$24+MAX(0,A30*Parametros!$C$25-B30)-MAX(0,E30-A30*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E30" s="28">
@@ -4794,7 +4794,7 @@
         <v/>
       </c>
       <c r="F30" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D30+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D30+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D30+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D30+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D30+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D30+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D30+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D30+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D30+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D30+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D30+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D30+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D30+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D30+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D30+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D30+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G30" s="43">
@@ -4802,15 +4802,15 @@
         <v/>
       </c>
       <c r="H30" s="28">
-        <f>MAX(0,A30-B30-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I30)</f>
+        <f>MAX(0,A30-B30-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I30)</f>
         <v/>
       </c>
       <c r="I30" s="28">
-        <f>MAX(MIN(MAX(A30-B30-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A30-B30-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J30" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H30+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H30+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H30+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H30+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H30+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H30+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H30+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H30+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H30+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H30+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H30+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H30+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H30+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H30+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H30+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H30+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K30" s="43">
@@ -4818,15 +4818,15 @@
         <v/>
       </c>
       <c r="L30" s="28">
-        <f>A30-B30-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A30-B30-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M30" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L30,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L30,0)</f>
         <v/>
       </c>
       <c r="N30" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M30+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M30+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M30+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M30+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M30+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M30+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M30+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M30+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M30+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M30+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M30+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M30+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M30+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M30+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M30+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M30+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O30" s="43">
@@ -4859,7 +4859,7 @@
         <v/>
       </c>
       <c r="D31" s="28">
-        <f>A31*Parametros!$C$19+MAX(0,A31*Parametros!$C$20-B31)-MAX(0,E31-A31*Parametros!$C$22)</f>
+        <f>A31*Parametros!$C$24+MAX(0,A31*Parametros!$C$25-B31)-MAX(0,E31-A31*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E31" s="28">
@@ -4867,7 +4867,7 @@
         <v/>
       </c>
       <c r="F31" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D31+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D31+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D31+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D31+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D31+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D31+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D31+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D31+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D31+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D31+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D31+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D31+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D31+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D31+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D31+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D31+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G31" s="43">
@@ -4875,15 +4875,15 @@
         <v/>
       </c>
       <c r="H31" s="28">
-        <f>MAX(0,A31-B31-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I31)</f>
+        <f>MAX(0,A31-B31-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I31)</f>
         <v/>
       </c>
       <c r="I31" s="28">
-        <f>MAX(MIN(MAX(A31-B31-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A31-B31-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J31" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H31+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H31+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H31+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H31+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H31+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H31+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H31+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H31+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H31+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H31+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H31+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H31+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H31+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H31+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H31+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H31+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K31" s="43">
@@ -4891,15 +4891,15 @@
         <v/>
       </c>
       <c r="L31" s="28">
-        <f>A31-B31-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A31-B31-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M31" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L31,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L31,0)</f>
         <v/>
       </c>
       <c r="N31" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M31+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M31+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M31+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M31+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M31+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M31+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M31+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M31+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M31+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M31+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M31+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M31+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M31+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M31+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M31+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M31+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O31" s="43">
@@ -4932,7 +4932,7 @@
         <v/>
       </c>
       <c r="D32" s="28">
-        <f>A32*Parametros!$C$19+MAX(0,A32*Parametros!$C$20-B32)-MAX(0,E32-A32*Parametros!$C$22)</f>
+        <f>A32*Parametros!$C$24+MAX(0,A32*Parametros!$C$25-B32)-MAX(0,E32-A32*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E32" s="28">
@@ -4940,7 +4940,7 @@
         <v/>
       </c>
       <c r="F32" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D32+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D32+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D32+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D32+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D32+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D32+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D32+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D32+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D32+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D32+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D32+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D32+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D32+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D32+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D32+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D32+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G32" s="43">
@@ -4948,15 +4948,15 @@
         <v/>
       </c>
       <c r="H32" s="28">
-        <f>MAX(0,A32-B32-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I32)</f>
+        <f>MAX(0,A32-B32-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I32)</f>
         <v/>
       </c>
       <c r="I32" s="28">
-        <f>MAX(MIN(MAX(A32-B32-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A32-B32-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J32" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H32+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H32+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H32+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H32+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H32+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H32+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H32+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H32+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H32+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H32+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H32+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H32+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H32+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H32+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H32+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H32+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K32" s="43">
@@ -4964,15 +4964,15 @@
         <v/>
       </c>
       <c r="L32" s="28">
-        <f>A32-B32-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A32-B32-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M32" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L32,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L32,0)</f>
         <v/>
       </c>
       <c r="N32" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M32+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M32+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M32+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M32+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M32+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M32+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M32+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M32+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M32+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M32+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M32+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M32+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M32+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M32+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M32+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M32+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O32" s="43">
@@ -5005,7 +5005,7 @@
         <v/>
       </c>
       <c r="D33" s="28">
-        <f>A33*Parametros!$C$19+MAX(0,A33*Parametros!$C$20-B33)-MAX(0,E33-A33*Parametros!$C$22)</f>
+        <f>A33*Parametros!$C$24+MAX(0,A33*Parametros!$C$25-B33)-MAX(0,E33-A33*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E33" s="28">
@@ -5013,7 +5013,7 @@
         <v/>
       </c>
       <c r="F33" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D33+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D33+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D33+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D33+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D33+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D33+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D33+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D33+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D33+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D33+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D33+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D33+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D33+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D33+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D33+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D33+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G33" s="43">
@@ -5021,15 +5021,15 @@
         <v/>
       </c>
       <c r="H33" s="28">
-        <f>MAX(0,A33-B33-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I33)</f>
+        <f>MAX(0,A33-B33-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I33)</f>
         <v/>
       </c>
       <c r="I33" s="28">
-        <f>MAX(MIN(MAX(A33-B33-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A33-B33-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J33" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H33+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H33+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H33+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H33+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H33+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H33+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H33+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H33+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H33+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H33+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H33+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H33+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H33+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H33+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H33+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H33+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K33" s="43">
@@ -5037,15 +5037,15 @@
         <v/>
       </c>
       <c r="L33" s="28">
-        <f>A33-B33-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A33-B33-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M33" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L33,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L33,0)</f>
         <v/>
       </c>
       <c r="N33" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M33+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M33+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M33+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M33+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M33+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M33+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M33+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M33+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M33+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M33+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M33+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M33+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M33+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M33+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M33+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M33+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O33" s="43">
@@ -5078,7 +5078,7 @@
         <v/>
       </c>
       <c r="D34" s="28">
-        <f>A34*Parametros!$C$19+MAX(0,A34*Parametros!$C$20-B34)-MAX(0,E34-A34*Parametros!$C$22)</f>
+        <f>A34*Parametros!$C$24+MAX(0,A34*Parametros!$C$25-B34)-MAX(0,E34-A34*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E34" s="28">
@@ -5086,7 +5086,7 @@
         <v/>
       </c>
       <c r="F34" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D34+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D34+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D34+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D34+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D34+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D34+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D34+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D34+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D34+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D34+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D34+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D34+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D34+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D34+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D34+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D34+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G34" s="43">
@@ -5094,15 +5094,15 @@
         <v/>
       </c>
       <c r="H34" s="28">
-        <f>MAX(0,A34-B34-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I34)</f>
+        <f>MAX(0,A34-B34-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I34)</f>
         <v/>
       </c>
       <c r="I34" s="28">
-        <f>MAX(MIN(MAX(A34-B34-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A34-B34-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J34" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H34+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H34+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H34+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H34+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H34+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H34+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H34+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H34+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H34+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H34+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H34+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H34+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H34+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H34+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H34+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H34+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K34" s="43">
@@ -5110,15 +5110,15 @@
         <v/>
       </c>
       <c r="L34" s="28">
-        <f>A34-B34-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A34-B34-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M34" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L34,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L34,0)</f>
         <v/>
       </c>
       <c r="N34" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M34+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M34+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M34+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M34+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M34+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M34+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M34+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M34+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M34+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M34+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M34+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M34+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M34+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M34+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M34+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M34+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O34" s="43">
@@ -5151,7 +5151,7 @@
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>A35*Parametros!$C$19+MAX(0,A35*Parametros!$C$20-B35)-MAX(0,E35-A35*Parametros!$C$22)</f>
+        <f>A35*Parametros!$C$24+MAX(0,A35*Parametros!$C$25-B35)-MAX(0,E35-A35*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E35" s="28">
@@ -5159,7 +5159,7 @@
         <v/>
       </c>
       <c r="F35" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D35+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((D35+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((D35+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((D35+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((D35+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((D35+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((D35+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((D35+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((D35+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((D35+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((D35+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((D35+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((D35+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((D35+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((D35+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((D35+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="G35" s="43">
@@ -5167,15 +5167,15 @@
         <v/>
       </c>
       <c r="H35" s="28">
-        <f>MAX(0,A35-B35-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-I35)</f>
+        <f>MAX(0,A35-B35-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-I35)</f>
         <v/>
       </c>
       <c r="I35" s="28">
-        <f>MAX(MIN(MAX(A35-B35-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
+        <f>MAX(MIN(MAX(A35-B35-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46),0),Parametros!$C$6*Parametros!$C$9*12)*Parametros!$C$8,Parametros!$C$10*12)</f>
         <v/>
       </c>
       <c r="J35" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H35+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((H35+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((H35+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((H35+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((H35+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((H35+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((H35+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((H35+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((H35+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((H35+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((H35+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((H35+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((H35+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((H35+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((H35+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((H35+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="K35" s="43">
@@ -5183,15 +5183,15 @@
         <v/>
       </c>
       <c r="L35" s="28">
-        <f>A35-B35-(Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
+        <f>A35-B35-(Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46)-(Inputs!$D$32)-((MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$11)</f>
         <v/>
       </c>
       <c r="M35" s="28">
-        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$25,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L35,0)</f>
+        <f>MAX(0,(Inputs!$D$32)-MIN((Inputs!$D$32),MAX(Parametros!$C$30,(MAX(Inputs!$D$32,Parametros!$C$6*Parametros!$C$13*12))*Parametros!$C$12)))+MAX(L35,0)</f>
         <v/>
       </c>
       <c r="N35" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M35+Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((M35+Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((M35+Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((M35+Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((M35+Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((M35+Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((M35+Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((M35+Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$50:$B$58)*(((Inputs!$D$37)/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$62:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$50:$B$58)*((Inputs!$D$37)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$62:$B$63)*((Inputs!$D$37)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((((M35+Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((M35+Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((M35+Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((M35+Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((M35+Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((M35+Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((M35+Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((M35+Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))-IF(Inputs!$D$38=1,2*(SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$55:$B$63)*(((Inputs!$D$37)/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((((Inputs!$D$37)/2)&gt;Parametros!$B$67:$B$68)*(((Inputs!$D$37)/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$55:$B$63)*((Inputs!$D$37)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(((Inputs!$D$37)&gt;Parametros!$B$67:$B$68)*((Inputs!$D$37)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="O35" s="43">
@@ -5993,11 +5993,11 @@
         </is>
       </c>
       <c r="C26" s="28">
-        <f>($C$9+$C$10)*Parametros!$C$36</f>
+        <f>($C$9+$C$10)*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="D26" s="28">
-        <f>($D$9+$D$10)*Parametros!$C$36</f>
+        <f>($D$9+$D$10)*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="E26" s="17" t="inlineStr">
@@ -7610,15 +7610,15 @@
         </is>
       </c>
       <c r="C13" s="28">
-        <f>$C$10*0.5</f>
+        <f>$C$10*Parametros!$C$18</f>
         <v/>
       </c>
       <c r="D13" s="28">
-        <f>$D$10*0.5</f>
+        <f>$D$10*Parametros!$C$18</f>
         <v/>
       </c>
       <c r="E13" s="28">
-        <f>$E$10*0.5</f>
+        <f>$E$10*Parametros!$C$18</f>
         <v/>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="B10" s="50">
-        <f>SUM(Parametros!$F$6:$F$45)</f>
+        <f>SUM(Parametros!$F$6:$F$50)</f>
         <v/>
       </c>
       <c r="C10" s="48">
@@ -8054,7 +8054,7 @@
         <v/>
       </c>
       <c r="C12" s="48">
-        <f>IF(B12&gt;1,"ATIVO","—")</f>
+        <f>IF(B12&gt;Parametros!$C$20,"ATIVO","—")</f>
         <v/>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -8079,7 +8079,7 @@
         <v/>
       </c>
       <c r="C13" s="48">
-        <f>IF(AND(B13&gt;0.85,B13&lt;=1),"ATIVO","—")</f>
+        <f>IF(AND(B13&gt;Parametros!$C$21,B13&lt;=Parametros!$C$20),"ATIVO","—")</f>
         <v/>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -8104,7 +8104,7 @@
         <v/>
       </c>
       <c r="C14" s="48">
-        <f>IF(B14&lt;0.3,"ATIVO","—")</f>
+        <f>IF(B14&lt;Parametros!$C$22,"ATIVO","—")</f>
         <v/>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -10318,7 +10318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -10723,61 +10723,61 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>IRS — categoria B e regras de determinação</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Coima estimada, em % das contribuições devidas pela entidade</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>COIMA_PCT</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Moldura das contraordenações do Cód. Contributivo</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>ESTIMATIVA GROSSEIRA — ver R1-38</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Coeficiente do regime simplificado (atividades do art. 151.º)</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>COEF</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Art. 31.º n.º 1 al. b) CIRS — fisioterapeutas constam da tabela do art. 151.º</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Limiares operacionais de alerta</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Limiar de justificação de despesas</t>
+          <t>Utilização acima da qual a projeção é impossível</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>LIM_JUST</t>
+          <t>UTIL_MAX</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 13 CIRS</t>
+          <t>Definição do modelo</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -10792,25 +10792,25 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Dedução específica considerada na justificação de despesas</t>
+          <t>Utilização acima da qual a operação é muito exigente</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>DED_ESP</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>4104</v>
+          <t>UTIL_ALTA</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0.85</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 13 al. a) CIRS</t>
+          <t>Convenção de trabalho VCLevel</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Confirmar valor em vigor</t>
+          <t>Decisão de equipa</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
@@ -10820,25 +10820,25 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Contribuições SS — dedutíveis na parte que excede esta % do rendimento bruto</t>
+          <t>Utilização abaixo da qual o espaço está subaproveitado</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>LIM_CONTRIB</t>
+          <t>UTIL_BAIXA</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 2 CIRS</t>
+          <t>Convenção de trabalho VCLevel</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Decisão de equipa</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
@@ -10846,55 +10846,38 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Limiar de permanência no regime simplificado (rendimento bruto)</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>LIM_SIMPL</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Art. 28.º n.º 2 CIRS</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>IRS — categoria B e regras de determinação</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Período mínimo de permanência na opção por contabilidade organizada (anos)</t>
+          <t>Coeficiente do regime simplificado (atividades do art. 151.º)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>PERM_OPCAO</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="n">
-        <v>3</v>
+          <t>COEF</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>0.75</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Art. 28.º n.º 5 CIRS</t>
+          <t>Art. 31.º n.º 1 al. b) CIRS — fisioterapeutas constam da tabela do art. 151.º</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Validado</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
@@ -10904,25 +10887,25 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Dedução específica da categoria A</t>
+          <t>Limiar de justificação de despesas</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>DED_CATA</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>4104</v>
+          <t>LIM_JUST</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>0.15</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Art. 25.º n.º 1 al. a) CIRS</t>
+          <t>Art. 31.º n.º 13 CIRS</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Confirmar valor em vigor</t>
+          <t>Validado</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
@@ -10932,148 +10915,165 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Coeficiente do simplificado aplicável à receita de cedência de espaço</t>
+          <t>Dedução específica considerada na justificação de despesas</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>COEF_SALA</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>0.35</v>
+          <t>DED_ESP</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>4104</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Art. 31.º n.º 1 al. c) CIRS — restantes prestações de serviços</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR (ver R1-29). Depende de N1-04</t>
+          <t>Art. 31.º n.º 13 al. a) CIRS</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar valor em vigor</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>IRC e tributação da distribuição</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Contribuições SS — dedutíveis na parte que excede esta % do rendimento bruto</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>LIM_CONTRIB</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Art. 31.º n.º 2 CIRS</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>IRC — taxa aplicável ao primeiro escalão (PME)</t>
+          <t>Limiar de permanência no regime simplificado (rendimento bruto)</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>IRC_PME</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="n">
-        <v>0.16</v>
+          <t>LIM_SIMPL</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>200000</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Art. 87.º n.º 2 CIRC</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
+          <t>Art. 28.º n.º 2 CIRS</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>IRC — limite da matéria coletável do primeiro escalão</t>
+          <t>Período mínimo de permanência na opção por contabilidade organizada (anos)</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>IRC_LIM</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>50000</v>
+          <t>PERM_OPCAO</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Art. 87.º n.º 2 CIRC</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR 2026</t>
+          <t>Art. 28.º n.º 5 CIRS</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>IRC — taxa geral</t>
+          <t>Dedução específica da categoria A</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>IRC_GER</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="n">
-        <v>0.2</v>
+          <t>DED_CATA</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>4104</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Art. 87.º n.º 1 CIRC</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
+          <t>Art. 25.º n.º 1 al. a) CIRS</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar valor em vigor</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Derrama municipal (município do Porto)</t>
+          <t>Coeficiente do simplificado aplicável à receita de cedência de espaço</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>DERRAMA</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>0.015</v>
+          <t>COEF_SALA</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>0.35</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Art. 18.º Lei 73/2013 + deliberação municipal</t>
+          <t>Art. 31.º n.º 1 al. c) CIRS — restantes prestações de serviços</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>CONFIRMAR município e isenção PME</t>
+          <t>CONFIRMAR (ver R1-29). Depende de N1-04</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
@@ -11081,350 +11081,378 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Derrama incide sobre sociedade transparente? (1=sim / 0=não)</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>DERR_TRANSP</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Questão controvertida — art. 12.º CIRC vs. art. 18.º Lei 73/2013</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>EM ABERTO (ver R1-13)</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>IRC e tributação da distribuição</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Dividendos — taxa liberatória</t>
+          <t>IRC — taxa aplicável ao primeiro escalão (PME)</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>DIV_LIB</t>
+          <t>IRC_PME</t>
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Art. 71.º n.º 1 CIRS</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
+          <t>Art. 87.º n.º 2 CIRC</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Dividendos — % considerada em caso de englobamento</t>
+          <t>IRC — limite da matéria coletável do primeiro escalão</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>DIV_ENG</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>0.5</v>
+          <t>IRC_LIM</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>50000</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Art. 40.º-A n.º 1 CIRS</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
+          <t>Art. 87.º n.º 2 CIRC</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR 2026</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>IRC — taxa geral</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>IRC_GER</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Art. 87.º n.º 1 CIRC</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR TAXA 2026 (ver R1-11)</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>IVA — taxa normal (continente)</t>
+          <t>Derrama municipal (município do Porto)</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>IVA_NORM</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="n">
-        <v>0.23</v>
+          <t>DERRAMA</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0.015</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Art. 18.º n.º 1 al. c) CIVA</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
+          <t>Art. 18.º Lei 73/2013 + deliberação municipal</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR município e isenção PME</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>IVA — taxa reduzida (continente)</t>
+          <t>Derrama incide sobre sociedade transparente? (1=sim / 0=não)</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>IVA_RED</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>0.06</v>
+          <t>DERR_TRANSP</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Art. 18.º n.º 1 al. a) CIVA + Lista I</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
+          <t>Questão controvertida — art. 12.º CIRC vs. art. 18.º Lei 73/2013</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>EM ABERTO (ver R1-13)</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Dividendos — taxa liberatória</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>DIV_LIB</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Art. 71.º n.º 1 CIRS</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Amortizações (vias com contabilidade)</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Taxa de amortização — obras / benfeitorias em imóvel alheio</t>
+          <t>Dividendos — % considerada em caso de englobamento</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>AM_OBRAS</t>
+          <t>DIV_ENG</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>DR 25/2009 — ou período do contrato de arrendamento, se inferior</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR código aplicável</t>
+          <t>Art. 40.º-A n.º 1 CIRS</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Taxa de amortização — equipamento clínico</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>AM_EQUIP</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>DR 25/2009, tabela II</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR código aplicável</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Taxa de amortização — software</t>
+          <t>IVA — taxa normal (continente)</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>AM_SOFT</t>
+          <t>IVA_NORM</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>0.3333</v>
+        <v>0.23</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>DR 25/2009</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>CONFIRMAR</t>
+          <t>Art. 18.º n.º 1 al. c) CIVA</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Transparência fiscal — limiares do teste (usados na N1, não no cálculo)</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>IVA — taxa reduzida (continente)</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>IVA_RED</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Art. 18.º n.º 1 al. a) CIVA + Lista I</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>% mínima de capital detida por profissionais das atividades do art. 151.º</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>TF_CAP</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Amortizações (vias com contabilidade)</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>% mínima de rendimentos provenientes de atividades do art. 151.º</t>
+          <t>Taxa de amortização — obras / benfeitorias em imóvel alheio</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>TF_REND</t>
+          <t>AM_OBRAS</t>
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
+          <t>DR 25/2009 — ou período do contrato de arrendamento, se inferior</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR código aplicável</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>N.º máximo de sócios para o teste da subal. ii)</t>
+          <t>Taxa de amortização — equipamento clínico</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>TF_SOCIOS</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="n">
-        <v>5</v>
+          <t>AM_EQUIP</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>0.2</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>Validado</t>
+          <t>DR 25/2009, tabela II</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR código aplicável</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Taxa de amortização — software</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>AM_SOFT</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>DR 25/2009</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>CONFIRMAR</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Escalões de IRS — taxas gerais</t>
+          <t>Transparência fiscal — limiares do teste (usados na N1, não no cálculo)</t>
         </is>
       </c>
       <c r="B47" s="7" t="n"/>
@@ -11432,160 +11460,165 @@
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
     </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>% mínima de capital detida por profissionais das atividades do art. 151.º</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>TF_CAP</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>% mínima de rendimentos provenientes de atividades do art. 151.º</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>TF_REND</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>N.º máximo de sócios para o teste da subal. ii)</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>TF_SOCIOS</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Art. 6.º n.º 4 al. b) subal. ii) CIRC</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Validado</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Escalões de IRS — taxas gerais</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>Tabela em vigor: 2025 (Lei n.º 33-A/2025). ATUALIZAR para os escalões do OE2026 antes de qualquer número entrar no relatório. A coluna 'Delta' é a mecânica de cálculo (taxa do escalão menos taxa do anterior) e recalcula sozinha.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Escalão</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Limite inferior</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>Limite superior</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>Taxa</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>Delta (calculado)</t>
         </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>8059</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E50" s="18">
-        <f>D50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>8059</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>12160</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E51" s="18">
-        <f>D51-D50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B52" s="16" t="n">
-        <v>12160</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>17233</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E52" s="18">
-        <f>D52-D51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B53" s="16" t="n">
-        <v>17233</v>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>22306</v>
-      </c>
-      <c r="D53" s="14" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="E53" s="18">
-        <f>D53-D52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>22306</v>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>28400</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="E54" s="18">
-        <f>D54-D53</f>
-        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B55" s="16" t="n">
-        <v>28400</v>
+        <v>0</v>
       </c>
       <c r="C55" s="16" t="n">
-        <v>41629</v>
+        <v>8059</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>0.349</v>
+        <v>0.125</v>
       </c>
       <c r="E55" s="18">
-        <f>D55-D54</f>
+        <f>D55</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B56" s="16" t="n">
-        <v>41629</v>
+        <v>8059</v>
       </c>
       <c r="C56" s="16" t="n">
-        <v>44987</v>
+        <v>12160</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>0.431</v>
+        <v>0.16</v>
       </c>
       <c r="E56" s="18">
         <f>D56-D55</f>
@@ -11594,16 +11627,16 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B57" s="16" t="n">
-        <v>44987</v>
+        <v>12160</v>
       </c>
       <c r="C57" s="16" t="n">
-        <v>83696</v>
+        <v>17233</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>0.446</v>
+        <v>0.215</v>
       </c>
       <c r="E57" s="18">
         <f>D57-D56</f>
@@ -11612,86 +11645,100 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B58" s="16" t="n">
-        <v>83696</v>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>sem limite</t>
-        </is>
+        <v>17233</v>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>22306</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>0.48</v>
+        <v>0.244</v>
       </c>
       <c r="E58" s="18">
         <f>D58-D57</f>
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" s="16" t="n">
+        <v>22306</v>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>28400</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="E59" s="18">
+        <f>D59-D58</f>
+        <v/>
+      </c>
+    </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Taxa adicional de solidariedade (art. 68.º-A CIRS)</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
-      <c r="E60" s="7" t="n"/>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Escalão</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>Limite inferior</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Limite superior</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Taxa</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Delta (calculado)</t>
-        </is>
+      <c r="A60" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B60" s="16" t="n">
+        <v>28400</v>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>41629</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="E60" s="18">
+        <f>D60-D59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" s="16" t="n">
+        <v>41629</v>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>44987</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="E61" s="18">
+        <f>D61-D60</f>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B62" s="16" t="n">
-        <v>80000</v>
+        <v>44987</v>
       </c>
       <c r="C62" s="16" t="n">
-        <v>250000</v>
+        <v>83696</v>
       </c>
       <c r="D62" s="14" t="n">
-        <v>0.025</v>
+        <v>0.446</v>
       </c>
       <c r="E62" s="18">
-        <f>D62</f>
+        <f>D62-D61</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B63" s="16" t="n">
-        <v>250000</v>
+        <v>83696</v>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
@@ -11699,7 +11746,7 @@
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>0.05</v>
+        <v>0.48</v>
       </c>
       <c r="E63" s="18">
         <f>D63-D62</f>
@@ -11707,7 +11754,83 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Taxa adicional de solidariedade (art. 68.º-A CIRS)</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="7" t="n"/>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Escalão</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Limite inferior</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Limite superior</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Taxa</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Delta (calculado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="16" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E67" s="18">
+        <f>D67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" s="16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>sem limite</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E68" s="18">
+        <f>D68-D67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>Legenda: células a azul sobre fundo amarelo são de preenchimento; tudo o resto é fórmula. Nenhuma taxa deve ser escrita dentro de uma fórmula noutra folha — se faltar um parâmetro, acrescenta-se aqui.</t>
         </is>
@@ -11715,8 +11838,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A70:E70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12297,15 +12420,15 @@
         </is>
       </c>
       <c r="C27" s="26">
-        <f>IF($C$26&gt;1,"IMPOSSÍVEL — a projeção não cabe no espaço",IF($C$26&gt;0.85,"MUITO EXIGENTE — pouca folga operacional",IF($C$26&lt;0.3,"FOLGA ELEVADA — capacidade subaproveitada","PLAUSÍVEL")))</f>
+        <f>IF($C$26&gt;Parametros!$C$20,"IMPOSSÍVEL — a projeção não cabe no espaço",IF($C$26&gt;Parametros!$C$21,"MUITO EXIGENTE — pouca folga operacional",IF($C$26&lt;Parametros!$C$22,"FOLGA ELEVADA — capacidade subaproveitada","PLAUSÍVEL")))</f>
         <v/>
       </c>
       <c r="D27" s="26">
-        <f>IF($D$26&gt;1,"IMPOSSÍVEL — a projeção não cabe no espaço",IF($D$26&gt;0.85,"MUITO EXIGENTE — pouca folga operacional",IF($D$26&lt;0.3,"FOLGA ELEVADA — capacidade subaproveitada","PLAUSÍVEL")))</f>
+        <f>IF($D$26&gt;Parametros!$C$20,"IMPOSSÍVEL — a projeção não cabe no espaço",IF($D$26&gt;Parametros!$C$21,"MUITO EXIGENTE — pouca folga operacional",IF($D$26&lt;Parametros!$C$22,"FOLGA ELEVADA — capacidade subaproveitada","PLAUSÍVEL")))</f>
         <v/>
       </c>
       <c r="E27" s="26">
-        <f>IF($E$26&gt;1,"IMPOSSÍVEL — a projeção não cabe no espaço",IF($E$26&gt;0.85,"MUITO EXIGENTE — pouca folga operacional",IF($E$26&lt;0.3,"FOLGA ELEVADA — capacidade subaproveitada","PLAUSÍVEL")))</f>
+        <f>IF($E$26&gt;Parametros!$C$20,"IMPOSSÍVEL — a projeção não cabe no espaço",IF($E$26&gt;Parametros!$C$21,"MUITO EXIGENTE — pouca folga operacional",IF($E$26&lt;Parametros!$C$22,"FOLGA ELEVADA — capacidade subaproveitada","PLAUSÍVEL")))</f>
         <v/>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
@@ -14276,15 +14399,15 @@
         </is>
       </c>
       <c r="C49" s="28">
-        <f>Inputs!$C$42*(1-Parametros!$C$44)/Parametros!$C$44</f>
+        <f>Inputs!$C$42*(1-Parametros!$C$49)/Parametros!$C$49</f>
         <v/>
       </c>
       <c r="D49" s="28">
-        <f>Inputs!$D$42*(1-Parametros!$C$44)/Parametros!$C$44</f>
+        <f>Inputs!$D$42*(1-Parametros!$C$49)/Parametros!$C$49</f>
         <v/>
       </c>
       <c r="E49" s="28">
-        <f>Inputs!$E$42*(1-Parametros!$C$44)/Parametros!$C$44</f>
+        <f>Inputs!$E$42*(1-Parametros!$C$49)/Parametros!$C$49</f>
         <v/>
       </c>
       <c r="F49" s="17" t="inlineStr">
@@ -14305,15 +14428,15 @@
         </is>
       </c>
       <c r="C50" s="26">
-        <f>IF(Inputs!$C$48&gt;Parametros!$C$44,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <f>IF(Inputs!$C$48&gt;Parametros!$C$49,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
         <v/>
       </c>
       <c r="D50" s="26">
-        <f>IF(Inputs!$D$48&gt;Parametros!$C$44,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <f>IF(Inputs!$D$48&gt;Parametros!$C$49,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
         <v/>
       </c>
       <c r="E50" s="26">
-        <f>IF(Inputs!$E$48&gt;Parametros!$C$44,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
+        <f>IF(Inputs!$E$48&gt;Parametros!$C$49,"VERIFICADO — transparência não é afastada por esta via","FALHADO — transparência afastada pelo critério de rendimentos")</f>
         <v/>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -14524,15 +14647,15 @@
         </is>
       </c>
       <c r="C9" s="36">
-        <f>Parametros!$C$19</f>
+        <f>Parametros!$C$24</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Parametros!$C$19</f>
+        <f>Parametros!$C$24</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>Parametros!$C$19</f>
+        <f>Parametros!$C$24</f>
         <v/>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -14553,15 +14676,15 @@
         </is>
       </c>
       <c r="C10" s="36">
-        <f>Parametros!$C$26</f>
+        <f>Parametros!$C$31</f>
         <v/>
       </c>
       <c r="D10" s="36">
-        <f>Parametros!$C$26</f>
+        <f>Parametros!$C$31</f>
         <v/>
       </c>
       <c r="E10" s="36">
-        <f>Parametros!$C$26</f>
+        <f>Parametros!$C$31</f>
         <v/>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -14607,15 +14730,15 @@
         </is>
       </c>
       <c r="C12" s="28">
-        <f>$C$8*Parametros!$C$20</f>
+        <f>$C$8*Parametros!$C$25</f>
         <v/>
       </c>
       <c r="D12" s="28">
-        <f>$D$8*Parametros!$C$20</f>
+        <f>$D$8*Parametros!$C$25</f>
         <v/>
       </c>
       <c r="E12" s="28">
-        <f>$E$8*Parametros!$C$20</f>
+        <f>$E$8*Parametros!$C$25</f>
         <v/>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -14636,15 +14759,15 @@
         </is>
       </c>
       <c r="C13" s="35">
-        <f>Parametros!$C$21</f>
+        <f>Parametros!$C$26</f>
         <v/>
       </c>
       <c r="D13" s="35">
-        <f>Parametros!$C$21</f>
+        <f>Parametros!$C$26</f>
         <v/>
       </c>
       <c r="E13" s="35">
-        <f>Parametros!$C$21</f>
+        <f>Parametros!$C$26</f>
         <v/>
       </c>
       <c r="F13" s="17" t="inlineStr"/>
@@ -14926,15 +15049,15 @@
         </is>
       </c>
       <c r="C24" s="28">
-        <f>MAX(0,$C$23-$C$8*Parametros!$C$22)</f>
+        <f>MAX(0,$C$23-$C$8*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="D24" s="28">
-        <f>MAX(0,$D$23-$D$8*Parametros!$C$22)</f>
+        <f>MAX(0,$D$23-$D$8*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="E24" s="28">
-        <f>MAX(0,$E$23-$E$8*Parametros!$C$22)</f>
+        <f>MAX(0,$E$23-$E$8*Parametros!$C$27)</f>
         <v/>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -15100,15 +15223,15 @@
         </is>
       </c>
       <c r="C31" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$29/2)&gt;Parametros!$B$50:$B$58)*(($C$29/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$29/2)&gt;Parametros!$B$62:$B$63)*(($C$29/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$29&gt;Parametros!$B$50:$B$58)*($C$29-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$29&gt;Parametros!$B$62:$B$63)*($C$29-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$29/2)&gt;Parametros!$B$55:$B$63)*(($C$29/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$29/2)&gt;Parametros!$B$67:$B$68)*(($C$29/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($C$29&gt;Parametros!$B$55:$B$63)*($C$29-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($C$29&gt;Parametros!$B$67:$B$68)*($C$29-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="D31" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$29/2)&gt;Parametros!$B$50:$B$58)*(($D$29/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$29/2)&gt;Parametros!$B$62:$B$63)*(($D$29/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$29&gt;Parametros!$B$50:$B$58)*($D$29-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$29&gt;Parametros!$B$62:$B$63)*($D$29-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$29/2)&gt;Parametros!$B$55:$B$63)*(($D$29/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($D$29/2)&gt;Parametros!$B$67:$B$68)*(($D$29/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($D$29&gt;Parametros!$B$55:$B$63)*($D$29-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($D$29&gt;Parametros!$B$67:$B$68)*($D$29-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="E31" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$29/2)&gt;Parametros!$B$50:$B$58)*(($E$29/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$29/2)&gt;Parametros!$B$62:$B$63)*(($E$29/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$29&gt;Parametros!$B$50:$B$58)*($E$29-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$29&gt;Parametros!$B$62:$B$63)*($E$29-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$29/2)&gt;Parametros!$B$55:$B$63)*(($E$29/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($E$29/2)&gt;Parametros!$B$67:$B$68)*(($E$29/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($E$29&gt;Parametros!$B$55:$B$63)*($E$29-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($E$29&gt;Parametros!$B$67:$B$68)*($E$29-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F31" s="17" t="inlineStr">
@@ -15129,15 +15252,15 @@
         </is>
       </c>
       <c r="C32" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$30/2)&gt;Parametros!$B$50:$B$58)*(($C$30/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$30/2)&gt;Parametros!$B$62:$B$63)*(($C$30/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$30&gt;Parametros!$B$50:$B$58)*($C$30-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$30&gt;Parametros!$B$62:$B$63)*($C$30-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$30/2)&gt;Parametros!$B$55:$B$63)*(($C$30/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$30/2)&gt;Parametros!$B$67:$B$68)*(($C$30/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($C$30&gt;Parametros!$B$55:$B$63)*($C$30-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($C$30&gt;Parametros!$B$67:$B$68)*($C$30-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="D32" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$30/2)&gt;Parametros!$B$50:$B$58)*(($D$30/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$30/2)&gt;Parametros!$B$62:$B$63)*(($D$30/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$30&gt;Parametros!$B$50:$B$58)*($D$30-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$30&gt;Parametros!$B$62:$B$63)*($D$30-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$30/2)&gt;Parametros!$B$55:$B$63)*(($D$30/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($D$30/2)&gt;Parametros!$B$67:$B$68)*(($D$30/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($D$30&gt;Parametros!$B$55:$B$63)*($D$30-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($D$30&gt;Parametros!$B$67:$B$68)*($D$30-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="E32" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$30/2)&gt;Parametros!$B$50:$B$58)*(($E$30/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$30/2)&gt;Parametros!$B$62:$B$63)*(($E$30/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$30&gt;Parametros!$B$50:$B$58)*($E$30-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$30&gt;Parametros!$B$62:$B$63)*($E$30-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$30/2)&gt;Parametros!$B$55:$B$63)*(($E$30/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($E$30/2)&gt;Parametros!$B$67:$B$68)*(($E$30/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($E$30&gt;Parametros!$B$55:$B$63)*($E$30-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($E$30&gt;Parametros!$B$67:$B$68)*($E$30-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F32" s="17" t="inlineStr"/>
@@ -15598,15 +15721,15 @@
         </is>
       </c>
       <c r="C9" s="28">
-        <f>Inputs!$C$27*Parametros!$C$39+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$40+Inputs!$C$30*Parametros!$C$41</f>
+        <f>Inputs!$C$27*Parametros!$C$44+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$45+Inputs!$C$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41</f>
+        <f>Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>Inputs!$E$27*Parametros!$C$39+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$40+Inputs!$E$30*Parametros!$C$41</f>
+        <f>Inputs!$E$27*Parametros!$C$44+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$45+Inputs!$E$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -15867,15 +15990,15 @@
         </is>
       </c>
       <c r="C20" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$18/2)&gt;Parametros!$B$50:$B$58)*(($C$18/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$18/2)&gt;Parametros!$B$62:$B$63)*(($C$18/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$18&gt;Parametros!$B$50:$B$58)*($C$18-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$18&gt;Parametros!$B$62:$B$63)*($C$18-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$18/2)&gt;Parametros!$B$55:$B$63)*(($C$18/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$18/2)&gt;Parametros!$B$67:$B$68)*(($C$18/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($C$18&gt;Parametros!$B$55:$B$63)*($C$18-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($C$18&gt;Parametros!$B$67:$B$68)*($C$18-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="D20" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$18/2)&gt;Parametros!$B$50:$B$58)*(($D$18/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$18/2)&gt;Parametros!$B$62:$B$63)*(($D$18/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$18&gt;Parametros!$B$50:$B$58)*($D$18-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$18&gt;Parametros!$B$62:$B$63)*($D$18-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$18/2)&gt;Parametros!$B$55:$B$63)*(($D$18/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($D$18/2)&gt;Parametros!$B$67:$B$68)*(($D$18/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($D$18&gt;Parametros!$B$55:$B$63)*($D$18-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($D$18&gt;Parametros!$B$67:$B$68)*($D$18-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="E20" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$18/2)&gt;Parametros!$B$50:$B$58)*(($E$18/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$18/2)&gt;Parametros!$B$62:$B$63)*(($E$18/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$18&gt;Parametros!$B$50:$B$58)*($E$18-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$18&gt;Parametros!$B$62:$B$63)*($E$18-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$18/2)&gt;Parametros!$B$55:$B$63)*(($E$18/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($E$18/2)&gt;Parametros!$B$67:$B$68)*(($E$18/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($E$18&gt;Parametros!$B$55:$B$63)*($E$18-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($E$18&gt;Parametros!$B$67:$B$68)*($E$18-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -15896,15 +16019,15 @@
         </is>
       </c>
       <c r="C21" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$19/2)&gt;Parametros!$B$50:$B$58)*(($C$19/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$19/2)&gt;Parametros!$B$62:$B$63)*(($C$19/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$19&gt;Parametros!$B$50:$B$58)*($C$19-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$19&gt;Parametros!$B$62:$B$63)*($C$19-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$19/2)&gt;Parametros!$B$55:$B$63)*(($C$19/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$19/2)&gt;Parametros!$B$67:$B$68)*(($C$19/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($C$19&gt;Parametros!$B$55:$B$63)*($C$19-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($C$19&gt;Parametros!$B$67:$B$68)*($C$19-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="D21" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$19/2)&gt;Parametros!$B$50:$B$58)*(($D$19/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$19/2)&gt;Parametros!$B$62:$B$63)*(($D$19/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$19&gt;Parametros!$B$50:$B$58)*($D$19-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$19&gt;Parametros!$B$62:$B$63)*($D$19-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$19/2)&gt;Parametros!$B$55:$B$63)*(($D$19/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($D$19/2)&gt;Parametros!$B$67:$B$68)*(($D$19/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($D$19&gt;Parametros!$B$55:$B$63)*($D$19-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($D$19&gt;Parametros!$B$67:$B$68)*($D$19-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="E21" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$19/2)&gt;Parametros!$B$50:$B$58)*(($E$19/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$19/2)&gt;Parametros!$B$62:$B$63)*(($E$19/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$19&gt;Parametros!$B$50:$B$58)*($E$19-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$19&gt;Parametros!$B$62:$B$63)*($E$19-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$19/2)&gt;Parametros!$B$55:$B$63)*(($E$19/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($E$19/2)&gt;Parametros!$B$67:$B$68)*(($E$19/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($E$19&gt;Parametros!$B$55:$B$63)*($E$19-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($E$19&gt;Parametros!$B$67:$B$68)*($E$19-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F21" s="17" t="inlineStr"/>
@@ -16361,15 +16484,15 @@
         </is>
       </c>
       <c r="C9" s="28">
-        <f>Inputs!$C$27*Parametros!$C$39+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$40+Inputs!$C$30*Parametros!$C$41</f>
+        <f>Inputs!$C$27*Parametros!$C$44+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$45+Inputs!$C$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41</f>
+        <f>Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>Inputs!$E$27*Parametros!$C$39+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$40+Inputs!$E$30*Parametros!$C$41</f>
+        <f>Inputs!$E$27*Parametros!$C$44+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$45+Inputs!$E$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="F9" s="17" t="inlineStr"/>
@@ -16523,15 +16646,15 @@
         </is>
       </c>
       <c r="C15" s="28">
-        <f>MAX($C$13,0)*Parametros!$C$31*Parametros!$C$32</f>
+        <f>MAX($C$13,0)*Parametros!$C$36*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>MAX($D$13,0)*Parametros!$C$31*Parametros!$C$32</f>
+        <f>MAX($D$13,0)*Parametros!$C$36*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>MAX($E$13,0)*Parametros!$C$31*Parametros!$C$32</f>
+        <f>MAX($E$13,0)*Parametros!$C$36*Parametros!$C$37</f>
         <v/>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -16618,15 +16741,15 @@
         </is>
       </c>
       <c r="C19" s="28">
-        <f>MIN($C$10,MAX(Parametros!$C$25,$C$18))</f>
+        <f>MIN($C$10,MAX(Parametros!$C$30,$C$18))</f>
         <v/>
       </c>
       <c r="D19" s="28">
-        <f>MIN($D$10,MAX(Parametros!$C$25,$D$18))</f>
+        <f>MIN($D$10,MAX(Parametros!$C$30,$D$18))</f>
         <v/>
       </c>
       <c r="E19" s="28">
-        <f>MIN($E$10,MAX(Parametros!$C$25,$E$18))</f>
+        <f>MIN($E$10,MAX(Parametros!$C$30,$E$18))</f>
         <v/>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -16792,15 +16915,15 @@
         </is>
       </c>
       <c r="C26" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$24/2)&gt;Parametros!$B$50:$B$58)*(($C$24/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$24/2)&gt;Parametros!$B$62:$B$63)*(($C$24/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$24&gt;Parametros!$B$50:$B$58)*($C$24-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$24&gt;Parametros!$B$62:$B$63)*($C$24-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$24/2)&gt;Parametros!$B$55:$B$63)*(($C$24/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$24/2)&gt;Parametros!$B$67:$B$68)*(($C$24/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($C$24&gt;Parametros!$B$55:$B$63)*($C$24-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($C$24&gt;Parametros!$B$67:$B$68)*($C$24-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="D26" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$24/2)&gt;Parametros!$B$50:$B$58)*(($D$24/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$24/2)&gt;Parametros!$B$62:$B$63)*(($D$24/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$24&gt;Parametros!$B$50:$B$58)*($D$24-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$24&gt;Parametros!$B$62:$B$63)*($D$24-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$24/2)&gt;Parametros!$B$55:$B$63)*(($D$24/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($D$24/2)&gt;Parametros!$B$67:$B$68)*(($D$24/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($D$24&gt;Parametros!$B$55:$B$63)*($D$24-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($D$24&gt;Parametros!$B$67:$B$68)*($D$24-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="E26" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$24/2)&gt;Parametros!$B$50:$B$58)*(($E$24/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$24/2)&gt;Parametros!$B$62:$B$63)*(($E$24/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$24&gt;Parametros!$B$50:$B$58)*($E$24-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$24&gt;Parametros!$B$62:$B$63)*($E$24-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$24/2)&gt;Parametros!$B$55:$B$63)*(($E$24/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($E$24/2)&gt;Parametros!$B$67:$B$68)*(($E$24/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($E$24&gt;Parametros!$B$55:$B$63)*($E$24-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($E$24&gt;Parametros!$B$67:$B$68)*($E$24-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -16821,15 +16944,15 @@
         </is>
       </c>
       <c r="C27" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$25/2)&gt;Parametros!$B$50:$B$58)*(($C$25/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$25/2)&gt;Parametros!$B$62:$B$63)*(($C$25/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$25&gt;Parametros!$B$50:$B$58)*($C$25-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$25&gt;Parametros!$B$62:$B$63)*($C$25-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$25/2)&gt;Parametros!$B$55:$B$63)*(($C$25/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$25/2)&gt;Parametros!$B$67:$B$68)*(($C$25/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($C$25&gt;Parametros!$B$55:$B$63)*($C$25-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($C$25&gt;Parametros!$B$67:$B$68)*($C$25-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$25/2)&gt;Parametros!$B$50:$B$58)*(($D$25/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$25/2)&gt;Parametros!$B$62:$B$63)*(($D$25/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$25&gt;Parametros!$B$50:$B$58)*($D$25-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$25&gt;Parametros!$B$62:$B$63)*($D$25-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$25/2)&gt;Parametros!$B$55:$B$63)*(($D$25/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($D$25/2)&gt;Parametros!$B$67:$B$68)*(($D$25/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($D$25&gt;Parametros!$B$55:$B$63)*($D$25-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($D$25&gt;Parametros!$B$67:$B$68)*($D$25-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="E27" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$25/2)&gt;Parametros!$B$50:$B$58)*(($E$25/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$25/2)&gt;Parametros!$B$62:$B$63)*(($E$25/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$25&gt;Parametros!$B$50:$B$58)*($E$25-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$25&gt;Parametros!$B$62:$B$63)*($E$25-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$25/2)&gt;Parametros!$B$55:$B$63)*(($E$25/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($E$25/2)&gt;Parametros!$B$67:$B$68)*(($E$25/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($E$25&gt;Parametros!$B$55:$B$63)*($E$25-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($E$25&gt;Parametros!$B$67:$B$68)*($E$25-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
@@ -17311,15 +17434,15 @@
         </is>
       </c>
       <c r="C10" s="28">
-        <f>Inputs!$C$27*Parametros!$C$39+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$40+Inputs!$C$30*Parametros!$C$41</f>
+        <f>Inputs!$C$27*Parametros!$C$44+(Inputs!$C$28+Inputs!$C$29)*Parametros!$C$45+Inputs!$C$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="D10" s="28">
-        <f>Inputs!$D$27*Parametros!$C$39+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$40+Inputs!$D$30*Parametros!$C$41</f>
+        <f>Inputs!$D$27*Parametros!$C$44+(Inputs!$D$28+Inputs!$D$29)*Parametros!$C$45+Inputs!$D$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="E10" s="28">
-        <f>Inputs!$E$27*Parametros!$C$39+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$40+Inputs!$E$30*Parametros!$C$41</f>
+        <f>Inputs!$E$27*Parametros!$C$44+(Inputs!$E$28+Inputs!$E$29)*Parametros!$C$45+Inputs!$E$30*Parametros!$C$46</f>
         <v/>
       </c>
       <c r="F10" s="17" t="inlineStr"/>
@@ -17436,15 +17559,15 @@
         </is>
       </c>
       <c r="C15" s="28">
-        <f>MIN(MAX($C$14,0),Parametros!$C$29)*Parametros!$C$28+MAX(0,MAX($C$14,0)-Parametros!$C$29)*Parametros!$C$30</f>
+        <f>MIN(MAX($C$14,0),Parametros!$C$34)*Parametros!$C$33+MAX(0,MAX($C$14,0)-Parametros!$C$34)*Parametros!$C$35</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>MIN(MAX($D$14,0),Parametros!$C$29)*Parametros!$C$28+MAX(0,MAX($D$14,0)-Parametros!$C$29)*Parametros!$C$30</f>
+        <f>MIN(MAX($D$14,0),Parametros!$C$34)*Parametros!$C$33+MAX(0,MAX($D$14,0)-Parametros!$C$34)*Parametros!$C$35</f>
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>MIN(MAX($E$14,0),Parametros!$C$29)*Parametros!$C$28+MAX(0,MAX($E$14,0)-Parametros!$C$29)*Parametros!$C$30</f>
+        <f>MIN(MAX($E$14,0),Parametros!$C$34)*Parametros!$C$33+MAX(0,MAX($E$14,0)-Parametros!$C$34)*Parametros!$C$35</f>
         <v/>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -17465,15 +17588,15 @@
         </is>
       </c>
       <c r="C16" s="28">
-        <f>MAX($C$14,0)*Parametros!$C$31</f>
+        <f>MAX($C$14,0)*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="D16" s="28">
-        <f>MAX($D$14,0)*Parametros!$C$31</f>
+        <f>MAX($D$14,0)*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="E16" s="28">
-        <f>MAX($E$14,0)*Parametros!$C$31</f>
+        <f>MAX($E$14,0)*Parametros!$C$36</f>
         <v/>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -17744,15 +17867,15 @@
         </is>
       </c>
       <c r="C27" s="28">
-        <f>IF($C$26=1,0,($C$24+$C$25)*Parametros!$C$33)</f>
+        <f>IF($C$26=1,0,($C$24+$C$25)*Parametros!$C$38)</f>
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>IF($D$26=1,0,($D$24+$D$25)*Parametros!$C$33)</f>
+        <f>IF($D$26=1,0,($D$24+$D$25)*Parametros!$C$38)</f>
         <v/>
       </c>
       <c r="E27" s="28">
-        <f>IF($E$26=1,0,($E$24+$E$25)*Parametros!$C$33)</f>
+        <f>IF($E$26=1,0,($E$24+$E$25)*Parametros!$C$38)</f>
         <v/>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
@@ -17781,15 +17904,15 @@
         </is>
       </c>
       <c r="C29" s="27">
-        <f>MAX(0,$C$11-MIN($C$11,MAX(Parametros!$C$25,$C$12*Parametros!$C$12)))+IF($C$26=1,$C$24*Parametros!$C$34,0)</f>
+        <f>MAX(0,$C$11-MIN($C$11,MAX(Parametros!$C$30,$C$12*Parametros!$C$12)))+IF($C$26=1,$C$24*Parametros!$C$39,0)</f>
         <v/>
       </c>
       <c r="D29" s="27">
-        <f>MAX(0,$D$11-MIN($D$11,MAX(Parametros!$C$25,$D$12*Parametros!$C$12)))+IF($D$26=1,$D$24*Parametros!$C$34,0)</f>
+        <f>MAX(0,$D$11-MIN($D$11,MAX(Parametros!$C$30,$D$12*Parametros!$C$12)))+IF($D$26=1,$D$24*Parametros!$C$39,0)</f>
         <v/>
       </c>
       <c r="E29" s="27">
-        <f>MAX(0,$E$11-MIN($E$11,MAX(Parametros!$C$25,$E$12*Parametros!$C$12)))+IF($E$26=1,$E$24*Parametros!$C$34,0)</f>
+        <f>MAX(0,$E$11-MIN($E$11,MAX(Parametros!$C$30,$E$12*Parametros!$C$12)))+IF($E$26=1,$E$24*Parametros!$C$39,0)</f>
         <v/>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -17810,15 +17933,15 @@
         </is>
       </c>
       <c r="C30" s="28">
-        <f>Inputs!$C$37+IF($C$26=1,$C$25*Parametros!$C$34,0)</f>
+        <f>Inputs!$C$37+IF($C$26=1,$C$25*Parametros!$C$39,0)</f>
         <v/>
       </c>
       <c r="D30" s="28">
-        <f>Inputs!$D$37+IF($D$26=1,$D$25*Parametros!$C$34,0)</f>
+        <f>Inputs!$D$37+IF($D$26=1,$D$25*Parametros!$C$39,0)</f>
         <v/>
       </c>
       <c r="E30" s="28">
-        <f>Inputs!$E$37+IF($E$26=1,$E$25*Parametros!$C$34,0)</f>
+        <f>Inputs!$E$37+IF($E$26=1,$E$25*Parametros!$C$39,0)</f>
         <v/>
       </c>
       <c r="F30" s="17" t="inlineStr"/>
@@ -17889,15 +18012,15 @@
         </is>
       </c>
       <c r="C33" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$31/2)&gt;Parametros!$B$50:$B$58)*(($C$31/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$31/2)&gt;Parametros!$B$62:$B$63)*(($C$31/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$31&gt;Parametros!$B$50:$B$58)*($C$31-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$31&gt;Parametros!$B$62:$B$63)*($C$31-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$31/2)&gt;Parametros!$B$55:$B$63)*(($C$31/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$31/2)&gt;Parametros!$B$67:$B$68)*(($C$31/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($C$31&gt;Parametros!$B$55:$B$63)*($C$31-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($C$31&gt;Parametros!$B$67:$B$68)*($C$31-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="D33" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$31/2)&gt;Parametros!$B$50:$B$58)*(($D$31/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$31/2)&gt;Parametros!$B$62:$B$63)*(($D$31/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$31&gt;Parametros!$B$50:$B$58)*($D$31-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$31&gt;Parametros!$B$62:$B$63)*($D$31-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$31/2)&gt;Parametros!$B$55:$B$63)*(($D$31/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($D$31/2)&gt;Parametros!$B$67:$B$68)*(($D$31/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($D$31&gt;Parametros!$B$55:$B$63)*($D$31-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($D$31&gt;Parametros!$B$67:$B$68)*($D$31-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="E33" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$31/2)&gt;Parametros!$B$50:$B$58)*(($E$31/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$31/2)&gt;Parametros!$B$62:$B$63)*(($E$31/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$31&gt;Parametros!$B$50:$B$58)*($E$31-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$31&gt;Parametros!$B$62:$B$63)*($E$31-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$31/2)&gt;Parametros!$B$55:$B$63)*(($E$31/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($E$31/2)&gt;Parametros!$B$67:$B$68)*(($E$31/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($E$31&gt;Parametros!$B$55:$B$63)*($E$31-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($E$31&gt;Parametros!$B$67:$B$68)*($E$31-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F33" s="17" t="inlineStr"/>
@@ -17914,15 +18037,15 @@
         </is>
       </c>
       <c r="C34" s="28">
-        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$32/2)&gt;Parametros!$B$50:$B$58)*(($C$32/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($C$32/2)&gt;Parametros!$B$62:$B$63)*(($C$32/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($C$32&gt;Parametros!$B$50:$B$58)*($C$32-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($C$32&gt;Parametros!$B$62:$B$63)*($C$32-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$C$38=1,2*(SUMPRODUCT((($C$32/2)&gt;Parametros!$B$55:$B$63)*(($C$32/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($C$32/2)&gt;Parametros!$B$67:$B$68)*(($C$32/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($C$32&gt;Parametros!$B$55:$B$63)*($C$32-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($C$32&gt;Parametros!$B$67:$B$68)*($C$32-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="D34" s="28">
-        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$32/2)&gt;Parametros!$B$50:$B$58)*(($D$32/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($D$32/2)&gt;Parametros!$B$62:$B$63)*(($D$32/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($D$32&gt;Parametros!$B$50:$B$58)*($D$32-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($D$32&gt;Parametros!$B$62:$B$63)*($D$32-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$D$38=1,2*(SUMPRODUCT((($D$32/2)&gt;Parametros!$B$55:$B$63)*(($D$32/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($D$32/2)&gt;Parametros!$B$67:$B$68)*(($D$32/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($D$32&gt;Parametros!$B$55:$B$63)*($D$32-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($D$32&gt;Parametros!$B$67:$B$68)*($D$32-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="E34" s="28">
-        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$32/2)&gt;Parametros!$B$50:$B$58)*(($E$32/2)-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT((($E$32/2)&gt;Parametros!$B$62:$B$63)*(($E$32/2)-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63)),SUMPRODUCT(($E$32&gt;Parametros!$B$50:$B$58)*($E$32-Parametros!$B$50:$B$58)*Parametros!$E$50:$E$58)+SUMPRODUCT(($E$32&gt;Parametros!$B$62:$B$63)*($E$32-Parametros!$B$62:$B$63)*Parametros!$E$62:$E$63))</f>
+        <f>IF(Inputs!$E$38=1,2*(SUMPRODUCT((($E$32/2)&gt;Parametros!$B$55:$B$63)*(($E$32/2)-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT((($E$32/2)&gt;Parametros!$B$67:$B$68)*(($E$32/2)-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68)),SUMPRODUCT(($E$32&gt;Parametros!$B$55:$B$63)*($E$32-Parametros!$B$55:$B$63)*Parametros!$E$55:$E$63)+SUMPRODUCT(($E$32&gt;Parametros!$B$67:$B$68)*($E$32-Parametros!$B$67:$B$68)*Parametros!$E$67:$E$68))</f>
         <v/>
       </c>
       <c r="F34" s="17" t="inlineStr"/>
@@ -18134,15 +18257,15 @@
         </is>
       </c>
       <c r="C43" s="28">
-        <f>$C$25-IF($C$26=1,0,$C$25*Parametros!$C$33)</f>
+        <f>$C$25-IF($C$26=1,0,$C$25*Parametros!$C$38)</f>
         <v/>
       </c>
       <c r="D43" s="28">
-        <f>$D$25-IF($D$26=1,0,$D$25*Parametros!$C$33)</f>
+        <f>$D$25-IF($D$26=1,0,$D$25*Parametros!$C$38)</f>
         <v/>
       </c>
       <c r="E43" s="28">
-        <f>$E$25-IF($E$26=1,0,$E$25*Parametros!$C$33)</f>
+        <f>$E$25-IF($E$26=1,0,$E$25*Parametros!$C$38)</f>
         <v/>
       </c>
       <c r="F43" s="17" t="inlineStr">
@@ -18325,15 +18448,15 @@
         </is>
       </c>
       <c r="C6" s="28">
-        <f>Inputs!$C$27*Parametros!$C$36</f>
+        <f>Inputs!$C$27*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="D6" s="28">
-        <f>Inputs!$D$27*Parametros!$C$36</f>
+        <f>Inputs!$D$27*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="E6" s="28">
-        <f>Inputs!$E$27*Parametros!$C$36</f>
+        <f>Inputs!$E$27*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="F6" s="17" t="inlineStr"/>
@@ -18350,15 +18473,15 @@
         </is>
       </c>
       <c r="C7" s="28">
-        <f>Inputs!$C$28*Parametros!$C$36</f>
+        <f>Inputs!$C$28*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="D7" s="28">
-        <f>Inputs!$D$28*Parametros!$C$36</f>
+        <f>Inputs!$D$28*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="E7" s="28">
-        <f>Inputs!$E$28*Parametros!$C$36</f>
+        <f>Inputs!$E$28*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="F7" s="17" t="inlineStr"/>
@@ -18375,15 +18498,15 @@
         </is>
       </c>
       <c r="C8" s="28">
-        <f>Inputs!$C$29*Parametros!$C$37</f>
+        <f>Inputs!$C$29*Parametros!$C$42</f>
         <v/>
       </c>
       <c r="D8" s="28">
-        <f>Inputs!$D$29*Parametros!$C$37</f>
+        <f>Inputs!$D$29*Parametros!$C$42</f>
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>Inputs!$E$29*Parametros!$C$37</f>
+        <f>Inputs!$E$29*Parametros!$C$42</f>
         <v/>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -18404,15 +18527,15 @@
         </is>
       </c>
       <c r="C9" s="28">
-        <f>Inputs!$C$30*Parametros!$C$36</f>
+        <f>Inputs!$C$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>Inputs!$D$30*Parametros!$C$36</f>
+        <f>Inputs!$D$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>Inputs!$E$30*Parametros!$C$36</f>
+        <f>Inputs!$E$30*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="F9" s="17" t="inlineStr"/>
@@ -18762,15 +18885,15 @@
         </is>
       </c>
       <c r="C24" s="27">
-        <f>Inputs!$C$28*$C$23*(Parametros!$C$36-Parametros!$C$37)</f>
+        <f>Inputs!$C$28*$C$23*(Parametros!$C$41-Parametros!$C$42)</f>
         <v/>
       </c>
       <c r="D24" s="27">
-        <f>Inputs!$D$28*$D$23*(Parametros!$C$36-Parametros!$C$37)</f>
+        <f>Inputs!$D$28*$D$23*(Parametros!$C$41-Parametros!$C$42)</f>
         <v/>
       </c>
       <c r="E24" s="27">
-        <f>Inputs!$E$28*$E$23*(Parametros!$C$36-Parametros!$C$37)</f>
+        <f>Inputs!$E$28*$E$23*(Parametros!$C$41-Parametros!$C$42)</f>
         <v/>
       </c>
       <c r="F24" s="17" t="inlineStr"/>
@@ -18828,15 +18951,15 @@
         </is>
       </c>
       <c r="C27" s="27">
-        <f>$C$26*Parametros!$C$36</f>
+        <f>$C$26*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="D27" s="27">
-        <f>$D$26*Parametros!$C$36</f>
+        <f>$D$26*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="E27" s="27">
-        <f>$E$26*Parametros!$C$36</f>
+        <f>$E$26*Parametros!$C$41</f>
         <v/>
       </c>
       <c r="F27" s="17" t="inlineStr"/>

--- a/01-modelo/M1_modelo_comparativo.xlsx
+++ b/01-modelo/M1_modelo_comparativo.xlsx
@@ -6072,7 +6072,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>N.º de gabinetes</t>
+          <t>N.º de gabinetes desta opção</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -6086,7 +6086,11 @@
       <c r="D6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="17" t="inlineStr"/>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Independente da folha Operacao, e é essa a intenção: aqui compara-se a hipótese de 2 com a hipótese de 3, enquanto na Operacao está o espaço efetivamente escolhido. Alterar um não altera o outro.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -7095,13 +7099,16 @@
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A62:E62"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="C7 C8 C9 C10 D7 D8 D9 D10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número. Valores monetários não podem ser negativos." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="C12 D12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentagem inválida" error="Introduza a percentagem como fração: 0,25 para 25%." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>2</formula2>
+    </dataValidation>
+    <dataValidation sqref="C6 D6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8306,6 +8313,11 @@
     <mergeCell ref="D49:G49"/>
     <mergeCell ref="A35:I35"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="H5 H6 H7 H8 H10 H11 H12 H13 H15 H16 H17 H18 H20 H21 H22 H23 H25 H26 H27 H28 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 I5 I6 I7 I8 I10 I11 I12 I13 I15 I16 I17 I18 I20 I21 I22 I23 I25 I26 I27 I28 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8854,9 +8866,12 @@
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="C29:E29"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C22 C23 C24 C25 C26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor não permitido" error="Só são admitidos 0 ou 1." type="list">
       <formula1>"0,1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C22 C23 C24 C25 C26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10382,13 +10397,16 @@
     <mergeCell ref="E28:N28"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 M21 N21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número. Valores monetários não podem ser negativos." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="C13 C16 D13 D16 D40 E13 E16 E40 F13 F16 G13 G16 H13 H16 I13 I16 J13 J16 K13 K16 L13 L16 M13 M16 N13 N16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentagem inválida" error="Introduza a percentagem como fração: 0,25 para 25%." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>2</formula2>
+    </dataValidation>
+    <dataValidation sqref="C7 C33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10876,9 +10894,12 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="B5 B6 B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor não permitido" error="Só são admitidos 0 ou 1." type="list">
       <formula1>"0,1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5 B6 B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12863,7 +12884,7 @@
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A70:E70"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="C37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor não permitido" error="Só são admitidos os valores: 0,1" type="list">
       <formula1>"0,1"</formula1>
     </dataValidation>
@@ -12873,6 +12894,9 @@
     <dataValidation sqref="C7 C8 C11 C12 C14 C15 C17 C18 C20 C21 C22 C24 C25 C27 C31 C33 C35 C36 C38 C39 C41 C42 C44 C45 C46 C48 C49 D55 D56 D57 D58 D59 D60 D61 D62 D63 D67 D68" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentagem inválida" error="Introduza a percentagem como fração: 0,25 para 25%." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>2</formula2>
+    </dataValidation>
+    <dataValidation sqref="C9 C13 C16 C29 C37 C50 C63 C68" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13289,18 +13313,22 @@
         </is>
       </c>
       <c r="C20" s="21">
-        <f>$C$8*60/$C$9</f>
+        <f>IF($C$9&lt;=0,0,$C$8*60/$C$9)</f>
         <v/>
       </c>
       <c r="D20" s="21">
-        <f>$D$8*60/$D$9</f>
+        <f>IF($D$9&lt;=0,0,$D$8*60/$D$9)</f>
         <v/>
       </c>
       <c r="E20" s="21">
-        <f>$E$8*60/$E$9</f>
-        <v/>
-      </c>
-      <c r="F20" s="17" t="inlineStr"/>
+        <f>IF($E$9&lt;=0,0,$E$8*60/$E$9)</f>
+        <v/>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>A guarda contra duração zero não é zelo excessivo: sem ela, um zero nesta coluna propaga erro de divisão por todas as folhas do ficheiro.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
@@ -13676,8 +13704,14 @@
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation sqref="C13 C18 D13 D18 E13 E18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número. Valores monetários não podem ser negativos." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C6 C7 C8 C9 C11 C12 C15 C16 C17 D6 D7 D8 D9 D11 D12 D15 D16 D17 E6 E7 E8 E9 E11 E12 E15 E16 E17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C6 C7 C8 C9 D6 D7 D8 D9 E6 E7 E8 E9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Tem de ser maior do que zero" error="Este valor é divisor no cálculo da capacidade. A zero, o modelo inteiro fica em erro." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -15521,7 +15555,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="C6 D6 E6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor não permitido" error="Só são admitidos os valores: 1,2" type="list">
       <formula1>"1,2"</formula1>
     </dataValidation>
@@ -15540,6 +15574,9 @@
     <dataValidation sqref="C12 C14 C23 C34 C35 D12 D14 D23 D34 D35 E12 E14 E23 E34 E35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentagem inválida" error="Introduza a percentagem como fração: 0,25 para 25%." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>2</formula2>
+    </dataValidation>
+    <dataValidation sqref="C6 C11 C16 C38 C39 D6 D11 D16 D38 D39 E6 E11 E16 E38 E39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01-modelo/M1_modelo_comparativo.xlsx
+++ b/01-modelo/M1_modelo_comparativo.xlsx
@@ -203,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -282,6 +282,7 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -895,7 +896,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Saldo de tesouraria acumulado — ano 1</a:t>
+              <a:t>Saldo de tesouraria acumulado no ano 1, por cenário</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -908,10 +909,13 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>Saldo acumulado</v>
+            <v>Baixo</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="A9C8E2"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -926,6 +930,90 @@
           <val>
             <numRef>
               <f>'Tesouraria'!$C$24:$N$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Base</v>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4A93CC"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Tesouraria'!$C$41:$N$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Alto</v>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="1F5E96"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Tesouraria'!$C$58:$N$58</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Tensão</v>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C0442F"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Tesouraria'!$C$75:$N$75</f>
             </numRef>
           </val>
         </ser>
@@ -1111,7 +1199,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="2880000"/>
+    <ext cx="7200000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2921,7 +3009,7 @@
         </is>
       </c>
       <c r="C59" s="27">
-        <f>Tesouraria!$O$15</f>
+        <f>Tesouraria!$O$32</f>
         <v/>
       </c>
       <c r="D59" s="39" t="n"/>
@@ -6006,7 +6094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7084,20 +7172,135 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>O ponto de viragem nos três cenários</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
+    </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="20" t="inlineStr">
         <is>
+          <t>O varrimento acima usa o cenário Base. O ponto de viragem, porém, resolve-se por álgebra e não precisa de varrimento: é a capacidade de dois gabinetes mais a renda adicional dividida pela margem de cada consulta. Aqui está para os três.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Cenário</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Consultas/ano para compensar</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Doentes por dia</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Utilização do espaço de 2</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="B64" s="23">
+        <f>IF((BreakEven!$C$14*BreakEven!$C$9)&lt;=0,0,(2*Operacao!$C$7*Operacao!$C$20)+($D$22-$C$22)/(BreakEven!$C$14*BreakEven!$C$9))</f>
+        <v/>
+      </c>
+      <c r="C64" s="21">
+        <f>B64/Operacao!$C$7</f>
+        <v/>
+      </c>
+      <c r="D64" s="37">
+        <f>IF((2*Operacao!$C$7*Operacao!$C$20)&lt;=0,0,B64/(2*Operacao!$C$7*Operacao!$C$20))</f>
+        <v/>
+      </c>
+      <c r="E64" s="50">
+        <f>IF(D64&gt;1,"Só compensa se a procura exceder o que dois gabinetes comportam","Compensa antes de esgotar dois gabinetes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B65" s="23">
+        <f>IF((BreakEven!$D$14*BreakEven!$D$9)&lt;=0,0,(2*Operacao!$D$7*Operacao!$D$20)+($D$22-$C$22)/(BreakEven!$D$14*BreakEven!$D$9))</f>
+        <v/>
+      </c>
+      <c r="C65" s="21">
+        <f>B65/Operacao!$D$7</f>
+        <v/>
+      </c>
+      <c r="D65" s="37">
+        <f>IF((2*Operacao!$D$7*Operacao!$D$20)&lt;=0,0,B65/(2*Operacao!$D$7*Operacao!$D$20))</f>
+        <v/>
+      </c>
+      <c r="E65" s="50">
+        <f>IF(D65&gt;1,"Só compensa se a procura exceder o que dois gabinetes comportam","Compensa antes de esgotar dois gabinetes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="B66" s="23">
+        <f>IF((BreakEven!$E$14*BreakEven!$E$9)&lt;=0,0,(2*Operacao!$E$7*Operacao!$E$20)+($D$22-$C$22)/(BreakEven!$E$14*BreakEven!$E$9))</f>
+        <v/>
+      </c>
+      <c r="C66" s="21">
+        <f>B66/Operacao!$E$7</f>
+        <v/>
+      </c>
+      <c r="D66" s="37">
+        <f>IF((2*Operacao!$E$7*Operacao!$E$20)&lt;=0,0,B66/(2*Operacao!$E$7*Operacao!$E$20))</f>
+        <v/>
+      </c>
+      <c r="E66" s="50">
+        <f>IF(D66&gt;1,"Só compensa se a procura exceder o que dois gabinetes comportam","Compensa antes de esgotar dois gabinetes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
           <t>Leitura: abaixo do ponto de viragem, o terceiro gabinete é renda e obras a mais sem receita adicional — a opção de dois gabinetes ganha por diferença de custo fixo. Acima, a opção de dois perde consultas por falta de espaço e a de três recupera o custo. A pergunta a fazer à cliente não é qual espaço prefere: é quantos doentes por dia espera atender no fim do segundo ano. Resolução do varrimento: 400 consultas por ano. O ponto de viragem real situa-se algures no intervalo anterior ao indicado — refinar por interpolação se a decisão ficar perto do limite. Registado em R1-34.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A68:E68"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="C7 C8 C9 C10 D7 D8 D9 D10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número. Valores monetários não podem ser negativos." type="decimal" operator="greaterThanOrEqual">
@@ -7218,19 +7421,19 @@
         <f>V1_ENI_Simplificado!$D$36</f>
         <v/>
       </c>
-      <c r="E5" s="50" t="n">
+      <c r="E5" s="51" t="n">
         <v>21022.94</v>
       </c>
       <c r="F5" s="29">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="G5" s="51">
+      <c r="G5" s="52">
         <f>IF(ABS(F5)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H5" s="52" t="n"/>
-      <c r="I5" s="52" t="n"/>
+      <c r="H5" s="53" t="n"/>
+      <c r="I5" s="53" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr"/>
@@ -7248,19 +7451,19 @@
         <f>V1_ENI_Simplificado!$D$23</f>
         <v/>
       </c>
-      <c r="E6" s="50" t="n">
+      <c r="E6" s="51" t="n">
         <v>15099.84</v>
       </c>
       <c r="F6" s="29">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="52">
         <f>IF(ABS(F6)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H6" s="52" t="n"/>
-      <c r="I6" s="52" t="n"/>
+      <c r="H6" s="53" t="n"/>
+      <c r="I6" s="53" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr"/>
@@ -7278,19 +7481,19 @@
         <f>V1_ENI_Simplificado!$D$40</f>
         <v/>
       </c>
-      <c r="E7" s="50" t="n">
+      <c r="E7" s="51" t="n">
         <v>36122.78</v>
       </c>
       <c r="F7" s="29">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="52">
         <f>IF(ABS(F7)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H7" s="52" t="n"/>
-      <c r="I7" s="52" t="n"/>
+      <c r="H7" s="53" t="n"/>
+      <c r="I7" s="53" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr"/>
@@ -7308,19 +7511,19 @@
         <f>V1_ENI_Simplificado!$D$44</f>
         <v/>
       </c>
-      <c r="E8" s="50" t="n">
+      <c r="E8" s="51" t="n">
         <v>11513.22</v>
       </c>
       <c r="F8" s="29">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="52">
         <f>IF(ABS(F8)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="52" t="n"/>
+      <c r="H8" s="53" t="n"/>
+      <c r="I8" s="53" t="n"/>
     </row>
     <row r="9"/>
     <row r="10">
@@ -7343,19 +7546,19 @@
         <f>V2_ENI_ContOrg!$D$25</f>
         <v/>
       </c>
-      <c r="E10" s="50" t="n">
+      <c r="E10" s="51" t="n">
         <v>7300.06</v>
       </c>
       <c r="F10" s="29">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="52">
         <f>IF(ABS(F10)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H10" s="52" t="n"/>
-      <c r="I10" s="52" t="n"/>
+      <c r="H10" s="53" t="n"/>
+      <c r="I10" s="53" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr"/>
@@ -7373,19 +7576,19 @@
         <f>V2_ENI_ContOrg!$D$13</f>
         <v/>
       </c>
-      <c r="E11" s="50" t="n">
+      <c r="E11" s="51" t="n">
         <v>8660.450000000001</v>
       </c>
       <c r="F11" s="29">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="51">
+      <c r="G11" s="52">
         <f>IF(ABS(F11)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H11" s="52" t="n"/>
-      <c r="I11" s="52" t="n"/>
+      <c r="H11" s="53" t="n"/>
+      <c r="I11" s="53" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr"/>
@@ -7403,19 +7606,19 @@
         <f>V2_ENI_ContOrg!$D$29</f>
         <v/>
       </c>
-      <c r="E12" s="50" t="n">
+      <c r="E12" s="51" t="n">
         <v>15960.51</v>
       </c>
       <c r="F12" s="29">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="51">
+      <c r="G12" s="52">
         <f>IF(ABS(F12)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H12" s="52" t="n"/>
-      <c r="I12" s="52" t="n"/>
+      <c r="H12" s="53" t="n"/>
+      <c r="I12" s="53" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr"/>
@@ -7433,19 +7636,19 @@
         <f>V2_ENI_ContOrg!$D$33</f>
         <v/>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="51" t="n">
         <v>31675.49</v>
       </c>
       <c r="F13" s="29">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="51">
+      <c r="G13" s="52">
         <f>IF(ABS(F13)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H13" s="52" t="n"/>
-      <c r="I13" s="52" t="n"/>
+      <c r="H13" s="53" t="n"/>
+      <c r="I13" s="53" t="n"/>
     </row>
     <row r="14"/>
     <row r="15">
@@ -7468,19 +7671,19 @@
         <f>V3_Soc_Transparente!$D$31</f>
         <v/>
       </c>
-      <c r="E15" s="50" t="n">
+      <c r="E15" s="51" t="n">
         <v>7477.92</v>
       </c>
       <c r="F15" s="29">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="52">
         <f>IF(ABS(F15)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H15" s="52" t="n"/>
-      <c r="I15" s="52" t="n"/>
+      <c r="H15" s="53" t="n"/>
+      <c r="I15" s="53" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr"/>
@@ -7498,19 +7701,19 @@
         <f>V3_Soc_Transparente!$D$18+V3_Soc_Transparente!$D$12</f>
         <v/>
       </c>
-      <c r="E16" s="50" t="n">
+      <c r="E16" s="51" t="n">
         <v>5838</v>
       </c>
       <c r="F16" s="29">
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="52">
         <f>IF(ABS(F16)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H16" s="52" t="n"/>
-      <c r="I16" s="52" t="n"/>
+      <c r="H16" s="53" t="n"/>
+      <c r="I16" s="53" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr"/>
@@ -7528,19 +7731,19 @@
         <f>V3_Soc_Transparente!$D$35</f>
         <v/>
       </c>
-      <c r="E17" s="50" t="n">
+      <c r="E17" s="51" t="n">
         <v>14115.92</v>
       </c>
       <c r="F17" s="29">
         <f>D17-E17</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="52">
         <f>IF(ABS(F17)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="52" t="n"/>
+      <c r="H17" s="53" t="n"/>
+      <c r="I17" s="53" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr"/>
@@ -7558,19 +7761,19 @@
         <f>V3_Soc_Transparente!$D$39</f>
         <v/>
       </c>
-      <c r="E18" s="50" t="n">
+      <c r="E18" s="51" t="n">
         <v>33520.08</v>
       </c>
       <c r="F18" s="29">
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="51">
+      <c r="G18" s="52">
         <f>IF(ABS(F18)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H18" s="52" t="n"/>
-      <c r="I18" s="52" t="n"/>
+      <c r="H18" s="53" t="n"/>
+      <c r="I18" s="53" t="n"/>
     </row>
     <row r="19"/>
     <row r="20">
@@ -7593,19 +7796,19 @@
         <f>V4_Soc_NaoTransparente!$D$38</f>
         <v/>
       </c>
-      <c r="E20" s="50" t="n">
+      <c r="E20" s="51" t="n">
         <v>2382.04</v>
       </c>
       <c r="F20" s="29">
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="52">
         <f>IF(ABS(F20)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H20" s="52" t="n"/>
-      <c r="I20" s="52" t="n"/>
+      <c r="H20" s="53" t="n"/>
+      <c r="I20" s="53" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr"/>
@@ -7623,19 +7826,19 @@
         <f>V4_Soc_NaoTransparente!$D$40+V4_Soc_NaoTransparente!$D$13</f>
         <v/>
       </c>
-      <c r="E21" s="50" t="n">
+      <c r="E21" s="51" t="n">
         <v>5838</v>
       </c>
       <c r="F21" s="29">
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="52">
         <f>IF(ABS(F21)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H21" s="52" t="n"/>
-      <c r="I21" s="52" t="n"/>
+      <c r="H21" s="53" t="n"/>
+      <c r="I21" s="53" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr"/>
@@ -7653,19 +7856,19 @@
         <f>V4_Soc_NaoTransparente!$D$43</f>
         <v/>
       </c>
-      <c r="E22" s="50" t="n">
+      <c r="E22" s="51" t="n">
         <v>18792.52</v>
       </c>
       <c r="F22" s="29">
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="52">
         <f>IF(ABS(F22)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H22" s="52" t="n"/>
-      <c r="I22" s="52" t="n"/>
+      <c r="H22" s="53" t="n"/>
+      <c r="I22" s="53" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr"/>
@@ -7683,19 +7886,19 @@
         <f>V4_Soc_NaoTransparente!$D$47</f>
         <v/>
       </c>
-      <c r="E23" s="50" t="n">
+      <c r="E23" s="51" t="n">
         <v>24612.36</v>
       </c>
       <c r="F23" s="29">
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="51">
+      <c r="G23" s="52">
         <f>IF(ABS(F23)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H23" s="52" t="n"/>
-      <c r="I23" s="52" t="n"/>
+      <c r="H23" s="53" t="n"/>
+      <c r="I23" s="53" t="n"/>
     </row>
     <row r="24"/>
     <row r="25">
@@ -7718,19 +7921,19 @@
         <f>V1_ENI_Simplificado!$E$36</f>
         <v/>
       </c>
-      <c r="E25" s="50" t="n">
+      <c r="E25" s="51" t="n">
         <v>38645.12</v>
       </c>
       <c r="F25" s="29">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="51">
+      <c r="G25" s="52">
         <f>IF(ABS(F25)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H25" s="52" t="n"/>
-      <c r="I25" s="52" t="n"/>
+      <c r="H25" s="53" t="n"/>
+      <c r="I25" s="53" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr"/>
@@ -7748,19 +7951,19 @@
         <f>V1_ENI_Simplificado!$E$23</f>
         <v/>
       </c>
-      <c r="E26" s="50" t="n">
+      <c r="E26" s="51" t="n">
         <v>16101.36</v>
       </c>
       <c r="F26" s="29">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="51">
+      <c r="G26" s="52">
         <f>IF(ABS(F26)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H26" s="52" t="n"/>
-      <c r="I26" s="52" t="n"/>
+      <c r="H26" s="53" t="n"/>
+      <c r="I26" s="53" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr"/>
@@ -7778,19 +7981,19 @@
         <f>V1_ENI_Simplificado!$E$40</f>
         <v/>
       </c>
-      <c r="E27" s="50" t="n">
+      <c r="E27" s="51" t="n">
         <v>54746.48</v>
       </c>
       <c r="F27" s="29">
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="51">
+      <c r="G27" s="52">
         <f>IF(ABS(F27)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H27" s="52" t="n"/>
-      <c r="I27" s="52" t="n"/>
+      <c r="H27" s="53" t="n"/>
+      <c r="I27" s="53" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr"/>
@@ -7808,19 +8011,19 @@
         <f>V1_ENI_Simplificado!$E$44</f>
         <v/>
       </c>
-      <c r="E28" s="50" t="n">
+      <c r="E28" s="51" t="n">
         <v>11088.52</v>
       </c>
       <c r="F28" s="29">
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="51">
+      <c r="G28" s="52">
         <f>IF(ABS(F28)&lt;0.5,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H28" s="52" t="n"/>
-      <c r="I28" s="52" t="n"/>
+      <c r="H28" s="53" t="n"/>
+      <c r="I28" s="53" t="n"/>
     </row>
     <row r="29"/>
     <row r="30">
@@ -7884,23 +8087,23 @@
           <t>Capacidade anual instalada (consultas)</t>
         </is>
       </c>
-      <c r="D36" s="53">
+      <c r="D36" s="54">
         <f>Operacao!$D$21</f>
         <v/>
       </c>
       <c r="E36" s="38" t="n">
         <v>4693.333333</v>
       </c>
-      <c r="F36" s="54">
+      <c r="F36" s="55">
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="51">
+      <c r="G36" s="52">
         <f>IF(ABS(F36)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H36" s="52" t="n"/>
-      <c r="I36" s="52" t="n"/>
+      <c r="H36" s="53" t="n"/>
+      <c r="I36" s="53" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7918,23 +8121,23 @@
           <t>Taxa de utilização dos gabinetes</t>
         </is>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="56">
         <f>Operacao!$D$26</f>
         <v/>
       </c>
-      <c r="E37" s="56" t="n">
+      <c r="E37" s="57" t="n">
         <v>0.447443</v>
       </c>
-      <c r="F37" s="54">
+      <c r="F37" s="55">
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="51">
+      <c r="G37" s="52">
         <f>IF(ABS(F37)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H37" s="52" t="n"/>
-      <c r="I37" s="52" t="n"/>
+      <c r="H37" s="53" t="n"/>
+      <c r="I37" s="53" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -7956,19 +8159,19 @@
         <f>Operacao!$D$31</f>
         <v/>
       </c>
-      <c r="E38" s="50" t="n">
+      <c r="E38" s="51" t="n">
         <v>100800</v>
       </c>
-      <c r="F38" s="54">
+      <c r="F38" s="55">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="51">
+      <c r="G38" s="52">
         <f>IF(ABS(F38)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H38" s="52" t="n"/>
-      <c r="I38" s="52" t="n"/>
+      <c r="H38" s="53" t="n"/>
+      <c r="I38" s="53" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7990,19 +8193,19 @@
         <f>IVA!$D$10</f>
         <v/>
       </c>
-      <c r="E39" s="50" t="n">
+      <c r="E39" s="51" t="n">
         <v>10810</v>
       </c>
-      <c r="F39" s="54">
+      <c r="F39" s="55">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="51">
+      <c r="G39" s="52">
         <f>IF(ABS(F39)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H39" s="52" t="n"/>
-      <c r="I39" s="52" t="n"/>
+      <c r="H39" s="53" t="n"/>
+      <c r="I39" s="53" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -8020,23 +8223,23 @@
           <t>Margem de contribuição (%)</t>
         </is>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="56">
         <f>BreakEven!$D$9</f>
         <v/>
       </c>
-      <c r="E40" s="56" t="n">
+      <c r="E40" s="57" t="n">
         <v>0.67</v>
       </c>
-      <c r="F40" s="54">
+      <c r="F40" s="55">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="51">
+      <c r="G40" s="52">
         <f>IF(ABS(F40)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H40" s="52" t="n"/>
-      <c r="I40" s="52" t="n"/>
+      <c r="H40" s="53" t="n"/>
+      <c r="I40" s="53" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -8058,19 +8261,19 @@
         <f>BreakEven!$D$11</f>
         <v/>
       </c>
-      <c r="E41" s="50" t="n">
+      <c r="E41" s="51" t="n">
         <v>29701.492537</v>
       </c>
-      <c r="F41" s="54">
+      <c r="F41" s="55">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="51">
+      <c r="G41" s="52">
         <f>IF(ABS(F41)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H41" s="52" t="n"/>
-      <c r="I41" s="52" t="n"/>
+      <c r="H41" s="53" t="n"/>
+      <c r="I41" s="53" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -8088,23 +8291,23 @@
           <t>Utilização necessária no break-even</t>
         </is>
       </c>
-      <c r="D42" s="55">
+      <c r="D42" s="56">
         <f>BreakEven!$D$16</f>
         <v/>
       </c>
-      <c r="E42" s="56" t="n">
+      <c r="E42" s="57" t="n">
         <v>0.131843</v>
       </c>
-      <c r="F42" s="54">
+      <c r="F42" s="55">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="51">
+      <c r="G42" s="52">
         <f>IF(ABS(F42)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H42" s="52" t="n"/>
-      <c r="I42" s="52" t="n"/>
+      <c r="H42" s="53" t="n"/>
+      <c r="I42" s="53" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -8126,19 +8329,19 @@
         <f>RiscoLaboral!$D$14</f>
         <v/>
       </c>
-      <c r="E43" s="50" t="n">
+      <c r="E43" s="51" t="n">
         <v>77064.75</v>
       </c>
-      <c r="F43" s="54">
+      <c r="F43" s="55">
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="51">
+      <c r="G43" s="52">
         <f>IF(ABS(F43)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H43" s="52" t="n"/>
-      <c r="I43" s="52" t="n"/>
+      <c r="H43" s="53" t="n"/>
+      <c r="I43" s="53" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8156,23 +8359,23 @@
           <t>Payback da opção A (2 gabinetes)</t>
         </is>
       </c>
-      <c r="D44" s="57">
+      <c r="D44" s="58">
         <f>Espaco!$C$28</f>
         <v/>
       </c>
-      <c r="E44" s="58" t="n">
+      <c r="E44" s="59" t="n">
         <v>1.733365</v>
       </c>
-      <c r="F44" s="54">
+      <c r="F44" s="55">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="51">
+      <c r="G44" s="52">
         <f>IF(ABS(F44)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H44" s="52" t="n"/>
-      <c r="I44" s="52" t="n"/>
+      <c r="H44" s="53" t="n"/>
+      <c r="I44" s="53" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -8191,22 +8394,22 @@
         </is>
       </c>
       <c r="D45" s="47">
-        <f>Tesouraria!$C$9</f>
-        <v/>
-      </c>
-      <c r="E45" s="50" t="n">
+        <f>Tesouraria!$D$10</f>
+        <v/>
+      </c>
+      <c r="E45" s="51" t="n">
         <v>61410</v>
       </c>
-      <c r="F45" s="54">
+      <c r="F45" s="55">
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="51">
+      <c r="G45" s="52">
         <f>IF(ABS(F45)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H45" s="52" t="n"/>
-      <c r="I45" s="52" t="n"/>
+      <c r="H45" s="53" t="n"/>
+      <c r="I45" s="53" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -8225,22 +8428,22 @@
         </is>
       </c>
       <c r="D46" s="47">
-        <f>Tesouraria!$C$28</f>
-        <v/>
-      </c>
-      <c r="E46" s="50" t="n">
+        <f>Tesouraria!$D$81</f>
+        <v/>
+      </c>
+      <c r="E46" s="51" t="n">
         <v>62330.9286</v>
       </c>
-      <c r="F46" s="54">
+      <c r="F46" s="55">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="51">
+      <c r="G46" s="52">
         <f>IF(ABS(F46)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H46" s="52" t="n"/>
-      <c r="I46" s="52" t="n"/>
+      <c r="H46" s="53" t="n"/>
+      <c r="I46" s="53" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -8259,22 +8462,22 @@
         </is>
       </c>
       <c r="D47" s="47">
-        <f>Tesouraria!$C$36</f>
-        <v/>
-      </c>
-      <c r="E47" s="50" t="n">
+        <f>Tesouraria!$D$88</f>
+        <v/>
+      </c>
+      <c r="E47" s="51" t="n">
         <v>67305.9286</v>
       </c>
-      <c r="F47" s="54">
+      <c r="F47" s="55">
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="51">
+      <c r="G47" s="52">
         <f>IF(ABS(F47)&lt;0.01,"OK","DIVERGE")</f>
         <v/>
       </c>
-      <c r="H47" s="52" t="n"/>
-      <c r="I47" s="52" t="n"/>
+      <c r="H47" s="53" t="n"/>
+      <c r="I47" s="53" t="n"/>
     </row>
     <row r="48"/>
     <row r="49">
@@ -8438,15 +8641,15 @@
           <t>ANOS</t>
         </is>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="54">
         <f>Parametros!$C$16</f>
         <v/>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="54">
         <f>Parametros!$C$16</f>
         <v/>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="54">
         <f>Parametros!$C$16</f>
         <v/>
       </c>
@@ -8842,7 +9045,7 @@
           <t>LEITURA</t>
         </is>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="60">
         <f>IF($C$28&gt;=3,"RISCO ELEVADO — presunção provável",IF($C$28=2,"RISCO ESTRUTURAL — os dois indícios inevitáveis já se verificam","RISCO CONTIDO"))</f>
         <v/>
       </c>
@@ -8884,7 +9087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -8912,10 +9115,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1">
+    <row r="2" ht="52" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Um negócio pode ser rentável e mesmo assim ficar sem dinheiro. O investimento paga-se todo no início, a receita sobe devagar, e há pagamentos que chegam em bloco. Esta folha responde à única pergunta que importa antes de assinar seja o que for: quanto dinheiro é preciso ter na mão para chegar ao fim do primeiro ano.</t>
+          <t>Um negócio pode ser rentável e mesmo assim ficar sem dinheiro. O investimento paga-se todo no início, a receita sobe devagar, e há pagamentos que chegam em bloco. Esta folha responde à pergunta que vem antes de todas as outras: quanto dinheiro é preciso ter na mão para chegar ao fim do primeiro ano — e responde-a nos três cenários, porque é no cenário baixo que a resposta interessa.</t>
         </is>
       </c>
     </row>
@@ -8929,104 +9132,175 @@
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Investimento em obras, equipamento e software</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>INV</t>
-        </is>
-      </c>
-      <c r="C5" s="35">
-        <f>Inputs!$D$27+Inputs!$D$28+Inputs!$D$29+Inputs!$D$30</f>
-        <v/>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>IVA irrecuperável sobre o investimento</t>
+          <t>Investimento em obras, equipamento e software</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>IVA_IRR</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="C6" s="35">
-        <f>IVA!$D$10</f>
-        <v/>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>Sai da conta e não volta: a fisioterapia é isenta sem direito à dedução.</t>
-        </is>
-      </c>
+        <f>Inputs!$C$27+Inputs!$C$28+Inputs!$C$29+Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="D6" s="35">
+        <f>Inputs!$D$27+Inputs!$D$28+Inputs!$D$29+Inputs!$D$30</f>
+        <v/>
+      </c>
+      <c r="E6" s="35">
+        <f>Inputs!$E$27+Inputs!$E$28+Inputs!$E$29+Inputs!$E$30</f>
+        <v/>
+      </c>
+      <c r="F6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Caução do arrendamento (meses de renda)</t>
+          <t>IVA irrecuperável sobre o investimento</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>MESES_CAUC</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Rubrica que quase sempre se esquece no plano de investimento. Confirmar com a proposta de arrendamento.</t>
+          <t>IVA_IRR</t>
+        </is>
+      </c>
+      <c r="C7" s="35">
+        <f>IVA!$C$10</f>
+        <v/>
+      </c>
+      <c r="D7" s="35">
+        <f>IVA!$D$10</f>
+        <v/>
+      </c>
+      <c r="E7" s="35">
+        <f>IVA!$E$10</f>
+        <v/>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Sai da conta e não volta: a fisioterapia é isenta sem direito à dedução.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
+          <t>Caução do arrendamento (meses de renda)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>MESES_CAUC</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Rubrica que quase sempre falta no plano de investimento. Confirmar com a proposta de arrendamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
           <t>Caução do arrendamento</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>CAUCAO</t>
         </is>
       </c>
-      <c r="C8" s="28">
-        <f>$C$7*Inputs!$D$19/12</f>
-        <v/>
-      </c>
-      <c r="D8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="C9" s="28">
+        <f>$C$8*Inputs!$C$19/12</f>
+        <v/>
+      </c>
+      <c r="D9" s="28">
+        <f>$D$8*Inputs!$D$19/12</f>
+        <v/>
+      </c>
+      <c r="E9" s="28">
+        <f>$E$8*Inputs!$E$19/12</f>
+        <v/>
+      </c>
+      <c r="F9" s="17" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>TOTAL A DESEMBOLSAR NO ARRANQUE</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>ARRANQUE</t>
         </is>
       </c>
-      <c r="C9" s="27">
-        <f>$C$5+$C$6+$C$8</f>
-        <v/>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10"/>
+      <c r="C10" s="27">
+        <f>$C$6+$C$7+$C$9</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>$D$6+$D$7+$D$9</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>$E$6+$E$7+$E$9</f>
+        <v/>
+      </c>
+      <c r="F10" s="17" t="inlineStr"/>
+    </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Ano 1, mês a mês</t>
+          <t>Ano 1, mês a mês — cenário Baixo</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -9139,44 +9413,44 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D13" s="13" t="n">
         <v>0.15</v>
       </c>
-      <c r="D13" s="13" t="n">
-        <v>0.2</v>
-      </c>
       <c r="E13" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G13" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L13" s="13" t="n">
         <v>0.33</v>
       </c>
-      <c r="H13" s="13" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>0.44</v>
-      </c>
       <c r="M13" s="13" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t>RAMPA DE ARRANQUE. É a fila de inputs mais importante desta folha e a que ninguém quer preencher com honestidade. Uma clínica nova não abre à ocupação de cruzeiro.</t>
+          <t>RAMPA DE ARRANQUE. É a fila de números mais influente desta folha e a que menos fundamento tem. Registada em R1-43.</t>
         </is>
       </c>
     </row>
@@ -9192,54 +9466,54 @@
         </is>
       </c>
       <c r="C14" s="24">
-        <f>(Operacao!$D$21/12)*C$13</f>
+        <f>(Operacao!$C$21/12)*C$13</f>
         <v/>
       </c>
       <c r="D14" s="24">
-        <f>(Operacao!$D$21/12)*D$13</f>
+        <f>(Operacao!$C$21/12)*D$13</f>
         <v/>
       </c>
       <c r="E14" s="24">
-        <f>(Operacao!$D$21/12)*E$13</f>
+        <f>(Operacao!$C$21/12)*E$13</f>
         <v/>
       </c>
       <c r="F14" s="24">
-        <f>(Operacao!$D$21/12)*F$13</f>
+        <f>(Operacao!$C$21/12)*F$13</f>
         <v/>
       </c>
       <c r="G14" s="24">
-        <f>(Operacao!$D$21/12)*G$13</f>
+        <f>(Operacao!$C$21/12)*G$13</f>
         <v/>
       </c>
       <c r="H14" s="24">
-        <f>(Operacao!$D$21/12)*H$13</f>
+        <f>(Operacao!$C$21/12)*H$13</f>
         <v/>
       </c>
       <c r="I14" s="24">
-        <f>(Operacao!$D$21/12)*I$13</f>
+        <f>(Operacao!$C$21/12)*I$13</f>
         <v/>
       </c>
       <c r="J14" s="24">
-        <f>(Operacao!$D$21/12)*J$13</f>
+        <f>(Operacao!$C$21/12)*J$13</f>
         <v/>
       </c>
       <c r="K14" s="24">
-        <f>(Operacao!$D$21/12)*K$13</f>
+        <f>(Operacao!$C$21/12)*K$13</f>
         <v/>
       </c>
       <c r="L14" s="24">
-        <f>(Operacao!$D$21/12)*L$13</f>
+        <f>(Operacao!$C$21/12)*L$13</f>
         <v/>
       </c>
       <c r="M14" s="24">
-        <f>(Operacao!$D$21/12)*M$13</f>
+        <f>(Operacao!$C$21/12)*M$13</f>
         <v/>
       </c>
       <c r="N14" s="24">
-        <f>(Operacao!$D$21/12)*N$13</f>
-        <v/>
-      </c>
-      <c r="O14" s="60">
+        <f>(Operacao!$C$21/12)*N$13</f>
+        <v/>
+      </c>
+      <c r="O14" s="61">
         <f>SUM(C14:N14)</f>
         <v/>
       </c>
@@ -9257,51 +9531,51 @@
         </is>
       </c>
       <c r="C15" s="27">
-        <f>C$14*BreakEven!$D$14</f>
+        <f>C$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="D15" s="27">
-        <f>D$14*BreakEven!$D$14</f>
+        <f>D$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="E15" s="27">
-        <f>E$14*BreakEven!$D$14</f>
+        <f>E$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>F$14*BreakEven!$D$14</f>
+        <f>F$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="G15" s="27">
-        <f>G$14*BreakEven!$D$14</f>
+        <f>G$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="H15" s="27">
-        <f>H$14*BreakEven!$D$14</f>
+        <f>H$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="I15" s="27">
-        <f>I$14*BreakEven!$D$14</f>
+        <f>I$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="J15" s="27">
-        <f>J$14*BreakEven!$D$14</f>
+        <f>J$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="K15" s="27">
-        <f>K$14*BreakEven!$D$14</f>
+        <f>K$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="L15" s="27">
-        <f>L$14*BreakEven!$D$14</f>
+        <f>L$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="M15" s="27">
-        <f>M$14*BreakEven!$D$14</f>
+        <f>M$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="N15" s="27">
-        <f>N$14*BreakEven!$D$14</f>
+        <f>N$14*BreakEven!$C$14</f>
         <v/>
       </c>
       <c r="O15" s="45">
@@ -9444,51 +9718,51 @@
         </is>
       </c>
       <c r="C18" s="28">
-        <f>C$15*(1-BreakEven!$D$9)</f>
+        <f>C$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="D18" s="28">
-        <f>D$15*(1-BreakEven!$D$9)</f>
+        <f>D$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="E18" s="28">
-        <f>E$15*(1-BreakEven!$D$9)</f>
+        <f>E$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="F18" s="28">
-        <f>F$15*(1-BreakEven!$D$9)</f>
+        <f>F$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="G18" s="28">
-        <f>G$15*(1-BreakEven!$D$9)</f>
+        <f>G$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="H18" s="28">
-        <f>H$15*(1-BreakEven!$D$9)</f>
+        <f>H$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="I18" s="28">
-        <f>I$15*(1-BreakEven!$D$9)</f>
+        <f>I$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="J18" s="28">
-        <f>J$15*(1-BreakEven!$D$9)</f>
+        <f>J$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="K18" s="28">
-        <f>K$15*(1-BreakEven!$D$9)</f>
+        <f>K$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="L18" s="28">
-        <f>L$15*(1-BreakEven!$D$9)</f>
+        <f>L$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="M18" s="28">
-        <f>M$15*(1-BreakEven!$D$9)</f>
+        <f>M$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="N18" s="28">
-        <f>N$15*(1-BreakEven!$D$9)</f>
+        <f>N$15*(1-BreakEven!$C$9)</f>
         <v/>
       </c>
       <c r="O18" s="45">
@@ -9509,62 +9783,58 @@
         </is>
       </c>
       <c r="C19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="D19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="E19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="F19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="G19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="H19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="I19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="J19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="K19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="L19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="M19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="N19" s="35">
-        <f>BreakEven!$D$10/12</f>
+        <f>BreakEven!$C$10/12</f>
         <v/>
       </c>
       <c r="O19" s="45">
         <f>SUM(C19:N19)</f>
         <v/>
       </c>
-      <c r="P19" s="17" t="inlineStr">
-        <is>
-          <t>Renda, condomínio, seguros, software e outros. Pagam-se haja ou não doentes.</t>
-        </is>
-      </c>
+      <c r="P19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -9578,51 +9848,51 @@
         </is>
       </c>
       <c r="C20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="D20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="E20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="F20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="G20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="H20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="I20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="J20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="K20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="L20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="M20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="N20" s="35">
-        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <f>V2_ENI_ContOrg!$C$13/12</f>
         <v/>
       </c>
       <c r="O20" s="45">
@@ -9688,7 +9958,7 @@
       </c>
       <c r="P21" s="17" t="inlineStr">
         <is>
-          <t>A PREENCHER, e é uma armadilha clássica: no ano 1 os pagamentos por conta são calculados sobre o rendimento do ano ANTERIOR, no regime antigo. Paga-se IRS do passado enquanto se está a investir no futuro. Vencem em julho, setembro e dezembro — meses 7, 9 e 12.</t>
+          <t>A PREENCHER. No ano 1 os pagamentos por conta são calculados sobre o rendimento do ano ANTERIOR, no regime antigo: paga-se IRS do passado enquanto se investe no futuro. Vencem em julho, setembro e dezembro.</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9974,7 @@
         </is>
       </c>
       <c r="C22" s="28">
-        <f>$C$9</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="D22" s="28" t="n">
@@ -9744,11 +10014,7 @@
         <f>SUM(C22:N22)</f>
         <v/>
       </c>
-      <c r="P22" s="17" t="inlineStr">
-        <is>
-          <t>Todo no mês 1. Se a empreitada for faseada, repartir.</t>
-        </is>
-      </c>
+      <c r="P22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
@@ -10002,410 +10268,3485 @@
       <c r="P26" s="17" t="inlineStr"/>
     </row>
     <row r="27"/>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>NECESSIDADE MÁXIMA DE TESOURARIA</t>
-        </is>
-      </c>
-      <c r="C28" s="27">
-        <f>-MIN($C$24:$N$24)</f>
-        <v/>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>O ponto mais fundo do saldo acumulado. JÁ INCLUI o investimento e a caução, porque eles saem da mesma conta bancária — não somar outra vez.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   da qual, investimento e caução</t>
-        </is>
-      </c>
-      <c r="C29" s="27">
-        <f>$C$9</f>
-        <v/>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Desembolso de uma só vez, no arranque.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Ano 1, mês a mês — cenário Base</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+      <c r="N28" s="7" t="n"/>
+      <c r="O28" s="7" t="n"/>
+      <c r="P28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 2</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 3</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 4</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 5</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 6</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 7</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 8</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 9</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 10</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 11</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>Mês 12</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>Ano 1</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   da qual, cobertura do défice operacional</t>
-        </is>
-      </c>
-      <c r="C30" s="27">
-        <f>-MIN($C$24:$N$24)-$C$9</f>
-        <v/>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>O que a operação consome enquanto a receita não chega para os custos. É a parte que quase ninguém orça, e é a que apanha quem abre pela primeira vez.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
+          <t>Taxa de ocupação dos gabinetes</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>OCUP</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P30" s="17" t="inlineStr">
+        <is>
+          <t>RAMPA DE ARRANQUE. É a fila de números mais influente desta folha e a que menos fundamento tem. Registada em R1-43.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Mês em que o saldo acumulado atinge o ponto mais baixo</t>
-        </is>
-      </c>
-      <c r="C31" s="23">
-        <f>MAX($C$25:$N$25)</f>
-        <v/>
-      </c>
-      <c r="E31" s="17" t="inlineStr"/>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Mês em que o saldo acumulado volta a ser positivo</t>
-        </is>
-      </c>
-      <c r="C32" s="23">
-        <f>IF(MAX($C$26:$N$26)=0,"Não recupera dentro do ano 1",MAX($C$26:$N$26))</f>
-        <v/>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>Se não recuperar dentro do ano 1, o fundo de maneio tem de cobrir também o ano 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
+          <t>Consultas do mês</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>CONS</t>
+        </is>
+      </c>
+      <c r="C31" s="24">
+        <f>(Operacao!$D$21/12)*C$30</f>
+        <v/>
+      </c>
+      <c r="D31" s="24">
+        <f>(Operacao!$D$21/12)*D$30</f>
+        <v/>
+      </c>
+      <c r="E31" s="24">
+        <f>(Operacao!$D$21/12)*E$30</f>
+        <v/>
+      </c>
+      <c r="F31" s="24">
+        <f>(Operacao!$D$21/12)*F$30</f>
+        <v/>
+      </c>
+      <c r="G31" s="24">
+        <f>(Operacao!$D$21/12)*G$30</f>
+        <v/>
+      </c>
+      <c r="H31" s="24">
+        <f>(Operacao!$D$21/12)*H$30</f>
+        <v/>
+      </c>
+      <c r="I31" s="24">
+        <f>(Operacao!$D$21/12)*I$30</f>
+        <v/>
+      </c>
+      <c r="J31" s="24">
+        <f>(Operacao!$D$21/12)*J$30</f>
+        <v/>
+      </c>
+      <c r="K31" s="24">
+        <f>(Operacao!$D$21/12)*K$30</f>
+        <v/>
+      </c>
+      <c r="L31" s="24">
+        <f>(Operacao!$D$21/12)*L$30</f>
+        <v/>
+      </c>
+      <c r="M31" s="24">
+        <f>(Operacao!$D$21/12)*M$30</f>
+        <v/>
+      </c>
+      <c r="N31" s="24">
+        <f>(Operacao!$D$21/12)*N$30</f>
+        <v/>
+      </c>
+      <c r="O31" s="61">
+        <f>SUM(C31:N31)</f>
+        <v/>
+      </c>
+      <c r="P31" s="17" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Faturação do mês</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
+      <c r="C32" s="27">
+        <f>C$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>D$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="E32" s="27">
+        <f>E$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="F32" s="27">
+        <f>F$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="G32" s="27">
+        <f>G$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="H32" s="27">
+        <f>H$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="I32" s="27">
+        <f>I$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="J32" s="27">
+        <f>J$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="K32" s="27">
+        <f>K$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="L32" s="27">
+        <f>L$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="M32" s="27">
+        <f>M$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="N32" s="27">
+        <f>N$31*BreakEven!$D$14</f>
+        <v/>
+      </c>
+      <c r="O32" s="45">
+        <f>SUM(C32:N32)</f>
+        <v/>
+      </c>
+      <c r="P32" s="17" t="inlineStr"/>
+    </row>
+    <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Margem de segurança (meses de custos fixos)</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>A PREENCHER. Nenhuma projeção acerta. Três meses é uma convenção prudente para quem não tem outra fonte de rendimento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
+          <t>% recebida no próprio mês</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>PCT_PRONTO</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P33" s="17" t="inlineStr">
+        <is>
+          <t>Consultas particulares pagam-se na hora; subsistemas e seguros pagam a 30 dias ou mais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Recebimentos</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="C34" s="27">
+        <f>C$32*C$33</f>
+        <v/>
+      </c>
+      <c r="D34" s="27">
+        <f>D$32*D$33+C$32*(1-C$33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="27">
+        <f>E$32*E$33+D$32*(1-D$33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="27">
+        <f>F$32*F$33+E$32*(1-E$33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="27">
+        <f>G$32*G$33+F$32*(1-F$33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="27">
+        <f>H$32*H$33+G$32*(1-G$33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="27">
+        <f>I$32*I$33+H$32*(1-H$33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="27">
+        <f>J$32*J$33+I$32*(1-I$33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="27">
+        <f>K$32*K$33+J$32*(1-J$33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="27">
+        <f>L$32*L$33+K$32*(1-K$33)</f>
+        <v/>
+      </c>
+      <c r="M34" s="27">
+        <f>M$32*M$33+L$32*(1-L$33)</f>
+        <v/>
+      </c>
+      <c r="N34" s="27">
+        <f>N$32*N$33+M$32*(1-M$33)</f>
+        <v/>
+      </c>
+      <c r="O34" s="45">
+        <f>SUM(C34:N34)</f>
+        <v/>
+      </c>
+      <c r="P34" s="17" t="inlineStr">
+        <is>
+          <t>O desfasamento entre faturar e receber é dinheiro que falta em caixa.</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Margem de segurança, em euros</t>
+          <t>Custos variáveis (consumíveis e colaboradores)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>CV</t>
         </is>
       </c>
       <c r="C35" s="28">
-        <f>$C$33*BreakEven!$D$10/12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>TOTAL DE DINHEIRO NECESSÁRIO ANTES DE ABRIR</t>
-        </is>
-      </c>
-      <c r="C36" s="61">
-        <f>$C$28+$C$35</f>
-        <v/>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>Investimento, caução e fundo de maneio. É este o número a dizer à cliente antes de qualquer conversa sobre estrutura fiscal. Se ela não o tiver ou não o conseguir financiar, a discussão sobre ENI ou sociedade é prematura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
+        <f>C$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="D35" s="28">
+        <f>D$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>E$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="F35" s="28">
+        <f>F$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="G35" s="28">
+        <f>G$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="H35" s="28">
+        <f>H$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="I35" s="28">
+        <f>I$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="J35" s="28">
+        <f>J$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="K35" s="28">
+        <f>K$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="L35" s="28">
+        <f>L$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="M35" s="28">
+        <f>M$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="N35" s="28">
+        <f>N$32*(1-BreakEven!$D$9)</f>
+        <v/>
+      </c>
+      <c r="O35" s="45">
+        <f>SUM(C35:N35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="17" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Custos fixos</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="C36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="D36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="E36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="F36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="G36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="H36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="I36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="J36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="K36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="L36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="M36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="N36" s="35">
+        <f>BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="O36" s="45">
+        <f>SUM(C36:N36)</f>
+        <v/>
+      </c>
+      <c r="P36" s="17" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Segurança Social</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="C37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="D37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="E37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="F37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="G37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="H37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="I37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="J37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="K37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="L37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="M37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="N37" s="35">
+        <f>V2_ENI_ContOrg!$D$13/12</f>
+        <v/>
+      </c>
+      <c r="O37" s="45">
+        <f>SUM(C37:N37)</f>
+        <v/>
+      </c>
+      <c r="P37" s="17" t="inlineStr">
+        <is>
+          <t>Aproximação de cruzeiro. No primeiro ano a base é a declarada, não o lucro do próprio ano. Ver R1-40.</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Visão a três anos</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Rubrica</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Ref.</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Ano 1</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Ano 2</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Ano 3</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>IRS — pagamentos por conta</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>IRS_PC</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="45">
+        <f>SUM(C38:N38)</f>
+        <v/>
+      </c>
+      <c r="P38" s="17" t="inlineStr">
+        <is>
+          <t>A PREENCHER. No ano 1 os pagamentos por conta são calculados sobre o rendimento do ano ANTERIOR, no regime antigo: paga-se IRS do passado enquanto se investe no futuro. Vencem em julho, setembro e dezembro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Investimento e caução</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>INV_M</t>
+        </is>
+      </c>
+      <c r="C39" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="D39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="45">
+        <f>SUM(C39:N39)</f>
+        <v/>
+      </c>
+      <c r="P39" s="17" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Taxa de ocupação média do ano</t>
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>SALDO DO MÊS</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>OCUP</t>
-        </is>
-      </c>
-      <c r="C40" s="62">
-        <f>AVERAGE($C$13:$N$13)</f>
-        <v/>
-      </c>
-      <c r="D40" s="13" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>Ano 1 é a média da rampa. Anos 2 e 3 a preencher — e a justificar com o plano de captação de doentes, que não existe e é o pressuposto silencioso de tudo isto (R1-41).</t>
-        </is>
-      </c>
+          <t>SALDO</t>
+        </is>
+      </c>
+      <c r="C40" s="27">
+        <f>C$34-C$35-C$36-C$37-C$38-C$39</f>
+        <v/>
+      </c>
+      <c r="D40" s="27">
+        <f>D$34-D$35-D$36-D$37-D$38-D$39</f>
+        <v/>
+      </c>
+      <c r="E40" s="27">
+        <f>E$34-E$35-E$36-E$37-E$38-E$39</f>
+        <v/>
+      </c>
+      <c r="F40" s="27">
+        <f>F$34-F$35-F$36-F$37-F$38-F$39</f>
+        <v/>
+      </c>
+      <c r="G40" s="27">
+        <f>G$34-G$35-G$36-G$37-G$38-G$39</f>
+        <v/>
+      </c>
+      <c r="H40" s="27">
+        <f>H$34-H$35-H$36-H$37-H$38-H$39</f>
+        <v/>
+      </c>
+      <c r="I40" s="27">
+        <f>I$34-I$35-I$36-I$37-I$38-I$39</f>
+        <v/>
+      </c>
+      <c r="J40" s="27">
+        <f>J$34-J$35-J$36-J$37-J$38-J$39</f>
+        <v/>
+      </c>
+      <c r="K40" s="27">
+        <f>K$34-K$35-K$36-K$37-K$38-K$39</f>
+        <v/>
+      </c>
+      <c r="L40" s="27">
+        <f>L$34-L$35-L$36-L$37-L$38-L$39</f>
+        <v/>
+      </c>
+      <c r="M40" s="27">
+        <f>M$34-M$35-M$36-M$37-M$38-M$39</f>
+        <v/>
+      </c>
+      <c r="N40" s="27">
+        <f>N$34-N$35-N$36-N$37-N$38-N$39</f>
+        <v/>
+      </c>
+      <c r="O40" s="45">
+        <f>SUM(C40:N40)</f>
+        <v/>
+      </c>
+      <c r="P40" s="17" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>Faturação</t>
+          <t>SALDO ACUMULADO</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>FAT</t>
+          <t>ACUM</t>
         </is>
       </c>
       <c r="C41" s="27">
-        <f>Operacao!$D$21*$C$40*BreakEven!$D$14</f>
+        <f>C$40</f>
         <v/>
       </c>
       <c r="D41" s="27">
-        <f>Operacao!$D$21*$D$40*BreakEven!$D$14</f>
+        <f>C$41+D$40</f>
         <v/>
       </c>
       <c r="E41" s="27">
-        <f>Operacao!$D$21*$E$40*BreakEven!$D$14</f>
-        <v/>
-      </c>
-      <c r="F41" s="17" t="inlineStr"/>
+        <f>D$41+E$40</f>
+        <v/>
+      </c>
+      <c r="F41" s="27">
+        <f>E$41+F$40</f>
+        <v/>
+      </c>
+      <c r="G41" s="27">
+        <f>F$41+G$40</f>
+        <v/>
+      </c>
+      <c r="H41" s="27">
+        <f>G$41+H$40</f>
+        <v/>
+      </c>
+      <c r="I41" s="27">
+        <f>H$41+I$40</f>
+        <v/>
+      </c>
+      <c r="J41" s="27">
+        <f>I$41+J$40</f>
+        <v/>
+      </c>
+      <c r="K41" s="27">
+        <f>J$41+K$40</f>
+        <v/>
+      </c>
+      <c r="L41" s="27">
+        <f>K$41+L$40</f>
+        <v/>
+      </c>
+      <c r="M41" s="27">
+        <f>L$41+M$40</f>
+        <v/>
+      </c>
+      <c r="N41" s="27">
+        <f>M$41+N$40</f>
+        <v/>
+      </c>
+      <c r="P41" s="17" t="inlineStr">
+        <is>
+          <t>É esta a linha que decide se o projeto sobrevive ao primeiro ano.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Custos variáveis</t>
+          <t>Marcador do ponto mais baixo</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="C42" s="28">
-        <f>$C$41*(1-BreakEven!$D$9)</f>
-        <v/>
-      </c>
-      <c r="D42" s="28">
-        <f>$D$41*(1-BreakEven!$D$9)</f>
-        <v/>
-      </c>
-      <c r="E42" s="28">
-        <f>$E$41*(1-BreakEven!$D$9)</f>
-        <v/>
-      </c>
-      <c r="F42" s="17" t="inlineStr"/>
+          <t>MARC_MIN</t>
+        </is>
+      </c>
+      <c r="C42" s="24">
+        <f>IF(C$41=MIN($C$41:$N$41),1,0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="24">
+        <f>IF(D$41=MIN($C$41:$N$41),2,0)</f>
+        <v/>
+      </c>
+      <c r="E42" s="24">
+        <f>IF(E$41=MIN($C$41:$N$41),3,0)</f>
+        <v/>
+      </c>
+      <c r="F42" s="24">
+        <f>IF(F$41=MIN($C$41:$N$41),4,0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="24">
+        <f>IF(G$41=MIN($C$41:$N$41),5,0)</f>
+        <v/>
+      </c>
+      <c r="H42" s="24">
+        <f>IF(H$41=MIN($C$41:$N$41),6,0)</f>
+        <v/>
+      </c>
+      <c r="I42" s="24">
+        <f>IF(I$41=MIN($C$41:$N$41),7,0)</f>
+        <v/>
+      </c>
+      <c r="J42" s="24">
+        <f>IF(J$41=MIN($C$41:$N$41),8,0)</f>
+        <v/>
+      </c>
+      <c r="K42" s="24">
+        <f>IF(K$41=MIN($C$41:$N$41),9,0)</f>
+        <v/>
+      </c>
+      <c r="L42" s="24">
+        <f>IF(L$41=MIN($C$41:$N$41),10,0)</f>
+        <v/>
+      </c>
+      <c r="M42" s="24">
+        <f>IF(M$41=MIN($C$41:$N$41),11,0)</f>
+        <v/>
+      </c>
+      <c r="N42" s="24">
+        <f>IF(N$41=MIN($C$41:$N$41),12,0)</f>
+        <v/>
+      </c>
+      <c r="P42" s="17" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
+          <t>Marcador de recuperação</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>MARC</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="24">
+        <f>IF(AND(D$41&gt;=0,C$41&lt;0),2,0)</f>
+        <v/>
+      </c>
+      <c r="E43" s="24">
+        <f>IF(AND(E$41&gt;=0,D$41&lt;0),3,0)</f>
+        <v/>
+      </c>
+      <c r="F43" s="24">
+        <f>IF(AND(F$41&gt;=0,E$41&lt;0),4,0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="24">
+        <f>IF(AND(G$41&gt;=0,F$41&lt;0),5,0)</f>
+        <v/>
+      </c>
+      <c r="H43" s="24">
+        <f>IF(AND(H$41&gt;=0,G$41&lt;0),6,0)</f>
+        <v/>
+      </c>
+      <c r="I43" s="24">
+        <f>IF(AND(I$41&gt;=0,H$41&lt;0),7,0)</f>
+        <v/>
+      </c>
+      <c r="J43" s="24">
+        <f>IF(AND(J$41&gt;=0,I$41&lt;0),8,0)</f>
+        <v/>
+      </c>
+      <c r="K43" s="24">
+        <f>IF(AND(K$41&gt;=0,J$41&lt;0),9,0)</f>
+        <v/>
+      </c>
+      <c r="L43" s="24">
+        <f>IF(AND(L$41&gt;=0,K$41&lt;0),10,0)</f>
+        <v/>
+      </c>
+      <c r="M43" s="24">
+        <f>IF(AND(M$41&gt;=0,L$41&lt;0),11,0)</f>
+        <v/>
+      </c>
+      <c r="N43" s="24">
+        <f>IF(AND(N$41&gt;=0,M$41&lt;0),12,0)</f>
+        <v/>
+      </c>
+      <c r="P43" s="17" t="inlineStr"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Ano 1, mês a mês — cenário Alto</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+      <c r="P45" s="7" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 2</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 3</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 4</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 5</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 6</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 7</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 8</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 9</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 10</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 11</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>Mês 12</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>Ano 1</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Taxa de ocupação dos gabinetes</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>OCUP</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="P47" s="17" t="inlineStr">
+        <is>
+          <t>RAMPA DE ARRANQUE. É a fila de números mais influente desta folha e a que menos fundamento tem. Registada em R1-43.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Consultas do mês</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>CONS</t>
+        </is>
+      </c>
+      <c r="C48" s="24">
+        <f>(Operacao!$E$21/12)*C$47</f>
+        <v/>
+      </c>
+      <c r="D48" s="24">
+        <f>(Operacao!$E$21/12)*D$47</f>
+        <v/>
+      </c>
+      <c r="E48" s="24">
+        <f>(Operacao!$E$21/12)*E$47</f>
+        <v/>
+      </c>
+      <c r="F48" s="24">
+        <f>(Operacao!$E$21/12)*F$47</f>
+        <v/>
+      </c>
+      <c r="G48" s="24">
+        <f>(Operacao!$E$21/12)*G$47</f>
+        <v/>
+      </c>
+      <c r="H48" s="24">
+        <f>(Operacao!$E$21/12)*H$47</f>
+        <v/>
+      </c>
+      <c r="I48" s="24">
+        <f>(Operacao!$E$21/12)*I$47</f>
+        <v/>
+      </c>
+      <c r="J48" s="24">
+        <f>(Operacao!$E$21/12)*J$47</f>
+        <v/>
+      </c>
+      <c r="K48" s="24">
+        <f>(Operacao!$E$21/12)*K$47</f>
+        <v/>
+      </c>
+      <c r="L48" s="24">
+        <f>(Operacao!$E$21/12)*L$47</f>
+        <v/>
+      </c>
+      <c r="M48" s="24">
+        <f>(Operacao!$E$21/12)*M$47</f>
+        <v/>
+      </c>
+      <c r="N48" s="24">
+        <f>(Operacao!$E$21/12)*N$47</f>
+        <v/>
+      </c>
+      <c r="O48" s="61">
+        <f>SUM(C48:N48)</f>
+        <v/>
+      </c>
+      <c r="P48" s="17" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>Faturação do mês</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
+      <c r="C49" s="27">
+        <f>C$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="D49" s="27">
+        <f>D$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="E49" s="27">
+        <f>E$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="F49" s="27">
+        <f>F$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="G49" s="27">
+        <f>G$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="H49" s="27">
+        <f>H$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="I49" s="27">
+        <f>I$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="J49" s="27">
+        <f>J$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="K49" s="27">
+        <f>K$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="L49" s="27">
+        <f>L$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="M49" s="27">
+        <f>M$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="N49" s="27">
+        <f>N$48*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="O49" s="45">
+        <f>SUM(C49:N49)</f>
+        <v/>
+      </c>
+      <c r="P49" s="17" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>% recebida no próprio mês</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>PCT_PRONTO</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P50" s="17" t="inlineStr">
+        <is>
+          <t>Consultas particulares pagam-se na hora; subsistemas e seguros pagam a 30 dias ou mais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Recebimentos</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="C51" s="27">
+        <f>C$49*C$50</f>
+        <v/>
+      </c>
+      <c r="D51" s="27">
+        <f>D$49*D$50+C$49*(1-C$50)</f>
+        <v/>
+      </c>
+      <c r="E51" s="27">
+        <f>E$49*E$50+D$49*(1-D$50)</f>
+        <v/>
+      </c>
+      <c r="F51" s="27">
+        <f>F$49*F$50+E$49*(1-E$50)</f>
+        <v/>
+      </c>
+      <c r="G51" s="27">
+        <f>G$49*G$50+F$49*(1-F$50)</f>
+        <v/>
+      </c>
+      <c r="H51" s="27">
+        <f>H$49*H$50+G$49*(1-G$50)</f>
+        <v/>
+      </c>
+      <c r="I51" s="27">
+        <f>I$49*I$50+H$49*(1-H$50)</f>
+        <v/>
+      </c>
+      <c r="J51" s="27">
+        <f>J$49*J$50+I$49*(1-I$50)</f>
+        <v/>
+      </c>
+      <c r="K51" s="27">
+        <f>K$49*K$50+J$49*(1-J$50)</f>
+        <v/>
+      </c>
+      <c r="L51" s="27">
+        <f>L$49*L$50+K$49*(1-K$50)</f>
+        <v/>
+      </c>
+      <c r="M51" s="27">
+        <f>M$49*M$50+L$49*(1-L$50)</f>
+        <v/>
+      </c>
+      <c r="N51" s="27">
+        <f>N$49*N$50+M$49*(1-M$50)</f>
+        <v/>
+      </c>
+      <c r="O51" s="45">
+        <f>SUM(C51:N51)</f>
+        <v/>
+      </c>
+      <c r="P51" s="17" t="inlineStr">
+        <is>
+          <t>O desfasamento entre faturar e receber é dinheiro que falta em caixa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Custos variáveis (consumíveis e colaboradores)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="C52" s="28">
+        <f>C$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="D52" s="28">
+        <f>D$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="E52" s="28">
+        <f>E$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="F52" s="28">
+        <f>F$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="G52" s="28">
+        <f>G$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="H52" s="28">
+        <f>H$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="I52" s="28">
+        <f>I$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="J52" s="28">
+        <f>J$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="K52" s="28">
+        <f>K$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="L52" s="28">
+        <f>L$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="M52" s="28">
+        <f>M$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="N52" s="28">
+        <f>N$49*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="O52" s="45">
+        <f>SUM(C52:N52)</f>
+        <v/>
+      </c>
+      <c r="P52" s="17" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
           <t>Custos fixos</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="C43" s="35">
-        <f>BreakEven!$D$10</f>
-        <v/>
-      </c>
-      <c r="D43" s="35">
-        <f>BreakEven!$D$10</f>
-        <v/>
-      </c>
-      <c r="E43" s="35">
-        <f>BreakEven!$D$10</f>
-        <v/>
-      </c>
-      <c r="F43" s="17" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="C53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="D53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="E53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="F53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="G53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="H53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="I53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="J53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="K53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="L53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="M53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="N53" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="O53" s="45">
+        <f>SUM(C53:N53)</f>
+        <v/>
+      </c>
+      <c r="P53" s="17" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Segurança Social</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="C54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="D54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="E54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="F54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="G54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="H54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="I54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="J54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="K54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="L54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="M54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="N54" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="O54" s="45">
+        <f>SUM(C54:N54)</f>
+        <v/>
+      </c>
+      <c r="P54" s="17" t="inlineStr">
+        <is>
+          <t>Aproximação de cruzeiro. No primeiro ano a base é a declarada, não o lucro do próprio ano. Ver R1-40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>IRS — pagamentos por conta</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>IRS_PC</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="45">
+        <f>SUM(C55:N55)</f>
+        <v/>
+      </c>
+      <c r="P55" s="17" t="inlineStr">
+        <is>
+          <t>A PREENCHER. No ano 1 os pagamentos por conta são calculados sobre o rendimento do ano ANTERIOR, no regime antigo: paga-se IRS do passado enquanto se investe no futuro. Vencem em julho, setembro e dezembro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Investimento e caução</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>INV_M</t>
+        </is>
+      </c>
+      <c r="C56" s="28">
+        <f>$E$10</f>
+        <v/>
+      </c>
+      <c r="D56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="45">
+        <f>SUM(C56:N56)</f>
+        <v/>
+      </c>
+      <c r="P56" s="17" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>SALDO DO MÊS</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>SALDO</t>
+        </is>
+      </c>
+      <c r="C57" s="27">
+        <f>C$51-C$52-C$53-C$54-C$55-C$56</f>
+        <v/>
+      </c>
+      <c r="D57" s="27">
+        <f>D$51-D$52-D$53-D$54-D$55-D$56</f>
+        <v/>
+      </c>
+      <c r="E57" s="27">
+        <f>E$51-E$52-E$53-E$54-E$55-E$56</f>
+        <v/>
+      </c>
+      <c r="F57" s="27">
+        <f>F$51-F$52-F$53-F$54-F$55-F$56</f>
+        <v/>
+      </c>
+      <c r="G57" s="27">
+        <f>G$51-G$52-G$53-G$54-G$55-G$56</f>
+        <v/>
+      </c>
+      <c r="H57" s="27">
+        <f>H$51-H$52-H$53-H$54-H$55-H$56</f>
+        <v/>
+      </c>
+      <c r="I57" s="27">
+        <f>I$51-I$52-I$53-I$54-I$55-I$56</f>
+        <v/>
+      </c>
+      <c r="J57" s="27">
+        <f>J$51-J$52-J$53-J$54-J$55-J$56</f>
+        <v/>
+      </c>
+      <c r="K57" s="27">
+        <f>K$51-K$52-K$53-K$54-K$55-K$56</f>
+        <v/>
+      </c>
+      <c r="L57" s="27">
+        <f>L$51-L$52-L$53-L$54-L$55-L$56</f>
+        <v/>
+      </c>
+      <c r="M57" s="27">
+        <f>M$51-M$52-M$53-M$54-M$55-M$56</f>
+        <v/>
+      </c>
+      <c r="N57" s="27">
+        <f>N$51-N$52-N$53-N$54-N$55-N$56</f>
+        <v/>
+      </c>
+      <c r="O57" s="45">
+        <f>SUM(C57:N57)</f>
+        <v/>
+      </c>
+      <c r="P57" s="17" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>SALDO ACUMULADO</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>ACUM</t>
+        </is>
+      </c>
+      <c r="C58" s="27">
+        <f>C$57</f>
+        <v/>
+      </c>
+      <c r="D58" s="27">
+        <f>C$58+D$57</f>
+        <v/>
+      </c>
+      <c r="E58" s="27">
+        <f>D$58+E$57</f>
+        <v/>
+      </c>
+      <c r="F58" s="27">
+        <f>E$58+F$57</f>
+        <v/>
+      </c>
+      <c r="G58" s="27">
+        <f>F$58+G$57</f>
+        <v/>
+      </c>
+      <c r="H58" s="27">
+        <f>G$58+H$57</f>
+        <v/>
+      </c>
+      <c r="I58" s="27">
+        <f>H$58+I$57</f>
+        <v/>
+      </c>
+      <c r="J58" s="27">
+        <f>I$58+J$57</f>
+        <v/>
+      </c>
+      <c r="K58" s="27">
+        <f>J$58+K$57</f>
+        <v/>
+      </c>
+      <c r="L58" s="27">
+        <f>K$58+L$57</f>
+        <v/>
+      </c>
+      <c r="M58" s="27">
+        <f>L$58+M$57</f>
+        <v/>
+      </c>
+      <c r="N58" s="27">
+        <f>M$58+N$57</f>
+        <v/>
+      </c>
+      <c r="P58" s="17" t="inlineStr">
+        <is>
+          <t>É esta a linha que decide se o projeto sobrevive ao primeiro ano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Marcador do ponto mais baixo</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>MARC_MIN</t>
+        </is>
+      </c>
+      <c r="C59" s="24">
+        <f>IF(C$58=MIN($C$58:$N$58),1,0)</f>
+        <v/>
+      </c>
+      <c r="D59" s="24">
+        <f>IF(D$58=MIN($C$58:$N$58),2,0)</f>
+        <v/>
+      </c>
+      <c r="E59" s="24">
+        <f>IF(E$58=MIN($C$58:$N$58),3,0)</f>
+        <v/>
+      </c>
+      <c r="F59" s="24">
+        <f>IF(F$58=MIN($C$58:$N$58),4,0)</f>
+        <v/>
+      </c>
+      <c r="G59" s="24">
+        <f>IF(G$58=MIN($C$58:$N$58),5,0)</f>
+        <v/>
+      </c>
+      <c r="H59" s="24">
+        <f>IF(H$58=MIN($C$58:$N$58),6,0)</f>
+        <v/>
+      </c>
+      <c r="I59" s="24">
+        <f>IF(I$58=MIN($C$58:$N$58),7,0)</f>
+        <v/>
+      </c>
+      <c r="J59" s="24">
+        <f>IF(J$58=MIN($C$58:$N$58),8,0)</f>
+        <v/>
+      </c>
+      <c r="K59" s="24">
+        <f>IF(K$58=MIN($C$58:$N$58),9,0)</f>
+        <v/>
+      </c>
+      <c r="L59" s="24">
+        <f>IF(L$58=MIN($C$58:$N$58),10,0)</f>
+        <v/>
+      </c>
+      <c r="M59" s="24">
+        <f>IF(M$58=MIN($C$58:$N$58),11,0)</f>
+        <v/>
+      </c>
+      <c r="N59" s="24">
+        <f>IF(N$58=MIN($C$58:$N$58),12,0)</f>
+        <v/>
+      </c>
+      <c r="P59" s="17" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Marcador de recuperação</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>MARC</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="24">
+        <f>IF(AND(D$58&gt;=0,C$58&lt;0),2,0)</f>
+        <v/>
+      </c>
+      <c r="E60" s="24">
+        <f>IF(AND(E$58&gt;=0,D$58&lt;0),3,0)</f>
+        <v/>
+      </c>
+      <c r="F60" s="24">
+        <f>IF(AND(F$58&gt;=0,E$58&lt;0),4,0)</f>
+        <v/>
+      </c>
+      <c r="G60" s="24">
+        <f>IF(AND(G$58&gt;=0,F$58&lt;0),5,0)</f>
+        <v/>
+      </c>
+      <c r="H60" s="24">
+        <f>IF(AND(H$58&gt;=0,G$58&lt;0),6,0)</f>
+        <v/>
+      </c>
+      <c r="I60" s="24">
+        <f>IF(AND(I$58&gt;=0,H$58&lt;0),7,0)</f>
+        <v/>
+      </c>
+      <c r="J60" s="24">
+        <f>IF(AND(J$58&gt;=0,I$58&lt;0),8,0)</f>
+        <v/>
+      </c>
+      <c r="K60" s="24">
+        <f>IF(AND(K$58&gt;=0,J$58&lt;0),9,0)</f>
+        <v/>
+      </c>
+      <c r="L60" s="24">
+        <f>IF(AND(L$58&gt;=0,K$58&lt;0),10,0)</f>
+        <v/>
+      </c>
+      <c r="M60" s="24">
+        <f>IF(AND(M$58&gt;=0,L$58&lt;0),11,0)</f>
+        <v/>
+      </c>
+      <c r="N60" s="24">
+        <f>IF(AND(N$58&gt;=0,M$58&lt;0),12,0)</f>
+        <v/>
+      </c>
+      <c r="P60" s="17" t="inlineStr"/>
+    </row>
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Ano 1, mês a mês — cenário TENSÃO — espaço do Alto com a procura do Baixo</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
+      <c r="N62" s="7" t="n"/>
+      <c r="O62" s="7" t="n"/>
+      <c r="P62" s="7" t="n"/>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 2</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 3</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 4</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 5</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 6</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 7</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 8</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 9</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 10</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 11</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>Mês 12</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>Ano 1</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Taxa de ocupação dos gabinetes</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>OCUP</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D64" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H64" s="13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I64" s="13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P64" s="17" t="inlineStr">
+        <is>
+          <t>RAMPA DE ARRANQUE. É a fila de números mais influente desta folha e a que menos fundamento tem. Registada em R1-43.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Consultas do mês</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>CONS</t>
+        </is>
+      </c>
+      <c r="C65" s="24">
+        <f>(Operacao!$E$21/12)*C$64</f>
+        <v/>
+      </c>
+      <c r="D65" s="24">
+        <f>(Operacao!$E$21/12)*D$64</f>
+        <v/>
+      </c>
+      <c r="E65" s="24">
+        <f>(Operacao!$E$21/12)*E$64</f>
+        <v/>
+      </c>
+      <c r="F65" s="24">
+        <f>(Operacao!$E$21/12)*F$64</f>
+        <v/>
+      </c>
+      <c r="G65" s="24">
+        <f>(Operacao!$E$21/12)*G$64</f>
+        <v/>
+      </c>
+      <c r="H65" s="24">
+        <f>(Operacao!$E$21/12)*H$64</f>
+        <v/>
+      </c>
+      <c r="I65" s="24">
+        <f>(Operacao!$E$21/12)*I$64</f>
+        <v/>
+      </c>
+      <c r="J65" s="24">
+        <f>(Operacao!$E$21/12)*J$64</f>
+        <v/>
+      </c>
+      <c r="K65" s="24">
+        <f>(Operacao!$E$21/12)*K$64</f>
+        <v/>
+      </c>
+      <c r="L65" s="24">
+        <f>(Operacao!$E$21/12)*L$64</f>
+        <v/>
+      </c>
+      <c r="M65" s="24">
+        <f>(Operacao!$E$21/12)*M$64</f>
+        <v/>
+      </c>
+      <c r="N65" s="24">
+        <f>(Operacao!$E$21/12)*N$64</f>
+        <v/>
+      </c>
+      <c r="O65" s="61">
+        <f>SUM(C65:N65)</f>
+        <v/>
+      </c>
+      <c r="P65" s="17" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>Faturação do mês</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
+      <c r="C66" s="27">
+        <f>C$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="D66" s="27">
+        <f>D$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="E66" s="27">
+        <f>E$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="F66" s="27">
+        <f>F$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="G66" s="27">
+        <f>G$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="H66" s="27">
+        <f>H$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="I66" s="27">
+        <f>I$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="J66" s="27">
+        <f>J$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="K66" s="27">
+        <f>K$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="L66" s="27">
+        <f>L$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="M66" s="27">
+        <f>M$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="N66" s="27">
+        <f>N$65*BreakEven!$E$14</f>
+        <v/>
+      </c>
+      <c r="O66" s="45">
+        <f>SUM(C66:N66)</f>
+        <v/>
+      </c>
+      <c r="P66" s="17" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>% recebida no próprio mês</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>PCT_PRONTO</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P67" s="17" t="inlineStr">
+        <is>
+          <t>Consultas particulares pagam-se na hora; subsistemas e seguros pagam a 30 dias ou mais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>Recebimentos</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="C68" s="27">
+        <f>C$66*C$67</f>
+        <v/>
+      </c>
+      <c r="D68" s="27">
+        <f>D$66*D$67+C$66*(1-C$67)</f>
+        <v/>
+      </c>
+      <c r="E68" s="27">
+        <f>E$66*E$67+D$66*(1-D$67)</f>
+        <v/>
+      </c>
+      <c r="F68" s="27">
+        <f>F$66*F$67+E$66*(1-E$67)</f>
+        <v/>
+      </c>
+      <c r="G68" s="27">
+        <f>G$66*G$67+F$66*(1-F$67)</f>
+        <v/>
+      </c>
+      <c r="H68" s="27">
+        <f>H$66*H$67+G$66*(1-G$67)</f>
+        <v/>
+      </c>
+      <c r="I68" s="27">
+        <f>I$66*I$67+H$66*(1-H$67)</f>
+        <v/>
+      </c>
+      <c r="J68" s="27">
+        <f>J$66*J$67+I$66*(1-I$67)</f>
+        <v/>
+      </c>
+      <c r="K68" s="27">
+        <f>K$66*K$67+J$66*(1-J$67)</f>
+        <v/>
+      </c>
+      <c r="L68" s="27">
+        <f>L$66*L$67+K$66*(1-K$67)</f>
+        <v/>
+      </c>
+      <c r="M68" s="27">
+        <f>M$66*M$67+L$66*(1-L$67)</f>
+        <v/>
+      </c>
+      <c r="N68" s="27">
+        <f>N$66*N$67+M$66*(1-M$67)</f>
+        <v/>
+      </c>
+      <c r="O68" s="45">
+        <f>SUM(C68:N68)</f>
+        <v/>
+      </c>
+      <c r="P68" s="17" t="inlineStr">
+        <is>
+          <t>O desfasamento entre faturar e receber é dinheiro que falta em caixa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Custos variáveis (consumíveis e colaboradores)</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="C69" s="28">
+        <f>C$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="D69" s="28">
+        <f>D$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="E69" s="28">
+        <f>E$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="F69" s="28">
+        <f>F$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="G69" s="28">
+        <f>G$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="H69" s="28">
+        <f>H$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="I69" s="28">
+        <f>I$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="J69" s="28">
+        <f>J$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="K69" s="28">
+        <f>K$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="L69" s="28">
+        <f>L$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="M69" s="28">
+        <f>M$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="N69" s="28">
+        <f>N$66*(1-BreakEven!$E$9)</f>
+        <v/>
+      </c>
+      <c r="O69" s="45">
+        <f>SUM(C69:N69)</f>
+        <v/>
+      </c>
+      <c r="P69" s="17" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>Custos fixos</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="C70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="D70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="E70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="F70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="G70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="H70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="I70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="J70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="K70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="L70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="M70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="N70" s="35">
+        <f>BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="O70" s="45">
+        <f>SUM(C70:N70)</f>
+        <v/>
+      </c>
+      <c r="P70" s="17" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Segurança Social</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="C71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="D71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="E71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="F71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="G71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="H71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="I71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="J71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="K71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="L71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="M71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="N71" s="35">
+        <f>V2_ENI_ContOrg!$E$13/12</f>
+        <v/>
+      </c>
+      <c r="O71" s="45">
+        <f>SUM(C71:N71)</f>
+        <v/>
+      </c>
+      <c r="P71" s="17" t="inlineStr">
+        <is>
+          <t>Aproximação de cruzeiro. No primeiro ano a base é a declarada, não o lucro do próprio ano. Ver R1-40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>IRS — pagamentos por conta</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>IRS_PC</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="45">
+        <f>SUM(C72:N72)</f>
+        <v/>
+      </c>
+      <c r="P72" s="17" t="inlineStr">
+        <is>
+          <t>A PREENCHER. No ano 1 os pagamentos por conta são calculados sobre o rendimento do ano ANTERIOR, no regime antigo: paga-se IRS do passado enquanto se investe no futuro. Vencem em julho, setembro e dezembro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Investimento e caução</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>INV_M</t>
+        </is>
+      </c>
+      <c r="C73" s="28">
+        <f>$E$10</f>
+        <v/>
+      </c>
+      <c r="D73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="45">
+        <f>SUM(C73:N73)</f>
+        <v/>
+      </c>
+      <c r="P73" s="17" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>SALDO DO MÊS</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>SALDO</t>
+        </is>
+      </c>
+      <c r="C74" s="27">
+        <f>C$68-C$69-C$70-C$71-C$72-C$73</f>
+        <v/>
+      </c>
+      <c r="D74" s="27">
+        <f>D$68-D$69-D$70-D$71-D$72-D$73</f>
+        <v/>
+      </c>
+      <c r="E74" s="27">
+        <f>E$68-E$69-E$70-E$71-E$72-E$73</f>
+        <v/>
+      </c>
+      <c r="F74" s="27">
+        <f>F$68-F$69-F$70-F$71-F$72-F$73</f>
+        <v/>
+      </c>
+      <c r="G74" s="27">
+        <f>G$68-G$69-G$70-G$71-G$72-G$73</f>
+        <v/>
+      </c>
+      <c r="H74" s="27">
+        <f>H$68-H$69-H$70-H$71-H$72-H$73</f>
+        <v/>
+      </c>
+      <c r="I74" s="27">
+        <f>I$68-I$69-I$70-I$71-I$72-I$73</f>
+        <v/>
+      </c>
+      <c r="J74" s="27">
+        <f>J$68-J$69-J$70-J$71-J$72-J$73</f>
+        <v/>
+      </c>
+      <c r="K74" s="27">
+        <f>K$68-K$69-K$70-K$71-K$72-K$73</f>
+        <v/>
+      </c>
+      <c r="L74" s="27">
+        <f>L$68-L$69-L$70-L$71-L$72-L$73</f>
+        <v/>
+      </c>
+      <c r="M74" s="27">
+        <f>M$68-M$69-M$70-M$71-M$72-M$73</f>
+        <v/>
+      </c>
+      <c r="N74" s="27">
+        <f>N$68-N$69-N$70-N$71-N$72-N$73</f>
+        <v/>
+      </c>
+      <c r="O74" s="45">
+        <f>SUM(C74:N74)</f>
+        <v/>
+      </c>
+      <c r="P74" s="17" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>SALDO ACUMULADO</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>ACUM</t>
+        </is>
+      </c>
+      <c r="C75" s="27">
+        <f>C$74</f>
+        <v/>
+      </c>
+      <c r="D75" s="27">
+        <f>C$75+D$74</f>
+        <v/>
+      </c>
+      <c r="E75" s="27">
+        <f>D$75+E$74</f>
+        <v/>
+      </c>
+      <c r="F75" s="27">
+        <f>E$75+F$74</f>
+        <v/>
+      </c>
+      <c r="G75" s="27">
+        <f>F$75+G$74</f>
+        <v/>
+      </c>
+      <c r="H75" s="27">
+        <f>G$75+H$74</f>
+        <v/>
+      </c>
+      <c r="I75" s="27">
+        <f>H$75+I$74</f>
+        <v/>
+      </c>
+      <c r="J75" s="27">
+        <f>I$75+J$74</f>
+        <v/>
+      </c>
+      <c r="K75" s="27">
+        <f>J$75+K$74</f>
+        <v/>
+      </c>
+      <c r="L75" s="27">
+        <f>K$75+L$74</f>
+        <v/>
+      </c>
+      <c r="M75" s="27">
+        <f>L$75+M$74</f>
+        <v/>
+      </c>
+      <c r="N75" s="27">
+        <f>M$75+N$74</f>
+        <v/>
+      </c>
+      <c r="P75" s="17" t="inlineStr">
+        <is>
+          <t>É esta a linha que decide se o projeto sobrevive ao primeiro ano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Marcador do ponto mais baixo</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>MARC_MIN</t>
+        </is>
+      </c>
+      <c r="C76" s="24">
+        <f>IF(C$75=MIN($C$75:$N$75),1,0)</f>
+        <v/>
+      </c>
+      <c r="D76" s="24">
+        <f>IF(D$75=MIN($C$75:$N$75),2,0)</f>
+        <v/>
+      </c>
+      <c r="E76" s="24">
+        <f>IF(E$75=MIN($C$75:$N$75),3,0)</f>
+        <v/>
+      </c>
+      <c r="F76" s="24">
+        <f>IF(F$75=MIN($C$75:$N$75),4,0)</f>
+        <v/>
+      </c>
+      <c r="G76" s="24">
+        <f>IF(G$75=MIN($C$75:$N$75),5,0)</f>
+        <v/>
+      </c>
+      <c r="H76" s="24">
+        <f>IF(H$75=MIN($C$75:$N$75),6,0)</f>
+        <v/>
+      </c>
+      <c r="I76" s="24">
+        <f>IF(I$75=MIN($C$75:$N$75),7,0)</f>
+        <v/>
+      </c>
+      <c r="J76" s="24">
+        <f>IF(J$75=MIN($C$75:$N$75),8,0)</f>
+        <v/>
+      </c>
+      <c r="K76" s="24">
+        <f>IF(K$75=MIN($C$75:$N$75),9,0)</f>
+        <v/>
+      </c>
+      <c r="L76" s="24">
+        <f>IF(L$75=MIN($C$75:$N$75),10,0)</f>
+        <v/>
+      </c>
+      <c r="M76" s="24">
+        <f>IF(M$75=MIN($C$75:$N$75),11,0)</f>
+        <v/>
+      </c>
+      <c r="N76" s="24">
+        <f>IF(N$75=MIN($C$75:$N$75),12,0)</f>
+        <v/>
+      </c>
+      <c r="P76" s="17" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Marcador de recuperação</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>MARC</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="24">
+        <f>IF(AND(D$75&gt;=0,C$75&lt;0),2,0)</f>
+        <v/>
+      </c>
+      <c r="E77" s="24">
+        <f>IF(AND(E$75&gt;=0,D$75&lt;0),3,0)</f>
+        <v/>
+      </c>
+      <c r="F77" s="24">
+        <f>IF(AND(F$75&gt;=0,E$75&lt;0),4,0)</f>
+        <v/>
+      </c>
+      <c r="G77" s="24">
+        <f>IF(AND(G$75&gt;=0,F$75&lt;0),5,0)</f>
+        <v/>
+      </c>
+      <c r="H77" s="24">
+        <f>IF(AND(H$75&gt;=0,G$75&lt;0),6,0)</f>
+        <v/>
+      </c>
+      <c r="I77" s="24">
+        <f>IF(AND(I$75&gt;=0,H$75&lt;0),7,0)</f>
+        <v/>
+      </c>
+      <c r="J77" s="24">
+        <f>IF(AND(J$75&gt;=0,I$75&lt;0),8,0)</f>
+        <v/>
+      </c>
+      <c r="K77" s="24">
+        <f>IF(AND(K$75&gt;=0,J$75&lt;0),9,0)</f>
+        <v/>
+      </c>
+      <c r="L77" s="24">
+        <f>IF(AND(L$75&gt;=0,K$75&lt;0),10,0)</f>
+        <v/>
+      </c>
+      <c r="M77" s="24">
+        <f>IF(AND(M$75&gt;=0,L$75&lt;0),11,0)</f>
+        <v/>
+      </c>
+      <c r="N77" s="24">
+        <f>IF(AND(N$75&gt;=0,M$75&lt;0),12,0)</f>
+        <v/>
+      </c>
+      <c r="P77" s="17" t="inlineStr"/>
+    </row>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Quanto dinheiro é preciso ter, em cada cenário</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>NECESSIDADE MÁXIMA DE TESOURARIA</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>NEC</t>
+        </is>
+      </c>
+      <c r="C81" s="27">
+        <f>-MIN($C$24:$N$24)</f>
+        <v/>
+      </c>
+      <c r="D81" s="27">
+        <f>-MIN($C$41:$N$41)</f>
+        <v/>
+      </c>
+      <c r="E81" s="27">
+        <f>-MIN($C$58:$N$58)</f>
+        <v/>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>Ponto mais fundo do saldo acumulado. JÁ INCLUI o investimento e a caução — não somar outra vez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   da qual, investimento e caução</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>NEC_INV</t>
+        </is>
+      </c>
+      <c r="C82" s="28">
+        <f>$C$10</f>
+        <v/>
+      </c>
+      <c r="D82" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="E82" s="28">
+        <f>$E$10</f>
+        <v/>
+      </c>
+      <c r="F82" s="17" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   da qual, cobertura do défice operacional</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>NEC_OP</t>
+        </is>
+      </c>
+      <c r="C83" s="28">
+        <f>-MIN($C$24:$N$24)-$C$10</f>
+        <v/>
+      </c>
+      <c r="D83" s="28">
+        <f>-MIN($C$41:$N$41)-$D$10</f>
+        <v/>
+      </c>
+      <c r="E83" s="28">
+        <f>-MIN($C$58:$N$58)-$E$10</f>
+        <v/>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>O que a operação consome enquanto a receita não chega para os custos. É a parte que quase ninguém orça.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>Mês do ponto mais baixo</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>MES_MIN</t>
+        </is>
+      </c>
+      <c r="C84" s="24">
+        <f>MAX($C$25:$N$25)</f>
+        <v/>
+      </c>
+      <c r="D84" s="24">
+        <f>MAX($C$42:$N$42)</f>
+        <v/>
+      </c>
+      <c r="E84" s="24">
+        <f>MAX($C$59:$N$59)</f>
+        <v/>
+      </c>
+      <c r="F84" s="17" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>Mês em que o saldo volta a ser positivo</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>MES_POS</t>
+        </is>
+      </c>
+      <c r="C85" s="24">
+        <f>IF(MAX($C$26:$N$26)=0,"não recupera no ano 1",MAX($C$26:$N$26))</f>
+        <v/>
+      </c>
+      <c r="D85" s="24">
+        <f>IF(MAX($C$43:$N$43)=0,"não recupera no ano 1",MAX($C$43:$N$43))</f>
+        <v/>
+      </c>
+      <c r="E85" s="24">
+        <f>IF(MAX($C$60:$N$60)=0,"não recupera no ano 1",MAX($C$60:$N$60))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>Margem de segurança (meses de custos fixos)</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>MARGEM_M</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" s="17" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>Margem de segurança, em euros</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>MARGEM</t>
+        </is>
+      </c>
+      <c r="C87" s="28">
+        <f>$C$86*BreakEven!$C$10/12</f>
+        <v/>
+      </c>
+      <c r="D87" s="28">
+        <f>$D$86*BreakEven!$D$10/12</f>
+        <v/>
+      </c>
+      <c r="E87" s="28">
+        <f>$E$86*BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="F87" s="17" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL DE DINHEIRO NECESSÁRIO ANTES DE ABRIR</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C88" s="27">
+        <f>$C$81+$C$87</f>
+        <v/>
+      </c>
+      <c r="D88" s="27">
+        <f>$D$81+$D$87</f>
+        <v/>
+      </c>
+      <c r="E88" s="27">
+        <f>$E$81+$E$87</f>
+        <v/>
+      </c>
+      <c r="F88" s="17" t="inlineStr"/>
+    </row>
+    <row r="89"/>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>TESTE DE ESFORÇO — espaço do Alto, procura do Baixo</t>
+        </is>
+      </c>
+      <c r="C90" s="62">
+        <f>-MIN($C$75:$N$75)+$E$86*BreakEven!$E$10/12</f>
+        <v/>
+      </c>
+      <c r="D90" s="39" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>Os três cenários movem o investimento e a receita ao mesmo tempo, pelo que o Baixo é uma clínica mais pequena, não uma clínica em dificuldade. Este é o cenário que não estava representado: comprometer-se com o espaço grande e a procura não aparecer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92" ht="34" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>É a linha TOTAL que se diz à cliente antes de qualquer conversa sobre estrutura fiscal. E diz-se a do cenário BAIXO, não a do Base: quem abre pela primeira vez precisa de saber de quanto precisa se as coisas correrem mal, não se correrem como espera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Visão a três anos</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="7" t="n"/>
+      <c r="D94" s="7" t="n"/>
+      <c r="E94" s="7" t="n"/>
+      <c r="F94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>Cenário usado nesta secção (1 = Baixo · 2 = Base · 3 = Alto)</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Rubrica</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Ano 1</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Ano 2</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Ano 3</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>Taxa de ocupação média do ano</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>OCUP</t>
+        </is>
+      </c>
+      <c r="C97" s="63">
+        <f>AVERAGE(INDEX($C$30:$N$30,1,1):INDEX($C$30:$N$30,1,12))</f>
+        <v/>
+      </c>
+      <c r="D97" s="13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>Ano 1 é a média da rampa do cenário Base. Anos 2 e 3 a preencher, e a justificar com o plano de captação de doentes, que não existe e é o pressuposto silencioso de tudo isto (R1-41).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>Faturação</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
+      <c r="C98" s="27">
+        <f>INDEX(Operacao!$C$21:$E$21,1,$C$95)*$C$97*INDEX(BreakEven!$C$14:$E$14,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="D98" s="27">
+        <f>INDEX(Operacao!$C$21:$E$21,1,$C$95)*$D$97*INDEX(BreakEven!$C$14:$E$14,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="E98" s="27">
+        <f>INDEX(Operacao!$C$21:$E$21,1,$C$95)*$E$97*INDEX(BreakEven!$C$14:$E$14,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="F98" s="17" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>Custos variáveis</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="C99" s="28">
+        <f>$C$98*(1-INDEX(BreakEven!$C$9:$E$9,1,$C$95))</f>
+        <v/>
+      </c>
+      <c r="D99" s="28">
+        <f>$D$98*(1-INDEX(BreakEven!$C$9:$E$9,1,$C$95))</f>
+        <v/>
+      </c>
+      <c r="E99" s="28">
+        <f>$E$98*(1-INDEX(BreakEven!$C$9:$E$9,1,$C$95))</f>
+        <v/>
+      </c>
+      <c r="F99" s="17" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>Custos fixos</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="C100" s="35">
+        <f>INDEX(BreakEven!$C$10:$E$10,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="D100" s="35">
+        <f>INDEX(BreakEven!$C$10:$E$10,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="E100" s="35">
+        <f>INDEX(BreakEven!$C$10:$E$10,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="F100" s="17" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="22" t="inlineStr">
         <is>
           <t>Resultado operacional</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>RES</t>
         </is>
       </c>
-      <c r="C44" s="27">
-        <f>$C$41-$C$42-$C$43</f>
-        <v/>
-      </c>
-      <c r="D44" s="27">
-        <f>$D$41-$D$42-$D$43</f>
-        <v/>
-      </c>
-      <c r="E44" s="27">
-        <f>$E$41-$E$42-$E$43</f>
-        <v/>
-      </c>
-      <c r="F44" s="17" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="C101" s="27">
+        <f>$C$98-$C$99-$C$100</f>
+        <v/>
+      </c>
+      <c r="D101" s="27">
+        <f>$D$98-$D$99-$D$100</f>
+        <v/>
+      </c>
+      <c r="E101" s="27">
+        <f>$E$98-$E$99-$E$100</f>
+        <v/>
+      </c>
+      <c r="F101" s="17" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>Impostos e contribuições estimados</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr">
         <is>
           <t>CARGA</t>
         </is>
       </c>
-      <c r="C45" s="28">
-        <f>MAX(0,$C$44)*V2_ENI_ContOrg!$D$30</f>
-        <v/>
-      </c>
-      <c r="D45" s="28">
-        <f>MAX(0,$D$44)*V2_ENI_ContOrg!$D$30</f>
-        <v/>
-      </c>
-      <c r="E45" s="28">
-        <f>MAX(0,$E$44)*V2_ENI_ContOrg!$D$30</f>
-        <v/>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>Aplica a taxa de esforço da via 2 no cenário Base. Aproximação: a taxa real varia com o nível de rendimento. Ver R1-33.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="C102" s="28">
+        <f>MAX(0,$C$101)*INDEX(V2_ENI_ContOrg!$C$30:$E$30,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="D102" s="28">
+        <f>MAX(0,$D$101)*INDEX(V2_ENI_ContOrg!$C$30:$E$30,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="E102" s="28">
+        <f>MAX(0,$E$101)*INDEX(V2_ENI_ContOrg!$C$30:$E$30,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>Aplica a taxa de esforço da via 2 no cenário selecionado. Aproximação: a taxa real varia com o nível de rendimento. Ver R1-33.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="22" t="inlineStr">
         <is>
           <t>Resultado líquido</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>LIQ</t>
         </is>
       </c>
-      <c r="C46" s="27">
-        <f>$C$44-$C$45</f>
-        <v/>
-      </c>
-      <c r="D46" s="27">
-        <f>$D$44-$D$45</f>
-        <v/>
-      </c>
-      <c r="E46" s="27">
-        <f>$E$44-$E$45</f>
-        <v/>
-      </c>
-      <c r="F46" s="17" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="C103" s="27">
+        <f>$C$101-$C$102</f>
+        <v/>
+      </c>
+      <c r="D103" s="27">
+        <f>$D$101-$D$102</f>
+        <v/>
+      </c>
+      <c r="E103" s="27">
+        <f>$E$101-$E$102</f>
+        <v/>
+      </c>
+      <c r="F103" s="17" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="22" t="inlineStr">
         <is>
           <t>Caixa acumulada desde o arranque</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>CX</t>
         </is>
       </c>
-      <c r="C47" s="27">
-        <f>$C$46-$C$9</f>
-        <v/>
-      </c>
-      <c r="D47" s="27">
-        <f>$C$47+$D$46</f>
-        <v/>
-      </c>
-      <c r="E47" s="27">
-        <f>$D$47+$E$46</f>
-        <v/>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="C104" s="27">
+        <f>$C$103-INDEX(Tesouraria!$C$10:$E$10,1,$C$95)</f>
+        <v/>
+      </c>
+      <c r="D104" s="27">
+        <f>$C$104+$D$103</f>
+        <v/>
+      </c>
+      <c r="E104" s="27">
+        <f>$D$104+$E$103</f>
+        <v/>
+      </c>
+      <c r="F104" s="17" t="inlineStr">
         <is>
           <t>Inclui o desembolso inicial. O ano em que esta linha passa a positiva é o payback real.</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49" ht="44" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>Esta visão a três anos assume custos fixos constantes e preço constante. Não é uma projeção financeira completa — é o suficiente para responder a «quando é que recupero o que meti» e a «o ano 1 é sustentável». Uma projeção completa exigiria inflação de custos, renovação de equipamento e evolução da tabela de preços, e nenhuma dessas coisas está informada. Registado em R1-42.</t>
+    <row r="105"/>
+    <row r="106" ht="44" customHeight="1">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>A visão a três anos assume custos fixos e preço constantes. Não é uma projeção financeira completa — responde a «quando recupero o que meti» e a «o ano 1 é sustentável». Uma projeção completa exigiria inflação de custos, renovação de equipamento e evolução da tabela de preços, e nenhuma dessas coisas está informada. Registado em R1-42.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="E33:N33"/>
-    <mergeCell ref="E36:N36"/>
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="E31:N31"/>
-    <mergeCell ref="E30:N30"/>
-    <mergeCell ref="E29:N29"/>
-    <mergeCell ref="E32:N32"/>
-    <mergeCell ref="E28:N28"/>
+  <mergeCells count="4">
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="A106:P106"/>
+    <mergeCell ref="A92:P92"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 M21 N21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número. Valores monetários não podem ser negativos." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="C21 C38 C55 C72 D21 D38 D55 D72 E21 E38 E55 E72 F21 F38 F55 F72 G21 G38 G55 G72 H21 H38 H55 H72 I21 I38 I55 I72 J21 J38 J55 J72 K21 K38 K55 K72 L21 L38 L55 L72 M21 M38 M55 M72 N21 N38 N55 N72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número. Valores monetários não podem ser negativos." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="C13 C16 D13 D16 D40 E13 E16 E40 F13 F16 G13 G16 H13 H16 I13 I16 J13 J16 K13 K16 L13 L16 M13 M16 N13 N16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentagem inválida" error="Introduza a percentagem como fração: 0,25 para 25%." type="decimal" operator="between">
+    <dataValidation sqref="C13 C16 C30 C33 C47 C50 C64 C67 D13 D16 D30 D33 D47 D50 D64 D67 D97 E13 E16 E30 E33 E47 E50 E64 E67 E97 F13 F16 F30 F33 F47 F50 F64 F67 G13 G16 G30 G33 G47 G50 G64 G67 H13 H16 H30 H33 H47 H50 H64 H67 I13 I16 I30 I33 I47 I50 I64 I67 J13 J16 J30 J33 J47 J50 J64 J67 K13 K16 K30 K33 K47 K50 K64 K67 L13 L16 L30 L33 L47 L50 L64 L67 M13 M16 M30 M33 M47 M50 M64 M67 N13 N16 N30 N33 N47 N50 N64 N67" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentagem inválida" error="Introduza a percentagem como fração: 0,25 para 25%." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation sqref="C7 C33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="C8 C86 C95 D8 D86 E8 E86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Introduza um número não negativo." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -10535,11 +13876,11 @@
           <t>Parâmetros fiscais por validar para 2026</t>
         </is>
       </c>
-      <c r="B10" s="53">
+      <c r="B10" s="54">
         <f>SUM(Parametros!$F$6:$F$50)</f>
         <v/>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="52">
         <f>IF(B10&gt;0,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10560,11 +13901,11 @@
           <t>Inputs da cliente por confirmar</t>
         </is>
       </c>
-      <c r="B11" s="53">
+      <c r="B11" s="54">
         <f>SUM(Inputs!$J$6:$J$40)</f>
         <v/>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="52">
         <f>IF(B11&gt;0,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10589,7 +13930,7 @@
         <f>Operacao!$D$26</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="52">
         <f>IF(B12&gt;Parametros!$C$20,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10614,7 +13955,7 @@
         <f>Operacao!$D$26</f>
         <v/>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="52">
         <f>IF(AND(B13&gt;Parametros!$C$21,B13&lt;=Parametros!$C$20),"ATIVO","—")</f>
         <v/>
       </c>
@@ -10639,7 +13980,7 @@
         <f>Operacao!$D$26</f>
         <v/>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="52">
         <f>IF(B14&lt;Parametros!$C$22,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10664,7 +14005,7 @@
         <f>BreakEven!$D$13</f>
         <v/>
       </c>
-      <c r="C15" s="51">
+      <c r="C15" s="52">
         <f>IF(B15&lt;0,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10689,7 +14030,7 @@
         <f>BreakEven!$D$9</f>
         <v/>
       </c>
-      <c r="C16" s="51">
+      <c r="C16" s="52">
         <f>IF(B16&lt;=0,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10714,7 +14055,7 @@
         <f>BreakEven!$D$16</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="52">
         <f>IF(B17&gt;1,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10735,11 +14076,11 @@
           <t>Premissa da atividade do cônjuge por verificar</t>
         </is>
       </c>
-      <c r="B18" s="53">
+      <c r="B18" s="54">
         <f>1-$B$5</f>
         <v/>
       </c>
-      <c r="C18" s="51">
+      <c r="C18" s="52">
         <f>IF(B18=1,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10760,11 +14101,11 @@
           <t>Qualificação da cedência de sala por fixar</t>
         </is>
       </c>
-      <c r="B19" s="53">
+      <c r="B19" s="54">
         <f>1-$B$6</f>
         <v/>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="52">
         <f>IF(B19=1,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10785,11 +14126,11 @@
           <t>Investimento sem financiamento identificado</t>
         </is>
       </c>
-      <c r="B20" s="53">
+      <c r="B20" s="54">
         <f>1-$B$7</f>
         <v/>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="52">
         <f>IF(B20=1,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10814,7 +14155,7 @@
         <f>Inputs!$D$47</f>
         <v/>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="52">
         <f>IF(B21&gt;0,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10835,11 +14176,11 @@
           <t>Recálculo independente com divergências</t>
         </is>
       </c>
-      <c r="B22" s="53">
+      <c r="B22" s="54">
         <f>IF(AND(Validacao!$D$30="TODAS AS VERIFICAÇÕES OK",Validacao!$D$49="TODAS AS VERIFICAÇÕES OK"),0,1)</f>
         <v/>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="52">
         <f>IF(B22=1,"ATIVO","—")</f>
         <v/>
       </c>
@@ -10872,7 +14213,7 @@
           <t>O FICHEIRO PODE PRODUZIR NÚMEROS CITÁVEIS?</t>
         </is>
       </c>
-      <c r="B25" s="59">
+      <c r="B25" s="60">
         <f>IF(COUNTIF($C$10:$C$22,"ATIVO")=0,"SIM","NÃO — resolver os alertas ativos")</f>
         <v/>
       </c>
@@ -11000,15 +14341,15 @@
           <t>PREMISSA</t>
         </is>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="54">
         <f>Alertas!$B$5</f>
         <v/>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="54">
         <f>Alertas!$B$5</f>
         <v/>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="54">
         <f>Alertas!$B$5</f>
         <v/>
       </c>
